--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1757" uniqueCount="463">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1760" uniqueCount="465">
   <si>
     <t>Player</t>
   </si>
@@ -100,133 +100,145 @@
     <t>Cora</t>
   </si>
   <si>
+    <t>Shiloh</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - </t>
   </si>
   <si>
-    <t>Shiloh</t>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
   </si>
   <si>
     <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
     <t>Anna</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Annabelle</t>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
     <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
   </si>
   <si>
-    <t xml:space="preserve">Nataly </t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
     <t>Addy</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
+    <t>Agnes</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
   </si>
   <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+    <t xml:space="preserve">2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
   </si>
   <si>
     <t>Kinley</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - </t>
-  </si>
-  <si>
-    <t>Agnes</t>
+    <t>Gaby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t>Audri</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t>Gaby</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
   </si>
   <si>
     <t>3 - 3 - 5 - 1 - 3 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">0 - 0 - </t>
   </si>
   <si>
     <t>3 - 0 - 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - </t>
+    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+  </si>
+  <si>
+    <t>Bridget</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
@@ -235,79 +247,70 @@
     <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t>1 - 1 - 1 - 0 - 0</t>
   </si>
   <si>
-    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
   </si>
   <si>
     <t>Corena</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Bridget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
-  </si>
-  <si>
     <t>Tea</t>
   </si>
   <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
     <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
     <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - </t>
+    <t xml:space="preserve">2 - </t>
   </si>
   <si>
     <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
@@ -316,27 +319,24 @@
     <t>Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
     <t>Emma</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
     <t>Piper</t>
   </si>
   <si>
@@ -349,6 +349,9 @@
     <t>Rotation (follow setter starting position)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
     <t>Kill Efficiency</t>
   </si>
   <si>
@@ -358,9 +361,6 @@
     <t xml:space="preserve">3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
     <t>Block (partial touch)</t>
   </si>
   <si>
@@ -385,12 +385,12 @@
     <t>Points Scored Against Rotation</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
     <t>Rotation Net Score (+ or -)</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
     <t>Team</t>
   </si>
   <si>
@@ -406,96 +406,96 @@
     <t>Ace % (us)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
     <t>Service Error % (us)</t>
   </si>
   <si>
     <t>Aces (them)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+    <t>Service Errors (them)</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t>Service Errors (them)</t>
-  </si>
-  <si>
     <t>Ace % (them)</t>
   </si>
   <si>
     <t>Service Error % (Them)</t>
   </si>
   <si>
+    <t>Set 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
   </si>
   <si>
-    <t>Set 1</t>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
   </si>
   <si>
     <t>Set 2</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
   </si>
   <si>
     <t>Set 3</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Set 4</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Set 4</t>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t>Set 5</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
     <t>Team Passer Rating (all games)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
     <t>Team Kill Efficiency (all games)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -514,258 +514,258 @@
     <t xml:space="preserve">1 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 2 - 2 - 1 - 3 - 3 - 0 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 1 - 1 - 1 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 2 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 2 - 3 - 2 - 5 - 2 - 5 - 0 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 3 - 1 - 0 - 1 - 3 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
     <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - </t>
+    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
   </si>
   <si>
     <t>2- 1- 0- 3- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
+    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
   </si>
   <si>
     <t>2- 2- 3- 3- 2- 3- 2- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+    <t xml:space="preserve">3- 3- 2- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
     <t>0- 0</t>
   </si>
   <si>
+    <t>2- 1- 2- 0- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
     <t>2- 2- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 5 - 2 - 2 - 1 - 3 - 3 - 0 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 3 - 1 - 1 - 1 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 2 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
+  </si>
+  <si>
+    <t>3- 1- 2- 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 2 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 3 - 3 - 2 - 0 - 1 - 0 - 2 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 3 - 2 - 1 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
   </si>
   <si>
     <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+    <t>3- 1- 5- 2</t>
   </si>
   <si>
     <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
     <t>2- 3- 2- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+    <t>3- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
   </si>
   <si>
     <t>3- 2- 3- 5- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 3 - 2 - 3 - 2 - 5 - 2 - 5 - 0 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 3 - 1 - 0 - 1 - 3 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0- 2- 3- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - </t>
+  </si>
+  <si>
+    <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
   </si>
   <si>
     <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - </t>
+    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t>2- 2- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- </t>
   </si>
   <si>
     <t>1- 3- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
+    <t>1- 3- 0- 1- 0</t>
   </si>
   <si>
     <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 2 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - </t>
+    <t>1- 2- 0- 0- 1- 0</t>
   </si>
   <si>
     <t>3- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 3 - 3 - 2 - 0 - 1 - 0 - 2 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 3 - 2 - 1 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
+    <t>2- 3- 1- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t>5- 3- 0- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0- 3- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>0- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
     <t>1- 3- 0- 3- 1</t>
   </si>
   <si>
-    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
+    <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
   </si>
   <si>
-    <t xml:space="preserve">3- 3- 2- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t>2- 1- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
-  </si>
-  <si>
-    <t>3- 1- 2- 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
+    <t>0- 1- 1- 0- 1- 2- 1- 0- 0- 0- 2- 1- 0- 3- 2- 1- 3- 2</t>
+  </si>
+  <si>
+    <t>0- 1- 2- 1- 0- 2- 2- 2- 2- 2</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
   </si>
   <si>
-    <t>3- 1- 5- 2</t>
+    <t>2- 2- 1- 2</t>
   </si>
   <si>
     <t xml:space="preserve">2- 1- 1- </t>
   </si>
   <si>
-    <t>3- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t>2- 1- 1- 3- 1- 1- 3- 2- 1- 3- 2</t>
+  </si>
+  <si>
     <t>1- 0- 3- 2- 0- 1- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">0- 2- 3- </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>2- 0- 2- 2- 3- 1- 0- 0</t>
   </si>
   <si>
     <t>0- 1- 3</t>
   </si>
   <si>
-    <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>2- 2- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
   </si>
   <si>
-    <t>1- 3- 0- 1- 0</t>
+    <t>1- 2- 1- 3- 1- 2- 0- 1</t>
   </si>
   <si>
     <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
-    <t>1- 2- 0- 0- 1- 0</t>
-  </si>
-  <si>
-    <t>2- 3- 1- 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t>5- 3- 0- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0- 3- </t>
-  </si>
-  <si>
-    <t>0- 2</t>
-  </si>
-  <si>
-    <t>0- 1- 1- 0- 1- 2- 1- 0- 0- 0- 2- 1- 0- 3- 2- 1- 3- 2</t>
-  </si>
-  <si>
-    <t>0- 1- 2- 1- 0- 2- 2- 2- 2- 2</t>
-  </si>
-  <si>
-    <t>2- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>2- 1- 1- 3- 1- 1- 3- 2- 1- 3- 2</t>
-  </si>
-  <si>
-    <t>2- 0- 2- 2- 3- 1- 0- 0</t>
-  </si>
-  <si>
-    <t>1- 2- 1- 3- 1- 2- 0- 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 3 - 5 - 2 - 2 - 2 - </t>
   </si>
   <si>
@@ -781,18 +781,33 @@
     <t xml:space="preserve">2 - 1 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 3 - 2 - 3 - 1 - 2 - 0 - 2 - 3 - 3 - 3 - 1 - 2 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 2 - 1 - 2 - 2 - 0 -1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 0 - 1 - 2 - 0 - 0 - 1 - 0 - 2 - 1 - 2 - 0 - 2 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 5 - 5 - 0 - 5 - 2 - 5 - 5 - 5 - 0 - 2 - 3 - 5 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 1 - 1 - 1 - 1 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 3 - 5 - 0 - 0 - 0 - 2 - 1 - 3 - 3 - 3 - 0 - 0 - </t>
   </si>
   <si>
@@ -802,12 +817,27 @@
     <t xml:space="preserve">3 - 5 - 5 - 1 - 5 -  0 - 3 - 5 - 0 - 5 - 0 - 0 - 0 - 3 - 5 - 3 - 0 - 2 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 3 - 3 - 0 - 3 - 2 - 2 - 0 - 1 - 2 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 5 - 2 - 3 - 5 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 1 - 2 - 3 - 1 - 2 - 1 - 2 - 1 - 1 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 1 - 3 - 1 - 5 - 0 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 2 - </t>
   </si>
   <si>
@@ -817,132 +847,147 @@
     <t xml:space="preserve">0 - 3 - 3 - 5 - 3 - 3 - 0 - 3 - 2 - 3 - 1 - 3 - 3 - 1 - 1 - 1 - 5 - 3 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 1 - 3 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 2 - 2 - 2 - 3 - 2 - 2 - 0 - 3 - 3 - 2 - 5 - 2 - 5 - 5 - 3 - 3 - 5 - 3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - 2 - 3 - 1 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 0 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 2 - 1 - 2 - 2 - 0 -1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 1 - 2 - 0 - 0 - 1 - 0 - 2 - 1 - 2 - 0 - 2 - 1 - 1 - 2 - </t>
+    <t xml:space="preserve">3 - 5 - 0 - 0 - 2 - 2 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 1 - 2 - 3 - 1 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 1 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 0 - </t>
+    <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 3 - 1 - 1 - 2 - 3 - 2 - 3 - 1 - 2 - 2 - 0 -0 - 1 -2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
+    <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>5 - 2 - 3 - 0 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 3 - 0 - 3 - 2 - 3 - 1 - 0 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 0 - 1 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 2 - 1 - 2 - 2 - 2 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 2- 2- 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 1 - 0 - 1 - 0 - 0 - 2 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 5 - 2 - 3 - 5 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 1 - 2 - 3 - 1 - 2 - 1 - 2 - 1 - 1 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 1 - 3 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 2 - 1 - 2 - 2 - 2 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 1 - 0 - 1 - 0 - 0 - 2 - 1 - 1 - 3 - </t>
+    <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 0 - 0 - 1 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - 2 - 2 - 3 - 2 - 2 - 0 - 3 - 3 - 2 - 5 - 2 - 5 - 5 - 3 - 3 - 5 - 3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 0 - 0 - 2 - 2 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 1 - 2 - 3 - 1 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>5 - 2 - 3 - 0 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 1 - 0 - </t>
   </si>
   <si>
@@ -952,69 +997,24 @@
     <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 2- 2- 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1- 1 - 1 - 1 - </t>
   </si>
   <si>
@@ -1051,15 +1051,51 @@
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
   </si>
   <si>
@@ -1069,190 +1105,157 @@
     <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 2 - 3 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 2 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 0 - 1 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 3 - 1 - 0 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 0 - 5 - 2 - 2 - 0 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 5 - 5 - 0 - 1 - 1 - 1 - 5 -  3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 3 - 3 - 5 - 5 - 3 - 5 - 5 - 2 - 5 - 5 - 2 - 5 - 0 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 3 - 3 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 5 - 3 - 1 - 5 - 5 - 2 - 5 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
+    <t xml:space="preserve">0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
     <t>119 attack attempts</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 3 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 2 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 0 - 1 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 3 - 1 - 0 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 5 - 2 - 2 - 0 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 5 - 0 - 1 - 1 - 1 - 5 -  3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 3 - 3 - 5 - 5 - 3 - 5 - 5 - 2 - 5 - 5 - 2 - 5 - 0 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 3 - 3 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 3 - 1 - 5 - 5 - 2 - 5 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - </t>
+    <t xml:space="preserve">0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
@@ -1267,6 +1270,39 @@
     <t xml:space="preserve">5 - 5 - 5 - 3- 5 - 3 - 0 - 2 - 0- 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 5 - 1 - 3 - 5 - 5 - 3 - 2 - 3 - 3 - 3 - 1 - 5 - 1 - 5 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 2 - 3 - 3 - 2 - 1 - 2 - 2 - 1 - 0 - 1 - 2 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 2 - 1 - 2 - 1 - 5 - 3 - 2 - 1 - 2 - 3 - 1 - 5 - 2 - 3 - 3 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1276,30 +1312,15 @@
     <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 5 - 1 - 3 - 5 - 5 - 3 - 2 - 3 - 3 - 3 - 1 - 5 - 1 - 5 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 2 - 3 - 3 - 2 - 1 - 2 - 2 - 1 - 0 - 1 - 2 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 2 - 1 - 2 - 1 - 5 - 3 - 2 - 1 - 2 - 3 - 1 - 5 - 2 - 3 - 3 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
   </si>
   <si>
@@ -1312,24 +1333,9 @@
     <t xml:space="preserve">2 - 2 - 2 - 3 - 0 - 2 - 2 - 0 - 2 - 2 - 2 - 1 - 2 - 3 - 3 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 2 - 1 - 2 - 2 - 2 - 0 - 1 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 2 - 3 - 3 - 2 - 3 - 1 - 3 - 2 - 3 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 1 - 2 - 3 - 2 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
@@ -1372,13 +1378,13 @@
     <t xml:space="preserve">3 - 2 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - 3 - 2 - 1 - 2 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 2 - 2 - 0 - 3 - 3 - 0 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 2 - 1 - 2 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 2 - 2 - 0 - 3 - 3 - 0 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 2 - 2 - 2 - 2 - </t>
@@ -1534,10 +1540,10 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -1970,7 +1976,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -1982,7 +1988,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -1991,7 +1997,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2018,7 +2024,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2030,7 +2036,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2039,7 +2045,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2057,7 +2063,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2072,7 +2078,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2093,7 +2099,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2102,7 +2108,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2111,7 +2117,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2135,7 +2141,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2144,7 +2150,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2153,7 +2159,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2165,7 +2171,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2177,7 +2183,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2186,7 +2192,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2199,7 +2205,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2226,7 +2232,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2241,7 +2247,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2250,7 +2256,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2277,7 +2283,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2286,7 +2292,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2295,7 +2301,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2316,7 +2322,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2373,10 +2379,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -2406,7 +2412,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2458,13 +2464,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -2476,7 +2482,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2505,7 +2511,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2589,12 +2595,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2602,10 +2608,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.33</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.12</v>
       </c>
       <c r="F31" s="3">
@@ -2614,19 +2620,19 @@
       <c r="G31" s="3">
         <v>17.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.18</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
     </row>
     <row r="34">
@@ -2735,7 +2741,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2756,7 +2762,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>263</v>
+        <v>249</v>
       </c>
       <c r="L2" s="3">
         <v>1.56</v>
@@ -2768,7 +2774,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>264</v>
+        <v>251</v>
       </c>
       <c r="R2" s="3">
         <v>1.06</v>
@@ -2777,7 +2783,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2785,7 +2791,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2800,7 +2806,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>266</v>
+        <v>253</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -2812,7 +2818,7 @@
         <v>12.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>268</v>
+        <v>255</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -2821,7 +2827,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2848,7 +2854,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="L4" s="3">
         <v>2.2</v>
@@ -2861,7 +2867,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2869,7 +2875,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2896,7 +2902,7 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
       <c r="L5" s="3">
         <v>2.33</v>
@@ -2908,7 +2914,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -2917,7 +2923,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2925,7 +2931,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -2952,7 +2958,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="L6" s="3">
         <v>2.3</v>
@@ -2964,7 +2970,7 @@
         <v>15.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="R6" s="3">
         <v>1.53</v>
@@ -2973,7 +2979,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="U6" s="3">
         <v>2.67</v>
@@ -3002,7 +3008,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3017,7 +3023,7 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -3026,7 +3032,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3050,7 +3056,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="L8" s="3">
         <v>1.89</v>
@@ -3062,7 +3068,7 @@
         <v>6.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -3071,7 +3077,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -3079,7 +3085,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3091,7 +3097,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3104,7 +3110,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3113,7 +3119,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3154,10 +3160,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -3183,7 +3189,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3216,7 +3222,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -3263,7 +3269,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="M17" s="3">
         <v>1.18</v>
@@ -3301,7 +3307,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="M18" s="3">
         <v>1.2</v>
@@ -3345,7 +3351,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>284</v>
+        <v>304</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -3386,7 +3392,7 @@
         <v>2.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -3430,7 +3436,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>286</v>
+        <v>313</v>
       </c>
       <c r="M21" s="3">
         <v>0.9</v>
@@ -3465,13 +3471,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -3483,7 +3489,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3497,7 +3503,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3536,12 +3542,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3549,10 +3555,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.14</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.18</v>
       </c>
       <c r="F31" s="3">
@@ -3561,16 +3567,16 @@
       <c r="G31" s="3">
         <v>14.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.25</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3701,7 +3707,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>287</v>
+        <v>271</v>
       </c>
       <c r="L2" s="3">
         <v>2.33</v>
@@ -3713,7 +3719,7 @@
         <v>8.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -3722,7 +3728,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3730,7 +3736,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3760,7 +3766,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>289</v>
+        <v>277</v>
       </c>
       <c r="L3" s="3">
         <v>3.08</v>
@@ -3772,7 +3778,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3781,7 +3787,7 @@
         <v>7.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>290</v>
+        <v>278</v>
       </c>
       <c r="U3" s="3">
         <v>2.71</v>
@@ -3789,7 +3795,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3819,7 +3825,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>291</v>
+        <v>279</v>
       </c>
       <c r="L4" s="3">
         <v>2.78</v>
@@ -3831,7 +3837,7 @@
         <v>8.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>292</v>
+        <v>280</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -3840,7 +3846,7 @@
         <v>13.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>293</v>
+        <v>281</v>
       </c>
       <c r="U4" s="3">
         <v>2.31</v>
@@ -3848,7 +3854,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3875,7 +3881,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="L5" s="3">
         <v>2.36</v>
@@ -3887,7 +3893,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -3896,7 +3902,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -3904,7 +3910,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3927,7 +3933,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3935,7 +3941,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -3959,7 +3965,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="L7" s="3">
         <v>2.0</v>
@@ -3968,7 +3974,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -3977,7 +3983,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -3985,7 +3991,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -3998,7 +4004,7 @@
         <v>7.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="R8" s="3">
         <v>2.29</v>
@@ -4007,7 +4013,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4015,7 +4021,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4033,7 +4039,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4043,7 +4049,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4051,7 +4057,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4066,7 +4072,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4076,7 +4082,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4094,7 +4100,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4103,7 +4109,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4124,7 +4130,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4133,7 +4139,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4151,7 +4157,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4163,7 +4169,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4184,7 +4190,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4196,7 +4202,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4208,7 +4214,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4218,7 +4224,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4243,10 +4249,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
@@ -4272,7 +4278,7 @@
         <v>116</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4305,7 +4311,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4352,7 +4358,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4396,7 +4402,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4440,7 +4446,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>307</v>
+        <v>324</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -4487,7 +4493,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4531,7 +4537,7 @@
         <v>7.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="M22" s="3">
         <v>2.29</v>
@@ -4566,13 +4572,13 @@
         <v>123</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>129</v>
@@ -4584,7 +4590,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4601,7 +4607,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4640,12 +4646,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4653,10 +4659,10 @@
       <c r="C32" s="3">
         <v>12.0</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.23</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.16</v>
       </c>
       <c r="F32" s="3">
@@ -4665,16 +4671,16 @@
       <c r="G32" s="3">
         <v>9.0</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.27</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4809,7 +4815,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>309</v>
+        <v>287</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4818,7 +4824,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="U2" s="3">
         <v>2.33</v>
@@ -4826,7 +4832,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4853,7 +4859,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>310</v>
+        <v>291</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4865,7 +4871,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>311</v>
+        <v>292</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4874,7 +4880,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>312</v>
+        <v>293</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4882,7 +4888,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4909,7 +4915,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4921,7 +4927,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4930,7 +4936,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>315</v>
+        <v>303</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4938,7 +4944,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -4965,7 +4971,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -4977,7 +4983,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -4986,7 +4992,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -4994,7 +5000,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5006,7 +5012,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5018,7 +5024,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5027,7 +5033,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5042,7 +5048,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5051,7 +5057,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5075,7 +5081,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5087,7 +5093,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5095,7 +5101,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5115,7 +5121,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -5123,7 +5129,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5150,7 +5156,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5191,10 +5197,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -5220,7 +5226,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5253,7 +5259,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5300,7 +5306,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5347,7 +5353,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5514,13 +5520,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -5532,7 +5538,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5561,7 +5567,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5612,12 +5618,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5625,34 +5631,34 @@
       <c r="C31" s="3">
         <v>15.0</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="3">
         <v>13.0</v>
       </c>
       <c r="G31" s="3">
         <v>17.0</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32">
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.28</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.16</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.19</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5759,7 +5765,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5815,7 +5821,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5874,7 +5880,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5936,7 +5942,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -5959,7 +5965,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -5967,7 +5973,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -5989,7 +5995,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -5998,7 +6004,7 @@
         <v>4.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -6006,7 +6012,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6026,7 +6032,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6040,7 +6046,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6049,7 +6055,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6068,7 +6074,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6083,7 +6089,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6092,7 +6098,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6101,7 +6107,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6135,7 +6141,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6162,7 +6168,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>345</v>
+        <v>359</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -6175,7 +6181,7 @@
         <v>7.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="U10" s="3">
         <v>2.14</v>
@@ -6183,7 +6189,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6227,10 +6233,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -6256,7 +6262,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6289,7 +6295,7 @@
         <v>6.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>347</v>
+        <v>375</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -6336,7 +6342,7 @@
         <v>14.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>348</v>
+        <v>381</v>
       </c>
       <c r="M17" s="3">
         <v>1.79</v>
@@ -6383,7 +6389,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>349</v>
+        <v>383</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6430,7 +6436,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>350</v>
+        <v>387</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6477,7 +6483,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>351</v>
+        <v>394</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6524,7 +6530,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>352</v>
+        <v>397</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6559,13 +6565,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -6577,7 +6583,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6594,7 +6600,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6645,7 +6651,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6662,7 +6668,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6670,10 +6676,10 @@
       <c r="C31" s="3">
         <v>14.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.17</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.13</v>
       </c>
       <c r="F31" s="3">
@@ -6682,16 +6688,16 @@
       <c r="G31" s="3">
         <v>15.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.17</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6798,7 +6804,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6816,7 +6822,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>353</v>
+        <v>339</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6829,7 +6835,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6859,7 +6865,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>354</v>
+        <v>340</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6871,7 +6877,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>355</v>
+        <v>341</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6880,7 +6886,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>356</v>
+        <v>343</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6888,7 +6894,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6900,7 +6906,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6909,7 +6915,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>358</v>
+        <v>345</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6918,7 +6924,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>359</v>
+        <v>346</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6926,7 +6932,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -6950,7 +6956,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>360</v>
+        <v>347</v>
       </c>
       <c r="L5" s="3">
         <v>2.75</v>
@@ -6962,7 +6968,7 @@
         <v>16.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>361</v>
+        <v>348</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -6971,7 +6977,7 @@
         <v>13.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>362</v>
+        <v>350</v>
       </c>
       <c r="U5" s="3">
         <v>2.15</v>
@@ -6979,7 +6985,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7009,7 +7015,7 @@
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -7024,7 +7030,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -7033,7 +7039,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7041,7 +7047,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7063,7 +7069,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7072,7 +7078,7 @@
         <v>7.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="U7" s="3">
         <v>1.86</v>
@@ -7080,7 +7086,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7104,7 +7110,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="L8" s="3">
         <v>1.67</v>
@@ -7116,7 +7122,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -7124,7 +7130,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7148,7 +7154,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>367</v>
+        <v>360</v>
       </c>
       <c r="L9" s="3">
         <v>2.56</v>
@@ -7157,7 +7163,7 @@
         <v>12.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
       <c r="R9" s="3">
         <v>1.67</v>
@@ -7166,7 +7172,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>285</v>
+        <v>308</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -7201,7 +7207,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7225,7 +7231,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="L11" s="3">
         <v>2.45</v>
@@ -7234,7 +7240,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7249,7 +7255,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7258,7 +7264,7 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="U13" s="3">
         <v>1.5</v>
@@ -7285,10 +7291,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -7314,7 +7320,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7347,7 +7353,7 @@
         <v>12.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -7391,7 +7397,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>371</v>
+        <v>392</v>
       </c>
       <c r="M17" s="3">
         <v>2.55</v>
@@ -7438,7 +7444,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>372</v>
+        <v>396</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7485,7 +7491,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>373</v>
+        <v>400</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7532,7 +7538,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>374</v>
+        <v>402</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7576,7 +7582,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>405</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7611,13 +7617,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -7629,7 +7635,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7646,7 +7652,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7697,12 +7703,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7710,10 +7716,10 @@
       <c r="C31" s="3">
         <v>13.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.2</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.15</v>
       </c>
       <c r="F31" s="3">
@@ -7722,16 +7728,16 @@
       <c r="G31" s="3">
         <v>13.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.1</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7740,7 +7746,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>376</v>
+        <v>406</v>
       </c>
     </row>
   </sheetData>
@@ -7841,7 +7847,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7868,7 +7874,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7886,7 +7892,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7895,7 +7901,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7916,7 +7922,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>379</v>
+        <v>366</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7929,7 +7935,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7956,7 +7962,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -7968,7 +7974,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -7977,7 +7983,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -7985,7 +7991,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8006,7 +8012,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8018,7 +8024,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>378</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8027,7 +8033,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8035,7 +8041,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8058,7 +8064,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8066,7 +8072,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8078,7 +8084,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8087,7 +8093,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8096,7 +8102,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8104,7 +8110,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8125,7 +8131,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8137,7 +8143,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8161,7 +8167,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8174,7 +8180,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8211,7 +8217,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8226,7 +8232,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8235,7 +8241,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8259,7 +8265,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8271,7 +8277,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8301,13 +8307,13 @@
         <v>123</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>129</v>
@@ -8319,7 +8325,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8336,7 +8342,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8387,7 +8393,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8404,7 +8410,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8412,10 +8418,10 @@
       <c r="C23" s="3">
         <v>21.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.3</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.24</v>
       </c>
       <c r="F23" s="3">
@@ -8424,16 +8430,16 @@
       <c r="G23" s="3">
         <v>22.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.32</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <v>0.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8540,7 +8546,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8564,7 +8570,7 @@
         <v>8.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>395</v>
+        <v>365</v>
       </c>
       <c r="L2" s="3">
         <v>3.87</v>
@@ -8576,7 +8582,7 @@
         <v>15.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="R2" s="3">
         <v>1.53</v>
@@ -8585,7 +8591,7 @@
         <v>5.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>397</v>
+        <v>369</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -8593,7 +8599,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8608,7 +8614,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>398</v>
+        <v>370</v>
       </c>
       <c r="L3" s="3">
         <v>1.86</v>
@@ -8617,7 +8623,7 @@
         <v>8.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>399</v>
+        <v>372</v>
       </c>
       <c r="R3" s="3">
         <v>1.63</v>
@@ -8626,7 +8632,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8634,7 +8640,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8664,7 +8670,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>400</v>
+        <v>376</v>
       </c>
       <c r="L4" s="3">
         <v>2.11</v>
@@ -8673,7 +8679,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8682,7 +8688,7 @@
         <v>3.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>401</v>
+        <v>379</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -8710,7 +8716,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8737,7 +8743,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>402</v>
+        <v>382</v>
       </c>
       <c r="L6" s="3">
         <v>2.6</v>
@@ -8750,7 +8756,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8758,7 +8764,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8785,7 +8791,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>403</v>
+        <v>385</v>
       </c>
       <c r="L7" s="3">
         <v>3.59</v>
@@ -8797,7 +8803,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>404</v>
+        <v>388</v>
       </c>
       <c r="R7" s="3">
         <v>2.15</v>
@@ -8806,7 +8812,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8814,7 +8820,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8826,7 +8832,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>405</v>
+        <v>391</v>
       </c>
       <c r="L8" s="3">
         <v>2.64</v>
@@ -8835,7 +8841,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8855,14 +8861,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8871,7 +8877,7 @@
         <v>3.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="U10" s="3">
         <v>2.0</v>
@@ -8879,7 +8885,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8891,7 +8897,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8918,13 +8924,13 @@
         <v>123</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>129</v>
@@ -8936,7 +8942,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8953,7 +8959,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -8992,12 +8998,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9005,10 +9011,10 @@
       <c r="C23" s="3">
         <v>8.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.35</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.12</v>
       </c>
       <c r="F23" s="3">
@@ -9017,16 +9023,16 @@
       <c r="G23" s="3">
         <v>13.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.18</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9204,10 +9210,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -9233,7 +9239,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9291,13 +9297,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -9309,12 +9315,12 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27">
@@ -9329,21 +9335,21 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
+        <v>144</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9444,7 +9450,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D2" s="3">
         <v>3.0</v>
@@ -9452,96 +9458,126 @@
       <c r="E2" s="3">
         <v>1.0</v>
       </c>
-      <c r="K2" s="4"/>
+      <c r="H2" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="I2" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J2" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>315</v>
+      </c>
       <c r="M2" s="4"/>
       <c r="P2" s="3">
         <v>3.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="T2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="K3" s="4"/>
+        <v>2.0</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J3" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="P3" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>22</v>
+        <v>407</v>
       </c>
       <c r="S3" s="3">
         <v>1.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H4" s="3">
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q4" s="4"/>
       <c r="T4" s="4"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
       </c>
       <c r="K5" s="4"/>
       <c r="M5" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="Q5" s="4"/>
       <c r="S5" s="3">
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
       </c>
       <c r="H6" s="3">
+        <v>4.0</v>
+      </c>
+      <c r="J6" s="3">
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>108</v>
+        <v>412</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="T6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
       </c>
-      <c r="K7" s="4"/>
+      <c r="H7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="J7" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>23</v>
+      </c>
       <c r="T7" s="5"/>
     </row>
     <row r="8">
@@ -9584,13 +9620,13 @@
         <v>123</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>129</v>
@@ -9602,18 +9638,24 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
+      </c>
+      <c r="B17" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="C17" s="3">
+        <v>4.0</v>
       </c>
       <c r="F17" s="3">
         <v>2.0</v>
       </c>
       <c r="G17" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="19">
@@ -9628,21 +9670,21 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="D23" s="16"/>
-      <c r="E23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
+        <v>144</v>
+      </c>
+      <c r="D23" s="17"/>
+      <c r="E23" s="17"/>
+      <c r="H23" s="17"/>
+      <c r="I23" s="17"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9744,7 +9786,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -9774,7 +9816,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L2" s="3">
         <v>2.69</v>
@@ -9786,7 +9828,7 @@
         <v>22.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R2" s="3">
         <v>1.45</v>
@@ -9795,7 +9837,7 @@
         <v>4.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -9803,7 +9845,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -9827,7 +9869,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -9846,7 +9888,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -9864,7 +9906,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -9877,7 +9919,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -9885,7 +9927,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -9915,7 +9957,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="L5" s="3">
         <v>2.63</v>
@@ -9927,7 +9969,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="R5" s="3">
         <v>1.71</v>
@@ -9936,7 +9978,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -9944,7 +9986,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -9965,7 +10007,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L6" s="3">
         <v>2.65</v>
@@ -9977,7 +10019,7 @@
         <v>20.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="R6" s="3">
         <v>1.0</v>
@@ -9986,7 +10028,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10019,7 +10061,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10049,7 +10091,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -10061,7 +10103,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>428</v>
+        <v>419</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -10070,7 +10112,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>429</v>
+        <v>420</v>
       </c>
       <c r="U8" s="3">
         <v>1.83</v>
@@ -10078,7 +10120,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10090,7 +10132,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -10100,7 +10142,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10118,7 +10160,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>431</v>
+        <v>422</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10155,13 +10197,13 @@
         <v>123</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H16" s="13" t="s">
         <v>129</v>
@@ -10173,7 +10215,7 @@
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10190,7 +10232,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10241,12 +10283,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10254,10 +10296,10 @@
       <c r="C23" s="3">
         <v>9.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.27</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.11</v>
       </c>
       <c r="F23" s="3">
@@ -10266,16 +10308,16 @@
       <c r="G23" s="3">
         <v>17.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.26</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10382,7 +10424,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10406,7 +10448,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10418,7 +10460,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10427,7 +10469,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10435,7 +10477,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10453,7 +10495,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10466,7 +10508,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10474,7 +10516,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10501,7 +10543,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10513,7 +10555,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10522,7 +10564,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10530,7 +10572,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10542,7 +10584,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10551,7 +10593,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10560,7 +10602,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10568,7 +10610,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10592,7 +10634,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10604,7 +10646,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10613,7 +10655,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10621,7 +10663,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10648,7 +10690,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10685,7 +10727,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10694,7 +10736,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10712,7 +10754,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10725,7 +10767,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10733,7 +10775,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10747,7 +10789,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10762,7 +10804,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -10771,13 +10813,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -10808,10 +10850,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -10841,7 +10883,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -10874,7 +10916,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -10891,7 +10933,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="16">
         <f>10</f>
         <v>10</v>
       </c>
@@ -10922,7 +10964,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -10969,7 +11011,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11016,7 +11058,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11063,7 +11105,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11107,7 +11149,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11139,13 +11181,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -11157,7 +11199,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11174,7 +11216,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11225,7 +11267,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11242,7 +11284,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11250,10 +11292,10 @@
       <c r="C31" s="3">
         <v>22.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.29</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.22</v>
       </c>
       <c r="F31" s="3">
@@ -11262,16 +11304,16 @@
       <c r="G31" s="3">
         <v>8.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.19</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11378,7 +11420,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11402,7 +11444,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -11414,7 +11456,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="R2" s="3">
         <v>1.46</v>
@@ -11423,7 +11465,7 @@
         <v>12.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="U2" s="3">
         <v>2.58</v>
@@ -11431,7 +11473,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11461,7 +11503,7 @@
         <v>7.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="L3" s="3">
         <v>1.62</v>
@@ -11473,7 +11515,7 @@
         <v>6.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="R3" s="3">
         <v>1.17</v>
@@ -11482,7 +11524,7 @@
         <v>11.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="U3" s="3">
         <v>2.36</v>
@@ -11490,7 +11532,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11517,7 +11559,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>422</v>
+        <v>429</v>
       </c>
       <c r="L4" s="3">
         <v>2.0</v>
@@ -11530,7 +11572,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>423</v>
+        <v>430</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -11538,7 +11580,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11568,7 +11610,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>424</v>
+        <v>431</v>
       </c>
       <c r="L5" s="3">
         <v>2.86</v>
@@ -11580,7 +11622,7 @@
         <v>32.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>425</v>
+        <v>432</v>
       </c>
       <c r="R5" s="3">
         <v>1.59</v>
@@ -11589,7 +11631,7 @@
         <v>23.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="U5" s="3">
         <v>2.43</v>
@@ -11597,7 +11639,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11618,7 +11660,7 @@
         <v>15.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="L6" s="3">
         <v>2.33</v>
@@ -11630,7 +11672,7 @@
         <v>19.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="R6" s="3">
         <v>1.79</v>
@@ -11639,7 +11681,7 @@
         <v>17.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="U6" s="3">
         <v>2.47</v>
@@ -11647,7 +11689,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11678,7 +11720,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11686,7 +11728,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11710,7 +11752,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="L8" s="3">
         <v>2.76</v>
@@ -11722,7 +11764,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11760,7 +11802,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -11774,7 +11816,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -11783,7 +11825,7 @@
         <v>2.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="U11" s="3">
         <v>2.0</v>
@@ -11791,7 +11833,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -11803,7 +11845,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -11829,13 +11871,13 @@
         <v>123</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>129</v>
@@ -11847,7 +11889,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -11864,7 +11906,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -11915,7 +11957,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -11932,7 +11974,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -11940,10 +11982,10 @@
       <c r="C24" s="3">
         <v>14.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>0.16</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.15</v>
       </c>
       <c r="F24" s="3">
@@ -11952,16 +11994,16 @@
       <c r="G24" s="3">
         <v>14.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.18</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12068,7 +12110,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12080,7 +12122,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="L2" s="3">
         <v>2.4</v>
@@ -12092,7 +12134,7 @@
         <v>26.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="R2" s="3">
         <v>1.73</v>
@@ -12101,7 +12143,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12109,7 +12151,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12133,7 +12175,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -12145,7 +12187,7 @@
         <v>19.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="R3" s="3">
         <v>1.59</v>
@@ -12154,7 +12196,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="U3" s="3">
         <v>2.8</v>
@@ -12162,7 +12204,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12189,7 +12231,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -12201,7 +12243,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12210,7 +12252,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12218,7 +12260,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12248,7 +12290,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="L5" s="3">
         <v>2.1</v>
@@ -12260,7 +12302,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="R5" s="3">
         <v>1.7</v>
@@ -12269,7 +12311,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="U5" s="3">
         <v>2.75</v>
@@ -12277,7 +12319,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12289,7 +12331,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="L6" s="3">
         <v>2.67</v>
@@ -12299,7 +12341,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12320,7 +12362,7 @@
         <v>4.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="L7" s="3">
         <v>0.0</v>
@@ -12335,7 +12377,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12344,7 +12386,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12389,13 +12431,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12404,7 +12446,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12413,7 +12455,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12434,7 +12476,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12473,7 +12515,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12488,7 +12530,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12500,7 +12542,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12548,13 +12590,13 @@
         <v>123</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>129</v>
@@ -12566,7 +12608,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12583,7 +12625,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12616,12 +12658,12 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12629,10 +12671,10 @@
       <c r="C24" s="3">
         <v>5.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>0.12</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.12</v>
       </c>
       <c r="F24" s="3">
@@ -12641,16 +12683,16 @@
       <c r="G24" s="3">
         <v>8.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.26</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>0.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12757,7 +12799,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -12769,7 +12811,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L2" s="3">
         <v>1.36</v>
@@ -12779,7 +12821,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="R2" s="3">
         <v>1.38</v>
@@ -12788,7 +12830,7 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="U2" s="3">
         <v>2.17</v>
@@ -12816,7 +12858,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -12840,7 +12882,7 @@
         <v>6.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L4" s="3">
         <v>3.12</v>
@@ -12849,7 +12891,7 @@
         <v>18.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="R4" s="3">
         <v>1.39</v>
@@ -12858,7 +12900,7 @@
         <v>10.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="U4" s="3">
         <v>2.4</v>
@@ -12866,7 +12908,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12896,7 +12938,7 @@
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="L5" s="3">
         <v>2.17</v>
@@ -12908,7 +12950,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -12917,7 +12959,7 @@
         <v>7.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="U5" s="3">
         <v>2.57</v>
@@ -12925,7 +12967,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -12952,7 +12994,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="L6" s="3">
         <v>2.18</v>
@@ -12964,7 +13006,7 @@
         <v>22.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -12973,7 +13015,7 @@
         <v>10.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="U6" s="3">
         <v>2.4</v>
@@ -12981,7 +13023,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13003,7 +13045,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13011,7 +13053,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13035,7 +13077,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="L8" s="3">
         <v>2.31</v>
@@ -13044,7 +13086,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13081,7 +13123,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13104,7 +13146,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13112,7 +13154,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13124,7 +13166,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="L11" s="3">
         <v>2.4</v>
@@ -13136,7 +13178,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13154,7 +13196,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13166,7 +13208,7 @@
         <v>5.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -13175,7 +13217,7 @@
         <v>4.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -13227,13 +13269,13 @@
         <v>123</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H17" s="13" t="s">
         <v>129</v>
@@ -13245,7 +13287,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13262,7 +13304,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13310,7 +13352,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13324,7 +13366,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13332,10 +13374,10 @@
       <c r="C24" s="3">
         <v>9.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>0.16</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.11</v>
       </c>
       <c r="F24" s="3">
@@ -13344,16 +13386,16 @@
       <c r="G24" s="3">
         <v>13.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.25</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13488,7 +13530,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13503,7 +13545,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13515,7 +13557,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13524,7 +13566,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13548,7 +13590,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13561,7 +13603,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13569,7 +13611,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13596,7 +13638,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13608,7 +13650,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13617,7 +13659,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13644,7 +13686,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13656,7 +13698,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13665,7 +13707,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13673,7 +13715,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13697,7 +13739,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13709,7 +13751,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13718,7 +13760,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13726,7 +13768,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13744,7 +13786,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13765,7 +13807,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -13773,7 +13815,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -13787,7 +13829,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -13796,7 +13838,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -13808,7 +13850,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -13817,7 +13859,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -13825,7 +13867,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -13846,7 +13888,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -13883,10 +13925,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -13916,7 +13958,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -13991,7 +14033,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14038,7 +14080,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14129,7 +14171,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14167,7 +14209,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14202,13 +14244,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -14220,7 +14262,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14237,7 +14279,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14276,12 +14318,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14289,10 +14331,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.27</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.16</v>
       </c>
       <c r="F31" s="3">
@@ -14301,16 +14343,16 @@
       <c r="G31" s="3">
         <v>12.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.32</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14417,7 +14459,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14456,7 +14498,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14465,7 +14507,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14473,7 +14515,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14500,7 +14542,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14515,7 +14557,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14524,7 +14566,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14545,7 +14587,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14557,7 +14599,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14566,7 +14608,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14574,7 +14616,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14584,7 +14626,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14597,7 +14639,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14624,7 +14666,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14636,7 +14678,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14645,7 +14687,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14653,7 +14695,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14680,7 +14722,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14692,7 +14734,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14701,7 +14743,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14737,7 +14779,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14746,7 +14788,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14776,7 +14818,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -14784,7 +14826,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -14808,7 +14850,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -14817,7 +14859,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -14838,7 +14880,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -14851,7 +14893,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -14859,7 +14901,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -14874,7 +14916,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -14883,7 +14925,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -14892,7 +14934,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -14900,7 +14942,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -14930,7 +14972,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -14964,10 +15006,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
@@ -14993,7 +15035,7 @@
         <v>116</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15026,7 +15068,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15114,7 +15156,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15161,7 +15203,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15202,7 +15244,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15249,7 +15291,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15281,13 +15323,13 @@
         <v>123</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>129</v>
@@ -15299,7 +15341,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15316,7 +15358,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15367,12 +15409,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15380,10 +15422,10 @@
       <c r="C32" s="3">
         <v>8.0</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.19</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.14</v>
       </c>
       <c r="F32" s="3">
@@ -15392,16 +15434,16 @@
       <c r="G32" s="3">
         <v>13.0</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.22</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15508,7 +15550,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15556,7 +15598,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15605,7 +15647,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15654,7 +15696,7 @@
         <v>3.0</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="U4" s="21">
         <v>2.33</v>
@@ -15673,7 +15715,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15700,7 +15742,7 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="L5" s="3">
         <v>2.38</v>
@@ -15712,7 +15754,7 @@
         <v>20.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>171</v>
+        <v>162</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -15721,7 +15763,7 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>172</v>
+        <v>163</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -15729,7 +15771,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15748,7 +15790,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -15766,7 +15808,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>180</v>
+        <v>166</v>
       </c>
       <c r="L7" s="3">
         <v>2.38</v>
@@ -15778,7 +15820,7 @@
         <v>16.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="R7" s="3">
         <v>1.69</v>
@@ -15816,7 +15858,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -15831,7 +15873,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="L9" s="3">
         <v>2.36</v>
@@ -15843,7 +15885,7 @@
         <v>24.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>191</v>
+        <v>184</v>
       </c>
       <c r="R9" s="3">
         <v>2.04</v>
@@ -15852,7 +15894,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15860,7 +15902,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -15872,7 +15914,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -15884,7 +15926,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -15902,7 +15944,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -15911,7 +15953,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -15942,10 +15984,10 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
@@ -15971,7 +16013,7 @@
         <v>116</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16001,7 +16043,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>200</v>
+        <v>212</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16048,7 +16090,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -16092,7 +16134,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>208</v>
+        <v>218</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16139,7 +16181,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16186,7 +16228,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16233,7 +16275,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16268,13 +16310,13 @@
         <v>123</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>129</v>
@@ -16286,7 +16328,7 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16303,7 +16345,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16354,7 +16396,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16362,7 +16404,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16370,10 +16412,10 @@
       <c r="C30" s="3">
         <v>23.0</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <v>0.32</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>0.22</v>
       </c>
       <c r="F30" s="3">
@@ -16382,16 +16424,16 @@
       <c r="G30" s="3">
         <v>13.0</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="17">
         <v>0.16</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16498,7 +16540,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16522,7 +16564,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -16534,7 +16576,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -16543,7 +16585,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -16551,7 +16593,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16562,7 +16604,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16589,7 +16631,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -16601,7 +16643,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -16610,7 +16652,7 @@
         <v>7.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="U4" s="3">
         <v>2.29</v>
@@ -16618,7 +16660,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16630,7 +16672,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16639,7 +16681,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="R5" s="3">
         <v>1.45</v>
@@ -16648,7 +16690,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16656,7 +16698,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16686,7 +16728,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>182</v>
+        <v>192</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -16701,7 +16743,7 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="R6" s="3">
         <v>0.5</v>
@@ -16710,7 +16752,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16718,7 +16760,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16736,7 +16778,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="L7" s="3">
         <v>2.36</v>
@@ -16748,7 +16790,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -16756,7 +16798,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -16777,7 +16819,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -16789,7 +16831,7 @@
         <v>9.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="R8" s="3">
         <v>1.11</v>
@@ -16798,7 +16840,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="U8" s="3">
         <v>2.0</v>
@@ -16831,7 +16873,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -16840,7 +16882,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16852,7 +16894,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>197</v>
+        <v>214</v>
       </c>
       <c r="L10" s="3">
         <v>1.75</v>
@@ -16864,7 +16906,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -16873,7 +16915,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -16894,7 +16936,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -16906,7 +16948,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16915,7 +16957,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -16936,7 +16978,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>198</v>
+        <v>220</v>
       </c>
       <c r="L12" s="3">
         <v>2.25</v>
@@ -16948,7 +16990,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>199</v>
+        <v>222</v>
       </c>
       <c r="R12" s="3">
         <v>0.75</v>
@@ -16957,7 +16999,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -16965,7 +17007,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -16992,14 +17034,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>203</v>
+        <v>225</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17024,10 +17066,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
@@ -17053,7 +17095,7 @@
         <v>116</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17083,7 +17125,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>213</v>
+        <v>230</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17130,7 +17172,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>219</v>
+        <v>233</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17174,7 +17216,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17221,7 +17263,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>228</v>
+        <v>239</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17268,7 +17310,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>233</v>
+        <v>242</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17315,7 +17357,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17350,13 +17392,13 @@
         <v>123</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H25" s="13" t="s">
         <v>129</v>
@@ -17368,7 +17410,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17385,7 +17427,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17430,12 +17472,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17443,10 +17485,10 @@
       <c r="C32" s="3">
         <v>13.0</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.21</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.18</v>
       </c>
       <c r="F32" s="3">
@@ -17455,16 +17497,16 @@
       <c r="G32" s="3">
         <v>12.0</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.31</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17571,7 +17613,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17595,7 +17637,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17607,7 +17649,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17616,7 +17658,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17624,7 +17666,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17645,7 +17687,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17655,7 +17697,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17663,7 +17705,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17690,7 +17732,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17699,7 +17741,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17708,7 +17750,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17716,7 +17758,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17740,7 +17782,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -17764,7 +17806,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -17782,7 +17824,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>183</v>
+        <v>198</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -17803,7 +17845,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -17811,7 +17853,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -17827,7 +17869,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -17836,7 +17878,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -17863,7 +17905,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -17875,7 +17917,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>194</v>
+        <v>213</v>
       </c>
       <c r="L9" s="3">
         <v>1.833</v>
@@ -17885,7 +17927,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -17932,10 +17974,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -17961,7 +18003,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -17991,7 +18033,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>201</v>
+        <v>224</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18035,7 +18077,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18049,7 +18091,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="16">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18077,7 +18119,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>215</v>
+        <v>232</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18118,7 +18160,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>220</v>
+        <v>235</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18153,7 +18195,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>223</v>
+        <v>238</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18200,7 +18242,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>230</v>
+        <v>241</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18232,13 +18274,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -18250,7 +18292,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18279,7 +18321,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18287,10 +18329,10 @@
       <c r="C26" s="3">
         <v>5.0</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <v>0.16</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="17">
         <v>0.2</v>
       </c>
       <c r="F26" s="3">
@@ -18318,12 +18360,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18334,7 +18376,7 @@
       <c r="D31" s="24">
         <v>0.14286</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.14286</v>
       </c>
       <c r="F31" s="3">
@@ -18343,16 +18385,16 @@
       <c r="G31" s="3">
         <v>9.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.1212</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.2727</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18459,7 +18501,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18489,7 +18531,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>202</v>
+        <v>170</v>
       </c>
       <c r="L2" s="3">
         <v>2.364</v>
@@ -18501,7 +18543,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>205</v>
+        <v>172</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18510,7 +18552,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18518,7 +18560,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18542,7 +18584,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>209</v>
+        <v>177</v>
       </c>
       <c r="L3" s="3">
         <v>2.5</v>
@@ -18557,7 +18599,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18566,7 +18608,7 @@
         <v>4.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="U3" s="3">
         <v>1.75</v>
@@ -18574,7 +18616,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18598,7 +18640,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>214</v>
+        <v>187</v>
       </c>
       <c r="L4" s="3">
         <v>2.75</v>
@@ -18608,7 +18650,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18620,7 +18662,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>216</v>
+        <v>191</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -18632,7 +18674,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>218</v>
+        <v>194</v>
       </c>
       <c r="R5" s="3">
         <v>1.176</v>
@@ -18641,7 +18683,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>221</v>
+        <v>195</v>
       </c>
       <c r="U5" s="3">
         <v>1.667</v>
@@ -18649,7 +18691,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18673,7 +18715,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>224</v>
+        <v>197</v>
       </c>
       <c r="L6" s="3">
         <v>3.375</v>
@@ -18685,7 +18727,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="R6" s="3">
         <v>1.667</v>
@@ -18694,7 +18736,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -18702,7 +18744,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -18720,7 +18762,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="L7" s="3">
         <v>2.5</v>
@@ -18732,7 +18774,7 @@
         <v>8.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>231</v>
+        <v>206</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -18741,7 +18783,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>232</v>
+        <v>209</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -18765,7 +18807,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18785,7 +18827,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -18809,7 +18851,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>235</v>
+        <v>215</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -18822,7 +18864,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -18830,7 +18872,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -18848,7 +18890,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>236</v>
+        <v>217</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -18857,7 +18899,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -18866,7 +18908,7 @@
         <v>2.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>237</v>
+        <v>219</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -18875,7 +18917,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -18890,7 +18932,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -18918,10 +18960,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -18947,7 +18989,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18974,7 +19016,7 @@
         <v>19.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="M16" s="3">
         <v>1.053</v>
@@ -19021,7 +19063,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="M17" s="3">
         <v>1.4</v>
@@ -19062,7 +19104,7 @@
         <v>4.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="M18" s="3">
         <v>1.75</v>
@@ -19109,7 +19151,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="M19" s="3">
         <v>1.818</v>
@@ -19150,7 +19192,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="M20" s="3">
         <v>1.25</v>
@@ -19188,7 +19230,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="M21" s="3">
         <v>1.375</v>
@@ -19220,13 +19262,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -19239,7 +19281,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19247,7 +19289,7 @@
       <c r="D25" s="24">
         <v>0.0769</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="17">
         <v>0.0</v>
       </c>
       <c r="F25" s="3">
@@ -19256,17 +19298,17 @@
       <c r="G25" s="3">
         <v>3.0</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="17">
         <v>0.2</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="17">
         <v>0.12</v>
       </c>
       <c r="L25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19307,7 +19349,7 @@
       <c r="D27" s="24">
         <v>0.125</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="17">
         <v>0.25</v>
       </c>
       <c r="F27" s="3">
@@ -19316,10 +19358,10 @@
       <c r="G27" s="3">
         <v>2.0</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="17">
         <v>0.24</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="17">
         <v>0.08</v>
       </c>
     </row>
@@ -19330,12 +19372,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19343,10 +19385,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.15</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.22</v>
       </c>
       <c r="F31" s="3">
@@ -19355,16 +19397,16 @@
       <c r="G31" s="3">
         <v>10.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.18</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19471,7 +19513,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19510,7 +19552,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19558,7 +19600,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -19566,7 +19608,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19590,7 +19632,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="L4" s="3">
         <v>3.33</v>
@@ -19602,7 +19644,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="R4" s="3">
         <v>0.86</v>
@@ -19611,7 +19653,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="U4" s="3">
         <v>2.4</v>
@@ -19619,7 +19661,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19649,7 +19691,7 @@
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="L5" s="3">
         <v>1.76</v>
@@ -19661,7 +19703,7 @@
         <v>8.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -19670,7 +19712,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19678,7 +19720,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19708,7 +19750,7 @@
         <v>7.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L6" s="3">
         <v>2.43</v>
@@ -19726,7 +19768,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>256</v>
+        <v>263</v>
       </c>
       <c r="R6" s="3">
         <v>1.69</v>
@@ -19735,7 +19777,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19743,7 +19785,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -19768,7 +19810,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -19800,7 +19842,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="L8" s="3">
         <v>2.44</v>
@@ -19818,7 +19860,7 @@
         <v>3.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="R8" s="3">
         <v>2.33</v>
@@ -19827,7 +19869,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="U8" s="3">
         <v>1.0</v>
@@ -19835,7 +19877,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -19862,7 +19904,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="L9" s="3">
         <v>2.18</v>
@@ -19875,7 +19917,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>261</v>
+        <v>272</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -19916,10 +19958,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -19945,7 +19987,7 @@
         <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19978,7 +20020,7 @@
         <v>23.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>262</v>
+        <v>282</v>
       </c>
       <c r="M16" s="3">
         <v>1.48</v>
@@ -20025,7 +20067,7 @@
         <v>9.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="M17" s="3">
         <v>2.33</v>
@@ -20072,7 +20114,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>267</v>
+        <v>288</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -20119,7 +20161,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>270</v>
+        <v>294</v>
       </c>
       <c r="M19" s="3">
         <v>1.64</v>
@@ -20163,7 +20205,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>271</v>
+        <v>298</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -20210,7 +20252,7 @@
         <v>9.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>272</v>
+        <v>305</v>
       </c>
       <c r="M21" s="3">
         <v>1.67</v>
@@ -20245,13 +20287,13 @@
         <v>123</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H24" s="13" t="s">
         <v>129</v>
@@ -20263,7 +20305,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20280,7 +20322,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20331,7 +20373,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20348,7 +20390,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20356,10 +20398,10 @@
       <c r="C31" s="3">
         <v>19.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.19</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.19</v>
       </c>
       <c r="F31" s="3">
@@ -20368,16 +20410,16 @@
       <c r="G31" s="3">
         <v>23.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.16</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -103,97 +103,130 @@
     <t>Cora</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t>Nataly</t>
   </si>
   <si>
     <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
   </si>
   <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>Annabelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
     <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
   </si>
   <si>
-    <t xml:space="preserve">Nataly </t>
-  </si>
-  <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>Bridget</t>
   </si>
   <si>
     <t>Addy</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t>Gaby</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+  </si>
+  <si>
     <t>Kinley</t>
   </si>
   <si>
-    <t>Agnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
@@ -202,91 +235,250 @@
     <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
   </si>
   <si>
     <t>Audri</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
   </si>
   <si>
     <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+    <t>3 - 0 - 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
   </si>
   <si>
-    <t>3 - 0 - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>1 - 1 - 1 - 0 - 0</t>
   </si>
   <si>
     <t>Tea</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
+    <t xml:space="preserve">3 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
-  </si>
-  <si>
-    <t>Bridget</t>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t>Corena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 2 - </t>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>Rotation (follow setter starting position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - </t>
+  </si>
+  <si>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
+  </si>
+  <si>
+    <t>Serve Errors</t>
+  </si>
+  <si>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>Piper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
+  </si>
+  <si>
+    <t>Service error (us)</t>
+  </si>
+  <si>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>Service Errors (them)</t>
+  </si>
+  <si>
+    <t>Ace % (them)</t>
+  </si>
+  <si>
+    <t>Service Error % (Them)</t>
+  </si>
+  <si>
+    <t>Set 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>Set 2</t>
+  </si>
+  <si>
+    <t>Set 3</t>
+  </si>
+  <si>
+    <t>Set 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
+  </si>
+  <si>
+    <t>Set 5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
+  </si>
+  <si>
+    <t>Team Kill Efficiency (all games)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
   </si>
   <si>
     <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
@@ -295,207 +487,15 @@
     <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
     <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - </t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
-  </si>
-  <si>
-    <t>Kill Efficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
-  </si>
-  <si>
-    <t>Serve Receive Avg Score</t>
-  </si>
-  <si>
-    <t>Serve Aces</t>
-  </si>
-  <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
-  </si>
-  <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t>Service error (us)</t>
-  </si>
-  <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
-  </si>
-  <si>
-    <t>Aces (them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>Service Errors (them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t>Ace % (them)</t>
-  </si>
-  <si>
-    <t>Service Error % (Them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Set 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t>Set 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
-  </si>
-  <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 5</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>Team Passer Rating (all games)</t>
   </si>
   <si>
-    <t>Team Kill Efficiency (all games)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -604,30 +604,48 @@
     <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
   </si>
   <si>
     <t>2- 1- 0- 3- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
-  </si>
-  <si>
     <t>2- 2- 3- 3- 2- 3- 2- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
     <t>0- 0</t>
   </si>
   <si>
     <t>2- 2- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - </t>
-  </si>
-  <si>
     <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
   </si>
   <si>
@@ -640,37 +658,22 @@
     <t>3- 2- 3- 5- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
     <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
     <t>1- 3- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
   </si>
   <si>
     <t>3- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
+    <t>1- 3- 0- 3- 1</t>
   </si>
   <si>
     <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
@@ -682,21 +685,18 @@
     <t xml:space="preserve">3- 3- 2- </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
+  </si>
+  <si>
     <t>2- 1- 2- 0- 0</t>
   </si>
   <si>
-    <t>1- 3- 0- 3- 1</t>
-  </si>
-  <si>
     <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
   </si>
   <si>
     <t>3- 1- 2- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
-  </si>
-  <si>
     <t>3- 1- 5- 2</t>
   </si>
   <si>
@@ -715,24 +715,24 @@
     <t>1- 0- 3- 2- 0- 1- 1</t>
   </si>
   <si>
+    <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
+  </si>
+  <si>
+    <t>2- 2- 0</t>
+  </si>
+  <si>
     <t>0- 1- 3</t>
   </si>
   <si>
-    <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
-  </si>
-  <si>
-    <t>2- 2- 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">3- </t>
   </si>
   <si>
+    <t>1- 3- 0- 1- 0</t>
+  </si>
+  <si>
     <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
-    <t>1- 3- 0- 1- 0</t>
-  </si>
-  <si>
     <t>1- 2- 0- 0- 1- 0</t>
   </si>
   <si>
@@ -919,15 +919,51 @@
     <t xml:space="preserve">3 - 5 - 0 - 0 - 2 - 2 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 1 - 2 - 3 - 1 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>5 - 2 - 3 - 0 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 1 - 2 - 3 - 1 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
   </si>
   <si>
@@ -937,9 +973,6 @@
     <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t>5 - 2 - 3 - 0 -</t>
-  </si>
-  <si>
     <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
   </si>
   <si>
@@ -949,21 +982,12 @@
     <t xml:space="preserve">2- 2- 2- 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
@@ -976,51 +1000,39 @@
     <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1033,9 +1045,6 @@
     <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
   </si>
   <si>
@@ -1045,19 +1054,13 @@
     <t xml:space="preserve">1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
+    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
@@ -1069,72 +1072,69 @@
     <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
   </si>
   <si>
@@ -1207,39 +1207,39 @@
     <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 0 - 2 - 3 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 2 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 0 - 1 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 3 - 1 - 0 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 0 - 5 - 2 - 2 - 0 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 3 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 2 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 0 - 1 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 3 - 1 - 0 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 5 - 2 - 2 - 0 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 5 - 5 - 0 - 1 - 1 - 1 - 5 -  3 - 3 - </t>
   </si>
   <si>
@@ -1258,13 +1258,13 @@
     <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - </t>
+    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - </t>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - </t>
@@ -1276,7 +1276,7 @@
     <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - </t>
+    <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
@@ -1300,67 +1300,67 @@
     <t xml:space="preserve">2 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 5 - 2 - 1 - 2 - 1 - 5 - 3 - 2 - 1 - 2 - 3 - 1 - 5 - 2 - 3 - 3 - 3 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 5 - 3 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 2 - 0 - 3 - 2 - 3 - 5 - 1 - 2 - 3 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 2 - 2 - 3 - 0 - 2 - 2 - 0 - 2 - 2 - 2 - 1 - 2 - 3 - 3 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 2 - 1 - 2 - 2 - 2 - 0 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 2 - 3 - 3 - 2 - 3 - 1 - 3 - 2 - 3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 1 - 2 - 3 - 2 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - 0 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 2 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 3 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 3 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 2 - 0 - 3 - 2 - 3 - 5 - 1 - 2 - 3 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - 3 - 0 - 2 - 2 - 0 - 2 - 2 - 2 - 1 - 2 - 3 - 3 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 2 - 1 - 2 - 2 - 2 - 0 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 2 - 3 - 3 - 2 - 3 - 1 - 3 - 2 - 3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 1 - 2 - 3 - 2 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - 0 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 2 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 3 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 5 - 3 - 0 - 0 - 5 - 5 - 1 - 3 - 5 - 3 - 2 - 3 - 0 - 2 - 5 - 0 - </t>
@@ -1537,6 +1537,7 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1558,7 +1559,6 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1994,7 +1994,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2006,7 +2006,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2042,7 +2042,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2054,7 +2054,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2063,7 +2063,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2081,7 +2081,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2096,7 +2096,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2117,7 +2117,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2126,7 +2126,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>55</v>
+        <v>66</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2135,7 +2135,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2159,7 +2159,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2168,7 +2168,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2177,7 +2177,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2189,7 +2189,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2201,7 +2201,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2210,7 +2210,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2223,7 +2223,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2250,7 +2250,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>85</v>
+        <v>149</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2265,7 +2265,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>86</v>
+        <v>150</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2274,7 +2274,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2301,7 +2301,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2310,7 +2310,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2319,7 +2319,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2340,7 +2340,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2379,7 +2379,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2397,40 +2397,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2470,37 +2470,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2529,7 +2529,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2555,7 +2555,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2584,7 +2584,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2613,12 +2613,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2647,10 +2647,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="34">
@@ -2759,7 +2759,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2801,7 +2801,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2809,7 +2809,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2845,7 +2845,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2885,7 +2885,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2893,7 +2893,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2941,7 +2941,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -3026,7 +3026,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3050,7 +3050,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3103,7 +3103,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3115,7 +3115,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3128,7 +3128,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3137,7 +3137,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3162,7 +3162,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3178,36 +3178,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3477,37 +3477,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3521,7 +3521,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3538,7 +3538,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3555,17 +3555,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3746,7 +3746,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3796,7 +3796,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3813,7 +3813,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3872,7 +3872,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3911,7 +3911,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -3920,7 +3920,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -3928,7 +3928,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3951,7 +3951,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3959,7 +3959,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -3983,7 +3983,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="L7" s="3">
         <v>2.0</v>
@@ -3992,7 +3992,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4001,7 +4001,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4009,7 +4009,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4022,7 +4022,7 @@
         <v>7.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="R8" s="3">
         <v>2.29</v>
@@ -4031,7 +4031,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4039,7 +4039,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4057,7 +4057,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4067,7 +4067,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4075,7 +4075,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4090,7 +4090,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4100,7 +4100,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4118,7 +4118,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4127,7 +4127,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4148,7 +4148,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4157,7 +4157,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4175,7 +4175,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4187,7 +4187,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4208,7 +4208,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>317</v>
+        <v>302</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4232,7 +4232,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4242,7 +4242,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4251,7 +4251,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4267,36 +4267,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4329,7 +4329,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4376,7 +4376,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4420,7 +4420,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4464,7 +4464,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -4511,7 +4511,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>326</v>
+        <v>308</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4555,7 +4555,7 @@
         <v>7.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="M22" s="3">
         <v>2.29</v>
@@ -4578,37 +4578,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="F25" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4625,7 +4625,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4642,7 +4642,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4659,17 +4659,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4698,7 +4698,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4833,7 +4833,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4877,7 +4877,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4889,7 +4889,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4898,7 +4898,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4906,7 +4906,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4933,7 +4933,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4945,7 +4945,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4954,7 +4954,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4962,7 +4962,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -4989,7 +4989,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5001,7 +5001,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5010,7 +5010,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5018,7 +5018,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5030,7 +5030,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5042,7 +5042,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5051,7 +5051,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5066,7 +5066,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5075,7 +5075,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5099,7 +5099,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5111,7 +5111,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5119,7 +5119,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5147,7 +5147,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5174,7 +5174,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5199,7 +5199,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5215,36 +5215,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5277,7 +5277,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5324,7 +5324,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5371,7 +5371,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5415,7 +5415,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5459,7 +5459,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>338</v>
+        <v>328</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5503,7 +5503,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5526,37 +5526,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5585,7 +5585,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5602,7 +5602,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5619,7 +5619,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5636,12 +5636,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5676,7 +5676,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5783,7 +5783,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5810,7 +5810,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5822,7 +5822,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5831,7 +5831,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5869,7 +5869,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5881,7 +5881,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5890,7 +5890,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5898,7 +5898,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5928,7 +5928,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5943,7 +5943,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5952,7 +5952,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5960,7 +5960,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -5983,7 +5983,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -5991,7 +5991,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6013,7 +6013,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6030,7 +6030,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6050,7 +6050,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6064,7 +6064,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6073,7 +6073,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6092,7 +6092,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6107,7 +6107,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6116,7 +6116,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6125,7 +6125,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6159,7 +6159,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6186,7 +6186,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -6199,7 +6199,7 @@
         <v>7.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="U10" s="3">
         <v>2.14</v>
@@ -6207,7 +6207,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6235,7 +6235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6251,36 +6251,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6313,7 +6313,7 @@
         <v>6.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -6360,7 +6360,7 @@
         <v>14.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="M17" s="3">
         <v>1.79</v>
@@ -6407,7 +6407,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6454,7 +6454,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>350</v>
+        <v>363</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6501,7 +6501,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>351</v>
+        <v>365</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6548,7 +6548,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>352</v>
+        <v>366</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6571,37 +6571,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6618,7 +6618,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6635,7 +6635,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6652,7 +6652,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6669,7 +6669,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6686,7 +6686,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6715,7 +6715,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6822,7 +6822,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6840,7 +6840,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>353</v>
+        <v>342</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6883,7 +6883,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6895,7 +6895,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6904,7 +6904,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6912,7 +6912,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6924,7 +6924,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6933,7 +6933,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6942,7 +6942,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6950,7 +6950,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -6974,7 +6974,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="L5" s="3">
         <v>2.75</v>
@@ -6986,7 +6986,7 @@
         <v>16.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -6995,7 +6995,7 @@
         <v>13.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="U5" s="3">
         <v>2.15</v>
@@ -7003,7 +7003,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7033,7 +7033,7 @@
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>363</v>
+        <v>358</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -7048,7 +7048,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>364</v>
+        <v>359</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -7057,7 +7057,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7065,7 +7065,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7087,7 +7087,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7096,7 +7096,7 @@
         <v>7.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="U7" s="3">
         <v>1.86</v>
@@ -7104,7 +7104,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7128,7 +7128,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="L8" s="3">
         <v>1.67</v>
@@ -7148,7 +7148,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7225,7 +7225,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7258,7 +7258,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7293,7 +7293,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7309,36 +7309,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7623,37 +7623,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7670,7 +7670,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7687,7 +7687,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7704,7 +7704,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7721,12 +7721,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7755,7 +7755,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7865,7 +7865,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -8009,7 +8009,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8059,7 +8059,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8082,7 +8082,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8090,7 +8090,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8128,7 +8128,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8161,7 +8161,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8198,7 +8198,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8235,7 +8235,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8250,7 +8250,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8259,7 +8259,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8283,7 +8283,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>400</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8295,7 +8295,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8313,37 +8313,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="F16" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8360,7 +8360,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8377,7 +8377,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8394,7 +8394,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8411,7 +8411,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8428,7 +8428,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8457,7 +8457,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8588,7 +8588,7 @@
         <v>8.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="L2" s="3">
         <v>3.87</v>
@@ -8600,7 +8600,7 @@
         <v>15.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="R2" s="3">
         <v>1.53</v>
@@ -8609,7 +8609,7 @@
         <v>5.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -8617,7 +8617,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8632,7 +8632,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="L3" s="3">
         <v>1.86</v>
@@ -8641,7 +8641,7 @@
         <v>8.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="R3" s="3">
         <v>1.63</v>
@@ -8650,7 +8650,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8658,7 +8658,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8688,7 +8688,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="L4" s="3">
         <v>2.11</v>
@@ -8697,7 +8697,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8706,7 +8706,7 @@
         <v>3.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -8734,7 +8734,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8774,7 +8774,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8782,7 +8782,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8830,7 +8830,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8838,7 +8838,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8859,7 +8859,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8879,14 +8879,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8903,7 +8903,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8915,7 +8915,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8930,37 +8930,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="F16" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8977,7 +8977,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -8994,7 +8994,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9011,17 +9011,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9050,7 +9050,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9212,7 +9212,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9228,36 +9228,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9303,62 +9303,62 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -9367,7 +9367,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9468,7 +9468,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="D2" s="3">
         <v>6.0</v>
@@ -9492,7 +9492,7 @@
         <v>2.0</v>
       </c>
       <c r="P2" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>408</v>
@@ -9501,7 +9501,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -9516,7 +9516,7 @@
         <v>409</v>
       </c>
       <c r="P3" s="3">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>410</v>
@@ -9533,13 +9533,13 @@
         <v>21</v>
       </c>
       <c r="B4" s="3">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="D4" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F4" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H4" s="3">
         <v>4.0</v>
@@ -9557,18 +9557,18 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3">
         <v>7.0</v>
       </c>
       <c r="C5" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -9592,19 +9592,22 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
       </c>
       <c r="D6" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
+      </c>
+      <c r="E6" s="3">
+        <v>1.0</v>
       </c>
       <c r="F6" s="3">
         <v>1.0</v>
       </c>
       <c r="H6" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="I6" s="3">
         <v>1.0</v>
@@ -9620,7 +9623,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -9653,13 +9656,13 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="S7" s="3">
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
     </row>
     <row r="8">
@@ -9699,37 +9702,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="F16" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9746,27 +9749,30 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
@@ -9775,7 +9781,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9877,7 +9883,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -9936,7 +9942,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -9979,7 +9985,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -9997,7 +10003,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10010,7 +10016,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10077,7 +10083,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10098,7 +10104,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="L6" s="3">
         <v>2.65</v>
@@ -10110,7 +10116,7 @@
         <v>20.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="R6" s="3">
         <v>1.0</v>
@@ -10119,7 +10125,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10152,7 +10158,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10182,7 +10188,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>424</v>
+        <v>432</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -10194,7 +10200,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>425</v>
+        <v>433</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -10203,7 +10209,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="U8" s="3">
         <v>1.83</v>
@@ -10211,7 +10217,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10223,7 +10229,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>427</v>
+        <v>438</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -10233,7 +10239,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10251,7 +10257,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10276,37 +10282,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D16" s="10" t="s">
+      <c r="C16" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E16" s="10" t="s">
+      <c r="D16" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="E16" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H16" s="13" t="s">
+      <c r="F16" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H16" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I16" s="14" t="s">
+      <c r="I16" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10323,7 +10329,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10340,7 +10346,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10357,7 +10363,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10374,12 +10380,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10408,7 +10414,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10539,7 +10545,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>31</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10551,7 +10557,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>35</v>
+        <v>25</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10560,7 +10566,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10568,7 +10574,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10586,7 +10592,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>46</v>
+        <v>33</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10599,7 +10605,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10607,7 +10613,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10634,7 +10640,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10646,7 +10652,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>59</v>
+        <v>43</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10655,7 +10661,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>61</v>
+        <v>44</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10663,7 +10669,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10675,7 +10681,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10684,7 +10690,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10693,7 +10699,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>74</v>
+        <v>52</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10701,7 +10707,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10725,7 +10731,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10737,7 +10743,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10746,7 +10752,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10754,7 +10760,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10781,7 +10787,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10818,7 +10824,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10827,7 +10833,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10845,7 +10851,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10858,7 +10864,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10866,7 +10872,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10880,7 +10886,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10895,7 +10901,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -10904,13 +10910,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -10925,7 +10931,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -10941,40 +10947,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11007,7 +11013,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11024,7 +11030,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="9">
         <f>10</f>
         <v>10</v>
       </c>
@@ -11055,7 +11061,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>137</v>
+        <v>113</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11102,7 +11108,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>142</v>
+        <v>115</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11149,7 +11155,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>146</v>
+        <v>117</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11196,7 +11202,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11240,7 +11246,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>153</v>
+        <v>121</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11260,37 +11266,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11307,7 +11313,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11324,7 +11330,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11341,7 +11347,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11358,7 +11364,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11375,7 +11381,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11404,7 +11410,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11511,7 +11517,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11535,7 +11541,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>429</v>
+        <v>422</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -11547,7 +11553,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>430</v>
+        <v>423</v>
       </c>
       <c r="R2" s="3">
         <v>1.46</v>
@@ -11556,7 +11562,7 @@
         <v>12.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>431</v>
+        <v>425</v>
       </c>
       <c r="U2" s="3">
         <v>2.58</v>
@@ -11564,7 +11570,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11594,7 +11600,7 @@
         <v>7.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
       <c r="L3" s="3">
         <v>1.62</v>
@@ -11606,7 +11612,7 @@
         <v>6.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
       <c r="R3" s="3">
         <v>1.17</v>
@@ -11615,7 +11621,7 @@
         <v>11.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
       <c r="U3" s="3">
         <v>2.36</v>
@@ -11623,7 +11629,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11650,7 +11656,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
       <c r="L4" s="3">
         <v>2.0</v>
@@ -11663,7 +11669,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -11701,7 +11707,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="L5" s="3">
         <v>2.86</v>
@@ -11713,7 +11719,7 @@
         <v>32.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="R5" s="3">
         <v>1.59</v>
@@ -11722,7 +11728,7 @@
         <v>23.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="U5" s="3">
         <v>2.43</v>
@@ -11730,7 +11736,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11751,7 +11757,7 @@
         <v>15.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="L6" s="3">
         <v>2.33</v>
@@ -11763,7 +11769,7 @@
         <v>19.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="R6" s="3">
         <v>1.79</v>
@@ -11772,7 +11778,7 @@
         <v>17.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="U6" s="3">
         <v>2.47</v>
@@ -11780,7 +11786,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11811,7 +11817,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11819,7 +11825,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11855,7 +11861,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11893,7 +11899,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -11907,7 +11913,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -11924,7 +11930,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -11936,7 +11942,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -11950,37 +11956,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="F17" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -11997,7 +12003,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12014,7 +12020,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12031,7 +12037,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12048,7 +12054,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12065,7 +12071,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12094,7 +12100,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12201,7 +12207,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12234,7 +12240,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>84</v>
+        <v>64</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12295,7 +12301,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12334,7 +12340,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12343,7 +12349,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12351,7 +12357,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12410,7 +12416,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12432,7 +12438,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12468,7 +12474,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12477,7 +12483,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12499,7 +12505,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12522,13 +12528,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12537,7 +12543,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12546,7 +12552,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12567,7 +12573,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12606,7 +12612,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12621,7 +12627,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12633,7 +12639,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12669,37 +12675,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="F17" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12716,7 +12722,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12727,7 +12733,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12744,17 +12750,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12783,7 +12789,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12890,7 +12896,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -12929,7 +12935,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -12949,7 +12955,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -12999,7 +13005,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13114,7 +13120,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13136,7 +13142,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13144,7 +13150,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13177,7 +13183,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13214,7 +13220,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13237,7 +13243,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13245,7 +13251,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13269,7 +13275,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13287,7 +13293,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13348,37 +13354,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C17" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D17" s="10" t="s">
+      <c r="C17" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E17" s="10" t="s">
+      <c r="D17" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F17" s="11" t="s">
+      <c r="E17" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H17" s="13" t="s">
+      <c r="F17" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H17" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I17" s="14" t="s">
+      <c r="I17" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13395,7 +13401,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13412,7 +13418,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13426,7 +13432,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13443,7 +13449,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13457,7 +13463,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13486,7 +13492,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13621,7 +13627,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13636,7 +13642,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13648,7 +13654,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13657,7 +13663,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13681,7 +13687,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13694,7 +13700,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13702,7 +13708,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13729,7 +13735,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13741,7 +13747,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13777,7 +13783,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13789,7 +13795,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13798,7 +13804,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13806,7 +13812,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13830,7 +13836,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13842,7 +13848,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13851,7 +13857,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13859,7 +13865,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13877,7 +13883,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13889,7 +13895,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -13898,7 +13904,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -13906,7 +13912,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -13920,7 +13926,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -13929,7 +13935,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -13941,7 +13947,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -13950,7 +13956,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -13958,7 +13964,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -13967,7 +13973,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -13979,7 +13985,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14000,7 +14006,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14016,40 +14022,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>110</v>
+        <v>97</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14082,7 +14088,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14124,7 +14130,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14171,7 +14177,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14218,7 +14224,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14323,37 +14329,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14370,7 +14376,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14387,7 +14393,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14404,17 +14410,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14443,7 +14449,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14577,7 +14583,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14589,7 +14595,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14598,7 +14604,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14606,7 +14612,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14633,7 +14639,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14648,7 +14654,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14657,7 +14663,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14678,7 +14684,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14690,7 +14696,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14699,7 +14705,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14707,7 +14713,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14717,7 +14723,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14730,7 +14736,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14757,7 +14763,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14769,7 +14775,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>62</v>
+        <v>76</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14778,7 +14784,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14786,7 +14792,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14813,7 +14819,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14825,7 +14831,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14834,7 +14840,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14870,7 +14876,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14879,7 +14885,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14891,7 +14897,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -14900,7 +14906,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -14909,7 +14915,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -14917,7 +14923,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -14932,7 +14938,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>98</v>
+        <v>111</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -14941,7 +14947,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -14950,7 +14956,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -14971,7 +14977,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -14984,7 +14990,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -14992,7 +14998,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15007,7 +15013,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15016,7 +15022,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15025,7 +15031,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15033,7 +15039,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15045,7 +15051,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15063,7 +15069,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15081,7 +15087,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15097,36 +15103,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15159,7 +15165,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15206,7 +15212,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15247,7 +15253,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15294,7 +15300,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15335,7 +15341,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15382,7 +15388,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15402,37 +15408,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="F25" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15449,7 +15455,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15466,7 +15472,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15483,7 +15489,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15500,12 +15506,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15534,7 +15540,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15689,7 +15695,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15738,7 +15744,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15806,7 +15812,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15862,7 +15868,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15881,7 +15887,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -15949,7 +15955,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -15985,7 +15991,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15993,7 +15999,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16017,7 +16023,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16035,7 +16041,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16044,7 +16050,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16059,7 +16065,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16075,36 +16081,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16389,37 +16395,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C23" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D23" s="10" t="s">
+      <c r="C23" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E23" s="10" t="s">
+      <c r="D23" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F23" s="11" t="s">
+      <c r="E23" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H23" s="13" t="s">
+      <c r="F23" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H23" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I23" s="14" t="s">
+      <c r="I23" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K23" s="15"/>
+      <c r="K23" s="16"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16436,7 +16442,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16453,7 +16459,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16470,7 +16476,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16487,7 +16493,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16495,7 +16501,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16524,7 +16530,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16684,7 +16690,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16695,7 +16701,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16751,7 +16757,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16763,7 +16769,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16781,7 +16787,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16789,7 +16795,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16843,7 +16849,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16851,7 +16857,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16889,7 +16895,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -16964,7 +16970,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -16973,7 +16979,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16997,7 +17003,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17006,7 +17012,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17027,7 +17033,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17039,7 +17045,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17048,7 +17054,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17069,7 +17075,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="L12" s="3">
         <v>2.25</v>
@@ -17081,7 +17087,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="R12" s="3">
         <v>0.75</v>
@@ -17090,7 +17096,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17098,7 +17104,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17113,7 +17119,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>118</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17125,14 +17131,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17141,7 +17147,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17157,36 +17163,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17216,7 +17222,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17263,7 +17269,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17307,7 +17313,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>208</v>
+        <v>195</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17354,7 +17360,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17401,7 +17407,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17448,7 +17454,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17471,37 +17477,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C25" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D25" s="10" t="s">
+      <c r="C25" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E25" s="10" t="s">
+      <c r="D25" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F25" s="11" t="s">
+      <c r="E25" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H25" s="13" t="s">
+      <c r="F25" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H25" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I25" s="14" t="s">
+      <c r="I25" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17518,7 +17524,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17535,7 +17541,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17552,7 +17558,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17563,12 +17569,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17597,7 +17603,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17728,7 +17734,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17740,7 +17746,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17749,7 +17755,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17757,7 +17763,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17778,7 +17784,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17788,7 +17794,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17796,7 +17802,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17823,7 +17829,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17832,7 +17838,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17841,7 +17847,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17849,7 +17855,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17873,7 +17879,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -17897,7 +17903,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -17915,7 +17921,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -17936,7 +17942,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -17944,7 +17950,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -17960,7 +17966,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -17969,7 +17975,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -17996,7 +18002,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18008,7 +18014,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="L9" s="3">
         <v>1.833</v>
@@ -18018,7 +18024,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18049,7 +18055,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18065,36 +18071,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18124,7 +18130,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18168,7 +18174,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18182,7 +18188,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="9">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18286,7 +18292,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18333,7 +18339,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18353,37 +18359,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18412,7 +18418,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18441,22 +18447,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18485,7 +18491,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18622,7 +18628,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="L2" s="3">
         <v>2.364</v>
@@ -18634,7 +18640,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18643,7 +18649,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18651,7 +18657,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18675,7 +18681,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="L3" s="3">
         <v>2.5</v>
@@ -18690,7 +18696,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18699,7 +18705,7 @@
         <v>4.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="U3" s="3">
         <v>1.75</v>
@@ -18707,7 +18713,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18741,7 +18747,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18782,7 +18788,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18806,7 +18812,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="L6" s="3">
         <v>3.375</v>
@@ -18818,7 +18824,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="R6" s="3">
         <v>1.667</v>
@@ -18835,7 +18841,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -18853,7 +18859,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L7" s="3">
         <v>2.5</v>
@@ -18898,7 +18904,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18918,7 +18924,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -18955,7 +18961,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>195</v>
+        <v>202</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -18963,7 +18969,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -18990,7 +18996,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19008,7 +19014,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19023,7 +19029,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19035,7 +19041,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19051,36 +19057,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19341,38 +19347,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19399,7 +19405,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19429,7 +19435,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19458,17 +19464,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19497,7 +19503,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19604,7 +19610,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19643,7 +19649,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19699,7 +19705,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>54</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19752,7 +19758,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19803,7 +19809,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19811,7 +19817,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19868,7 +19874,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19876,7 +19882,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -19968,7 +19974,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20033,7 +20039,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>105</v>
+        <v>92</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20049,36 +20055,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>108</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>112</v>
+        <v>99</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>113</v>
+        <v>100</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>114</v>
+        <v>101</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>115</v>
+        <v>102</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>116</v>
+        <v>103</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>118</v>
+        <v>105</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20366,37 +20372,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>122</v>
-      </c>
-      <c r="C24" s="9" t="s">
+        <v>123</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="D24" s="10" t="s">
+      <c r="C24" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="E24" s="10" t="s">
+      <c r="D24" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="F24" s="11" t="s">
+      <c r="E24" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>129</v>
-      </c>
-      <c r="H24" s="13" t="s">
+      <c r="F24" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="H24" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="I24" s="14" t="s">
+      <c r="I24" s="15" t="s">
         <v>132</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20413,7 +20419,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20430,7 +20436,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20447,7 +20453,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20464,7 +20470,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>140</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20481,7 +20487,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20510,7 +20516,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1768" uniqueCount="474">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="474">
   <si>
     <t>Player</t>
   </si>
@@ -97,405 +97,405 @@
     <t>FB receive rating (grade divided by attempts)</t>
   </si>
   <si>
+    <t>Shiloh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Agnes</t>
+  </si>
+  <si>
     <t>Cora</t>
   </si>
   <si>
-    <t>Shiloh</t>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - </t>
+  </si>
+  <si>
+    <t>Addy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Gaby</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>Elena</t>
   </si>
   <si>
     <t xml:space="preserve">0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+    <t>Rotation (follow setter starting position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
+  </si>
+  <si>
+    <t>Serve Errors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - </t>
   </si>
   <si>
     <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nataly </t>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - </t>
+  </si>
+  <si>
+    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+    <t>Tea</t>
   </si>
   <si>
     <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>Addy</t>
-  </si>
-  <si>
-    <t>Agnes</t>
+    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
   </si>
   <si>
     <t>Kinley</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+    <t>Service error (us)</t>
+  </si>
+  <si>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+    <t>Service Errors (them)</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
   </si>
   <si>
-    <t>Anna</t>
+    <t>Ace % (them)</t>
+  </si>
+  <si>
+    <t>Service Error % (Them)</t>
   </si>
   <si>
     <t>Audri</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Set 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
   </si>
   <si>
     <t>3 - 3 - 5 - 1 - 3 - 0</t>
   </si>
   <si>
-    <t>Bridget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+    <t>Set 2</t>
   </si>
   <si>
     <t>3 - 0 - 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>Annabelle</t>
-  </si>
-  <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+    <t>Set 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>Set 4</t>
+  </si>
+  <si>
+    <t>Set 5</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
     <t>1 - 1 - 1 - 0 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>Corena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - </t>
+  </si>
+  <si>
+    <t>Team Kill Efficiency (all games)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
   </si>
   <si>
     <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
   </si>
   <si>
     <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - </t>
-  </si>
-  <si>
-    <t>Gaby</t>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+    <t>Piper</t>
   </si>
   <si>
     <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
-  </si>
-  <si>
-    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Kill Efficiency</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
-  </si>
-  <si>
-    <t>Tea</t>
-  </si>
-  <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
-  </si>
-  <si>
-    <t>Serve Receive Avg Score</t>
-  </si>
-  <si>
-    <t>Serve Aces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
-  </si>
-  <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - </t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
-  </si>
-  <si>
-    <t>Service error (us)</t>
-  </si>
-  <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
-  </si>
-  <si>
-    <t>Aces (them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Service Errors (them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>Ace % (them)</t>
-  </si>
-  <si>
-    <t>Service Error % (Them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 1</t>
-  </si>
-  <si>
-    <t>Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - </t>
-  </si>
-  <si>
-    <t>Set 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Set 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
   </si>
   <si>
     <t>Team Passer Rating (all games)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>Team Kill Efficiency (all games)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -640,19 +640,52 @@
     <t>2- 2- 3- 3- 2- 3- 2- 3</t>
   </si>
   <si>
+    <t>0- 0</t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2</t>
+  </si>
+  <si>
+    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
+  </si>
+  <si>
+    <t>2- 3- 2- 2</t>
+  </si>
+  <si>
+    <t>3- 2- 3- 5- 3</t>
+  </si>
+  <si>
+    <t>1- 2- 2- 3- 1- 1- 0</t>
+  </si>
+  <si>
+    <t>1- 3- 0</t>
+  </si>
+  <si>
+    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
+  </si>
+  <si>
+    <t>3- 3- 3- 2</t>
+  </si>
+  <si>
+    <t>2- 0- 3- 2- 1- 3</t>
+  </si>
+  <si>
+    <t>1- 3- 0- 3- 1</t>
+  </si>
+  <si>
     <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
   </si>
   <si>
     <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
   </si>
   <si>
-    <t>0- 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 3- 2- </t>
   </si>
   <si>
-    <t>2- 2- 3- 3- 2</t>
+    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
   </si>
   <si>
     <t>2- 1- 2- 0- 0</t>
@@ -664,61 +697,46 @@
     <t>3- 1- 2- 1</t>
   </si>
   <si>
-    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
-  </si>
-  <si>
     <t>3- 1- 5- 2</t>
   </si>
   <si>
-    <t>2- 3- 2- 2</t>
-  </si>
-  <si>
     <t>3- 0</t>
   </si>
   <si>
     <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
   </si>
   <si>
-    <t>3- 2- 3- 5- 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">0- 2- 3- </t>
   </si>
   <si>
     <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
   </si>
   <si>
-    <t>1- 2- 2- 3- 1- 1- 0</t>
-  </si>
-  <si>
     <t>2- 2- 0</t>
   </si>
   <si>
-    <t>1- 3- 0</t>
+    <t xml:space="preserve">2- 1- 1- </t>
   </si>
   <si>
     <t xml:space="preserve">3- </t>
   </si>
   <si>
-    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
-  </si>
-  <si>
-    <t>3- 3- 3- 2</t>
-  </si>
-  <si>
     <t>1- 3- 0- 1- 0</t>
   </si>
   <si>
     <t>1- 2- 0- 0- 1- 0</t>
   </si>
   <si>
+    <t>1- 0- 3- 2- 0- 1- 1</t>
+  </si>
+  <si>
     <t>2- 3- 1- 2</t>
   </si>
   <si>
-    <t>2- 0- 3- 2- 1- 3</t>
+    <t>0- 1- 3</t>
+  </si>
+  <si>
+    <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
     <t>5- 3- 0- 0</t>
@@ -727,12 +745,30 @@
     <t xml:space="preserve">0- 3- </t>
   </si>
   <si>
+    <t>0- 2</t>
+  </si>
+  <si>
+    <t>0- 1- 1- 0- 1- 2- 1- 0- 0- 0- 2- 1- 0- 3- 2- 1- 3- 2</t>
+  </si>
+  <si>
+    <t>0- 1- 2- 1- 0- 2- 2- 2- 2- 2</t>
+  </si>
+  <si>
+    <t>2- 2- 1- 2</t>
+  </si>
+  <si>
+    <t>2- 1- 1- 3- 1- 1- 3- 2- 1- 3- 2</t>
+  </si>
+  <si>
+    <t>2- 0- 2- 2- 3- 1- 0- 0</t>
+  </si>
+  <si>
+    <t>1- 2- 1- 3- 1- 2- 0- 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 3 - 5 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t>0- 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - 3 - 0 - 1 - 1 - 1 - 1 - 3 - 3 - 3 - 0 - 2 - </t>
   </si>
   <si>
@@ -742,18 +778,12 @@
     <t xml:space="preserve">3 - 3 - 5 - 2 - 3 - 3 - 3 - 1 - 2 - 0 - 2 - 3 - 0 - </t>
   </si>
   <si>
-    <t>1- 3- 0- 3- 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 3 - 2 - 3 - 1 - 2 - 0 - 2 - 3 - 3 - 3 - 1 - 2 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 5 - 5 - 0 - 5 - 2 - 5 - 5 - 5 - 0 - 2 - 3 - 5 - 3 - </t>
   </si>
   <si>
@@ -769,30 +799,15 @@
     <t xml:space="preserve">0 - 0 - 1 - 2 - 2 - 0 - 0 - 3 - </t>
   </si>
   <si>
-    <t>0- 1- 1- 0- 1- 2- 1- 0- 0- 0- 2- 1- 0- 3- 2- 1- 3- 2</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 5 - 1 - 5 -  0 - 3 - 5 - 0 - 5 - 0 - 0 - 0 - 3 - 5 - 3 - 0 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 3 - 3 - 0 - 3 - 2 - 2 - 0 - 1 - 2 - 3 - 1 - </t>
   </si>
   <si>
-    <t>0- 1- 2- 1- 0- 2- 2- 2- 2- 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1- 1- </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 1 - 3 - 1 - 5 - 0 - 3 - 3 - </t>
   </si>
   <si>
-    <t>2- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>1- 0- 3- 2- 0- 1- 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 2 - </t>
   </si>
   <si>
@@ -802,24 +817,9 @@
     <t xml:space="preserve">0 - 3 - 3 - 5 - 3 - 3 - 0 - 3 - 2 - 3 - 1 - 3 - 3 - 1 - 1 - 1 - 5 - 3 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
-    <t>0- 1- 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 3 - 1 - </t>
   </si>
   <si>
-    <t>2- 1- 1- 3- 1- 1- 3- 2- 1- 3- 2</t>
-  </si>
-  <si>
-    <t>2- 1- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>2- 0- 2- 2- 3- 1- 0- 0</t>
-  </si>
-  <si>
-    <t>1- 2- 1- 3- 1- 2- 0- 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - 2 - 3 - 1 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 0 - 2 - 3 - </t>
   </si>
   <si>
@@ -964,28 +964,133 @@
     <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 2- 2- 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
+    <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
@@ -997,36 +1102,24 @@
     <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
+    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 2- 2- 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
   </si>
   <si>
@@ -1036,78 +1129,27 @@
     <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
@@ -1117,54 +1159,12 @@
     <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
     <t>119 attack attempts</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
   </si>
   <si>
@@ -1255,6 +1255,39 @@
     <t xml:space="preserve">0 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - 1 - 3 - 3 - 5 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
   </si>
   <si>
@@ -1291,45 +1324,12 @@
     <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - 1 - 3 - 3 - 5 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1372,22 +1372,22 @@
     <t xml:space="preserve">3 - 3 - 2 - 3 - 2 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 3 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 1 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - 0 - 3 - 2 - 3 - 0 - 0 - 3 - 1 - 0 - 3 - 2 - 2 - 3 - 3 - 2 - 2 - 3 - 0 - 3 - 1 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 3 - 1 - 1 - 3 - 5 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 2 - 0 - 3 - 2 - 2 - 2 - 0 - 1 - 0 - 3 - 3 - 3 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 5 - 3 - 0 - 0 - 5 - 5 - 1 - 3 - 5 - 3 - 2 - 3 - 0 - 2 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 1 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 0 - 0 - 3 - 2 - 3 - 0 - 0 - 3 - 1 - 0 - 3 - 2 - 2 - 3 - 3 - 2 - 2 - 3 - 0 - 3 - 1 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 3 - 1 - 1 - 3 - 5 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 2 - 0 - 3 - 2 - 2 - 2 - 0 - 1 - 0 - 3 - 3 - 3 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 3 - 1 - 5 - 5 - 2 - 0 - </t>
@@ -1546,6 +1546,7 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1567,7 +1568,6 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1979,7 +1979,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -2003,7 +2003,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2015,7 +2015,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2024,7 +2024,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2051,7 +2051,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>29</v>
+        <v>98</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2063,7 +2063,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>31</v>
+        <v>100</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2072,7 +2072,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2090,7 +2090,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>35</v>
+        <v>105</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2105,7 +2105,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2126,7 +2126,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2135,7 +2135,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>41</v>
+        <v>115</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2144,7 +2144,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>118</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2168,7 +2168,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2177,7 +2177,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>51</v>
+        <v>125</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2186,7 +2186,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2198,7 +2198,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>55</v>
+        <v>130</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2210,7 +2210,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>56</v>
+        <v>133</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2219,7 +2219,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2232,7 +2232,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2259,7 +2259,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2274,7 +2274,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>65</v>
+        <v>141</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2283,7 +2283,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2310,7 +2310,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2319,7 +2319,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>72</v>
+        <v>146</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2328,7 +2328,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2349,7 +2349,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2367,7 +2367,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2388,7 +2388,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2406,40 +2406,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2479,37 +2479,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2538,7 +2538,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2564,7 +2564,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2593,7 +2593,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2622,12 +2622,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2656,10 +2656,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
@@ -2768,7 +2768,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2810,7 +2810,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2854,7 +2854,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2894,7 +2894,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2902,7 +2902,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2950,7 +2950,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2958,7 +2958,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -3014,7 +3014,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3">
         <v>8.0</v>
@@ -3059,7 +3059,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3112,7 +3112,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3124,7 +3124,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3137,7 +3137,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3146,7 +3146,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3171,7 +3171,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3187,36 +3187,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3486,37 +3486,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3530,7 +3530,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3547,7 +3547,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3564,17 +3564,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3603,7 +3603,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3710,7 +3710,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
         <v>17.0</v>
@@ -3755,7 +3755,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3763,7 +3763,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3805,7 +3805,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3881,7 +3881,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3937,7 +3937,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3960,7 +3960,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3968,7 +3968,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -4001,7 +4001,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4010,7 +4010,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4018,7 +4018,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4048,7 +4048,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4076,7 +4076,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4084,7 +4084,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4099,7 +4099,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4109,7 +4109,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4127,7 +4127,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4136,7 +4136,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4166,7 +4166,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4184,7 +4184,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4196,7 +4196,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4229,7 +4229,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4241,7 +4241,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4260,7 +4260,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4276,36 +4276,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4587,37 +4587,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="12" t="s">
+      <c r="C25" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="14" t="s">
+      <c r="F25" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="H25" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4634,7 +4634,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4651,7 +4651,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4668,17 +4668,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4707,7 +4707,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4814,7 +4814,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -4851,7 +4851,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="U2" s="3">
         <v>2.33</v>
@@ -4859,7 +4859,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4886,7 +4886,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4898,7 +4898,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4907,7 +4907,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>317</v>
+        <v>312</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4915,7 +4915,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4942,7 +4942,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4954,7 +4954,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4963,7 +4963,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>330</v>
+        <v>315</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4971,7 +4971,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -4998,7 +4998,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>335</v>
+        <v>316</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5010,7 +5010,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>338</v>
+        <v>317</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5019,7 +5019,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>340</v>
+        <v>318</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5027,7 +5027,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5039,7 +5039,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>343</v>
+        <v>319</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5051,7 +5051,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>346</v>
+        <v>320</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5060,7 +5060,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5075,7 +5075,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>348</v>
+        <v>322</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5084,7 +5084,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5108,7 +5108,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>350</v>
+        <v>325</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5120,7 +5120,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>352</v>
+        <v>326</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5128,7 +5128,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5156,7 +5156,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5183,7 +5183,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5224,36 +5224,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5286,7 +5286,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>364</v>
+        <v>334</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5333,7 +5333,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>367</v>
+        <v>337</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5380,7 +5380,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>369</v>
+        <v>338</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5424,7 +5424,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5468,7 +5468,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>373</v>
+        <v>343</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5512,7 +5512,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>345</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5535,37 +5535,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5594,7 +5594,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5611,7 +5611,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5628,7 +5628,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5645,12 +5645,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5685,7 +5685,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5792,7 +5792,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5819,7 +5819,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5831,7 +5831,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5840,7 +5840,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5848,7 +5848,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5878,7 +5878,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5890,7 +5890,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5899,7 +5899,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5907,7 +5907,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5937,7 +5937,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5952,7 +5952,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>336</v>
+        <v>331</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5961,7 +5961,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5969,7 +5969,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -5992,7 +5992,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -6000,7 +6000,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6022,7 +6022,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6031,7 +6031,7 @@
         <v>4.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -6039,7 +6039,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6059,7 +6059,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>349</v>
+        <v>335</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6073,7 +6073,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6082,7 +6082,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6101,7 +6101,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6116,7 +6116,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>354</v>
+        <v>339</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6125,7 +6125,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6134,7 +6134,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6142,7 +6142,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3">
         <v>28.0</v>
@@ -6168,7 +6168,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6195,7 +6195,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>361</v>
+        <v>344</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -6208,7 +6208,7 @@
         <v>7.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>362</v>
+        <v>346</v>
       </c>
       <c r="U10" s="3">
         <v>2.14</v>
@@ -6216,7 +6216,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6244,7 +6244,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6260,36 +6260,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6322,7 +6322,7 @@
         <v>6.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>366</v>
+        <v>347</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -6369,7 +6369,7 @@
         <v>14.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>368</v>
+        <v>348</v>
       </c>
       <c r="M17" s="3">
         <v>1.79</v>
@@ -6416,7 +6416,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>370</v>
+        <v>350</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6463,7 +6463,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>372</v>
+        <v>352</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6510,7 +6510,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>374</v>
+        <v>356</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6557,7 +6557,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>376</v>
+        <v>359</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6580,37 +6580,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6627,7 +6627,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6644,7 +6644,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6661,7 +6661,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6678,7 +6678,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6695,7 +6695,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6724,7 +6724,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6831,7 +6831,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6849,7 +6849,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>311</v>
+        <v>349</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6862,7 +6862,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6892,7 +6892,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>316</v>
+        <v>351</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6904,7 +6904,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>318</v>
+        <v>353</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6913,7 +6913,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>319</v>
+        <v>354</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6921,7 +6921,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6933,7 +6933,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>320</v>
+        <v>355</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6942,7 +6942,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>321</v>
+        <v>357</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6951,7 +6951,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>322</v>
+        <v>358</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6959,7 +6959,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -6983,7 +6983,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>326</v>
+        <v>360</v>
       </c>
       <c r="L5" s="3">
         <v>2.75</v>
@@ -6995,7 +6995,7 @@
         <v>16.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>329</v>
+        <v>361</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -7004,7 +7004,7 @@
         <v>13.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>331</v>
+        <v>362</v>
       </c>
       <c r="U5" s="3">
         <v>2.15</v>
@@ -7012,7 +7012,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7042,7 +7042,7 @@
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>332</v>
+        <v>363</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -7057,7 +7057,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>333</v>
+        <v>364</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -7066,7 +7066,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7074,7 +7074,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7096,7 +7096,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7105,7 +7105,7 @@
         <v>7.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>337</v>
+        <v>365</v>
       </c>
       <c r="U7" s="3">
         <v>1.86</v>
@@ -7113,7 +7113,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7137,7 +7137,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>341</v>
+        <v>366</v>
       </c>
       <c r="L8" s="3">
         <v>1.67</v>
@@ -7157,7 +7157,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7181,7 +7181,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>342</v>
+        <v>367</v>
       </c>
       <c r="L9" s="3">
         <v>2.56</v>
@@ -7190,7 +7190,7 @@
         <v>12.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>345</v>
+        <v>368</v>
       </c>
       <c r="R9" s="3">
         <v>1.67</v>
@@ -7207,7 +7207,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
         <v>14.0</v>
@@ -7234,7 +7234,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7258,7 +7258,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>347</v>
+        <v>369</v>
       </c>
       <c r="L11" s="3">
         <v>2.45</v>
@@ -7267,7 +7267,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7282,7 +7282,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7302,7 +7302,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7318,36 +7318,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7380,7 +7380,7 @@
         <v>12.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -7424,7 +7424,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="M17" s="3">
         <v>2.55</v>
@@ -7471,7 +7471,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>358</v>
+        <v>372</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7518,7 +7518,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>359</v>
+        <v>373</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7565,7 +7565,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>360</v>
+        <v>374</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7609,7 +7609,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7632,37 +7632,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7679,7 +7679,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7696,7 +7696,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7713,7 +7713,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7730,12 +7730,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7764,7 +7764,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7773,7 +7773,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -7874,7 +7874,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7962,7 +7962,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -8018,7 +8018,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8068,7 +8068,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8091,7 +8091,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8099,7 +8099,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8137,7 +8137,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8170,7 +8170,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -8244,7 +8244,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8268,7 +8268,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8322,37 +8322,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="C16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="14" t="s">
+      <c r="F16" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="H16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8369,7 +8369,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8386,7 +8386,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8403,7 +8403,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8420,7 +8420,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8437,7 +8437,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8466,7 +8466,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8573,7 +8573,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8626,7 +8626,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8659,7 +8659,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8667,7 +8667,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8706,7 +8706,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8723,7 +8723,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D5" s="3">
         <v>10.0</v>
@@ -8743,7 +8743,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8783,7 +8783,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8791,7 +8791,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8839,7 +8839,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8847,7 +8847,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8868,7 +8868,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8888,14 +8888,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8912,7 +8912,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8924,7 +8924,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8939,37 +8939,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="C16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="14" t="s">
+      <c r="F16" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="H16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8986,7 +8986,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9003,7 +9003,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9020,17 +9020,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9059,7 +9059,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9221,7 +9221,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9237,36 +9237,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9312,62 +9312,62 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -9376,7 +9376,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9477,7 +9477,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -9498,7 +9498,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>419</v>
+        <v>407</v>
       </c>
       <c r="M2" s="4">
         <v>2.0</v>
@@ -9507,13 +9507,13 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>420</v>
+        <v>408</v>
       </c>
       <c r="T2" s="4"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -9525,24 +9525,24 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="P3" s="3">
         <v>15.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="S3" s="3">
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -9554,13 +9554,13 @@
         <v>2.0</v>
       </c>
       <c r="F4" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H4" s="3">
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>426</v>
+        <v>412</v>
       </c>
       <c r="M4" s="3">
         <v>1.0</v>
@@ -9569,18 +9569,18 @@
         <v>9.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>427</v>
+        <v>413</v>
       </c>
       <c r="S4" s="3">
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3">
         <v>7.0</v>
@@ -9598,7 +9598,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="M5" s="3">
         <v>3.0</v>
@@ -9613,7 +9613,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -9637,14 +9637,14 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="Q6" s="4"/>
       <c r="T6" s="4"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -9671,7 +9671,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="M7" s="3">
         <v>3.0</v>
@@ -9680,18 +9680,18 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>344</v>
+        <v>333</v>
       </c>
       <c r="S7" s="3">
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -9704,7 +9704,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -9721,7 +9721,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -9731,6 +9731,15 @@
       <c r="T10" s="5"/>
     </row>
     <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="P11" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>58</v>
+      </c>
       <c r="T11" s="5"/>
     </row>
     <row r="12">
@@ -9744,37 +9753,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="C16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="14" t="s">
+      <c r="F16" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="H16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9791,7 +9800,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3">
         <v>3.0</v>
@@ -9800,7 +9809,7 @@
         <v>2.0</v>
       </c>
       <c r="F18" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="G18" s="3">
         <v>3.0</v>
@@ -9808,22 +9817,22 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
@@ -9832,7 +9841,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9934,7 +9943,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -9964,7 +9973,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="L2" s="3">
         <v>2.69</v>
@@ -9976,7 +9985,7 @@
         <v>22.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="R2" s="3">
         <v>1.45</v>
@@ -9985,7 +9994,7 @@
         <v>4.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -9993,7 +10002,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10017,7 +10026,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>410</v>
+        <v>421</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -10036,7 +10045,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -10054,7 +10063,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10067,7 +10076,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10075,7 +10084,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10105,7 +10114,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>411</v>
+        <v>422</v>
       </c>
       <c r="L5" s="3">
         <v>2.63</v>
@@ -10117,7 +10126,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>412</v>
+        <v>423</v>
       </c>
       <c r="R5" s="3">
         <v>1.71</v>
@@ -10126,7 +10135,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>413</v>
+        <v>424</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -10134,7 +10143,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10155,7 +10164,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>414</v>
+        <v>425</v>
       </c>
       <c r="L6" s="3">
         <v>2.65</v>
@@ -10167,7 +10176,7 @@
         <v>20.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>415</v>
+        <v>426</v>
       </c>
       <c r="R6" s="3">
         <v>1.0</v>
@@ -10176,7 +10185,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10184,7 +10193,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D7" s="3">
         <v>14.0</v>
@@ -10209,7 +10218,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10239,7 +10248,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>416</v>
+        <v>427</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -10251,7 +10260,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>417</v>
+        <v>428</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -10260,7 +10269,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>418</v>
+        <v>429</v>
       </c>
       <c r="U8" s="3">
         <v>1.83</v>
@@ -10268,7 +10277,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10280,7 +10289,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -10290,7 +10299,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10308,7 +10317,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10333,37 +10342,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E16" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B16" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F16" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G16" s="12" t="s">
+      <c r="C16" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H16" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="14" t="s">
+      <c r="F16" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G16" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K16" s="15"/>
+      <c r="H16" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10380,7 +10389,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10397,7 +10406,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10414,7 +10423,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10431,12 +10440,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10465,7 +10474,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10572,7 +10581,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10596,7 +10605,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10608,7 +10617,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10617,7 +10626,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10625,7 +10634,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10643,7 +10652,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10656,7 +10665,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10664,7 +10673,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10691,7 +10700,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10703,7 +10712,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>38</v>
+        <v>31</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10712,7 +10721,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10720,7 +10729,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10732,7 +10741,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10741,7 +10750,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10750,7 +10759,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10758,7 +10767,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10782,7 +10791,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10794,7 +10803,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10803,7 +10812,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10811,7 +10820,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10838,7 +10847,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10850,7 +10859,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>15.0</v>
@@ -10875,7 +10884,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10884,7 +10893,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10902,7 +10911,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>71</v>
+        <v>50</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10915,7 +10924,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10923,7 +10932,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10937,7 +10946,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10952,7 +10961,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -10961,13 +10970,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -10982,7 +10991,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -10998,40 +11007,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11064,7 +11073,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>102</v>
+        <v>80</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11081,7 +11090,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="16">
+      <c r="R16" s="9">
         <f>10</f>
         <v>10</v>
       </c>
@@ -11112,7 +11121,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>122</v>
+        <v>91</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11159,7 +11168,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>127</v>
+        <v>95</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11206,7 +11215,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>131</v>
+        <v>97</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11253,7 +11262,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>135</v>
+        <v>102</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11297,7 +11306,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>138</v>
+        <v>104</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11317,37 +11326,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11364,7 +11373,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11381,7 +11390,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11398,7 +11407,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11415,7 +11424,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11432,7 +11441,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11461,7 +11470,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11568,7 +11577,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11621,7 +11630,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11680,7 +11689,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11728,7 +11737,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11787,7 +11796,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11837,7 +11846,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11868,7 +11877,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11876,7 +11885,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11900,7 +11909,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c r="L8" s="3">
         <v>2.76</v>
@@ -11912,7 +11921,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11921,7 +11930,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3">
         <v>1.0</v>
@@ -11950,7 +11959,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -11964,7 +11973,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -11981,7 +11990,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -11993,7 +12002,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12007,37 +12016,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="C17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="14" t="s">
+      <c r="F17" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="H17" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12054,7 +12063,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12071,7 +12080,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12088,7 +12097,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12105,7 +12114,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12122,7 +12131,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12151,7 +12160,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12258,7 +12267,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12270,7 +12279,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="L2" s="3">
         <v>2.4</v>
@@ -12282,7 +12291,7 @@
         <v>26.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R2" s="3">
         <v>1.73</v>
@@ -12291,7 +12300,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12299,7 +12308,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12323,7 +12332,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -12335,7 +12344,7 @@
         <v>19.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R3" s="3">
         <v>1.59</v>
@@ -12344,7 +12353,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="U3" s="3">
         <v>2.8</v>
@@ -12352,7 +12361,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12391,7 +12400,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12400,7 +12409,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12408,7 +12417,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12467,7 +12476,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12489,7 +12498,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12525,7 +12534,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12534,7 +12543,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12556,7 +12565,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12579,13 +12588,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12594,7 +12603,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12603,7 +12612,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12624,7 +12633,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12645,7 +12654,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -12663,7 +12672,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12678,7 +12687,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12690,7 +12699,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12726,37 +12735,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="C17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="14" t="s">
+      <c r="F17" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="H17" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12773,7 +12782,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12784,7 +12793,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12801,17 +12810,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12840,7 +12849,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12947,7 +12956,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -12986,7 +12995,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13006,7 +13015,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13056,7 +13065,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13115,7 +13124,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13171,7 +13180,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13193,7 +13202,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13201,7 +13210,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13234,7 +13243,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13242,7 +13251,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3">
         <v>18.0</v>
@@ -13271,7 +13280,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13294,7 +13303,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13302,7 +13311,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13326,7 +13335,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13344,7 +13353,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13405,37 +13414,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E17" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B17" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G17" s="12" t="s">
+      <c r="C17" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H17" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="14" t="s">
+      <c r="F17" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K17" s="15"/>
+      <c r="H17" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13452,7 +13461,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13469,7 +13478,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13483,7 +13492,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13500,7 +13509,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13514,7 +13523,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13543,7 +13552,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13650,7 +13659,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D2" s="3">
         <v>3.0</v>
@@ -13678,7 +13687,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13693,7 +13702,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13705,7 +13714,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>88</v>
+        <v>42</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13714,7 +13723,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13738,7 +13747,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>99</v>
+        <v>46</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13751,7 +13760,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>100</v>
+        <v>49</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13759,7 +13768,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13786,7 +13795,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>110</v>
+        <v>53</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13798,7 +13807,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>112</v>
+        <v>56</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13807,7 +13816,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13834,7 +13843,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>118</v>
+        <v>60</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13846,7 +13855,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>121</v>
+        <v>62</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13855,7 +13864,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>124</v>
+        <v>64</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13863,7 +13872,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13887,7 +13896,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13899,7 +13908,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13908,7 +13917,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>134</v>
+        <v>79</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13916,7 +13925,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13934,7 +13943,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13946,7 +13955,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>137</v>
+        <v>84</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -13955,7 +13964,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>139</v>
+        <v>85</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -13963,7 +13972,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -13977,7 +13986,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -13986,7 +13995,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -13998,7 +14007,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>140</v>
+        <v>89</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14007,7 +14016,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14015,7 +14024,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14024,7 +14033,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>142</v>
+        <v>92</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14036,7 +14045,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14057,7 +14066,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14073,40 +14082,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>87</v>
+        <v>65</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14139,7 +14148,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>147</v>
+        <v>120</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14181,7 +14190,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>149</v>
+        <v>127</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14228,7 +14237,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14275,7 +14284,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14319,7 +14328,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14357,7 +14366,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>153</v>
+        <v>143</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14380,37 +14389,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14427,7 +14436,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14444,7 +14453,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14461,17 +14470,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14500,7 +14509,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14607,7 +14616,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14634,7 +14643,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14646,7 +14655,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>50</v>
+        <v>72</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14655,7 +14664,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14663,7 +14672,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14690,7 +14699,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>58</v>
+        <v>81</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14705,7 +14714,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14714,7 +14723,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14735,7 +14744,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14747,7 +14756,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>66</v>
+        <v>87</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14756,7 +14765,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14764,7 +14773,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14774,7 +14783,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14787,7 +14796,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14814,7 +14823,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14826,7 +14835,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14835,7 +14844,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14843,7 +14852,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14870,7 +14879,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14882,7 +14891,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14891,7 +14900,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14899,7 +14908,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>13.0</v>
@@ -14927,7 +14936,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14936,7 +14945,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14948,7 +14957,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>106</v>
+        <v>119</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -14957,7 +14966,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>109</v>
+        <v>122</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -14966,7 +14975,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -14974,7 +14983,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -14989,7 +14998,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -14998,7 +15007,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15007,7 +15016,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15028,7 +15037,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15041,7 +15050,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15049,7 +15058,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15064,7 +15073,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15073,7 +15082,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15082,7 +15091,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15090,7 +15099,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15102,7 +15111,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15120,7 +15129,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15138,7 +15147,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15154,36 +15163,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15216,7 +15225,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15263,7 +15272,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15304,7 +15313,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15351,7 +15360,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15392,7 +15401,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15439,7 +15448,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15459,37 +15468,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="12" t="s">
+      <c r="C25" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="14" t="s">
+      <c r="F25" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="H25" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15506,7 +15515,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15523,7 +15532,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15540,7 +15549,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15557,12 +15566,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15591,7 +15600,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15698,7 +15707,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15746,7 +15755,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15795,7 +15804,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15863,7 +15872,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15919,7 +15928,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15938,7 +15947,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -15977,7 +15986,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>22.0</v>
@@ -16006,7 +16015,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16042,7 +16051,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16050,7 +16059,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16074,7 +16083,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16092,7 +16101,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16101,7 +16110,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16116,7 +16125,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16132,36 +16141,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16446,37 +16455,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E23" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B23" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F23" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G23" s="12" t="s">
+      <c r="C23" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H23" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" s="14" t="s">
+      <c r="F23" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G23" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K23" s="15"/>
+      <c r="H23" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K23" s="16"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16493,7 +16502,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16510,7 +16519,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16527,7 +16536,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16544,7 +16553,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16552,7 +16561,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16581,7 +16590,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16688,7 +16697,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16741,7 +16750,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16752,7 +16761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16808,7 +16817,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16820,7 +16829,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16838,7 +16847,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16846,7 +16855,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16900,7 +16909,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16908,7 +16917,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16946,7 +16955,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -16996,7 +17005,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C9" s="3">
         <v>1.0</v>
@@ -17021,7 +17030,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17030,7 +17039,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17054,7 +17063,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17063,7 +17072,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17084,7 +17093,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17096,7 +17105,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>58</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17105,7 +17114,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17147,7 +17156,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>67</v>
+        <v>47</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17155,7 +17164,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17170,7 +17179,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>78</v>
+        <v>145</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17182,7 +17191,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
@@ -17198,7 +17207,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17214,36 +17223,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17528,37 +17537,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E25" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B25" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F25" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G25" s="12" t="s">
+      <c r="C25" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E25" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H25" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="14" t="s">
+      <c r="F25" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G25" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K25" s="15"/>
+      <c r="H25" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17575,7 +17584,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17592,7 +17601,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17609,7 +17618,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17620,12 +17629,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17654,7 +17663,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17761,7 +17770,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17814,7 +17823,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17835,7 +17844,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17845,7 +17854,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17853,7 +17862,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17880,7 +17889,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17889,7 +17898,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17898,7 +17907,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17906,7 +17915,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17930,7 +17939,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -17954,7 +17963,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -17972,7 +17981,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -17993,7 +18002,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -18001,7 +18010,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18017,7 +18026,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -18026,7 +18035,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -18034,7 +18043,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -18053,7 +18062,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18065,7 +18074,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>228</v>
+        <v>212</v>
       </c>
       <c r="L9" s="3">
         <v>1.833</v>
@@ -18075,7 +18084,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18106,7 +18115,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18122,36 +18131,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18181,7 +18190,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18225,7 +18234,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>239</v>
+        <v>217</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18239,7 +18248,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="16">
+      <c r="R17" s="9">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18267,7 +18276,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>249</v>
+        <v>227</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18308,7 +18317,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>252</v>
+        <v>231</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18343,7 +18352,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18390,7 +18399,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18410,37 +18419,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18469,7 +18478,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18498,22 +18507,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18542,7 +18551,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18649,7 +18658,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18679,7 +18688,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>202</v>
+        <v>214</v>
       </c>
       <c r="L2" s="3">
         <v>2.364</v>
@@ -18691,7 +18700,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18700,7 +18709,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>205</v>
+        <v>216</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18708,7 +18717,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18732,7 +18741,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>207</v>
+        <v>218</v>
       </c>
       <c r="L3" s="3">
         <v>2.5</v>
@@ -18747,7 +18756,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18756,7 +18765,7 @@
         <v>4.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>209</v>
+        <v>220</v>
       </c>
       <c r="U3" s="3">
         <v>1.75</v>
@@ -18764,7 +18773,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18788,7 +18797,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="L4" s="3">
         <v>2.75</v>
@@ -18798,7 +18807,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18810,7 +18819,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -18822,7 +18831,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="R5" s="3">
         <v>1.176</v>
@@ -18831,7 +18840,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="U5" s="3">
         <v>1.667</v>
@@ -18839,7 +18848,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18863,7 +18872,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="L6" s="3">
         <v>3.375</v>
@@ -18875,7 +18884,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="R6" s="3">
         <v>1.667</v>
@@ -18884,7 +18893,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -18892,7 +18901,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -18910,7 +18919,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="L7" s="3">
         <v>2.5</v>
@@ -18922,7 +18931,7 @@
         <v>8.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -18931,7 +18940,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -18939,7 +18948,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -18955,7 +18964,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18975,7 +18984,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -18999,7 +19008,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -19012,7 +19021,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19020,7 +19029,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19038,7 +19047,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -19047,7 +19056,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19056,7 +19065,7 @@
         <v>2.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -19065,7 +19074,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>75</v>
+        <v>142</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19080,7 +19089,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19092,7 +19101,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19108,36 +19117,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19164,7 +19173,7 @@
         <v>19.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="M16" s="3">
         <v>1.053</v>
@@ -19211,7 +19220,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="M17" s="3">
         <v>1.4</v>
@@ -19252,7 +19261,7 @@
         <v>4.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="M18" s="3">
         <v>1.75</v>
@@ -19299,7 +19308,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>258</v>
+        <v>241</v>
       </c>
       <c r="M19" s="3">
         <v>1.818</v>
@@ -19340,7 +19349,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>260</v>
+        <v>242</v>
       </c>
       <c r="M20" s="3">
         <v>1.25</v>
@@ -19378,7 +19387,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="M21" s="3">
         <v>1.375</v>
@@ -19398,38 +19407,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19456,7 +19465,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19486,7 +19495,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19515,17 +19524,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19554,7 +19563,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19661,7 +19670,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19673,7 +19682,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>231</v>
+        <v>244</v>
       </c>
       <c r="L2" s="3">
         <v>3.14</v>
@@ -19683,7 +19692,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>233</v>
+        <v>245</v>
       </c>
       <c r="R2" s="3">
         <v>1.3</v>
@@ -19692,7 +19701,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>234</v>
+        <v>246</v>
       </c>
       <c r="U2" s="3">
         <v>1.86</v>
@@ -19700,7 +19709,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19727,7 +19736,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="L3" s="3">
         <v>2.31</v>
@@ -19739,7 +19748,7 @@
         <v>27.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="R3" s="3">
         <v>2.19</v>
@@ -19748,7 +19757,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>238</v>
+        <v>249</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -19756,7 +19765,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19780,7 +19789,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="L4" s="3">
         <v>3.33</v>
@@ -19792,7 +19801,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
       <c r="R4" s="3">
         <v>0.86</v>
@@ -19801,7 +19810,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="U4" s="3">
         <v>2.4</v>
@@ -19809,7 +19818,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19839,7 +19848,7 @@
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="L5" s="3">
         <v>1.76</v>
@@ -19851,7 +19860,7 @@
         <v>8.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -19860,7 +19869,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>73</v>
+        <v>51</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19868,7 +19877,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19898,7 +19907,7 @@
         <v>7.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="L6" s="3">
         <v>2.43</v>
@@ -19916,7 +19925,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="R6" s="3">
         <v>1.69</v>
@@ -19925,7 +19934,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>77</v>
+        <v>55</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19933,7 +19942,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -19966,7 +19975,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="D8" s="3">
         <v>16.0</v>
@@ -19990,7 +19999,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="L8" s="3">
         <v>2.44</v>
@@ -20008,7 +20017,7 @@
         <v>3.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="R8" s="3">
         <v>2.33</v>
@@ -20017,7 +20026,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="U8" s="3">
         <v>1.0</v>
@@ -20025,7 +20034,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20052,7 +20061,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L9" s="3">
         <v>2.18</v>
@@ -20065,7 +20074,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -20090,7 +20099,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>79</v>
+        <v>59</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20106,36 +20115,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>82</v>
+        <v>61</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>84</v>
+        <v>63</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>90</v>
+        <v>68</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>91</v>
+        <v>69</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>98</v>
+        <v>77</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20423,37 +20432,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>105</v>
-      </c>
-      <c r="E24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="B24" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="11" t="s">
-        <v>108</v>
-      </c>
-      <c r="G24" s="12" t="s">
+      <c r="C24" s="10" t="s">
+        <v>109</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="E24" s="11" t="s">
         <v>111</v>
       </c>
-      <c r="H24" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="14" t="s">
+      <c r="F24" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="G24" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="K24" s="15"/>
+      <c r="H24" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20470,7 +20479,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20487,7 +20496,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20504,7 +20513,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20521,7 +20530,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20538,7 +20547,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20567,7 +20576,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="475">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="476">
   <si>
     <t>Player</t>
   </si>
@@ -100,94 +100,307 @@
     <t>Cora</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - </t>
+  </si>
+  <si>
+    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+  </si>
+  <si>
     <t>Shiloh</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - </t>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+  </si>
+  <si>
+    <t>Addy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Kinley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t>Audri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t>3 - 0 - 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t>1 - 1 - 1 - 0 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
-    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+  </si>
+  <si>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - </t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - </t>
+  </si>
+  <si>
+    <t>Piper</t>
+  </si>
+  <si>
+    <t>Gaby</t>
+  </si>
+  <si>
+    <t>Rotation (follow setter starting position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+  </si>
+  <si>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Serve Errors</t>
+  </si>
+  <si>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - </t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
+  </si>
+  <si>
+    <t>Service error (us)</t>
+  </si>
+  <si>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
+    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nataly </t>
+    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Service Errors (them)</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t>Ace % (them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
   </si>
   <si>
     <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - </t>
   </si>
   <si>
-    <t>Annabelle</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
+    <t>Service Error % (Them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
-    <t>Addy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Agnes</t>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t>Set 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+    <t>Set 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>Set 3</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t>Kinley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
@@ -196,306 +409,93 @@
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>Audri</t>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Set 4</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+    <t>Set 5</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+    <t>Total</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - </t>
-  </si>
-  <si>
-    <t>3 - 0 - 1</t>
-  </si>
-  <si>
-    <t>Bridget</t>
-  </si>
-  <si>
-    <t>Gaby</t>
-  </si>
-  <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+    <t xml:space="preserve">0 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+    <t>Team Passer Rating (all games)</t>
+  </si>
+  <si>
+    <t>Team Kill Efficiency (all games)</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
   </si>
   <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - </t>
   </si>
   <si>
-    <t>Corena</t>
-  </si>
-  <si>
-    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+    <t xml:space="preserve">3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 1 - </t>
   </si>
   <si>
-    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
-  </si>
-  <si>
-    <t>Tea</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
-    <t>Kill Efficiency</t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
-  </si>
-  <si>
-    <t>Serve Receive Avg Score</t>
-  </si>
-  <si>
-    <t>Serve Aces</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
-  </si>
-  <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - </t>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
-  </si>
-  <si>
-    <t>Service error (us)</t>
-  </si>
-  <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
-  </si>
-  <si>
-    <t>Aces (them)</t>
-  </si>
-  <si>
-    <t>Service Errors (them)</t>
-  </si>
-  <si>
-    <t>Ace % (them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Service Error % (Them)</t>
-  </si>
-  <si>
-    <t>Set 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Set 2</t>
-  </si>
-  <si>
-    <t>Set 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Set 5</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Team Kill Efficiency (all games)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Team Passer Rating (all games)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -541,6 +541,24 @@
     <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
@@ -550,6 +568,69 @@
     <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
   </si>
   <si>
@@ -559,138 +640,57 @@
     <t>2- 2- 3- 3- 2- 3- 2- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
     <t>0- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
     <t>2- 2- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
     <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
   </si>
   <si>
     <t>2- 3- 2- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>3- 2- 3- 5- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
     <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - </t>
-  </si>
-  <si>
     <t>1- 3- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
     <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>3- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - </t>
-  </si>
-  <si>
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
     <t>1- 3- 0- 3- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
   </si>
   <si>
     <t xml:space="preserve">2- 1- 1- </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
     <t>1- 0- 3- 2- 0- 1- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t>0- 1- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
   </si>
   <si>
@@ -850,45 +850,72 @@
     <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 5 - 2 - 3 - 5 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 1 - 2 - 3 - 1 - 2 - 1 - 2 - 1 - 1 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 1 - 3 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 2 - 1 - 2 - 2 - 2 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 1 - 0 - 1 - 0 - 0 - 2 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 0 - 1 - 0 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 2 - 2 - 2 - 2 - 3 - 2 - 2 - 0 - 3 - 3 - 2 - 5 - 2 - 5 - 5 - 3 - 3 - 5 - 3 - 3 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 5 - 2 - 3 - 5 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 2 - 1 - 2 - 3 - 1 - 2 - 1 - 2 - 1 - 1 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 0 - 0 - 2 - 2 - 5 - 2 - </t>
   </si>
   <si>
@@ -898,15 +925,6 @@
     <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 1 - 1 - 3 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>5 - 2 - 3 - 0 -</t>
   </si>
   <si>
@@ -922,30 +940,12 @@
     <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 2 - 1 - 2 - 2 - 2 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 1 - 0 - 1 - 0 - 0 - 2 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 0 - 0 - 1 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
@@ -982,33 +982,69 @@
     <t xml:space="preserve">2- 2- 2- 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
@@ -1018,57 +1054,21 @@
     <t xml:space="preserve">1- 1 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
@@ -1081,39 +1081,39 @@
     <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
   </si>
   <si>
@@ -1150,27 +1150,30 @@
     <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>119 attack attempts</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1201,9 +1204,6 @@
     <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
   </si>
   <si>
-    <t>119 attack attempts</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
   </si>
   <si>
@@ -1255,10 +1255,10 @@
     <t xml:space="preserve">0 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - </t>
+    <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 1 - 3 - </t>
@@ -1273,10 +1273,10 @@
     <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - 5 - 5 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - </t>
+    <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - 0 - </t>
@@ -1291,6 +1291,9 @@
     <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - 1 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
   </si>
   <si>
@@ -1315,49 +1318,49 @@
     <t xml:space="preserve">2 - 5 - 2 - 1 - 2 - 1 - 5 - 3 - 2 - 1 - 2 - 3 - 1 - 5 - 2 - 3 - 3 - 3 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
+    <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 5 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 5 - 3 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 2 - 0 - 3 - 2 - 3 - 5 - 1 - 2 - 3 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - 2 - 3 - 0 - 2 - 2 - 0 - 2 - 2 - 2 - 1 - 2 - 3 - 3 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 2 - 1 - 2 - 2 - 2 - 0 - 1 - 2 - 1 - </t>
@@ -1555,13 +1558,13 @@
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -2006,7 +2009,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2018,7 +2021,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2027,7 +2030,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2054,7 +2057,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2066,7 +2069,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2075,7 +2078,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2093,7 +2096,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2108,7 +2111,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2129,7 +2132,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2138,7 +2141,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2147,7 +2150,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2171,7 +2174,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>66</v>
+        <v>39</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2180,7 +2183,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>70</v>
+        <v>41</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2189,7 +2192,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2201,7 +2204,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>75</v>
+        <v>43</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2213,7 +2216,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>78</v>
+        <v>45</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2222,7 +2225,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2235,7 +2238,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2262,7 +2265,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>86</v>
+        <v>54</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2277,7 +2280,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>88</v>
+        <v>56</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2286,7 +2289,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2313,7 +2316,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>95</v>
+        <v>60</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2322,7 +2325,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>97</v>
+        <v>61</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2331,7 +2334,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2352,7 +2355,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2370,7 +2373,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2391,7 +2394,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2409,40 +2412,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2482,37 +2485,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2541,7 +2544,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2567,7 +2570,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2596,7 +2599,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2625,12 +2628,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2659,10 +2662,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>153</v>
+        <v>134</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
     </row>
     <row r="34">
@@ -2771,7 +2774,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2813,7 +2816,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2821,7 +2824,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2857,7 +2860,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2884,7 +2887,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="L4" s="3">
         <v>2.2</v>
@@ -2897,7 +2900,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2905,7 +2908,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2932,7 +2935,7 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="L5" s="3">
         <v>2.33</v>
@@ -2944,7 +2947,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -2953,7 +2956,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2961,7 +2964,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -2988,7 +2991,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="L6" s="3">
         <v>2.3</v>
@@ -3000,7 +3003,7 @@
         <v>15.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="R6" s="3">
         <v>1.53</v>
@@ -3009,7 +3012,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="U6" s="3">
         <v>2.67</v>
@@ -3038,7 +3041,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3053,7 +3056,7 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -3062,7 +3065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3086,7 +3089,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="L8" s="3">
         <v>1.89</v>
@@ -3098,7 +3101,7 @@
         <v>6.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -3107,7 +3110,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -3115,7 +3118,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3127,7 +3130,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3140,7 +3143,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3149,7 +3152,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3174,7 +3177,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3190,36 +3193,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3252,7 +3255,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -3299,7 +3302,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="M17" s="3">
         <v>1.18</v>
@@ -3337,7 +3340,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="M18" s="3">
         <v>1.2</v>
@@ -3381,7 +3384,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>301</v>
+        <v>284</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -3422,7 +3425,7 @@
         <v>2.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -3466,7 +3469,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="M21" s="3">
         <v>0.9</v>
@@ -3489,37 +3492,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3533,7 +3536,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3550,7 +3553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3567,17 +3570,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3606,7 +3609,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3737,7 +3740,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
       <c r="L2" s="3">
         <v>2.33</v>
@@ -3749,7 +3752,7 @@
         <v>8.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -3758,7 +3761,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3766,7 +3769,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3796,7 +3799,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="L3" s="3">
         <v>3.08</v>
@@ -3808,7 +3811,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3817,7 +3820,7 @@
         <v>7.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="U3" s="3">
         <v>2.71</v>
@@ -3825,7 +3828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3855,7 +3858,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>279</v>
+        <v>291</v>
       </c>
       <c r="L4" s="3">
         <v>2.78</v>
@@ -3867,7 +3870,7 @@
         <v>8.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>281</v>
+        <v>292</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -3876,7 +3879,7 @@
         <v>13.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="U4" s="3">
         <v>2.31</v>
@@ -3884,7 +3887,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3911,7 +3914,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="L5" s="3">
         <v>2.36</v>
@@ -3923,7 +3926,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -3932,7 +3935,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -3940,7 +3943,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3963,7 +3966,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3971,7 +3974,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -3995,7 +3998,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="L7" s="3">
         <v>2.0</v>
@@ -4004,7 +4007,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4013,7 +4016,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4021,7 +4024,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4034,7 +4037,7 @@
         <v>7.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="R8" s="3">
         <v>2.29</v>
@@ -4043,7 +4046,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4051,7 +4054,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4069,7 +4072,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4079,7 +4082,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4102,7 +4105,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4112,7 +4115,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4130,7 +4133,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4139,7 +4142,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4160,7 +4163,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4169,7 +4172,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4187,7 +4190,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4199,7 +4202,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4220,7 +4223,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4232,7 +4235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4244,7 +4247,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4254,7 +4257,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4263,7 +4266,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4279,36 +4282,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4567,7 +4570,7 @@
         <v>7.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="M22" s="3">
         <v>2.29</v>
@@ -4590,37 +4593,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4637,7 +4640,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4654,7 +4657,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4671,17 +4674,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4710,7 +4713,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4862,7 +4865,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4918,7 +4921,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4974,7 +4977,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5001,7 +5004,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5013,7 +5016,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5022,7 +5025,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5030,7 +5033,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5042,7 +5045,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5054,7 +5057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5063,7 +5066,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5078,7 +5081,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5087,7 +5090,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5111,7 +5114,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5123,7 +5126,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5131,7 +5134,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5151,7 +5154,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -5159,7 +5162,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5186,7 +5189,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5211,7 +5214,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5227,36 +5230,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5289,7 +5292,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5336,7 +5339,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5383,7 +5386,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5427,7 +5430,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5471,7 +5474,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>328</v>
+        <v>341</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5515,7 +5518,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5538,37 +5541,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5597,7 +5600,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5614,7 +5617,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5631,7 +5634,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5648,12 +5651,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5688,7 +5691,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5795,7 +5798,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5822,7 +5825,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>330</v>
+        <v>316</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5834,7 +5837,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>331</v>
+        <v>317</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5843,7 +5846,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>332</v>
+        <v>319</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5851,7 +5854,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5881,7 +5884,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5893,7 +5896,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5902,7 +5905,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5910,7 +5913,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5940,7 +5943,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5955,7 +5958,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5964,7 +5967,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5972,7 +5975,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -5995,7 +5998,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -6003,7 +6006,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6025,7 +6028,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6042,7 +6045,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6062,7 +6065,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6076,7 +6079,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>341</v>
+        <v>336</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6085,7 +6088,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6104,7 +6107,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6119,7 +6122,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6128,7 +6131,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6137,7 +6140,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6171,7 +6174,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6219,7 +6222,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6247,7 +6250,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6263,36 +6266,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6419,7 +6422,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6466,7 +6469,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6513,7 +6516,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6560,7 +6563,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>352</v>
+        <v>359</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6583,37 +6586,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6630,7 +6633,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6647,7 +6650,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6664,7 +6667,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6681,7 +6684,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6698,7 +6701,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6727,7 +6730,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6834,7 +6837,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6852,7 +6855,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6865,7 +6868,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6895,7 +6898,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6907,7 +6910,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6916,7 +6919,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6924,7 +6927,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6936,7 +6939,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6945,7 +6948,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6954,7 +6957,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6962,7 +6965,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -7015,7 +7018,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7069,7 +7072,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7077,7 +7080,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7099,7 +7102,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7116,7 +7119,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7152,7 +7155,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -7160,7 +7163,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7202,7 +7205,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -7237,7 +7240,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7270,7 +7273,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7285,7 +7288,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7294,7 +7297,7 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="U13" s="3">
         <v>1.5</v>
@@ -7305,7 +7308,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7321,36 +7324,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7474,7 +7477,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7521,7 +7524,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7568,7 +7571,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7612,7 +7615,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7635,37 +7638,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7682,7 +7685,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7699,7 +7702,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7716,7 +7719,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7733,12 +7736,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7767,7 +7770,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7776,7 +7779,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>389</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -7877,7 +7880,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7904,7 +7907,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7922,7 +7925,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7931,7 +7934,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7952,7 +7955,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7965,7 +7968,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7992,7 +7995,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8004,7 +8007,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8013,7 +8016,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8021,7 +8024,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8042,7 +8045,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8054,7 +8057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8063,7 +8066,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8071,7 +8074,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8094,7 +8097,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8102,7 +8105,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8114,7 +8117,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8123,7 +8126,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8132,7 +8135,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8140,7 +8143,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8161,7 +8164,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8173,7 +8176,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8247,7 +8250,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8271,7 +8274,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8325,37 +8328,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8372,7 +8375,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8389,7 +8392,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8406,7 +8409,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8423,7 +8426,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8440,7 +8443,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8469,7 +8472,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8576,7 +8579,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8629,7 +8632,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8662,7 +8665,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8670,7 +8673,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8709,7 +8712,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8746,7 +8749,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8786,7 +8789,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8794,7 +8797,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8842,7 +8845,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8850,7 +8853,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8871,7 +8874,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8891,14 +8894,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8915,7 +8918,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8927,7 +8930,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8942,37 +8945,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8989,7 +8992,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9006,7 +9009,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9023,17 +9026,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9062,7 +9065,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9224,7 +9227,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9240,36 +9243,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9315,62 +9318,62 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -9379,7 +9382,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9480,19 +9483,19 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="D2" s="3">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E2" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="H2" s="3">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="I2" s="3">
         <v>2.0</v>
@@ -9507,7 +9510,7 @@
         <v>3.0</v>
       </c>
       <c r="P2" s="3">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>408</v>
@@ -9516,7 +9519,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
         <v>8.0</v>
@@ -9545,19 +9548,19 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
       </c>
       <c r="D4" s="3">
-        <v>10.0</v>
+        <v>12.0</v>
       </c>
       <c r="E4" s="3">
         <v>3.0</v>
       </c>
       <c r="F4" s="3">
-        <v>4.0</v>
+        <v>6.0</v>
       </c>
       <c r="H4" s="3">
         <v>9.0</v>
@@ -9572,13 +9575,13 @@
         <v>1.0</v>
       </c>
       <c r="P4" s="3">
-        <v>9.0</v>
+        <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>413</v>
       </c>
       <c r="S4" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>414</v>
@@ -9586,13 +9589,13 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B5" s="3">
         <v>8.0</v>
       </c>
       <c r="C5" s="3">
-        <v>6.0</v>
+        <v>8.0</v>
       </c>
       <c r="D5" s="3">
         <v>3.0</v>
@@ -9619,7 +9622,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -9653,22 +9656,22 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3">
-        <v>7.0</v>
+        <v>9.0</v>
       </c>
       <c r="C7" s="3">
         <v>2.0</v>
       </c>
       <c r="D7" s="3">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
       <c r="E7" s="3">
         <v>1.0</v>
       </c>
       <c r="F7" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H7" s="3">
         <v>9.0</v>
@@ -9692,10 +9695,10 @@
         <v>259</v>
       </c>
       <c r="S7" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>91</v>
+        <v>419</v>
       </c>
     </row>
     <row r="8">
@@ -9703,7 +9706,10 @@
         <v>21</v>
       </c>
       <c r="D8" s="3">
-        <v>5.0</v>
+        <v>7.0</v>
+      </c>
+      <c r="E8" s="3">
+        <v>1.0</v>
       </c>
       <c r="F8" s="3">
         <v>2.0</v>
@@ -9713,7 +9719,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D9" s="3">
         <v>6.0</v>
@@ -9728,7 +9734,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3">
         <v>1.0</v>
@@ -9738,7 +9744,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -9752,7 +9758,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
@@ -9773,37 +9779,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9820,7 +9826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -9837,13 +9843,16 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
       </c>
       <c r="C19" s="3">
         <v>2.0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>1.0</v>
       </c>
       <c r="G19" s="3">
         <v>2.0</v>
@@ -9851,17 +9860,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
@@ -9870,7 +9879,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9972,7 +9981,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -10002,7 +10011,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L2" s="3">
         <v>2.69</v>
@@ -10014,7 +10023,7 @@
         <v>22.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="R2" s="3">
         <v>1.45</v>
@@ -10023,7 +10032,7 @@
         <v>4.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -10031,7 +10040,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10055,7 +10064,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -10074,7 +10083,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -10092,7 +10101,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10105,7 +10114,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10113,7 +10122,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10143,7 +10152,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="L5" s="3">
         <v>2.63</v>
@@ -10155,7 +10164,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="R5" s="3">
         <v>1.71</v>
@@ -10164,7 +10173,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -10172,7 +10181,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10193,7 +10202,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="L6" s="3">
         <v>2.65</v>
@@ -10214,7 +10223,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10247,7 +10256,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10277,7 +10286,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -10289,7 +10298,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -10306,7 +10315,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10318,7 +10327,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -10328,7 +10337,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10346,7 +10355,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10371,37 +10380,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G16" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F16" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G16" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10418,7 +10427,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10435,7 +10444,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10452,7 +10461,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10469,12 +10478,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10503,7 +10512,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10610,7 +10619,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10634,7 +10643,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10646,7 +10655,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10655,7 +10664,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10663,7 +10672,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10681,7 +10690,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10694,7 +10703,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10702,7 +10711,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10729,7 +10738,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10741,7 +10750,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10750,7 +10759,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10758,7 +10767,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10770,7 +10779,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10779,7 +10788,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10788,7 +10797,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>67</v>
+        <v>52</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10796,7 +10805,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10820,7 +10829,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10832,7 +10841,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>76</v>
+        <v>57</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10841,7 +10850,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10849,7 +10858,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10876,7 +10885,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10913,7 +10922,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10922,7 +10931,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10940,7 +10949,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>96</v>
+        <v>64</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10953,7 +10962,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10961,7 +10970,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10975,7 +10984,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10990,7 +10999,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -10999,13 +11008,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -11020,7 +11029,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -11036,40 +11045,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11102,7 +11111,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11119,7 +11128,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="11">
+      <c r="R16" s="13">
         <f>10</f>
         <v>10</v>
       </c>
@@ -11150,7 +11159,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11197,7 +11206,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11244,7 +11253,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>141</v>
+        <v>119</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11291,7 +11300,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11335,7 +11344,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>148</v>
+        <v>125</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11355,37 +11364,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11402,7 +11411,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11419,7 +11428,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11436,7 +11445,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11453,7 +11462,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11470,7 +11479,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11499,7 +11508,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11606,7 +11615,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11630,7 +11639,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -11642,7 +11651,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="R2" s="3">
         <v>1.46</v>
@@ -11651,7 +11660,7 @@
         <v>12.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="U2" s="3">
         <v>2.58</v>
@@ -11659,7 +11668,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11689,7 +11698,7 @@
         <v>7.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="L3" s="3">
         <v>1.62</v>
@@ -11701,7 +11710,7 @@
         <v>6.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="R3" s="3">
         <v>1.17</v>
@@ -11710,7 +11719,7 @@
         <v>11.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="U3" s="3">
         <v>2.36</v>
@@ -11718,7 +11727,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11745,7 +11754,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="L4" s="3">
         <v>2.0</v>
@@ -11758,7 +11767,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -11766,7 +11775,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11796,7 +11805,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="L5" s="3">
         <v>2.86</v>
@@ -11808,7 +11817,7 @@
         <v>32.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="R5" s="3">
         <v>1.59</v>
@@ -11817,7 +11826,7 @@
         <v>23.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="U5" s="3">
         <v>2.43</v>
@@ -11825,7 +11834,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11846,7 +11855,7 @@
         <v>15.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L6" s="3">
         <v>2.33</v>
@@ -11858,7 +11867,7 @@
         <v>19.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="R6" s="3">
         <v>1.79</v>
@@ -11867,7 +11876,7 @@
         <v>17.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="U6" s="3">
         <v>2.47</v>
@@ -11875,7 +11884,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11906,7 +11915,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11914,7 +11923,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11938,7 +11947,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L8" s="3">
         <v>2.76</v>
@@ -11950,7 +11959,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11988,7 +11997,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -12002,7 +12011,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12011,7 +12020,7 @@
         <v>2.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="U11" s="3">
         <v>2.0</v>
@@ -12019,7 +12028,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12031,7 +12040,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12045,37 +12054,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12092,7 +12101,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12109,7 +12118,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12126,7 +12135,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12143,7 +12152,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12160,7 +12169,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12189,7 +12198,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12296,7 +12305,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12308,7 +12317,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L2" s="3">
         <v>2.4</v>
@@ -12320,7 +12329,7 @@
         <v>26.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="R2" s="3">
         <v>1.73</v>
@@ -12329,7 +12338,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>79</v>
+        <v>58</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12337,7 +12346,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12361,7 +12370,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -12373,7 +12382,7 @@
         <v>19.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R3" s="3">
         <v>1.59</v>
@@ -12382,7 +12391,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="U3" s="3">
         <v>2.8</v>
@@ -12390,7 +12399,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12417,7 +12426,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -12429,7 +12438,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12438,7 +12447,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12446,7 +12455,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12476,7 +12485,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L5" s="3">
         <v>2.1</v>
@@ -12488,7 +12497,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="R5" s="3">
         <v>1.7</v>
@@ -12497,7 +12506,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="U5" s="3">
         <v>2.75</v>
@@ -12505,7 +12514,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12517,7 +12526,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="L6" s="3">
         <v>2.67</v>
@@ -12527,7 +12536,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12548,7 +12557,7 @@
         <v>4.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="L7" s="3">
         <v>0.0</v>
@@ -12563,7 +12572,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12572,7 +12581,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12594,7 +12603,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12617,13 +12626,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12632,7 +12641,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12641,7 +12650,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12662,7 +12671,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12701,7 +12710,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12716,7 +12725,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12728,7 +12737,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12764,37 +12773,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12811,7 +12820,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12822,7 +12831,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12839,17 +12848,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12878,7 +12887,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12985,7 +12994,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -12997,7 +13006,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L2" s="3">
         <v>1.36</v>
@@ -13007,7 +13016,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="R2" s="3">
         <v>1.38</v>
@@ -13016,7 +13025,7 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="U2" s="3">
         <v>2.17</v>
@@ -13024,7 +13033,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13044,7 +13053,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13068,7 +13077,7 @@
         <v>6.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="L4" s="3">
         <v>3.12</v>
@@ -13077,7 +13086,7 @@
         <v>18.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="R4" s="3">
         <v>1.39</v>
@@ -13086,7 +13095,7 @@
         <v>10.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="U4" s="3">
         <v>2.4</v>
@@ -13094,7 +13103,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13124,7 +13133,7 @@
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="L5" s="3">
         <v>2.17</v>
@@ -13136,7 +13145,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -13145,7 +13154,7 @@
         <v>7.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="U5" s="3">
         <v>2.57</v>
@@ -13153,7 +13162,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13180,7 +13189,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="L6" s="3">
         <v>2.18</v>
@@ -13192,7 +13201,7 @@
         <v>22.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -13201,7 +13210,7 @@
         <v>10.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="U6" s="3">
         <v>2.4</v>
@@ -13209,7 +13218,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13231,7 +13240,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13239,7 +13248,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13263,7 +13272,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="L8" s="3">
         <v>2.31</v>
@@ -13272,7 +13281,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13309,7 +13318,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13332,7 +13341,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13340,7 +13349,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13352,7 +13361,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L11" s="3">
         <v>2.4</v>
@@ -13364,7 +13373,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13382,7 +13391,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13394,7 +13403,7 @@
         <v>5.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -13403,7 +13412,7 @@
         <v>4.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -13443,37 +13452,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G17" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F17" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G17" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13490,7 +13499,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13507,7 +13516,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13521,7 +13530,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13538,7 +13547,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13552,7 +13561,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13581,7 +13590,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13716,7 +13725,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13731,7 +13740,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13743,7 +13752,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>28</v>
+        <v>101</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13752,7 +13761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13776,7 +13785,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>33</v>
+        <v>108</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13789,7 +13798,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>35</v>
+        <v>109</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13797,7 +13806,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13824,7 +13833,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>41</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13836,7 +13845,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>45</v>
+        <v>117</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13845,7 +13854,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13872,7 +13881,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13884,7 +13893,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>52</v>
+        <v>123</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13893,7 +13902,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>53</v>
+        <v>124</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13901,7 +13910,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13925,7 +13934,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>60</v>
+        <v>127</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13937,7 +13946,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>64</v>
+        <v>129</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13946,7 +13955,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13954,7 +13963,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13972,7 +13981,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>74</v>
+        <v>133</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13984,7 +13993,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>77</v>
+        <v>136</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -13993,7 +14002,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>80</v>
+        <v>137</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14001,7 +14010,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -14015,7 +14024,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14024,7 +14033,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14036,7 +14045,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14045,7 +14054,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14053,7 +14062,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14062,7 +14071,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>90</v>
+        <v>141</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14074,7 +14083,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14095,7 +14104,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14111,40 +14120,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14177,7 +14186,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14219,7 +14228,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>119</v>
+        <v>148</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14266,7 +14275,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14313,7 +14322,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>122</v>
+        <v>151</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14357,7 +14366,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>124</v>
+        <v>152</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14395,7 +14404,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>125</v>
+        <v>153</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14418,37 +14427,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14465,7 +14474,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14482,7 +14491,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14499,17 +14508,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14538,7 +14547,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14645,7 +14654,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14672,7 +14681,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14684,7 +14693,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>43</v>
+        <v>79</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14693,7 +14702,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>46</v>
+        <v>82</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14701,7 +14710,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14728,7 +14737,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>51</v>
+        <v>85</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14743,7 +14752,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14752,7 +14761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14773,7 +14782,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14785,7 +14794,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14794,7 +14803,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14802,7 +14811,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14812,7 +14821,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14825,7 +14834,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14852,7 +14861,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14864,7 +14873,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14873,7 +14882,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14881,7 +14890,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14908,7 +14917,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14920,7 +14929,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14929,7 +14938,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14965,7 +14974,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14974,7 +14983,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14986,7 +14995,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -14995,7 +15004,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15004,7 +15013,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15012,7 +15021,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15027,7 +15036,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15036,7 +15045,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15045,7 +15054,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15066,7 +15075,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15079,7 +15088,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15087,7 +15096,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15102,7 +15111,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15111,7 +15120,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15120,7 +15129,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15128,7 +15137,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15140,7 +15149,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15158,7 +15167,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15176,7 +15185,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15192,36 +15201,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15254,7 +15263,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15342,7 +15351,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15389,7 +15398,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15430,7 +15439,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15477,7 +15486,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15497,37 +15506,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15544,7 +15553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15561,7 +15570,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15578,7 +15587,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15595,12 +15604,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15629,7 +15638,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15736,7 +15745,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15784,7 +15793,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15833,7 +15842,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15901,7 +15910,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15957,7 +15966,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15976,7 +15985,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16044,7 +16053,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16080,7 +16089,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16088,7 +16097,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16112,7 +16121,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16130,7 +16139,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16139,7 +16148,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16154,7 +16163,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16170,36 +16179,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16229,7 +16238,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>187</v>
+        <v>169</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16276,7 +16285,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>192</v>
+        <v>170</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -16320,7 +16329,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16367,7 +16376,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16414,7 +16423,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16461,7 +16470,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>207</v>
+        <v>174</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16484,37 +16493,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G23" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F23" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G23" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K23" s="16"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16531,7 +16540,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16548,7 +16557,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16565,7 +16574,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16582,7 +16591,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16590,7 +16599,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16619,7 +16628,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16726,7 +16735,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16750,7 +16759,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -16762,7 +16771,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -16771,7 +16780,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -16779,7 +16788,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16790,7 +16799,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16817,7 +16826,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -16829,7 +16838,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -16838,7 +16847,7 @@
         <v>7.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="U4" s="3">
         <v>2.29</v>
@@ -16846,7 +16855,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16858,7 +16867,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16876,7 +16885,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16884,7 +16893,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16914,7 +16923,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -16929,7 +16938,7 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="R6" s="3">
         <v>0.5</v>
@@ -16938,7 +16947,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>69</v>
+        <v>90</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16946,7 +16955,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16964,7 +16973,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L7" s="3">
         <v>2.36</v>
@@ -16976,7 +16985,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -16984,7 +16993,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17005,7 +17014,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -17017,7 +17026,7 @@
         <v>9.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="R8" s="3">
         <v>1.11</v>
@@ -17026,7 +17035,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="U8" s="3">
         <v>2.0</v>
@@ -17059,7 +17068,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17068,7 +17077,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17080,7 +17089,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L10" s="3">
         <v>1.75</v>
@@ -17092,7 +17101,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>118</v>
+        <v>138</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17101,7 +17110,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17122,7 +17131,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17134,7 +17143,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17143,7 +17152,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17164,7 +17173,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="L12" s="3">
         <v>2.25</v>
@@ -17176,7 +17185,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="R12" s="3">
         <v>0.75</v>
@@ -17185,7 +17194,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17193,7 +17202,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17208,7 +17217,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>67</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17220,14 +17229,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>206</v>
+        <v>192</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17236,7 +17245,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17252,36 +17261,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17311,7 +17320,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17358,7 +17367,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>212</v>
+        <v>194</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17402,7 +17411,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>214</v>
+        <v>195</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17449,7 +17458,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>216</v>
+        <v>196</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17496,7 +17505,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>217</v>
+        <v>197</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17543,7 +17552,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>218</v>
+        <v>198</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17566,37 +17575,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F25" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F25" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G25" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17613,7 +17622,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17630,7 +17639,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17647,7 +17656,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17658,12 +17667,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17692,7 +17701,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17799,7 +17808,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17823,7 +17832,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>172</v>
+        <v>199</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17835,7 +17844,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>173</v>
+        <v>200</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17844,7 +17853,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>174</v>
+        <v>201</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17852,7 +17861,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17873,7 +17882,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17883,7 +17892,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17891,7 +17900,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17918,7 +17927,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>180</v>
+        <v>204</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17927,7 +17936,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17936,7 +17945,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>183</v>
+        <v>206</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17944,7 +17953,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17968,7 +17977,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>185</v>
+        <v>207</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -17992,7 +18001,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -18010,7 +18019,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>188</v>
+        <v>208</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -18031,7 +18040,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -18039,7 +18048,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18055,7 +18064,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>193</v>
+        <v>210</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -18064,7 +18073,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -18091,7 +18100,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18103,7 +18112,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="L9" s="3">
         <v>1.833</v>
@@ -18113,7 +18122,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18144,7 +18153,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18160,36 +18169,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18219,7 +18228,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18263,7 +18272,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18277,7 +18286,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="11">
+      <c r="R17" s="13">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18305,7 +18314,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18346,7 +18355,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18381,7 +18390,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18428,7 +18437,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18448,37 +18457,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18507,7 +18516,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18536,22 +18545,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18580,7 +18589,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18687,7 +18696,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18746,7 +18755,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18802,7 +18811,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18836,7 +18845,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18877,7 +18886,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18930,7 +18939,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -18993,7 +19002,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -19013,7 +19022,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -19050,7 +19059,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>176</v>
+        <v>202</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19058,7 +19067,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19085,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19103,7 +19112,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>102</v>
+        <v>65</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19118,7 +19127,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19130,7 +19139,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19146,36 +19155,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19436,38 +19445,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19494,7 +19503,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19524,7 +19533,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19553,17 +19562,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19592,7 +19601,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19699,7 +19708,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19738,7 +19747,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>104</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19794,7 +19803,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19847,7 +19856,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19898,7 +19907,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19906,7 +19915,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>49</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19963,7 +19972,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19971,7 +19980,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -19996,7 +20005,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -20063,7 +20072,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>95</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20128,7 +20137,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20144,36 +20153,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>100</v>
+        <v>71</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>101</v>
+        <v>72</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>106</v>
+        <v>74</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>110</v>
+        <v>78</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>112</v>
+        <v>80</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>114</v>
+        <v>83</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>115</v>
+        <v>84</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20461,37 +20470,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>127</v>
+        <v>92</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>128</v>
+        <v>93</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>129</v>
+        <v>94</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
-      </c>
-      <c r="F24" s="12" t="s">
-        <v>131</v>
-      </c>
-      <c r="G24" s="13" t="s">
-        <v>132</v>
+        <v>96</v>
+      </c>
+      <c r="F24" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="G24" s="12" t="s">
+        <v>103</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>133</v>
+        <v>105</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>135</v>
+        <v>110</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20508,7 +20517,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20525,7 +20534,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>140</v>
+        <v>120</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20542,7 +20551,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>142</v>
+        <v>126</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20559,7 +20568,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20576,7 +20585,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20605,7 +20614,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>149</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -100,93 +100,93 @@
     <t>Cora</t>
   </si>
   <si>
+    <t>Shiloh</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - </t>
   </si>
   <si>
     <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
   </si>
   <si>
-    <t>Shiloh</t>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
     <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
   </si>
   <si>
     <t>Addy</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>Kinley</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">Nataly </t>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+    <t>Agnes</t>
   </si>
   <si>
     <t>Audri</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t>3 - 3 - 5 - 1 - 3 - 0</t>
   </si>
   <si>
-    <t>Agnes</t>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
   </si>
   <si>
     <t>3 - 0 - 1</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t>1 - 1 - 1 - 0 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+    <t>Anna</t>
   </si>
   <si>
     <t>Corena</t>
   </si>
   <si>
-    <t>Anna</t>
+    <t xml:space="preserve">0 - 0 - </t>
   </si>
   <si>
     <t>Annabelle</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
@@ -199,94 +199,202 @@
     <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
   </si>
   <si>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
     <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
   </si>
   <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
+    <t>Emma</t>
+  </si>
+  <si>
+    <t>Piper</t>
+  </si>
+  <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
+    <t>Rotation (follow setter starting position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - </t>
   </si>
   <si>
-    <t>Elena</t>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t>Emma</t>
+    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - </t>
   </si>
   <si>
-    <t>Piper</t>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
+  </si>
+  <si>
+    <t>Serve Errors</t>
   </si>
   <si>
     <t>Gaby</t>
   </si>
   <si>
-    <t>Rotation (follow setter starting position)</t>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
   </si>
   <si>
     <t xml:space="preserve">1 - </t>
   </si>
   <si>
-    <t>Kill Efficiency</t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
+    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
+  </si>
+  <si>
+    <t>Service error (us)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - </t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
+  </si>
+  <si>
+    <t>Service Errors (them)</t>
+  </si>
+  <si>
+    <t>Ace % (them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>Service Error % (Them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t>Set 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - </t>
+  </si>
+  <si>
+    <t>Set 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>Set 3</t>
+  </si>
+  <si>
+    <t>Set 4</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t>Serve Receive Avg Score</t>
-  </si>
-  <si>
-    <t>Serve Aces</t>
+    <t xml:space="preserve">1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Set 5</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
   </si>
   <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
+    <t>Total</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
+    <t xml:space="preserve">5 - 3 - </t>
+  </si>
+  <si>
+    <t>Team Passer Rating (all games)</t>
+  </si>
+  <si>
+    <t>Team Kill Efficiency (all games)</t>
   </si>
   <si>
     <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
@@ -295,61 +403,49 @@
     <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - </t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
-  </si>
-  <si>
-    <t>Service error (us)</t>
-  </si>
-  <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
   </si>
   <si>
-    <t>Aces (them)</t>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
   </si>
   <si>
-    <t>Service Errors (them)</t>
-  </si>
-  <si>
     <t>Tea</t>
   </si>
   <si>
-    <t>Ace % (them)</t>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
@@ -358,108 +454,30 @@
     <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - </t>
-  </si>
-  <si>
-    <t>Service Error % (Them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t>Set 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t>Set 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Team Passer Rating (all games)</t>
-  </si>
-  <si>
-    <t>Team Kill Efficiency (all games)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
   </si>
   <si>
@@ -472,30 +490,12 @@
     <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -613,63 +613,63 @@
     <t xml:space="preserve">1 - 0 - 2 - </t>
   </si>
   <si>
+    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
+  </si>
+  <si>
+    <t>2- 1- 0- 3- 1</t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
+  </si>
+  <si>
+    <t>0- 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
   </si>
   <si>
+    <t>2- 2- 3- 3- 2</t>
+  </si>
+  <si>
+    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t>2- 3- 2- 2</t>
+  </si>
+  <si>
+    <t>3- 2- 3- 5- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
   </si>
   <si>
+    <t>1- 2- 2- 3- 1- 1- 0</t>
+  </si>
+  <si>
+    <t>1- 3- 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
   </si>
   <si>
+    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
+  </si>
+  <si>
+    <t>3- 3- 3- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
-  </si>
-  <si>
-    <t>2- 1- 0- 3- 1</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
-  </si>
-  <si>
-    <t>0- 0</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2</t>
-  </si>
-  <si>
-    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>2- 3- 2- 2</t>
-  </si>
-  <si>
-    <t>3- 2- 3- 5- 3</t>
-  </si>
-  <si>
-    <t>1- 2- 2- 3- 1- 1- 0</t>
-  </si>
-  <si>
-    <t>1- 3- 0</t>
-  </si>
-  <si>
-    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
-  </si>
-  <si>
-    <t>3- 3- 3- 2</t>
-  </si>
-  <si>
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
@@ -931,18 +931,63 @@
     <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 2- 2- 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 1 - 0 - </t>
   </si>
   <si>
@@ -955,31 +1000,28 @@
     <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 2- 2- 2 - </t>
+    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
@@ -988,36 +1030,18 @@
     <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
   </si>
   <si>
@@ -1027,37 +1051,37 @@
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
+    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
@@ -1066,7 +1090,19 @@
     <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
@@ -1075,150 +1111,114 @@
     <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
+    <t>119 attack attempts</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 1 - 2 - 3 - 3 - 2 - 2 - 0 - 3 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t>119 attack attempts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1261,7 +1261,7 @@
     <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 1 - 3 - </t>
+    <t xml:space="preserve">0 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - </t>
@@ -1273,13 +1273,13 @@
     <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - 5 - 5 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - 2 - 3 - </t>
+    <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - 2 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 2 - </t>
@@ -1291,7 +1291,7 @@
     <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - 1 - 5 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 3 - </t>
+    <t xml:space="preserve">2 - 1 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
@@ -1321,6 +1321,21 @@
     <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1330,31 +1345,16 @@
     <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 1 - </t>
@@ -1564,7 +1564,6 @@
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
@@ -1577,6 +1576,7 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -2009,7 +2009,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2021,7 +2021,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2057,7 +2057,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2069,7 +2069,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2096,7 +2096,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2132,7 +2132,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2141,7 +2141,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2174,7 +2174,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2183,7 +2183,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2204,7 +2204,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2216,7 +2216,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2280,7 +2280,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2316,7 +2316,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2325,7 +2325,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2412,40 +2412,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2485,37 +2485,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2628,12 +2628,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2641,10 +2641,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.33</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.12</v>
       </c>
       <c r="F31" s="3">
@@ -2653,19 +2653,19 @@
       <c r="G31" s="3">
         <v>17.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.18</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.19</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>134</v>
+        <v>119</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
     </row>
     <row r="34">
@@ -2774,7 +2774,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2816,7 +2816,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2900,7 +2900,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2956,7 +2956,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3130,7 +3130,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3152,7 +3152,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3193,36 +3193,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3492,37 +3492,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3570,17 +3570,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3588,10 +3588,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.14</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.18</v>
       </c>
       <c r="F31" s="3">
@@ -3600,16 +3600,16 @@
       <c r="G31" s="3">
         <v>14.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.25</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3761,7 +3761,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3811,7 +3811,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3966,7 +3966,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -4007,7 +4007,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4016,7 +4016,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4046,7 +4046,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4072,7 +4072,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4082,7 +4082,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4105,7 +4105,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4115,7 +4115,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4133,7 +4133,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4163,7 +4163,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4190,7 +4190,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4223,7 +4223,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>302</v>
+        <v>315</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4247,7 +4247,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4257,7 +4257,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4282,36 +4282,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4344,7 +4344,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4391,7 +4391,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4435,7 +4435,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4479,7 +4479,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -4526,7 +4526,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>308</v>
+        <v>325</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4593,37 +4593,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K25" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4674,17 +4674,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4692,10 +4692,10 @@
       <c r="C32" s="3">
         <v>12.0</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>0.23</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>0.16</v>
       </c>
       <c r="F32" s="3">
@@ -4704,16 +4704,16 @@
       <c r="G32" s="3">
         <v>9.0</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>0.27</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <v>0.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4848,7 +4848,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4892,7 +4892,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4904,7 +4904,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4913,7 +4913,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4948,7 +4948,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4960,7 +4960,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4969,7 +4969,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5004,7 +5004,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5016,7 +5016,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>320</v>
+        <v>309</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5025,7 +5025,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>321</v>
+        <v>310</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5045,7 +5045,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>323</v>
+        <v>312</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5057,7 +5057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>325</v>
+        <v>313</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>327</v>
+        <v>314</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5114,7 +5114,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>331</v>
+        <v>316</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5126,7 +5126,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5189,7 +5189,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5230,36 +5230,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5292,7 +5292,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>335</v>
+        <v>322</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5339,7 +5339,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>337</v>
+        <v>324</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5386,7 +5386,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5430,7 +5430,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5474,7 +5474,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>341</v>
+        <v>328</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5518,7 +5518,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5541,37 +5541,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5651,12 +5651,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5664,34 +5664,34 @@
       <c r="C31" s="3">
         <v>15.0</v>
       </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
       <c r="F31" s="3">
         <v>13.0</v>
       </c>
       <c r="G31" s="3">
         <v>17.0</v>
       </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
     </row>
     <row r="32">
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>0.28</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>0.16</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>0.19</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <v>0.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5825,7 +5825,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>316</v>
+        <v>330</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5837,7 +5837,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>317</v>
+        <v>331</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5846,7 +5846,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>319</v>
+        <v>332</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5884,7 +5884,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5896,7 +5896,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5905,7 +5905,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5943,7 +5943,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5958,7 +5958,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5967,7 +5967,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -5998,7 +5998,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6028,7 +6028,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6065,7 +6065,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6079,7 +6079,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6088,7 +6088,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6122,7 +6122,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6131,7 +6131,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6140,7 +6140,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6174,7 +6174,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6201,7 +6201,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -6214,7 +6214,7 @@
         <v>7.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="U10" s="3">
         <v>2.14</v>
@@ -6266,36 +6266,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6328,7 +6328,7 @@
         <v>6.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>347</v>
+        <v>373</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -6375,7 +6375,7 @@
         <v>14.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>348</v>
+        <v>376</v>
       </c>
       <c r="M17" s="3">
         <v>1.79</v>
@@ -6422,7 +6422,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6469,7 +6469,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>352</v>
+        <v>391</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6516,7 +6516,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>356</v>
+        <v>393</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6563,7 +6563,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>359</v>
+        <v>394</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6586,37 +6586,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6633,7 +6633,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6709,10 +6709,10 @@
       <c r="C31" s="3">
         <v>14.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.17</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.13</v>
       </c>
       <c r="F31" s="3">
@@ -6721,16 +6721,16 @@
       <c r="G31" s="3">
         <v>15.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.17</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6855,7 +6855,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6898,7 +6898,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6910,7 +6910,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6919,7 +6919,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6939,7 +6939,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6948,7 +6948,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6957,7 +6957,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -6989,7 +6989,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="L5" s="3">
         <v>2.75</v>
@@ -7001,7 +7001,7 @@
         <v>16.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -7010,7 +7010,7 @@
         <v>13.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="U5" s="3">
         <v>2.15</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7048,7 +7048,7 @@
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -7063,7 +7063,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -7072,7 +7072,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7102,7 +7102,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7111,7 +7111,7 @@
         <v>7.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="U7" s="3">
         <v>1.86</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7143,7 +7143,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>366</v>
+        <v>361</v>
       </c>
       <c r="L8" s="3">
         <v>1.67</v>
@@ -7187,7 +7187,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="L9" s="3">
         <v>2.56</v>
@@ -7196,7 +7196,7 @@
         <v>12.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="R9" s="3">
         <v>1.67</v>
@@ -7240,7 +7240,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7324,36 +7324,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7386,7 +7386,7 @@
         <v>12.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -7430,7 +7430,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="M17" s="3">
         <v>2.55</v>
@@ -7477,7 +7477,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7524,7 +7524,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7571,7 +7571,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7615,7 +7615,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>388</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7638,37 +7638,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7736,12 +7736,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7749,10 +7749,10 @@
       <c r="C31" s="3">
         <v>13.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.2</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.15</v>
       </c>
       <c r="F31" s="3">
@@ -7761,16 +7761,16 @@
       <c r="G31" s="3">
         <v>13.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.1</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7779,7 +7779,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>376</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -7880,7 +7880,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7907,7 +7907,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7925,7 +7925,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>378</v>
+        <v>362</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7955,7 +7955,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>379</v>
+        <v>364</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7995,7 +7995,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>380</v>
+        <v>366</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8007,7 +8007,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8016,7 +8016,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>382</v>
+        <v>368</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8045,7 +8045,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8057,7 +8057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>371</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8066,7 +8066,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>385</v>
+        <v>372</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8097,7 +8097,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8117,7 +8117,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8126,7 +8126,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>387</v>
+        <v>375</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8135,7 +8135,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>388</v>
+        <v>377</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8164,7 +8164,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>389</v>
+        <v>379</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8200,7 +8200,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8213,7 +8213,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8265,7 +8265,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8298,7 +8298,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8310,7 +8310,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8328,37 +8328,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8375,7 +8375,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8392,7 +8392,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8409,7 +8409,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8426,7 +8426,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8451,10 +8451,10 @@
       <c r="C23" s="3">
         <v>21.0</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>0.3</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>0.24</v>
       </c>
       <c r="F23" s="3">
@@ -8463,16 +8463,16 @@
       <c r="G23" s="3">
         <v>22.0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="16">
         <v>0.32</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="16">
         <v>0.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8579,7 +8579,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8632,7 +8632,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8665,7 +8665,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8712,7 +8712,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8749,7 +8749,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8789,7 +8789,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8797,7 +8797,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8845,7 +8845,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8874,7 +8874,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8901,7 +8901,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8930,7 +8930,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8945,37 +8945,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9026,17 +9026,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9044,10 +9044,10 @@
       <c r="C23" s="3">
         <v>8.0</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>0.35</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>0.12</v>
       </c>
       <c r="F23" s="3">
@@ -9056,16 +9056,16 @@
       <c r="G23" s="3">
         <v>13.0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="16">
         <v>0.18</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="16">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9243,36 +9243,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9318,71 +9318,71 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17"/>
+        <v>116</v>
+      </c>
+      <c r="D31" s="16"/>
+      <c r="E31" s="16"/>
+      <c r="H31" s="16"/>
+      <c r="I31" s="16"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9483,10 +9483,10 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="D2" s="3">
         <v>10.0</v>
@@ -9519,13 +9519,13 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3">
-        <v>8.0</v>
+        <v>10.0</v>
       </c>
       <c r="H3" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="J3" s="3">
         <v>1.0</v>
@@ -9548,16 +9548,16 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
       </c>
       <c r="D4" s="3">
-        <v>12.0</v>
+        <v>15.0</v>
       </c>
       <c r="E4" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="F4" s="3">
         <v>6.0</v>
@@ -9575,7 +9575,7 @@
         <v>1.0</v>
       </c>
       <c r="P4" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="Q4" s="4" t="s">
         <v>413</v>
@@ -9589,19 +9589,19 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B5" s="3">
         <v>8.0</v>
       </c>
       <c r="C5" s="3">
+        <v>9.0</v>
+      </c>
+      <c r="D5" s="3">
+        <v>3.0</v>
+      </c>
+      <c r="H5" s="3">
         <v>8.0</v>
-      </c>
-      <c r="D5" s="3">
-        <v>3.0</v>
-      </c>
-      <c r="H5" s="3">
-        <v>7.0</v>
       </c>
       <c r="J5" s="3">
         <v>2.0</v>
@@ -9610,7 +9610,7 @@
         <v>415</v>
       </c>
       <c r="M5" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="Q5" s="4"/>
       <c r="S5" s="3">
@@ -9656,7 +9656,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -9695,7 +9695,7 @@
         <v>259</v>
       </c>
       <c r="S7" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
         <v>419</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D9" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E9" s="3">
         <v>1.0</v>
@@ -9734,7 +9734,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M9" s="3">
         <v>1.0</v>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -9758,13 +9758,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>387</v>
       </c>
       <c r="T11" s="5"/>
     </row>
@@ -9779,37 +9779,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9826,7 +9826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -9843,7 +9843,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -9855,31 +9855,31 @@
         <v>1.0</v>
       </c>
       <c r="G19" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="D23" s="17"/>
-      <c r="E23" s="17"/>
-      <c r="H23" s="17"/>
-      <c r="I23" s="17"/>
+        <v>116</v>
+      </c>
+      <c r="D23" s="16"/>
+      <c r="E23" s="16"/>
+      <c r="H23" s="16"/>
+      <c r="I23" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -10040,7 +10040,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10083,7 +10083,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -10101,7 +10101,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10114,7 +10114,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10122,7 +10122,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10181,7 +10181,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10223,7 +10223,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10286,7 +10286,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -10298,7 +10298,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -10307,7 +10307,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
       <c r="U8" s="3">
         <v>1.83</v>
@@ -10327,7 +10327,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>438</v>
+        <v>432</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -10337,7 +10337,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10355,7 +10355,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>440</v>
+        <v>433</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10380,37 +10380,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H16" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I16" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K16" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H16" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I16" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10427,7 +10427,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10444,7 +10444,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10461,7 +10461,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10478,12 +10478,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10491,10 +10491,10 @@
       <c r="C23" s="3">
         <v>9.0</v>
       </c>
-      <c r="D23" s="17">
+      <c r="D23" s="16">
         <v>0.27</v>
       </c>
-      <c r="E23" s="17">
+      <c r="E23" s="16">
         <v>0.11</v>
       </c>
       <c r="F23" s="3">
@@ -10503,16 +10503,16 @@
       <c r="G23" s="3">
         <v>17.0</v>
       </c>
-      <c r="H23" s="17">
+      <c r="H23" s="16">
         <v>0.26</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="16">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10643,7 +10643,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10655,7 +10655,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10664,7 +10664,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10672,7 +10672,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10690,7 +10690,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10703,7 +10703,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10711,7 +10711,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10738,7 +10738,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10750,7 +10750,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10759,7 +10759,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10779,7 +10779,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10829,7 +10829,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10841,7 +10841,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10850,7 +10850,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10858,7 +10858,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10885,7 +10885,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10922,7 +10922,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10931,7 +10931,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10949,7 +10949,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10962,7 +10962,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10970,7 +10970,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10999,7 +10999,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -11014,7 +11014,7 @@
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -11045,40 +11045,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11111,7 +11111,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11128,7 +11128,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="13">
+      <c r="R16" s="17">
         <f>10</f>
         <v>10</v>
       </c>
@@ -11159,7 +11159,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>111</v>
+        <v>123</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11206,7 +11206,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>116</v>
+        <v>125</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11253,7 +11253,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11300,7 +11300,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11344,7 +11344,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11364,37 +11364,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11487,10 +11487,10 @@
       <c r="C31" s="3">
         <v>22.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.29</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.22</v>
       </c>
       <c r="F31" s="3">
@@ -11499,16 +11499,16 @@
       <c r="G31" s="3">
         <v>8.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.19</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11615,7 +11615,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11639,7 +11639,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -11651,7 +11651,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
       <c r="R2" s="3">
         <v>1.46</v>
@@ -11660,7 +11660,7 @@
         <v>12.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
       <c r="U2" s="3">
         <v>2.58</v>
@@ -11668,7 +11668,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11698,7 +11698,7 @@
         <v>7.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L3" s="3">
         <v>1.62</v>
@@ -11710,7 +11710,7 @@
         <v>6.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="R3" s="3">
         <v>1.17</v>
@@ -11719,7 +11719,7 @@
         <v>11.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="U3" s="3">
         <v>2.36</v>
@@ -11727,7 +11727,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11754,7 +11754,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="L4" s="3">
         <v>2.0</v>
@@ -11775,7 +11775,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11834,7 +11834,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11884,7 +11884,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11915,7 +11915,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11923,7 +11923,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11959,7 +11959,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11997,7 +11997,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -12011,7 +12011,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12040,7 +12040,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12054,37 +12054,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K17" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12101,7 +12101,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12118,7 +12118,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12135,7 +12135,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12152,7 +12152,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12169,7 +12169,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12177,10 +12177,10 @@
       <c r="C24" s="3">
         <v>14.0</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>0.16</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>0.15</v>
       </c>
       <c r="F24" s="3">
@@ -12189,16 +12189,16 @@
       <c r="G24" s="3">
         <v>14.0</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <v>0.18</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="16">
         <v>0.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12305,7 +12305,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12338,7 +12338,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12346,7 +12346,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12399,7 +12399,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12438,7 +12438,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12447,7 +12447,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12455,7 +12455,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12514,7 +12514,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12536,7 +12536,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12572,7 +12572,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12626,13 +12626,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12641,7 +12641,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12671,7 +12671,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12710,7 +12710,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12725,7 +12725,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12737,7 +12737,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12773,37 +12773,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K17" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12831,7 +12831,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12848,17 +12848,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12866,10 +12866,10 @@
       <c r="C24" s="3">
         <v>5.0</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>0.12</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>0.12</v>
       </c>
       <c r="F24" s="3">
@@ -12878,16 +12878,16 @@
       <c r="G24" s="3">
         <v>8.0</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <v>0.26</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="16">
         <v>0.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12994,7 +12994,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -13053,7 +13053,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13103,7 +13103,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13218,7 +13218,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13240,7 +13240,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13281,7 +13281,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13318,7 +13318,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13341,7 +13341,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13349,7 +13349,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13391,7 +13391,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13452,37 +13452,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H17" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I17" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K17" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H17" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I17" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13530,7 +13530,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13547,7 +13547,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13561,7 +13561,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13569,10 +13569,10 @@
       <c r="C24" s="3">
         <v>9.0</v>
       </c>
-      <c r="D24" s="17">
+      <c r="D24" s="16">
         <v>0.16</v>
       </c>
-      <c r="E24" s="17">
+      <c r="E24" s="16">
         <v>0.11</v>
       </c>
       <c r="F24" s="3">
@@ -13581,16 +13581,16 @@
       <c r="G24" s="3">
         <v>13.0</v>
       </c>
-      <c r="H24" s="17">
+      <c r="H24" s="16">
         <v>0.25</v>
       </c>
-      <c r="I24" s="17">
+      <c r="I24" s="16">
         <v>0.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13725,7 +13725,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13740,7 +13740,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>97</v>
+        <v>57</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13752,7 +13752,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>101</v>
+        <v>62</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13785,7 +13785,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>108</v>
+        <v>68</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13798,7 +13798,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>109</v>
+        <v>70</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13806,7 +13806,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13833,7 +13833,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13845,7 +13845,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13854,7 +13854,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13881,7 +13881,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13893,7 +13893,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>123</v>
+        <v>90</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13902,7 +13902,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>124</v>
+        <v>91</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13910,7 +13910,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13934,7 +13934,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>127</v>
+        <v>93</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13946,7 +13946,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>129</v>
+        <v>96</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13955,7 +13955,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>131</v>
+        <v>99</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13981,7 +13981,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>133</v>
+        <v>103</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13993,7 +13993,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -14002,7 +14002,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14033,7 +14033,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14045,7 +14045,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>140</v>
+        <v>113</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14054,7 +14054,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14071,7 +14071,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14120,40 +14120,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14186,7 +14186,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>146</v>
+        <v>130</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14228,7 +14228,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14275,7 +14275,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14322,7 +14322,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14366,7 +14366,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14404,7 +14404,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14427,37 +14427,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14474,7 +14474,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14491,7 +14491,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14508,17 +14508,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14526,10 +14526,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.27</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.16</v>
       </c>
       <c r="F31" s="3">
@@ -14538,16 +14538,16 @@
       <c r="G31" s="3">
         <v>12.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.32</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14654,7 +14654,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14681,7 +14681,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>76</v>
+        <v>112</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14693,7 +14693,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>79</v>
+        <v>115</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14702,7 +14702,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>82</v>
+        <v>117</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14710,7 +14710,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14737,7 +14737,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14752,7 +14752,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>86</v>
+        <v>122</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14761,7 +14761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14782,7 +14782,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14794,7 +14794,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>89</v>
+        <v>126</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14803,7 +14803,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14811,7 +14811,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14821,7 +14821,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14861,7 +14861,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>98</v>
+        <v>132</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14873,7 +14873,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>100</v>
+        <v>134</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14882,7 +14882,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>102</v>
+        <v>135</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14890,7 +14890,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14917,7 +14917,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14929,7 +14929,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14938,7 +14938,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14974,7 +14974,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14983,7 +14983,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14995,7 +14995,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>113</v>
+        <v>143</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -15004,7 +15004,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15013,7 +15013,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15021,7 +15021,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15036,7 +15036,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>132</v>
+        <v>145</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15045,7 +15045,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15054,7 +15054,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15075,7 +15075,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15088,7 +15088,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15111,7 +15111,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15120,7 +15120,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15129,7 +15129,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15137,7 +15137,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15201,36 +15201,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15263,7 +15263,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15310,7 +15310,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15351,7 +15351,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15398,7 +15398,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15439,7 +15439,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15486,7 +15486,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15506,37 +15506,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K25" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15553,7 +15553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15587,7 +15587,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15604,12 +15604,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15617,10 +15617,10 @@
       <c r="C32" s="3">
         <v>8.0</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>0.19</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>0.14</v>
       </c>
       <c r="F32" s="3">
@@ -15629,16 +15629,16 @@
       <c r="G32" s="3">
         <v>13.0</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>0.22</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <v>0.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15745,7 +15745,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15793,7 +15793,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15842,7 +15842,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15910,7 +15910,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15985,7 +15985,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16089,7 +16089,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16097,7 +16097,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16121,7 +16121,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16139,7 +16139,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16179,36 +16179,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16493,37 +16493,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I23" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K23" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K23" s="15"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16540,7 +16540,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16557,7 +16557,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16574,7 +16574,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16591,7 +16591,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16599,7 +16599,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16607,10 +16607,10 @@
       <c r="C30" s="3">
         <v>23.0</v>
       </c>
-      <c r="D30" s="17">
+      <c r="D30" s="16">
         <v>0.32</v>
       </c>
-      <c r="E30" s="17">
+      <c r="E30" s="16">
         <v>0.22</v>
       </c>
       <c r="F30" s="3">
@@ -16619,16 +16619,16 @@
       <c r="G30" s="3">
         <v>13.0</v>
       </c>
-      <c r="H30" s="17">
+      <c r="H30" s="16">
         <v>0.16</v>
       </c>
-      <c r="I30" s="17">
+      <c r="I30" s="16">
         <v>0.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16735,7 +16735,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16799,7 +16799,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16855,7 +16855,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16867,7 +16867,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16885,7 +16885,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16893,7 +16893,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16947,7 +16947,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>90</v>
+        <v>127</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16955,7 +16955,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16993,7 +16993,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17068,7 +17068,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17077,7 +17077,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17101,7 +17101,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17110,7 +17110,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17131,7 +17131,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17143,7 +17143,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17152,7 +17152,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17194,7 +17194,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17202,7 +17202,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17229,7 +17229,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
@@ -17261,36 +17261,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17320,7 +17320,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17367,7 +17367,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17411,7 +17411,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17458,7 +17458,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17505,7 +17505,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17552,7 +17552,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17575,37 +17575,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K25" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17622,7 +17622,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17639,7 +17639,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17656,7 +17656,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17667,12 +17667,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17680,10 +17680,10 @@
       <c r="C32" s="3">
         <v>13.0</v>
       </c>
-      <c r="D32" s="17">
+      <c r="D32" s="16">
         <v>0.21</v>
       </c>
-      <c r="E32" s="17">
+      <c r="E32" s="16">
         <v>0.18</v>
       </c>
       <c r="F32" s="3">
@@ -17692,16 +17692,16 @@
       <c r="G32" s="3">
         <v>12.0</v>
       </c>
-      <c r="H32" s="17">
+      <c r="H32" s="16">
         <v>0.31</v>
       </c>
-      <c r="I32" s="17">
+      <c r="I32" s="16">
         <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17808,7 +17808,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17832,7 +17832,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17844,7 +17844,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17853,7 +17853,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17861,7 +17861,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17882,7 +17882,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17892,7 +17892,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17900,7 +17900,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17927,7 +17927,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17936,7 +17936,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17945,7 +17945,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17953,7 +17953,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17977,7 +17977,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -18001,7 +18001,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -18019,7 +18019,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -18040,7 +18040,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -18048,7 +18048,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18064,7 +18064,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -18073,7 +18073,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -18100,7 +18100,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18122,7 +18122,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18169,36 +18169,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18286,7 +18286,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="13">
+      <c r="R17" s="17">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18457,37 +18457,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18516,7 +18516,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18524,10 +18524,10 @@
       <c r="C26" s="3">
         <v>5.0</v>
       </c>
-      <c r="D26" s="17">
+      <c r="D26" s="16">
         <v>0.16</v>
       </c>
-      <c r="E26" s="17">
+      <c r="E26" s="16">
         <v>0.2</v>
       </c>
       <c r="F26" s="3">
@@ -18545,22 +18545,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18571,7 +18571,7 @@
       <c r="D31" s="24">
         <v>0.14286</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.14286</v>
       </c>
       <c r="F31" s="3">
@@ -18580,16 +18580,16 @@
       <c r="G31" s="3">
         <v>9.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.1212</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.2727</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18696,7 +18696,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18755,7 +18755,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18811,7 +18811,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18845,7 +18845,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18886,7 +18886,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18939,7 +18939,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -19002,7 +19002,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -19059,7 +19059,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19067,7 +19067,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19155,36 +19155,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19445,38 +19445,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19484,7 +19484,7 @@
       <c r="D25" s="24">
         <v>0.0769</v>
       </c>
-      <c r="E25" s="17">
+      <c r="E25" s="16">
         <v>0.0</v>
       </c>
       <c r="F25" s="3">
@@ -19493,17 +19493,17 @@
       <c r="G25" s="3">
         <v>3.0</v>
       </c>
-      <c r="H25" s="17">
+      <c r="H25" s="16">
         <v>0.2</v>
       </c>
-      <c r="I25" s="17">
+      <c r="I25" s="16">
         <v>0.12</v>
       </c>
       <c r="L25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19533,7 +19533,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19544,7 +19544,7 @@
       <c r="D27" s="24">
         <v>0.125</v>
       </c>
-      <c r="E27" s="17">
+      <c r="E27" s="16">
         <v>0.25</v>
       </c>
       <c r="F27" s="3">
@@ -19553,26 +19553,26 @@
       <c r="G27" s="3">
         <v>2.0</v>
       </c>
-      <c r="H27" s="17">
+      <c r="H27" s="16">
         <v>0.24</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="16">
         <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19580,10 +19580,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.15</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.22</v>
       </c>
       <c r="F31" s="3">
@@ -19592,16 +19592,16 @@
       <c r="G31" s="3">
         <v>10.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.18</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19708,7 +19708,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19747,7 +19747,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19856,7 +19856,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19907,7 +19907,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19915,7 +19915,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19972,7 +19972,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19980,7 +19980,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -20072,7 +20072,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>95</v>
+        <v>64</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20153,36 +20153,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20470,37 +20470,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="K24" s="16"/>
+        <v>101</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="14" t="s">
+        <v>104</v>
+      </c>
+      <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20517,7 +20517,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20534,7 +20534,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20551,7 +20551,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>126</v>
+        <v>111</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20568,7 +20568,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20585,7 +20585,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>130</v>
+        <v>116</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20593,10 +20593,10 @@
       <c r="C31" s="3">
         <v>19.0</v>
       </c>
-      <c r="D31" s="17">
+      <c r="D31" s="16">
         <v>0.19</v>
       </c>
-      <c r="E31" s="17">
+      <c r="E31" s="16">
         <v>0.19</v>
       </c>
       <c r="F31" s="3">
@@ -20605,16 +20605,16 @@
       <c r="G31" s="3">
         <v>23.0</v>
       </c>
-      <c r="H31" s="17">
+      <c r="H31" s="16">
         <v>0.16</v>
       </c>
-      <c r="I31" s="17">
+      <c r="I31" s="16">
         <v>0.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -100,91 +100,163 @@
     <t>Cora</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - </t>
+  </si>
+  <si>
+    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+  </si>
+  <si>
     <t>Shiloh</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - </t>
-  </si>
-  <si>
-    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Addy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Kinley</t>
+  </si>
+  <si>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+    <t>Audri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
-  </si>
-  <si>
-    <t>Addy</t>
+    <t>3 - 0 - 1</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nataly </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Kinley</t>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+    <t>1 - 1 - 1 - 0 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>Agnes</t>
-  </si>
-  <si>
-    <t>Audri</t>
-  </si>
-  <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
   </si>
   <si>
-    <t>3 - 0 - 1</t>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
+    <t>Gaby</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t>Corena</t>
+    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - </t>
   </si>
   <si>
-    <t>Annabelle</t>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
@@ -193,202 +265,193 @@
     <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+  </si>
+  <si>
+    <t>Emma</t>
+  </si>
+  <si>
     <t>Bridget</t>
   </si>
   <si>
-    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Piper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
     <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
+    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - </t>
+  </si>
+  <si>
+    <t>Rotation (follow setter starting position)</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
+    <t>Tea</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t>Nataly</t>
+    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - </t>
+    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
+  </si>
+  <si>
+    <t>Serve Errors</t>
+  </si>
+  <si>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - </t>
   </si>
   <si>
-    <t>Kill Efficiency</t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+    <t xml:space="preserve">5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - </t>
   </si>
   <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
-  </si>
-  <si>
-    <t>Serve Receive Avg Score</t>
-  </si>
-  <si>
-    <t>Serve Aces</t>
-  </si>
-  <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Gaby</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
-  </si>
-  <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>Team</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
     <t>Total Aces (us)</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - </t>
+  </si>
+  <si>
     <t>Service error (us)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
     <t>Ace % (us)</t>
   </si>
   <si>
     <t>Service Error % (us)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - </t>
-  </si>
-  <si>
     <t>Aces (them)</t>
   </si>
   <si>
     <t>Service Errors (them)</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t>Ace % (them)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
     <t>Service Error % (Them)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
     <t>Set 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - </t>
-  </si>
-  <si>
     <t>Set 2</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>Set 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t>Set 3</t>
-  </si>
-  <si>
     <t>Set 4</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
   </si>
   <si>
     <t>Set 5</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
   </si>
   <si>
     <t>Team Passer Rating (all games)</t>
@@ -397,25 +460,31 @@
     <t>Team Kill Efficiency (all games)</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - </t>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
@@ -424,78 +493,9 @@
     <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Tea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -541,51 +541,51 @@
     <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
   </si>
   <si>
@@ -613,6 +613,24 @@
     <t xml:space="preserve">1 - 0 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
   </si>
   <si>
@@ -625,9 +643,6 @@
     <t>0- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
     <t>2- 2- 3- 3- 2</t>
   </si>
   <si>
@@ -637,39 +652,24 @@
     <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t>2- 3- 2- 2</t>
   </si>
   <si>
     <t>3- 2- 3- 5- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
     <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
     <t>1- 3- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
-  </si>
-  <si>
     <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
   </si>
   <si>
     <t>3- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
@@ -679,48 +679,48 @@
     <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
   </si>
   <si>
+    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
+  </si>
+  <si>
+    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 3- 2- </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 1- 1- </t>
   </si>
   <si>
+    <t>2- 1- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
+  </si>
+  <si>
+    <t>3- 1- 2- 1</t>
+  </si>
+  <si>
     <t>1- 0- 3- 2- 0- 1- 1</t>
   </si>
   <si>
+    <t>3- 1- 5- 2</t>
+  </si>
+  <si>
     <t>0- 1- 3</t>
   </si>
   <si>
+    <t>3- 0</t>
+  </si>
+  <si>
+    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0- 2- 3- </t>
+  </si>
+  <si>
     <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
-    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 3- 2- </t>
-  </si>
-  <si>
-    <t>2- 1- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
-  </si>
-  <si>
-    <t>3- 1- 2- 1</t>
-  </si>
-  <si>
-    <t>3- 1- 5- 2</t>
-  </si>
-  <si>
-    <t>3- 0</t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0- 2- 3- </t>
-  </si>
-  <si>
     <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
   </si>
   <si>
@@ -826,33 +826,33 @@
     <t xml:space="preserve">2 - 3 - 3 - 3 - 1 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 2 - 1 - 2 - 2 - 0 -1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 1 - 1 - 2 - 3 - 2 - 3 - 1 - 2 - 2 - 0 -0 - 1 -2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 0 - 1 - 2 - 0 - 0 - 1 - 0 - 2 - 1 - 2 - 0 - 2 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 3 - 0 - 3 - 2 - 3 - 1 - 0 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 0 - 1 - 2 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 2 - 1 - 2 - 2 - 0 -1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 1 - 2 - 0 - 0 - 1 - 0 - 2 - 1 - 2 - 0 - 2 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
   </si>
   <si>
@@ -883,30 +883,30 @@
     <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 2 - 1 - 2 - 2 - 2 - 1 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 1 - 0 - 1 - 0 - 0 - 2 - 1 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 0 - 0 - 1 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 2 - 2 - 2 - 2 - 3 - 2 - 2 - 0 - 3 - 3 - 2 - 5 - 2 - 5 - 5 - 3 - 3 - 5 - 3 - 3 - 3 - 1 - </t>
   </si>
   <si>
@@ -931,18 +931,42 @@
     <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
   </si>
   <si>
@@ -967,9 +991,6 @@
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
   </si>
   <si>
@@ -979,39 +1000,18 @@
     <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
@@ -1054,13 +1054,40 @@
     <t xml:space="preserve">1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
@@ -1069,6 +1096,9 @@
     <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1078,18 +1108,12 @@
     <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
+    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
   </si>
   <si>
@@ -1105,33 +1129,51 @@
     <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>119 attack attempts</t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1141,9 +1183,6 @@
     <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
   </si>
   <si>
@@ -1153,72 +1192,33 @@
     <t xml:space="preserve">2 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>119 attack attempts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1264,7 +1264,7 @@
     <t xml:space="preserve">0 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - </t>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 2 - 3 - </t>
@@ -2009,7 +2009,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2021,7 +2021,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2057,7 +2057,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2069,7 +2069,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2096,7 +2096,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2141,7 +2141,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2174,7 +2174,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2183,7 +2183,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2192,7 +2192,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2204,7 +2204,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2216,7 +2216,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2225,7 +2225,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2265,7 +2265,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2280,7 +2280,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2316,7 +2316,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2325,7 +2325,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2412,40 +2412,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2485,37 +2485,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2628,12 +2628,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2662,10 +2662,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
     </row>
     <row r="34">
@@ -2774,7 +2774,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2795,7 +2795,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="L2" s="3">
         <v>1.56</v>
@@ -2807,7 +2807,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="R2" s="3">
         <v>1.06</v>
@@ -2816,7 +2816,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2839,7 +2839,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -2851,7 +2851,7 @@
         <v>12.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2887,7 +2887,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="L4" s="3">
         <v>2.2</v>
@@ -2900,7 +2900,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2956,7 +2956,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -3056,7 +3056,7 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3118,7 +3118,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3130,7 +3130,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3143,7 +3143,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3152,7 +3152,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3193,36 +3193,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3340,7 +3340,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M18" s="3">
         <v>1.2</v>
@@ -3384,7 +3384,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -3425,7 +3425,7 @@
         <v>2.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -3469,7 +3469,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="M21" s="3">
         <v>0.9</v>
@@ -3492,37 +3492,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3570,17 +3570,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3609,7 +3609,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3740,7 +3740,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="L2" s="3">
         <v>2.33</v>
@@ -3752,7 +3752,7 @@
         <v>8.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -3761,7 +3761,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3799,7 +3799,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="L3" s="3">
         <v>3.08</v>
@@ -3811,7 +3811,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3820,7 +3820,7 @@
         <v>7.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="U3" s="3">
         <v>2.71</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3966,7 +3966,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3974,7 +3974,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -4007,7 +4007,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4016,7 +4016,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4046,7 +4046,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4072,7 +4072,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4082,7 +4082,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4105,7 +4105,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4115,7 +4115,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4133,7 +4133,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4163,7 +4163,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4190,7 +4190,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4202,7 +4202,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4223,7 +4223,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4247,7 +4247,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4257,7 +4257,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>318</v>
+        <v>303</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4282,36 +4282,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4344,7 +4344,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4391,7 +4391,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4435,7 +4435,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4479,7 +4479,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>323</v>
+        <v>307</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -4526,7 +4526,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4593,37 +4593,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4674,17 +4674,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4713,7 +4713,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4848,7 +4848,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4892,7 +4892,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4904,7 +4904,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4913,7 +4913,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4948,7 +4948,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4960,7 +4960,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4969,7 +4969,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5004,7 +5004,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5016,7 +5016,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5025,7 +5025,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5045,7 +5045,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5057,7 +5057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5114,7 +5114,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5126,7 +5126,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5134,7 +5134,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5154,7 +5154,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -5162,7 +5162,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5189,7 +5189,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5230,36 +5230,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5292,7 +5292,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5339,7 +5339,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5541,37 +5541,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5651,12 +5651,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5691,7 +5691,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5975,7 +5975,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -6006,7 +6006,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6028,7 +6028,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6065,7 +6065,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6079,7 +6079,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6088,7 +6088,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6122,7 +6122,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6131,7 +6131,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6140,7 +6140,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6174,7 +6174,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6201,7 +6201,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>357</v>
+        <v>345</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -6214,7 +6214,7 @@
         <v>7.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>358</v>
+        <v>346</v>
       </c>
       <c r="U10" s="3">
         <v>2.14</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6266,36 +6266,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6328,7 +6328,7 @@
         <v>6.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>373</v>
+        <v>347</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -6375,7 +6375,7 @@
         <v>14.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>376</v>
+        <v>348</v>
       </c>
       <c r="M17" s="3">
         <v>1.79</v>
@@ -6422,7 +6422,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>380</v>
+        <v>349</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6469,7 +6469,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>391</v>
+        <v>351</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6516,7 +6516,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>393</v>
+        <v>354</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6563,7 +6563,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>394</v>
+        <v>358</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6586,37 +6586,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6633,7 +6633,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6730,7 +6730,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6855,7 +6855,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6898,7 +6898,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6910,7 +6910,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6919,7 +6919,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6939,7 +6939,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6948,7 +6948,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6957,7 +6957,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -6989,7 +6989,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="L5" s="3">
         <v>2.75</v>
@@ -7001,7 +7001,7 @@
         <v>16.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -7010,7 +7010,7 @@
         <v>13.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="U5" s="3">
         <v>2.15</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7048,7 +7048,7 @@
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -7063,7 +7063,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -7072,7 +7072,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7102,7 +7102,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7111,7 +7111,7 @@
         <v>7.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="U7" s="3">
         <v>1.86</v>
@@ -7119,7 +7119,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7143,7 +7143,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="L8" s="3">
         <v>1.67</v>
@@ -7163,7 +7163,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7187,7 +7187,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="L9" s="3">
         <v>2.56</v>
@@ -7196,7 +7196,7 @@
         <v>12.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="R9" s="3">
         <v>1.67</v>
@@ -7205,7 +7205,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -7240,7 +7240,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7288,7 +7288,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7324,36 +7324,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7386,7 +7386,7 @@
         <v>12.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -7430,7 +7430,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="M17" s="3">
         <v>2.55</v>
@@ -7477,7 +7477,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>383</v>
+        <v>372</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7524,7 +7524,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>385</v>
+        <v>373</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7571,7 +7571,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>386</v>
+        <v>374</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7615,7 +7615,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>388</v>
+        <v>375</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7638,37 +7638,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7736,12 +7736,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7770,7 +7770,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7779,7 +7779,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>392</v>
+        <v>376</v>
       </c>
     </row>
   </sheetData>
@@ -7880,7 +7880,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7907,7 +7907,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7925,7 +7925,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>362</v>
+        <v>378</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7934,7 +7934,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7955,7 +7955,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7995,7 +7995,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>366</v>
+        <v>380</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8007,7 +8007,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>367</v>
+        <v>381</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8016,7 +8016,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>368</v>
+        <v>382</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8024,7 +8024,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8045,7 +8045,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>370</v>
+        <v>383</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8057,7 +8057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>371</v>
+        <v>384</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8066,7 +8066,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>372</v>
+        <v>385</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8074,7 +8074,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8097,7 +8097,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8117,7 +8117,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8126,7 +8126,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8135,7 +8135,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8164,7 +8164,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8200,7 +8200,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8213,7 +8213,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8265,7 +8265,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8298,7 +8298,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8310,7 +8310,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8328,37 +8328,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8375,7 +8375,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8392,7 +8392,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8409,7 +8409,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8426,7 +8426,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8472,7 +8472,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8579,7 +8579,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8632,7 +8632,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8665,7 +8665,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8712,7 +8712,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8749,7 +8749,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8789,7 +8789,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8797,7 +8797,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8845,7 +8845,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8874,7 +8874,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8894,14 +8894,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8930,7 +8930,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8945,37 +8945,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9026,17 +9026,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9065,7 +9065,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9227,7 +9227,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9243,36 +9243,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9318,62 +9318,62 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
@@ -9382,7 +9382,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9483,7 +9483,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -9534,7 +9534,7 @@
         <v>409</v>
       </c>
       <c r="P3" s="3">
-        <v>16.0</v>
+        <v>17.0</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>410</v>
@@ -9548,16 +9548,16 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
       </c>
       <c r="D4" s="3">
-        <v>15.0</v>
+        <v>16.0</v>
       </c>
       <c r="E4" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="F4" s="3">
         <v>6.0</v>
@@ -9589,10 +9589,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B5" s="3">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="C5" s="3">
         <v>9.0</v>
@@ -9622,7 +9622,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -9656,7 +9656,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -9719,10 +9719,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D9" s="3">
-        <v>7.0</v>
+        <v>8.0</v>
       </c>
       <c r="E9" s="3">
         <v>1.0</v>
@@ -9734,7 +9734,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M9" s="3">
         <v>1.0</v>
@@ -9744,7 +9744,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -9758,13 +9758,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c r="T11" s="5"/>
     </row>
@@ -9779,37 +9779,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9826,7 +9826,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -9843,7 +9843,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -9860,17 +9860,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
@@ -9879,7 +9879,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9981,7 +9981,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -10040,7 +10040,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10083,7 +10083,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -10101,7 +10101,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10114,7 +10114,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10122,7 +10122,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10181,7 +10181,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10223,7 +10223,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10256,7 +10256,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10315,7 +10315,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10337,7 +10337,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10380,37 +10380,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10427,7 +10427,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10444,7 +10444,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10461,7 +10461,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10478,12 +10478,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10512,7 +10512,7 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10619,7 +10619,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10643,7 +10643,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10655,7 +10655,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10664,7 +10664,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10672,7 +10672,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10690,7 +10690,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>34</v>
+        <v>53</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10703,7 +10703,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10711,7 +10711,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10738,7 +10738,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10750,7 +10750,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>43</v>
+        <v>66</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10759,7 +10759,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10767,7 +10767,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10779,7 +10779,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>49</v>
+        <v>72</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10788,7 +10788,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10797,7 +10797,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10805,7 +10805,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10829,7 +10829,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>56</v>
+        <v>84</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10841,7 +10841,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10850,7 +10850,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10858,7 +10858,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10885,7 +10885,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10922,7 +10922,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10931,7 +10931,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10949,7 +10949,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10962,7 +10962,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10970,7 +10970,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10984,7 +10984,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10999,7 +10999,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -11008,13 +11008,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -11029,7 +11029,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -11045,40 +11045,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11111,7 +11111,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>109</v>
+        <v>134</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11159,7 +11159,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11206,7 +11206,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>125</v>
+        <v>149</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11253,7 +11253,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>128</v>
+        <v>151</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11300,7 +11300,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>129</v>
+        <v>152</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11344,7 +11344,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11364,37 +11364,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11411,7 +11411,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11428,7 +11428,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11445,7 +11445,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11462,7 +11462,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11479,7 +11479,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11508,7 +11508,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11615,7 +11615,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11668,7 +11668,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11727,7 +11727,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11775,7 +11775,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11834,7 +11834,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11884,7 +11884,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11915,7 +11915,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11923,7 +11923,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11959,7 +11959,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11997,7 +11997,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -12011,7 +12011,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12028,7 +12028,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12040,7 +12040,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12054,37 +12054,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12101,7 +12101,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12118,7 +12118,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12135,7 +12135,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12152,7 +12152,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12169,7 +12169,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12198,7 +12198,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12305,7 +12305,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12338,7 +12338,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12346,7 +12346,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12399,7 +12399,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12438,7 +12438,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12447,7 +12447,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12455,7 +12455,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12514,7 +12514,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12536,7 +12536,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12572,7 +12572,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12581,7 +12581,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12603,7 +12603,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12626,13 +12626,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12641,7 +12641,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12650,7 +12650,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12671,7 +12671,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12710,7 +12710,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12725,7 +12725,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12737,7 +12737,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12773,37 +12773,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12820,7 +12820,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12831,7 +12831,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12848,17 +12848,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12887,7 +12887,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12994,7 +12994,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -13033,7 +13033,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13053,7 +13053,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13103,7 +13103,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13162,7 +13162,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13218,7 +13218,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13240,7 +13240,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13248,7 +13248,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13281,7 +13281,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13318,7 +13318,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13341,7 +13341,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13349,7 +13349,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13373,7 +13373,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13391,7 +13391,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13452,37 +13452,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13499,7 +13499,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13516,7 +13516,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13530,7 +13530,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13547,7 +13547,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13561,7 +13561,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13590,7 +13590,7 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13725,7 +13725,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13740,7 +13740,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>57</v>
+        <v>37</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13752,7 +13752,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13761,7 +13761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13785,7 +13785,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>68</v>
+        <v>48</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13798,7 +13798,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>70</v>
+        <v>51</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13806,7 +13806,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13833,7 +13833,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>75</v>
+        <v>59</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13845,7 +13845,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>78</v>
+        <v>62</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13854,7 +13854,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13881,7 +13881,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13893,7 +13893,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>90</v>
+        <v>71</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13902,7 +13902,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13910,7 +13910,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13934,7 +13934,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>93</v>
+        <v>80</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13946,7 +13946,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13955,7 +13955,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>99</v>
+        <v>86</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13963,7 +13963,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13981,7 +13981,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13993,7 +13993,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -14002,7 +14002,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14010,7 +14010,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -14024,7 +14024,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14033,7 +14033,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14045,7 +14045,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14054,7 +14054,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14062,7 +14062,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14071,7 +14071,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14083,7 +14083,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14104,7 +14104,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14120,40 +14120,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14186,7 +14186,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14228,7 +14228,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14275,7 +14275,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14322,7 +14322,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14366,7 +14366,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14427,37 +14427,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14474,7 +14474,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14491,7 +14491,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14508,17 +14508,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14547,7 +14547,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14654,7 +14654,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14681,7 +14681,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14693,7 +14693,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>115</v>
+        <v>30</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14702,7 +14702,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>117</v>
+        <v>31</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14710,7 +14710,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14737,7 +14737,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>121</v>
+        <v>40</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14752,7 +14752,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>122</v>
+        <v>43</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14761,7 +14761,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14782,7 +14782,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>124</v>
+        <v>55</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14794,7 +14794,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>126</v>
+        <v>58</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14803,7 +14803,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14811,7 +14811,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14821,7 +14821,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14834,7 +14834,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14861,7 +14861,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14873,7 +14873,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>134</v>
+        <v>81</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14882,7 +14882,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>135</v>
+        <v>85</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14890,7 +14890,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14917,7 +14917,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>138</v>
+        <v>93</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14929,7 +14929,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14938,7 +14938,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14974,7 +14974,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14983,7 +14983,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14995,7 +14995,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>143</v>
+        <v>111</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -15004,7 +15004,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15013,7 +15013,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15021,7 +15021,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15036,7 +15036,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15045,7 +15045,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15054,7 +15054,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15075,7 +15075,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15088,7 +15088,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15111,7 +15111,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15120,7 +15120,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>147</v>
+        <v>125</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15129,7 +15129,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15137,7 +15137,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15149,7 +15149,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15167,7 +15167,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15185,7 +15185,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15201,36 +15201,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15263,7 +15263,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15310,7 +15310,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15351,7 +15351,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15398,7 +15398,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15439,7 +15439,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15486,7 +15486,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15506,37 +15506,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15553,7 +15553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15570,7 +15570,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15587,7 +15587,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15604,12 +15604,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15638,7 +15638,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15745,7 +15745,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15793,7 +15793,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15842,7 +15842,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15910,7 +15910,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15966,7 +15966,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15985,7 +15985,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16053,7 +16053,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16089,7 +16089,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16097,7 +16097,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16121,7 +16121,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16139,7 +16139,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16148,7 +16148,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16163,7 +16163,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16179,36 +16179,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16238,7 +16238,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16285,7 +16285,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -16329,7 +16329,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16376,7 +16376,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16423,7 +16423,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16470,7 +16470,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16493,37 +16493,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K23" s="15"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16540,7 +16540,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16557,7 +16557,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16574,7 +16574,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16591,7 +16591,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16599,7 +16599,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16628,7 +16628,7 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16735,7 +16735,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16759,7 +16759,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>175</v>
+        <v>169</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -16771,7 +16771,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -16780,7 +16780,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -16788,7 +16788,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16799,7 +16799,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16826,7 +16826,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -16838,7 +16838,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -16847,7 +16847,7 @@
         <v>7.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="U4" s="3">
         <v>2.29</v>
@@ -16855,7 +16855,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16867,7 +16867,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16876,7 +16876,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="R5" s="3">
         <v>1.45</v>
@@ -16885,7 +16885,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16893,7 +16893,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16923,7 +16923,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -16938,7 +16938,7 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="R6" s="3">
         <v>0.5</v>
@@ -16947,7 +16947,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>127</v>
+        <v>60</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16955,7 +16955,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16993,7 +16993,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17068,7 +17068,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17077,7 +17077,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17101,7 +17101,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>146</v>
+        <v>119</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17110,7 +17110,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17131,7 +17131,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17143,7 +17143,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17152,7 +17152,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17194,7 +17194,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17202,7 +17202,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17217,7 +17217,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>67</v>
+        <v>82</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17229,7 +17229,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
@@ -17245,7 +17245,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17261,36 +17261,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17320,7 +17320,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17367,7 +17367,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17411,7 +17411,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17458,7 +17458,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17505,7 +17505,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17552,7 +17552,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17575,37 +17575,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17622,7 +17622,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17639,7 +17639,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17656,7 +17656,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17667,12 +17667,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17701,7 +17701,7 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17808,7 +17808,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17832,7 +17832,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17844,7 +17844,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17853,7 +17853,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17861,7 +17861,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17882,7 +17882,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17892,7 +17892,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17900,7 +17900,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17927,7 +17927,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17936,7 +17936,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17945,7 +17945,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17953,7 +17953,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17977,7 +17977,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -18001,7 +18001,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -18019,7 +18019,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -18040,7 +18040,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -18048,7 +18048,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18064,7 +18064,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -18073,7 +18073,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -18100,7 +18100,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18122,7 +18122,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18153,7 +18153,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18169,36 +18169,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18314,7 +18314,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18355,7 +18355,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18390,7 +18390,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18437,7 +18437,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18457,37 +18457,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18516,7 +18516,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18545,22 +18545,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18589,7 +18589,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18696,7 +18696,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18726,7 +18726,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="L2" s="3">
         <v>2.364</v>
@@ -18738,7 +18738,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18747,7 +18747,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18755,7 +18755,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18779,7 +18779,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="L3" s="3">
         <v>2.5</v>
@@ -18794,7 +18794,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18803,7 +18803,7 @@
         <v>4.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="U3" s="3">
         <v>1.75</v>
@@ -18811,7 +18811,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18835,7 +18835,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="L4" s="3">
         <v>2.75</v>
@@ -18845,7 +18845,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18857,7 +18857,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -18869,7 +18869,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="R5" s="3">
         <v>1.176</v>
@@ -18878,7 +18878,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="U5" s="3">
         <v>1.667</v>
@@ -18886,7 +18886,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18939,7 +18939,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -19002,7 +19002,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -19022,7 +19022,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -19059,7 +19059,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19067,7 +19067,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19094,7 +19094,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19112,7 +19112,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19127,7 +19127,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19139,7 +19139,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19155,36 +19155,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19445,38 +19445,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19503,7 +19503,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19533,7 +19533,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19562,17 +19562,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19601,7 +19601,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19708,7 +19708,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19747,7 +19747,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>136</v>
+        <v>89</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19803,7 +19803,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>79</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19856,7 +19856,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19907,7 +19907,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19915,7 +19915,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19972,7 +19972,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>88</v>
+        <v>116</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19980,7 +19980,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -20072,7 +20072,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20137,7 +20137,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20153,36 +20153,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20309,7 +20309,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -20356,7 +20356,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="M19" s="3">
         <v>1.64</v>
@@ -20400,7 +20400,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -20447,7 +20447,7 @@
         <v>9.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="M21" s="3">
         <v>1.67</v>
@@ -20470,37 +20470,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>92</v>
+        <v>117</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>94</v>
+        <v>118</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>95</v>
+        <v>120</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>121</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>98</v>
+        <v>122</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>102</v>
+        <v>127</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>130</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20517,7 +20517,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20534,7 +20534,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>110</v>
+        <v>133</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20551,7 +20551,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>111</v>
+        <v>135</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20568,7 +20568,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>114</v>
+        <v>137</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20585,7 +20585,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>116</v>
+        <v>138</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20614,7 +20614,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1772" uniqueCount="476">
   <si>
     <t>Player</t>
   </si>
@@ -100,369 +100,369 @@
     <t>Cora</t>
   </si>
   <si>
+    <t>Shiloh</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - </t>
   </si>
   <si>
     <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
   </si>
   <si>
-    <t>Shiloh</t>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Addy</t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
+    <t>Kinley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t>Audri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>3 - 0 - 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>1 - 1 - 1 - 0 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - </t>
+  </si>
+  <si>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t>Addy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t>Gaby</t>
+  </si>
+  <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+  </si>
+  <si>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
   </si>
   <si>
+    <t>Elena</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
-    <t>Kinley</t>
-  </si>
-  <si>
-    <t>Annabelle</t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Audri</t>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - </t>
+  </si>
+  <si>
+    <t>Emma</t>
   </si>
   <si>
     <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Nataly</t>
+    <t>Piper</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>3 - 0 - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nataly </t>
-  </si>
-  <si>
-    <t>Agnes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
+    <t xml:space="preserve">5 - 3 - </t>
+  </si>
+  <si>
+    <t>Rotation (follow setter starting position)</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - </t>
   </si>
   <si>
-    <t>Corena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
+    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+    <t>Kill Efficiency</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - </t>
   </si>
   <si>
-    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
-  </si>
-  <si>
-    <t>Gaby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - </t>
-  </si>
-  <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+  </si>
+  <si>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - </t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
+  </si>
+  <si>
+    <t>Serve Errors</t>
+  </si>
+  <si>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
   </si>
   <si>
     <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
   </si>
   <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>Bridget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - </t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
-  </si>
-  <si>
     <t>Tea</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Kill Efficiency</t>
+    <t xml:space="preserve">3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
-  </si>
-  <si>
-    <t>Serve Receive Avg Score</t>
-  </si>
-  <si>
-    <t>Serve Aces</t>
-  </si>
-  <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
-  </si>
-  <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - </t>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
+  </si>
+  <si>
+    <t>Service error (us)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>Service Errors (them)</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
   </si>
   <si>
+    <t>Ace % (them)</t>
+  </si>
+  <si>
+    <t>Service Error % (Them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
+    <t>Set 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
+  </si>
+  <si>
+    <t>Set 2</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - </t>
   </si>
   <si>
-    <t>Service error (us)</t>
-  </si>
-  <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
-  </si>
-  <si>
-    <t>Aces (them)</t>
-  </si>
-  <si>
-    <t>Service Errors (them)</t>
+    <t>Set 3</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Ace % (them)</t>
-  </si>
-  <si>
-    <t>Service Error % (Them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t>Set 1</t>
-  </si>
-  <si>
-    <t>Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t>Set 3</t>
+    <t>Set 4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
+  </si>
+  <si>
+    <t>Set 5</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t>Team Passer Rating (all games)</t>
+  </si>
+  <si>
+    <t>Team Kill Efficiency (all games)</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 5</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t>Team Passer Rating (all games)</t>
-  </si>
-  <si>
-    <t>Team Kill Efficiency (all games)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
   </si>
   <si>
@@ -475,18 +475,18 @@
     <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
@@ -538,147 +538,159 @@
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 3 - 3 - 2 - 0 - 1 - 0 - 2 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 3 - 2 - 1 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
+  </si>
+  <si>
+    <t>2- 1- 0- 3- 1</t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t>0- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
+  </si>
+  <si>
+    <t>2- 3- 2- 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>3- 2- 3- 5- 3</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+    <t xml:space="preserve">1 - 0 - </t>
+  </si>
+  <si>
+    <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
+    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t>1- 3- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>3- 3- 3- 2</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - </t>
+    <t>2- 0- 3- 2- 1- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
   </si>
   <si>
+    <t>1- 3- 0- 3- 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2- 1- 1- </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t>1- 0- 3- 2- 0- 1- 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
   </si>
   <si>
+    <t>0- 1- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
   </si>
   <si>
+    <t>2- 1- 2- 1- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
-  </si>
-  <si>
-    <t>2- 1- 0- 3- 1</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
-  </si>
-  <si>
-    <t>0- 0</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2</t>
-  </si>
-  <si>
-    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>2- 3- 2- 2</t>
-  </si>
-  <si>
-    <t>3- 2- 3- 5- 3</t>
-  </si>
-  <si>
-    <t>1- 2- 2- 3- 1- 1- 0</t>
-  </si>
-  <si>
-    <t>1- 3- 0</t>
-  </si>
-  <si>
-    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
-  </si>
-  <si>
-    <t>3- 3- 3- 2</t>
-  </si>
-  <si>
-    <t>2- 0- 3- 2- 1- 3</t>
-  </si>
-  <si>
-    <t>1- 3- 0- 3- 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
-  </si>
-  <si>
     <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
   </si>
   <si>
@@ -688,9 +700,6 @@
     <t xml:space="preserve">3- 3- 2- </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 1- 1- </t>
-  </si>
-  <si>
     <t>2- 1- 2- 0- 0</t>
   </si>
   <si>
@@ -700,15 +709,9 @@
     <t>3- 1- 2- 1</t>
   </si>
   <si>
-    <t>1- 0- 3- 2- 0- 1- 1</t>
-  </si>
-  <si>
     <t>3- 1- 5- 2</t>
   </si>
   <si>
-    <t>0- 1- 3</t>
-  </si>
-  <si>
     <t>3- 0</t>
   </si>
   <si>
@@ -718,9 +721,6 @@
     <t xml:space="preserve">0- 2- 3- </t>
   </si>
   <si>
-    <t>2- 1- 2- 1- 2</t>
-  </si>
-  <si>
     <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
   </si>
   <si>
@@ -826,10 +826,25 @@
     <t xml:space="preserve">2 - 3 - 3 - 3 - 1 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 1 - 1 - 2 - 3 - 2 - 3 - 1 - 2 - 2 - 0 -0 - 1 -2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 0 - 3 - 2 - 3 - 1 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 0 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 2 - 1 - 2 - 2 - 0 -1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 1 - 1 - 2 - 3 - 2 - 3 - 1 - 2 - 2 - 0 -0 - 1 -2 - 2 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 1 - 2 - 0 - 0 - 1 - 0 - 2 - 1 - 2 - 0 - 2 - 1 - 1 - 2 - </t>
@@ -838,19 +853,25 @@
     <t xml:space="preserve">2 - 5 - 3 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 3 - 0 - 3 - 2 - 3 - 1 - 0 - 3 - 1 - </t>
+    <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 0 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 3 - 1 - 1 - 2 - </t>
+    <t xml:space="preserve">2 - 2 - 2 - 2 - 2 - 3 - 2 - 2 - 0 - 3 - 3 - 2 - 5 - 2 - 5 - 5 - 3 - 3 - 5 - 3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
@@ -859,6 +880,9 @@
     <t xml:space="preserve">1 - 0 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 5 - 0 - 0 - 2 - 2 - 5 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 2 - 3 - 5 - 2 - 3 - 5 - 1 - 1 - </t>
   </si>
   <si>
@@ -868,6 +892,15 @@
     <t xml:space="preserve">3 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 1 - 2 - 3 - 1 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>5 - 2 - 3 - 0 -</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 1 - 1 - 3 - 1 - 3 - 3 - 0 - </t>
   </si>
   <si>
@@ -877,78 +910,45 @@
     <t xml:space="preserve">3 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 2 - 1 - 2 - 2 - 2 - 1 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 1 - 0 - 1 - 0 - 0 - 2 - 1 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 2 - 2 - 3 - 2 - 3 - 3 - </t>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 0 - 0 - 1 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 2 - 2 - 2 - 2 - 3 - 2 - 2 - 0 - 3 - 3 - 2 - 5 - 2 - 5 - 5 - 3 - 3 - 5 - 3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 1 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 0 - 0 - 2 - 2 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 1 - 2 - 3 - 1 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>5 - 2 - 3 - 0 -</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
   </si>
   <si>
@@ -973,45 +973,90 @@
     <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1- 1 - 2 - 1 - 1 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 2- 2- 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2- 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
@@ -1021,60 +1066,15 @@
     <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 1 - 2 - 3 - 3 - 0 - 1 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 2 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 5 - 1 - 5 - 5 - 3 - 3 - 2 - 0 - 1 - 0 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
   </si>
   <si>
@@ -1084,21 +1084,24 @@
     <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 3 - 2 - 3 - 3 - 1 - 3 - 3 - 1 - 1 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1108,9 +1111,6 @@
     <t xml:space="preserve">3 - 2 - 1 - 2 - 1 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
@@ -1123,30 +1123,84 @@
     <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 1 - 1 - 2 - 0 - 2 - 3 - 2 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 2 - 3 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 5 - 3 - 0 - 5 - 2 - 5 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
@@ -1165,60 +1219,6 @@
     <t>119 attack attempts</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1258,19 +1258,19 @@
     <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - 0 - </t>
+    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - 0 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - 3 - </t>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - 5 - 5 - 2 - 3 - </t>
+    <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - 5 - 5 - 2 - 3 - 1 - 3 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - 2 - 3 - 2 - </t>
@@ -1282,30 +1282,30 @@
     <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - 0 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 2 - </t>
+    <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 2 - 0 - 2 - 0 - 1 - 1 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 1 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - 1 - 3 - 3 - 5 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 5 - 5 - 3- 5 - 3 - 0 - 2 - 0- 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - 1 - 5 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 2 - 0 - 2 - 0 - 1 - 1 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 5 - 3- 5 - 3 - 0 - 2 - 0- 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 0 - 5 - 1 - 3 - 5 - 5 - 3 - 2 - 3 - 3 - 3 - 1 - 5 - 1 - 5 - 0 - 1 - 2 - </t>
   </si>
   <si>
@@ -1333,10 +1333,10 @@
     <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
@@ -1576,10 +1576,10 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
@@ -2009,7 +2009,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2021,7 +2021,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2030,7 +2030,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2057,7 +2057,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2069,7 +2069,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2078,7 +2078,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2096,7 +2096,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2111,7 +2111,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2132,7 +2132,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2141,7 +2141,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2174,7 +2174,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2183,7 +2183,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2204,7 +2204,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2216,7 +2216,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2238,7 +2238,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2280,7 +2280,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2289,7 +2289,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2316,7 +2316,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2325,7 +2325,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2334,7 +2334,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2373,7 +2373,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2394,7 +2394,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2415,37 +2415,37 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2485,31 +2485,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -2544,7 +2544,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2570,7 +2570,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2599,7 +2599,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2628,12 +2628,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2774,7 +2774,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2795,7 +2795,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="L2" s="3">
         <v>1.56</v>
@@ -2807,7 +2807,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="R2" s="3">
         <v>1.06</v>
@@ -2816,7 +2816,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2824,7 +2824,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2839,7 +2839,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -2851,7 +2851,7 @@
         <v>12.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -2860,7 +2860,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2887,7 +2887,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="L4" s="3">
         <v>2.2</v>
@@ -2900,7 +2900,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2908,7 +2908,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2935,7 +2935,7 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>273</v>
+        <v>280</v>
       </c>
       <c r="L5" s="3">
         <v>2.33</v>
@@ -2947,7 +2947,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>274</v>
+        <v>281</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -2956,7 +2956,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2964,7 +2964,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -2991,7 +2991,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="L6" s="3">
         <v>2.3</v>
@@ -3003,7 +3003,7 @@
         <v>15.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="R6" s="3">
         <v>1.53</v>
@@ -3012,7 +3012,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="U6" s="3">
         <v>2.67</v>
@@ -3041,7 +3041,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3056,7 +3056,7 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -3065,7 +3065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3089,7 +3089,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>278</v>
+        <v>289</v>
       </c>
       <c r="L8" s="3">
         <v>1.89</v>
@@ -3101,7 +3101,7 @@
         <v>6.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>279</v>
+        <v>290</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -3110,7 +3110,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -3130,7 +3130,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3152,7 +3152,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3177,7 +3177,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3196,33 +3196,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3255,7 +3255,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -3302,7 +3302,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="M17" s="3">
         <v>1.18</v>
@@ -3340,7 +3340,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="M18" s="3">
         <v>1.2</v>
@@ -3384,7 +3384,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -3425,7 +3425,7 @@
         <v>2.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -3469,7 +3469,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="M21" s="3">
         <v>0.9</v>
@@ -3492,31 +3492,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -3536,7 +3536,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3553,7 +3553,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3570,17 +3570,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3740,7 +3740,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="L2" s="3">
         <v>2.33</v>
@@ -3752,7 +3752,7 @@
         <v>8.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -3761,7 +3761,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3769,7 +3769,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3799,7 +3799,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>287</v>
+        <v>273</v>
       </c>
       <c r="L3" s="3">
         <v>3.08</v>
@@ -3811,7 +3811,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3820,7 +3820,7 @@
         <v>7.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="U3" s="3">
         <v>2.71</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3858,7 +3858,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="L4" s="3">
         <v>2.78</v>
@@ -3870,7 +3870,7 @@
         <v>8.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>292</v>
+        <v>278</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -3879,7 +3879,7 @@
         <v>13.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>293</v>
+        <v>279</v>
       </c>
       <c r="U4" s="3">
         <v>2.31</v>
@@ -3887,7 +3887,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3914,7 +3914,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>294</v>
+        <v>282</v>
       </c>
       <c r="L5" s="3">
         <v>2.36</v>
@@ -3926,7 +3926,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -3935,7 +3935,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -3943,7 +3943,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3966,7 +3966,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3998,7 +3998,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="L7" s="3">
         <v>2.0</v>
@@ -4007,7 +4007,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4016,7 +4016,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4024,7 +4024,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4037,7 +4037,7 @@
         <v>7.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="R8" s="3">
         <v>2.29</v>
@@ -4046,7 +4046,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4072,7 +4072,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4082,7 +4082,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4105,7 +4105,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4115,7 +4115,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4133,7 +4133,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4142,7 +4142,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4163,7 +4163,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4172,7 +4172,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4190,7 +4190,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4223,7 +4223,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4235,7 +4235,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4247,7 +4247,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4257,7 +4257,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4266,7 +4266,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4285,33 +4285,33 @@
         <v>92</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="O16" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="Q16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="R16" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4344,7 +4344,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4570,7 +4570,7 @@
         <v>7.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="M22" s="3">
         <v>2.29</v>
@@ -4593,31 +4593,31 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H25" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K25" s="15"/>
     </row>
@@ -4640,7 +4640,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4657,7 +4657,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4674,17 +4674,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4720,7 +4720,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18"/>
+      <c r="A35" s="17"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -4865,7 +4865,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4948,7 +4948,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4960,7 +4960,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4969,7 +4969,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4977,7 +4977,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5004,7 +5004,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5016,7 +5016,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5025,7 +5025,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5033,7 +5033,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5045,7 +5045,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5057,7 +5057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5066,7 +5066,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5081,7 +5081,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5114,7 +5114,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5126,7 +5126,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5154,7 +5154,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -5189,7 +5189,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5233,33 +5233,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5292,7 +5292,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5339,7 +5339,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5386,7 +5386,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5430,7 +5430,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5474,7 +5474,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5518,7 +5518,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5541,31 +5541,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="7"/>
     </row>
@@ -5600,7 +5600,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5617,7 +5617,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5634,7 +5634,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5651,12 +5651,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5798,7 +5798,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5825,7 +5825,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>330</v>
+        <v>313</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5837,7 +5837,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>331</v>
+        <v>314</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5846,7 +5846,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>332</v>
+        <v>317</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5854,7 +5854,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5884,7 +5884,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>333</v>
+        <v>320</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5896,7 +5896,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>334</v>
+        <v>322</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5905,7 +5905,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>335</v>
+        <v>324</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5913,7 +5913,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5943,7 +5943,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5958,7 +5958,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5967,7 +5967,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5998,7 +5998,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -6028,7 +6028,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6045,7 +6045,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6065,7 +6065,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6079,7 +6079,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6088,7 +6088,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6107,7 +6107,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6122,7 +6122,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6131,7 +6131,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6140,7 +6140,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6174,7 +6174,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6201,7 +6201,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -6214,7 +6214,7 @@
         <v>7.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="U10" s="3">
         <v>2.14</v>
@@ -6222,7 +6222,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6250,7 +6250,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6269,33 +6269,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6469,7 +6469,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6516,7 +6516,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6563,7 +6563,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6586,31 +6586,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -6633,7 +6633,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6650,7 +6650,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6667,7 +6667,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6684,7 +6684,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6701,7 +6701,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6837,7 +6837,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6855,7 +6855,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6868,7 +6868,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6898,7 +6898,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6910,7 +6910,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6919,7 +6919,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6927,7 +6927,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6939,7 +6939,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6948,7 +6948,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6965,7 +6965,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -7018,7 +7018,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7048,7 +7048,7 @@
         <v>5.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -7063,7 +7063,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -7072,7 +7072,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7080,7 +7080,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7102,7 +7102,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7111,7 +7111,7 @@
         <v>7.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="U7" s="3">
         <v>1.86</v>
@@ -7143,7 +7143,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="L8" s="3">
         <v>1.67</v>
@@ -7155,7 +7155,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>280</v>
+        <v>291</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -7163,7 +7163,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7187,7 +7187,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>367</v>
+        <v>374</v>
       </c>
       <c r="L9" s="3">
         <v>2.56</v>
@@ -7196,7 +7196,7 @@
         <v>12.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>368</v>
+        <v>375</v>
       </c>
       <c r="R9" s="3">
         <v>1.67</v>
@@ -7205,7 +7205,7 @@
         <v>2.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -7240,7 +7240,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7264,7 +7264,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="L11" s="3">
         <v>2.45</v>
@@ -7273,7 +7273,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7297,7 +7297,7 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="U13" s="3">
         <v>1.5</v>
@@ -7308,7 +7308,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7327,33 +7327,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7386,7 +7386,7 @@
         <v>12.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>370</v>
+        <v>386</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -7430,7 +7430,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>371</v>
+        <v>389</v>
       </c>
       <c r="M17" s="3">
         <v>2.55</v>
@@ -7477,7 +7477,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>372</v>
+        <v>390</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7524,7 +7524,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>373</v>
+        <v>391</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7571,7 +7571,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>374</v>
+        <v>392</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7615,7 +7615,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>393</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7638,31 +7638,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -7685,7 +7685,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7702,7 +7702,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7719,7 +7719,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7736,12 +7736,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7779,7 +7779,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -7880,7 +7880,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7907,7 +7907,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>377</v>
+        <v>363</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7925,7 +7925,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>378</v>
+        <v>365</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7955,7 +7955,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>379</v>
+        <v>367</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7968,7 +7968,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7995,7 +7995,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>380</v>
+        <v>369</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8007,7 +8007,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8016,7 +8016,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>382</v>
+        <v>372</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8024,7 +8024,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8045,7 +8045,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>383</v>
+        <v>373</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8057,7 +8057,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8066,7 +8066,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8097,7 +8097,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8105,7 +8105,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8117,7 +8117,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8126,7 +8126,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8135,7 +8135,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>388</v>
+        <v>381</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8143,7 +8143,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8164,7 +8164,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>389</v>
+        <v>382</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8176,7 +8176,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8200,7 +8200,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>390</v>
+        <v>383</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8213,7 +8213,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>384</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8250,7 +8250,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8265,7 +8265,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8274,7 +8274,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8298,7 +8298,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8310,7 +8310,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8328,31 +8328,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H16" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
@@ -8375,7 +8375,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8392,7 +8392,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8409,7 +8409,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8426,7 +8426,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8443,7 +8443,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8579,7 +8579,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8632,7 +8632,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8665,7 +8665,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8673,7 +8673,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8712,7 +8712,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8749,7 +8749,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8789,7 +8789,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8797,7 +8797,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8845,7 +8845,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8853,7 +8853,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8894,14 +8894,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8918,7 +8918,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8945,31 +8945,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H16" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
@@ -8992,7 +8992,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9009,7 +9009,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9026,17 +9026,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9227,7 +9227,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9246,33 +9246,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9318,31 +9318,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -9353,27 +9353,27 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
@@ -9387,7 +9387,7 @@
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
+      <c r="A34" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9483,13 +9483,13 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
       </c>
       <c r="D2" s="3">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="E2" s="3">
         <v>3.0</v>
@@ -9510,7 +9510,7 @@
         <v>3.0</v>
       </c>
       <c r="P2" s="3">
-        <v>11.0</v>
+        <v>13.0</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>408</v>
@@ -9519,7 +9519,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -9534,7 +9534,7 @@
         <v>409</v>
       </c>
       <c r="P3" s="3">
-        <v>17.0</v>
+        <v>18.0</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>410</v>
@@ -9548,10 +9548,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
-        <v>10.0</v>
+        <v>11.0</v>
       </c>
       <c r="D4" s="3">
         <v>16.0</v>
@@ -9563,10 +9563,13 @@
         <v>6.0</v>
       </c>
       <c r="H4" s="3">
-        <v>9.0</v>
+        <v>13.0</v>
       </c>
       <c r="I4" s="3">
         <v>2.0</v>
+      </c>
+      <c r="J4" s="3">
+        <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
         <v>412</v>
@@ -9589,16 +9592,16 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
       </c>
       <c r="C5" s="3">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="D5" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="H5" s="3">
         <v>8.0</v>
@@ -9610,19 +9613,19 @@
         <v>415</v>
       </c>
       <c r="M5" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="Q5" s="4"/>
       <c r="S5" s="3">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -9646,7 +9649,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="O6" s="3">
         <v>1.0</v>
@@ -9656,7 +9659,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -9665,7 +9668,7 @@
         <v>2.0</v>
       </c>
       <c r="D7" s="3">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
       <c r="E7" s="3">
         <v>1.0</v>
@@ -9683,7 +9686,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="M7" s="3">
         <v>3.0</v>
@@ -9698,7 +9701,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
     </row>
     <row r="8">
@@ -9722,25 +9725,30 @@
         <v>50</v>
       </c>
       <c r="D9" s="3">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
       <c r="E9" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="H9" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="J9" s="3">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="M9" s="3">
         <v>1.0</v>
       </c>
       <c r="Q9" s="4"/>
-      <c r="T9" s="4"/>
+      <c r="S9" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="T9" s="4" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
@@ -9758,13 +9766,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>385</v>
       </c>
       <c r="T11" s="5"/>
     </row>
@@ -9779,31 +9787,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H16" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
@@ -9826,7 +9834,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -9843,13 +9851,13 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
       </c>
       <c r="C19" s="3">
-        <v>2.0</v>
+        <v>4.0</v>
       </c>
       <c r="F19" s="3">
         <v>1.0</v>
@@ -9860,17 +9868,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D23" s="16"/>
       <c r="E23" s="16"/>
@@ -9884,7 +9892,7 @@
       <c r="B25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="18"/>
+      <c r="A26" s="17"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9981,7 +9989,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -10011,7 +10019,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="L2" s="3">
         <v>2.69</v>
@@ -10023,7 +10031,7 @@
         <v>22.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="R2" s="3">
         <v>1.45</v>
@@ -10032,7 +10040,7 @@
         <v>4.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -10040,7 +10048,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10064,7 +10072,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -10101,7 +10109,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10114,7 +10122,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10122,7 +10130,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10181,7 +10189,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10223,7 +10231,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10256,7 +10264,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10315,7 +10323,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10355,7 +10363,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10380,31 +10388,31 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C16" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D16" s="10" t="s">
+      <c r="E16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E16" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F16" s="11" t="s">
+      <c r="G16" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G16" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H16" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I16" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K16" s="15"/>
     </row>
@@ -10427,7 +10435,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10444,7 +10452,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10461,7 +10469,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10478,12 +10486,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10619,7 +10627,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10643,7 +10651,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10655,7 +10663,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10664,7 +10672,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10672,7 +10680,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10690,7 +10698,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10703,7 +10711,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10738,7 +10746,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10750,7 +10758,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10759,7 +10767,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10767,7 +10775,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10779,7 +10787,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10788,7 +10796,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10797,7 +10805,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10805,7 +10813,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10829,7 +10837,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10841,7 +10849,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10850,7 +10858,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10858,7 +10866,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10885,7 +10893,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10922,7 +10930,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10931,7 +10939,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10949,7 +10957,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>112</v>
+        <v>106</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10962,7 +10970,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10984,7 +10992,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10999,7 +11007,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -11008,13 +11016,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -11029,7 +11037,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -11048,37 +11056,37 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11111,7 +11119,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11128,7 +11136,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="18">
         <f>10</f>
         <v>10</v>
       </c>
@@ -11159,7 +11167,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11206,7 +11214,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11364,31 +11372,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -11411,7 +11419,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11428,7 +11436,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11445,7 +11453,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11462,7 +11470,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11479,7 +11487,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11513,7 +11521,7 @@
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="18">
+      <c r="A34" s="17">
         <v>0.186</v>
       </c>
     </row>
@@ -11615,7 +11623,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11639,7 +11647,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -11668,7 +11676,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11727,7 +11735,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11775,7 +11783,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11834,7 +11842,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11915,7 +11923,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11923,7 +11931,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11959,7 +11967,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -12011,7 +12019,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12020,7 +12028,7 @@
         <v>2.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="U11" s="3">
         <v>2.0</v>
@@ -12028,7 +12036,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12040,7 +12048,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12054,31 +12062,31 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H17" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K17" s="15"/>
     </row>
@@ -12101,7 +12109,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12118,7 +12126,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12135,7 +12143,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12152,7 +12160,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12169,7 +12177,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12305,7 +12313,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12338,7 +12346,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12346,7 +12354,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12399,7 +12407,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12438,7 +12446,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12447,7 +12455,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12455,7 +12463,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12514,7 +12522,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12536,7 +12544,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12572,7 +12580,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12581,7 +12589,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12603,7 +12611,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12626,13 +12634,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12641,7 +12649,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12650,7 +12658,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12725,7 +12733,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12737,7 +12745,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12773,31 +12781,31 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H17" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K17" s="15"/>
     </row>
@@ -12820,7 +12828,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12831,7 +12839,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12848,17 +12856,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12994,7 +13002,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -13033,7 +13041,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13053,7 +13061,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13103,7 +13111,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13162,7 +13170,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13240,7 +13248,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13248,7 +13256,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13281,7 +13289,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13341,7 +13349,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13349,7 +13357,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13373,7 +13381,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13391,7 +13399,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13452,31 +13460,31 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B17" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D17" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D17" s="10" t="s">
+      <c r="E17" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E17" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="G17" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G17" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H17" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I17" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K17" s="15"/>
     </row>
@@ -13499,7 +13507,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13516,7 +13524,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13530,7 +13538,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13547,7 +13555,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13561,7 +13569,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13725,7 +13733,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13740,7 +13748,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13752,7 +13760,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13761,7 +13769,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13785,7 +13793,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13798,7 +13806,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13806,7 +13814,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13833,7 +13841,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13845,7 +13853,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13854,7 +13862,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13881,7 +13889,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13893,7 +13901,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>71</v>
+        <v>55</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13902,7 +13910,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13934,7 +13942,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13946,7 +13954,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13955,7 +13963,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>86</v>
+        <v>64</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13963,7 +13971,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13981,7 +13989,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>91</v>
+        <v>68</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -13993,7 +14001,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -14002,7 +14010,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14024,7 +14032,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14033,7 +14041,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14045,7 +14053,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>108</v>
+        <v>81</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14054,7 +14062,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14062,7 +14070,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14071,7 +14079,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>110</v>
+        <v>87</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14083,7 +14091,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14104,7 +14112,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14123,37 +14131,37 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14186,7 +14194,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14228,7 +14236,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14275,7 +14283,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14322,7 +14330,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14366,7 +14374,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14404,7 +14412,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14427,31 +14435,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -14474,7 +14482,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14491,7 +14499,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14508,17 +14516,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14554,7 +14562,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
+      <c r="A34" s="17"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -14654,7 +14662,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14681,7 +14689,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>72</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14693,7 +14701,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>30</v>
+        <v>77</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14702,7 +14710,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14710,7 +14718,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14737,7 +14745,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14752,7 +14760,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>43</v>
+        <v>86</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14761,7 +14769,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14782,7 +14790,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14794,7 +14802,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>58</v>
+        <v>91</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14803,7 +14811,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14811,7 +14819,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14821,7 +14829,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14834,7 +14842,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14861,7 +14869,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14873,7 +14881,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>81</v>
+        <v>107</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14882,7 +14890,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>85</v>
+        <v>108</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14890,7 +14898,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14917,7 +14925,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14929,7 +14937,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>98</v>
+        <v>113</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14938,7 +14946,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14974,7 +14982,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14983,7 +14991,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -14995,7 +15003,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -15004,7 +15012,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15013,7 +15021,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15021,7 +15029,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15036,7 +15044,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15045,7 +15053,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15075,7 +15083,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15088,7 +15096,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15111,7 +15119,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15120,7 +15128,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15129,7 +15137,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15137,7 +15145,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15149,7 +15157,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15167,7 +15175,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15185,7 +15193,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15204,33 +15212,33 @@
         <v>92</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="O16" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="Q16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="R16" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15439,7 +15447,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15486,7 +15494,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15506,31 +15514,31 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H25" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K25" s="15"/>
     </row>
@@ -15553,7 +15561,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15570,7 +15578,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15587,7 +15595,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15604,12 +15612,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15745,7 +15753,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15793,7 +15801,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15842,7 +15850,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15878,7 +15886,7 @@
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
-      <c r="P4" s="18">
+      <c r="P4" s="17">
         <v>3.0</v>
       </c>
       <c r="Q4" s="23" t="s">
@@ -15887,7 +15895,7 @@
       <c r="R4" s="21">
         <v>1.0</v>
       </c>
-      <c r="S4" s="18">
+      <c r="S4" s="17">
         <v>3.0</v>
       </c>
       <c r="T4" s="23" t="s">
@@ -15910,7 +15918,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15966,7 +15974,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15985,7 +15993,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16053,7 +16061,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16089,7 +16097,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16097,7 +16105,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16109,7 +16117,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -16139,7 +16147,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16163,7 +16171,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16182,33 +16190,33 @@
         <v>92</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L14" s="6" t="s">
+      <c r="O14" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="P14" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="Q14" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="R14" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P14" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q14" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R14" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16238,7 +16246,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16285,7 +16293,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -16329,7 +16337,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16376,7 +16384,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>178</v>
+        <v>197</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16423,7 +16431,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16470,7 +16478,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>183</v>
+        <v>203</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16493,31 +16501,31 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B23" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C23" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D23" s="10" t="s">
+      <c r="E23" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F23" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E23" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F23" s="11" t="s">
+      <c r="G23" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G23" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H23" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I23" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K23" s="15"/>
     </row>
@@ -16540,7 +16548,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16557,7 +16565,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16574,7 +16582,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16591,7 +16599,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16599,7 +16607,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16735,7 +16743,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16759,7 +16767,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -16771,7 +16779,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -16780,7 +16788,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -16788,7 +16796,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16799,7 +16807,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16826,7 +16834,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -16838,7 +16846,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -16847,7 +16855,7 @@
         <v>7.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="U4" s="3">
         <v>2.29</v>
@@ -16855,7 +16863,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16867,7 +16875,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16876,7 +16884,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R5" s="3">
         <v>1.45</v>
@@ -16885,7 +16893,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16893,7 +16901,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16923,7 +16931,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -16938,7 +16946,7 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="R6" s="3">
         <v>0.5</v>
@@ -16947,7 +16955,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16955,7 +16963,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16973,7 +16981,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="L7" s="3">
         <v>2.36</v>
@@ -16985,7 +16993,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -16993,7 +17001,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17014,7 +17022,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -17026,7 +17034,7 @@
         <v>9.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>187</v>
+        <v>198</v>
       </c>
       <c r="R8" s="3">
         <v>1.11</v>
@@ -17035,7 +17043,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="U8" s="3">
         <v>2.0</v>
@@ -17068,7 +17076,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17077,7 +17085,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17089,7 +17097,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="L10" s="3">
         <v>1.75</v>
@@ -17101,7 +17109,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>119</v>
+        <v>133</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17131,7 +17139,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17143,7 +17151,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17173,7 +17181,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="L12" s="3">
         <v>2.25</v>
@@ -17185,7 +17193,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="R12" s="3">
         <v>0.75</v>
@@ -17194,7 +17202,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17202,7 +17210,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17217,7 +17225,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17229,14 +17237,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>192</v>
+        <v>207</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17245,7 +17253,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17264,33 +17272,33 @@
         <v>92</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L16" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M16" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L16" s="6" t="s">
+      <c r="O16" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="Q16" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="R16" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P16" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q16" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R16" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17320,7 +17328,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17367,7 +17375,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>194</v>
+        <v>211</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17411,7 +17419,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17458,7 +17466,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>196</v>
+        <v>215</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17505,7 +17513,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17552,7 +17560,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>198</v>
+        <v>218</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17575,31 +17583,31 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C25" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D25" s="10" t="s">
+      <c r="E25" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F25" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E25" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F25" s="11" t="s">
+      <c r="G25" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G25" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H25" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I25" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K25" s="15"/>
     </row>
@@ -17622,7 +17630,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17639,7 +17647,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17656,7 +17664,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17667,12 +17675,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17808,7 +17816,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17832,7 +17840,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17844,7 +17852,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>200</v>
+        <v>173</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17853,7 +17861,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>201</v>
+        <v>174</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17861,7 +17869,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17882,7 +17890,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17892,7 +17900,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>203</v>
+        <v>179</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17900,7 +17908,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17927,7 +17935,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>204</v>
+        <v>181</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17936,7 +17944,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>205</v>
+        <v>182</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17945,7 +17953,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>206</v>
+        <v>183</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17953,7 +17961,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17977,7 +17985,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>207</v>
+        <v>185</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -18019,7 +18027,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>208</v>
+        <v>188</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -18040,7 +18048,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>209</v>
+        <v>191</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -18048,7 +18056,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18064,7 +18072,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -18073,7 +18081,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -18100,7 +18108,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18112,7 +18120,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="L9" s="3">
         <v>1.833</v>
@@ -18122,7 +18130,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18153,7 +18161,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18172,33 +18180,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18228,7 +18236,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18272,7 +18280,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18286,7 +18294,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="18">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18314,7 +18322,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18355,7 +18363,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18390,7 +18398,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18437,7 +18445,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18457,31 +18465,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -18516,7 +18524,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18545,22 +18553,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18596,7 +18604,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
+      <c r="A34" s="17"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -18696,7 +18704,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18726,7 +18734,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L2" s="3">
         <v>2.364</v>
@@ -18738,7 +18746,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18747,7 +18755,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18755,7 +18763,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18779,7 +18787,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="L3" s="3">
         <v>2.5</v>
@@ -18794,7 +18802,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18803,7 +18811,7 @@
         <v>4.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
       <c r="U3" s="3">
         <v>1.75</v>
@@ -18811,7 +18819,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18835,7 +18843,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="L4" s="3">
         <v>2.75</v>
@@ -18845,7 +18853,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18857,7 +18865,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -18869,7 +18877,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="R5" s="3">
         <v>1.176</v>
@@ -18878,7 +18886,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="U5" s="3">
         <v>1.667</v>
@@ -18886,7 +18894,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -19002,7 +19010,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -19022,7 +19030,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -19059,7 +19067,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>202</v>
+        <v>176</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19067,7 +19075,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19094,7 +19102,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19112,7 +19120,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19127,7 +19135,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19139,7 +19147,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19158,33 +19166,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19445,31 +19453,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
       <c r="L24" s="3"/>
@@ -19503,7 +19511,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19533,7 +19541,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19562,17 +19570,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19608,7 +19616,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
+      <c r="A34" s="17"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -19708,7 +19716,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19747,7 +19755,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19803,7 +19811,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19907,7 +19915,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19915,7 +19923,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19972,7 +19980,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -20005,7 +20013,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>188</v>
+        <v>199</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -20072,7 +20080,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20137,7 +20145,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20156,33 +20164,33 @@
         <v>92</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>98</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="N15" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="L15" s="6" t="s">
+      <c r="O15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="8" t="s">
         <v>104</v>
-      </c>
-      <c r="P15" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="Q15" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="R15" s="8" t="s">
-        <v>107</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20309,7 +20317,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -20356,7 +20364,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="M19" s="3">
         <v>1.64</v>
@@ -20400,7 +20408,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -20447,7 +20455,7 @@
         <v>9.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="M21" s="3">
         <v>1.67</v>
@@ -20470,31 +20478,31 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C24" s="9" t="s">
-        <v>120</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="E24" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="F24" s="11" t="s">
         <v>121</v>
       </c>
-      <c r="E24" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="F24" s="11" t="s">
+      <c r="G24" s="12" t="s">
         <v>123</v>
       </c>
-      <c r="G24" s="12" t="s">
-        <v>124</v>
-      </c>
       <c r="H24" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="I24" s="14" t="s">
         <v>127</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>128</v>
       </c>
       <c r="K24" s="15"/>
     </row>
@@ -20517,7 +20525,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20534,7 +20542,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20551,7 +20559,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20568,7 +20576,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20585,7 +20593,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1773" uniqueCount="477">
   <si>
     <t>Player</t>
   </si>
@@ -97,273 +97,273 @@
     <t>FB receive rating (grade divided by attempts)</t>
   </si>
   <si>
+    <t>Cora</t>
+  </si>
+  <si>
     <t>Shiloh</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - </t>
+  </si>
+  <si>
+    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
+    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
   </si>
   <si>
-    <t>Cora</t>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t>Addy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - </t>
+  </si>
+  <si>
     <t>Annabelle</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - </t>
+    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>Kinley</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nataly </t>
+    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>Audri</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
     <t>Gaby</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t>Agnes</t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
-  </si>
-  <si>
-    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t>3 - 0 - 1</t>
+  </si>
+  <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
   </si>
   <si>
     <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t>Addy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+    <t xml:space="preserve">2 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
   </si>
   <si>
+    <t>1 - 1 - 1 - 0 - 0</t>
+  </si>
+  <si>
     <t>Tea</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">2 - 2 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+    <t xml:space="preserve">3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t>Kinley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>Audri</t>
-  </si>
-  <si>
-    <t>Bridget</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
-  </si>
-  <si>
-    <t>3 - 0 - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Corena</t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
+    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+    <t xml:space="preserve">5 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - </t>
   </si>
   <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - </t>
+    <t>Elena</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+    <t>Rotation (follow setter starting position)</t>
+  </si>
+  <si>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t>Emma</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - </t>
-  </si>
-  <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - </t>
-  </si>
-  <si>
-    <t>Elena</t>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
+    <t>Piper</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
-  </si>
-  <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t>Kill Efficiency</t>
-  </si>
-  <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
     <t>Block (partial touch)</t>
   </si>
   <si>
@@ -391,105 +391,105 @@
     <t>Rotation Net Score (+ or -)</t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
-    <t>Team</t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
-  </si>
-  <si>
     <t>Service error (us)</t>
   </si>
   <si>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
-  </si>
-  <si>
-    <t>Aces (them)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
     <t>Service Errors (them)</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
     <t>Ace % (them)</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
     <t>Service Error % (Them)</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
     <t>Set 1</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
     <t>Set 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
-  </si>
-  <si>
     <t>Set 3</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
     <t>Set 4</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>Set 5</t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>Team Passer Rating (all games)</t>
   </si>
   <si>
@@ -499,210 +499,219 @@
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 0 - 1 - 1 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 2 - 2 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 0 - 3 - 5 - 3 - 0 - 2 - 2 - 0 - 5 - 0 - 0 - 0 - 0 - 5 - 5 - 5 - 3 - 5 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 1 - 2 - 5 - 0 - 5 - 1 - 5 - 5 - 1 - 5 - 3 - 0 - 5 - 1 - 1 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - </t>
+  </si>
+  <si>
+    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 5 - 2 - 2 - 1 - 3 - 3 - 0 - 5 - 3 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t>2- 1- 0- 3- 1</t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 3 - 1 - 1 - 1 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 2 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - </t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 2 - 2 - </t>
   </si>
   <si>
+    <t>0- 0</t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 3 - 2 - 3 - 2 - 5 - 2 - 5 - 0 - 3 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 3 - 1 - 0 - 1 - 3 - 2 - 1 - 0 - </t>
   </si>
   <si>
+    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
+  </si>
+  <si>
+    <t>2- 3- 2- 2</t>
+  </si>
+  <si>
+    <t>3- 2- 3- 5- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 5 - 5 - 5 - 2 - 0 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 3 - 3 - 2 - 0 - 1 - 0 - 2 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 3 - 2 - 1 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t>1- 2- 2- 3- 1- 1- 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
   </si>
   <si>
+    <t>1- 3- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
+  </si>
+  <si>
+    <t>3- 3- 3- 2</t>
+  </si>
+  <si>
+    <t>2- 0- 3- 2- 1- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 3- 2- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t>2- 1- 2- 0- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t>3- 1- 2- 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t>3- 1- 5- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
   </si>
   <si>
+    <t>1- 3- 0- 3- 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t>3- 0</t>
+  </si>
+  <si>
+    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
+    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0- 2- 3- </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
-  </si>
-  <si>
-    <t>2- 1- 0- 3- 1</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
-  </si>
-  <si>
-    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
-  </si>
-  <si>
-    <t>0- 0</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2</t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 3- 2- </t>
-  </si>
-  <si>
-    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>2- 1- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>2- 3- 2- 2</t>
-  </si>
-  <si>
-    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
-  </si>
-  <si>
-    <t>3- 1- 2- 1</t>
-  </si>
-  <si>
-    <t>3- 2- 3- 5- 3</t>
-  </si>
-  <si>
-    <t>3- 1- 5- 2</t>
-  </si>
-  <si>
-    <t>3- 0</t>
-  </si>
-  <si>
-    <t>1- 2- 2- 3- 1- 1- 0</t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0- 2- 3- </t>
-  </si>
-  <si>
-    <t>1- 3- 0</t>
-  </si>
-  <si>
-    <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
-  </si>
-  <si>
     <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
   </si>
   <si>
-    <t>3- 3- 3- 2</t>
-  </si>
-  <si>
     <t>2- 2- 0</t>
   </si>
   <si>
@@ -712,54 +721,45 @@
     <t>1- 3- 0- 1- 0</t>
   </si>
   <si>
-    <t>2- 0- 3- 2- 1- 3</t>
-  </si>
-  <si>
     <t>1- 2- 0- 0- 1- 0</t>
   </si>
   <si>
     <t>2- 3- 1- 2</t>
   </si>
   <si>
+    <t xml:space="preserve">2- 1- 1- </t>
+  </si>
+  <si>
+    <t>1- 0- 3- 2- 0- 1- 1</t>
+  </si>
+  <si>
     <t>5- 3- 0- 0</t>
   </si>
   <si>
+    <t>0- 1- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">0- 3- </t>
   </si>
   <si>
+    <t>2- 1- 2- 1- 2</t>
+  </si>
+  <si>
     <t>0- 2</t>
   </si>
   <si>
-    <t>1- 3- 0- 3- 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
-  </si>
-  <si>
     <t>0- 1- 1- 0- 1- 2- 1- 0- 0- 0- 2- 1- 0- 3- 2- 1- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">2- 1- 1- </t>
-  </si>
-  <si>
     <t>0- 1- 2- 1- 0- 2- 2- 2- 2- 2</t>
   </si>
   <si>
-    <t>1- 0- 3- 2- 0- 1- 1</t>
-  </si>
-  <si>
     <t>2- 2- 1- 2</t>
   </si>
   <si>
-    <t>0- 1- 3</t>
-  </si>
-  <si>
     <t>2- 1- 1- 3- 1- 1- 3- 2- 1- 3- 2</t>
   </si>
   <si>
-    <t>2- 1- 2- 1- 2</t>
-  </si>
-  <si>
     <t>2- 0- 2- 2- 3- 1- 0- 0</t>
   </si>
   <si>
@@ -799,16 +799,31 @@
     <t xml:space="preserve">0 - 0 - 1 - 2 - 2 - 0 - 0 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 5 - 5 - 1 - 5 -  0 - 3 - 5 - 0 - 5 - 0 - 0 - 0 - 3 - 5 - 3 - 0 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 3 - 0 - 3 - 2 - 2 - 0 - 1 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 3 - 1 - 5 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 2 - 1 - 2 - 2 - 0 -1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 1 - 2 - 0 - 0 - 1 - 0 - 2 - 1 - 2 - 0 - 2 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 5 - 1 - 5 -  0 - 3 - 5 - 0 - 5 - 0 - 0 - 0 - 3 - 5 - 3 - 0 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 3 - 0 - 3 - 2 - 2 - 0 - 1 - 2 - 3 - 1 - </t>
+    <t xml:space="preserve">0 - 3 - 3 - 5 - 3 - 3 - 0 - 3 - 2 - 3 - 1 - 3 - 3 - 1 - 1 - 1 - 5 - 3 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 3 - 0 - 0 - </t>
@@ -817,24 +832,9 @@
     <t xml:space="preserve">0 - 3 - 1 - 1 - 0 - 0 - 1 - 1 - 1 - 0 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 1 - 3 - 1 - 5 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 1 - 5 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 5 - 3 - 3 - 0 - 3 - 2 - 3 - 1 - 3 - 3 - 1 - 1 - 1 - 5 - 3 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 2 - 5 - 5 - 3 - 5 - 1 - 0 - </t>
   </si>
   <si>
@@ -859,12 +859,12 @@
     <t xml:space="preserve">0 - 2 - 0 - 3 - 1 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 1 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 1 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - 1 - 1 - 2 - 3 - 2 - 3 - 1 - 2 - 2 - 0 -0 - 1 -2 - 2 - </t>
   </si>
   <si>
@@ -874,12 +874,12 @@
     <t xml:space="preserve">3 - 3 - 0 - 1 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 0 - 3 - 2 - 1 - 2 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 1 - 2 - 0 - 1 - 3 - 1 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
@@ -937,10 +937,16 @@
     <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+    <t xml:space="preserve">0 - 1 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
@@ -952,9 +958,6 @@
     <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
   </si>
   <si>
@@ -964,15 +967,15 @@
     <t xml:space="preserve">2- 2- 2- 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1- 1- 0 - 3 - 1 - 1 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
@@ -982,10 +985,13 @@
     <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
@@ -994,24 +1000,36 @@
     <t xml:space="preserve">2- 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
@@ -1030,33 +1048,18 @@
     <t xml:space="preserve">1 - 1 - 2 - 3 - 3 - 2 - 2 - 1 - 1 - 0 - 0 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
   </si>
   <si>
@@ -1066,9 +1069,6 @@
     <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
@@ -1144,111 +1144,111 @@
     <t xml:space="preserve">5 - 1 - 3 - 2 - 2 - 2 - 5 - 0 - 3 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 2 - 2 - 1 - 3 - 3 - 0 - 1 - 3 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 1 - 3 - 2 - 3 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 2 - 3 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 2 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 0 - 1 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 3 - 3 - 1 - 0 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 0 - 5 - 2 - 2 - 0 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 5 - 0 - 1 - 1 - 1 - 5 -  3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 3 - 3 - 5 - 5 - 3 - 5 - 5 - 2 - 5 - 5 - 2 - 5 - 0 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 3 - 3 - 1 - 3 - 3 - </t>
+  </si>
+  <si>
     <t>119 attack attempts</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 3 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 2 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 0 - 1 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 3 - 1 - 0 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 5 - 2 - 2 - 0 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 5 - 0 - 1 - 1 - 1 - 5 -  3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 3 - 3 - 5 - 5 - 3 - 5 - 5 - 2 - 5 - 5 - 2 - 5 - 0 - 5 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 3 - 3 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 5 - 3 - 1 - 5 - 5 - 2 - 5 - 3 - 0 - </t>
   </si>
   <si>
@@ -1258,19 +1258,19 @@
     <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - 0 - 2 - 2 - 3 - </t>
+    <t xml:space="preserve">0 - 3 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - 2 - 0 - 2 - 2 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 1 - 3 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - 3 - 2 - 2 - 3 - 3 - 2 - </t>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 0 - 2 - 1 - 0 - 1 - 0 - 1 - 2 - 3 - 2 - 1 - 3 - 3 - 2 - 2 - 3 - 3 - 2 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 2 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - 5 - 5 - 2 - 3 - 1 - 3 - 2 - 0 - </t>
+    <t xml:space="preserve">3 - 2 - 3 - 3 - 3 - 5 - 5 - 2 - 3 - 1 - 3 - 2 - 0 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 0 - 1 - 0 - 3 - 1 - 2 - 1 - 2 - 3 - 2 - 3 - </t>
@@ -1279,10 +1279,10 @@
     <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 2 - 1 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 1 - 0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 2 - 1 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - 1 - 3 - 3 - 5 - 5 - 2 - </t>
@@ -1291,12 +1291,12 @@
     <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - 1 - 5 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 0 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 2 - 0 - 2 - 0 - 1 - 1 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
@@ -1306,6 +1306,9 @@
     <t xml:space="preserve">5 - 5 - 5 - 3- 5 - 3 - 0 - 2 - 0- 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 0 - 5 - 1 - 3 - 5 - 5 - 3 - 2 - 3 - 3 - 3 - 1 - 5 - 1 - 5 - 0 - 1 - 2 - </t>
   </si>
   <si>
@@ -1327,24 +1330,24 @@
     <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
   </si>
   <si>
@@ -1381,42 +1384,57 @@
     <t xml:space="preserve">5 - 5 - 3 - 0 - 0 - 5 - 5 - 1 - 3 - 5 - 3 - 2 - 3 - 0 - 2 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 1 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - 0 - 3 - 2 - 3 - 0 - 0 - 3 - 1 - 0 - 3 - 2 - 2 - 3 - 3 - 2 - 2 - 3 - 0 - 3 - 1 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 3 - 1 - 1 - 3 - 5 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 2 - 0 - 3 - 2 - 2 - 2 - 0 - 1 - 0 - 3 - 3 - 3 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 1 - 5 - 5 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 1 - 1 - 2 - 2 - 5 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 1 - 1 - 3 - 1 - 1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 1 - 3 - 2 - 1 - 2 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 1 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 1 - 2 - 2 - 0 - 3 - 3 - 0 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 0 - 0 - 3 - 2 - 3 - 0 - 0 - 3 - 1 - 0 - 3 - 2 - 2 - 3 - 3 - 2 - 2 - 3 - 0 - 3 - 1 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 2 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 3 - 1 - 1 - 3 - 5 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 2 - 0 - 3 - 2 - 2 - 2 - 0 - 1 - 0 - 3 - 3 - 3 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 2 - 5 - 5 - 2 - 1 - 1 - 5 - 3 - 3 - 3 - 3 - 3 - 1 - 5 - 3 - 2 - 5 - 3 - 3 - 3 - 5 - 3 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 1 - 1 - 1 - 1 - 2 - 0 - 3 - 2 - 0 - 3 - 2 - 3 - 3 - 0 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 1 - 3 - 2 - 1 - 3 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 1 - 5 - 5 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 5 - 0 - 5 - 5 - 2 - 0 - 0 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1426,28 +1444,13 @@
     <t xml:space="preserve">3 - 3 - 3 - 3 - 1 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 1 - 1 - 2 - 2 - 5 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 1 - 1 - 3 - 1 - 1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 3 - 2 - 0 - 3 - 2 - 1 - 0 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - 2 - 3 - 1 - 0 - 0 - 2 - 1 - 2 - 1 - 1 - 3 - 1 - 3 - 0 - 3 - 3 - 2 - 3 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - 2 - 3 - 3 - 3 - 3 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 5 - 3 - 5 - 0 - 3 - 2 - 3 - 3 - 0 - 3 - 3 - 0 - 1 - 0 - </t>
@@ -1985,7 +1988,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -2009,7 +2012,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2021,7 +2024,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2030,7 +2033,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2057,7 +2060,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2069,7 +2072,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2078,7 +2081,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2096,7 +2099,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2111,7 +2114,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2132,7 +2135,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>63</v>
+        <v>54</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2141,7 +2144,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2150,7 +2153,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2174,7 +2177,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2183,7 +2186,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2192,7 +2195,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2204,7 +2207,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2225,7 +2228,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2238,7 +2241,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2265,7 +2268,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2289,7 +2292,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2316,7 +2319,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2325,7 +2328,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2334,7 +2337,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2355,7 +2358,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2373,7 +2376,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2394,7 +2397,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2412,10 +2415,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -2485,37 +2488,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2544,7 +2547,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2570,7 +2573,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2599,7 +2602,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2633,7 +2636,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2774,7 +2777,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2795,7 +2798,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="L2" s="3">
         <v>1.56</v>
@@ -2807,7 +2810,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="R2" s="3">
         <v>1.06</v>
@@ -2816,7 +2819,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2824,7 +2827,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2839,7 +2842,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -2851,7 +2854,7 @@
         <v>12.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -2860,7 +2863,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2887,7 +2890,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="L4" s="3">
         <v>2.2</v>
@@ -2900,7 +2903,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2908,7 +2911,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2956,7 +2959,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2964,7 +2967,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -3020,7 +3023,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3">
         <v>8.0</v>
@@ -3041,7 +3044,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3056,7 +3059,7 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -3065,7 +3068,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3110,7 +3113,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -3118,19 +3121,19 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B9" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="C9" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="H9" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="K9" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="B9" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="C9" s="3">
-        <v>1.0</v>
-      </c>
-      <c r="H9" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>61</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3143,7 +3146,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3152,7 +3155,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3177,7 +3180,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3193,10 +3196,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -3255,7 +3258,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -3492,37 +3495,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3536,7 +3539,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3553,7 +3556,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3570,7 +3573,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -3580,7 +3583,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3716,7 +3719,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3">
         <v>17.0</v>
@@ -3761,7 +3764,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3769,7 +3772,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3811,7 +3814,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3828,7 +3831,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3887,7 +3890,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3943,7 +3946,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3966,7 +3969,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3974,7 +3977,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -4007,7 +4010,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4016,7 +4019,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4024,7 +4027,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4054,7 +4057,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4082,7 +4085,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4090,7 +4093,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4105,7 +4108,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4115,7 +4118,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4133,7 +4136,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4142,7 +4145,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4163,7 +4166,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4172,7 +4175,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4190,7 +4193,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4202,7 +4205,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4223,7 +4226,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4235,7 +4238,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4247,7 +4250,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4257,7 +4260,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4266,7 +4269,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4282,10 +4285,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
@@ -4344,7 +4347,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4391,7 +4394,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4435,7 +4438,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4526,7 +4529,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4593,37 +4596,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4640,7 +4643,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4657,7 +4660,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4674,7 +4677,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30">
@@ -4684,7 +4687,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4820,7 +4823,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -4848,7 +4851,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4857,7 +4860,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="U2" s="3">
         <v>2.33</v>
@@ -4865,7 +4868,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4892,7 +4895,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4904,7 +4907,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4913,7 +4916,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4921,7 +4924,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4948,7 +4951,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4960,7 +4963,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4969,7 +4972,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4977,7 +4980,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5025,7 +5028,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5033,7 +5036,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5045,7 +5048,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5057,7 +5060,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5066,7 +5069,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5081,7 +5084,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5090,7 +5093,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5114,7 +5117,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5126,7 +5129,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5134,7 +5137,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5162,7 +5165,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5189,7 +5192,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5214,7 +5217,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5230,10 +5233,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -5292,7 +5295,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5339,7 +5342,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5386,7 +5389,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>336</v>
+        <v>326</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5430,7 +5433,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>338</v>
+        <v>327</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5474,7 +5477,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5518,7 +5521,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5541,37 +5544,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5600,7 +5603,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5617,7 +5620,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5634,7 +5637,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5656,7 +5659,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5798,7 +5801,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5825,7 +5828,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5837,7 +5840,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5846,7 +5849,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5854,7 +5857,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5884,7 +5887,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5896,7 +5899,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5905,7 +5908,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5913,7 +5916,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5943,7 +5946,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5958,7 +5961,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5967,7 +5970,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5975,7 +5978,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -5998,7 +6001,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -6006,7 +6009,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6028,7 +6031,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6037,7 +6040,7 @@
         <v>4.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -6045,7 +6048,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B7" s="18">
         <v>4.0</v>
@@ -6065,7 +6068,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6079,7 +6082,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6088,7 +6091,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6107,7 +6110,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6122,7 +6125,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6131,7 +6134,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6140,7 +6143,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6148,7 +6151,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3">
         <v>28.0</v>
@@ -6174,7 +6177,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6222,7 +6225,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6250,7 +6253,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6266,10 +6269,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -6586,37 +6589,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6633,7 +6636,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6650,7 +6653,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6667,7 +6670,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6701,7 +6704,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6837,7 +6840,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6868,7 +6871,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6927,7 +6930,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6965,7 +6968,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -7018,7 +7021,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7072,7 +7075,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7080,7 +7083,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7102,7 +7105,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7119,7 +7122,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7155,7 +7158,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -7163,7 +7166,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7213,7 +7216,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D10" s="3">
         <v>14.0</v>
@@ -7240,7 +7243,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7273,7 +7276,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7288,7 +7291,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7297,7 +7300,7 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="U13" s="3">
         <v>1.5</v>
@@ -7308,7 +7311,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7324,10 +7327,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -7386,7 +7389,7 @@
         <v>12.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="M16" s="3">
         <v>2.0</v>
@@ -7430,7 +7433,7 @@
         <v>11.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>371</v>
+        <v>378</v>
       </c>
       <c r="M17" s="3">
         <v>2.55</v>
@@ -7477,7 +7480,7 @@
         <v>22.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="M18" s="3">
         <v>2.14</v>
@@ -7524,7 +7527,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7571,7 +7574,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>374</v>
+        <v>387</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7615,7 +7618,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7638,37 +7641,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7685,7 +7688,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7702,7 +7705,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7719,7 +7722,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7741,7 +7744,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7779,7 +7782,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>376</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
@@ -7880,7 +7883,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7907,7 +7910,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>377</v>
+        <v>370</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7925,7 +7928,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>378</v>
+        <v>371</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7934,7 +7937,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7955,7 +7958,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>379</v>
+        <v>372</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7968,7 +7971,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7995,7 +7998,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>380</v>
+        <v>373</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8007,7 +8010,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>381</v>
+        <v>375</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8016,7 +8019,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>382</v>
+        <v>376</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8024,7 +8027,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8045,7 +8048,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>383</v>
+        <v>377</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8057,7 +8060,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>379</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8066,7 +8069,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>385</v>
+        <v>380</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8074,7 +8077,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8097,7 +8100,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8105,7 +8108,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8117,7 +8120,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8126,7 +8129,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8135,7 +8138,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8143,7 +8146,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8164,7 +8167,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8176,7 +8179,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8200,7 +8203,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8213,7 +8216,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8221,7 +8224,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -8250,7 +8253,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8265,7 +8268,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8274,7 +8277,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8298,7 +8301,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8310,7 +8313,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8328,37 +8331,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8375,7 +8378,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8392,7 +8395,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8409,7 +8412,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8443,7 +8446,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8579,7 +8582,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8603,7 +8606,7 @@
         <v>8.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="L2" s="3">
         <v>3.87</v>
@@ -8615,7 +8618,7 @@
         <v>15.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="R2" s="3">
         <v>1.53</v>
@@ -8624,7 +8627,7 @@
         <v>5.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -8632,7 +8635,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8647,7 +8650,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="L3" s="3">
         <v>1.86</v>
@@ -8656,7 +8659,7 @@
         <v>8.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="R3" s="3">
         <v>1.63</v>
@@ -8665,7 +8668,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8673,7 +8676,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8703,7 +8706,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="L4" s="3">
         <v>2.11</v>
@@ -8712,7 +8715,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8721,7 +8724,7 @@
         <v>3.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -8729,7 +8732,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D5" s="3">
         <v>10.0</v>
@@ -8749,7 +8752,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8776,7 +8779,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="L6" s="3">
         <v>2.6</v>
@@ -8789,7 +8792,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8797,7 +8800,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8824,7 +8827,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="L7" s="3">
         <v>3.59</v>
@@ -8836,7 +8839,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="R7" s="3">
         <v>2.15</v>
@@ -8845,7 +8848,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8853,7 +8856,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8874,7 +8877,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8894,14 +8897,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8918,7 +8921,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8930,7 +8933,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8945,37 +8948,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8992,7 +8995,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9009,7 +9012,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9026,7 +9029,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -9036,7 +9039,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9227,7 +9230,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9243,10 +9246,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -9318,52 +9321,52 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -9373,7 +9376,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D31" s="17"/>
       <c r="E31" s="17"/>
@@ -9483,16 +9486,19 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
       </c>
       <c r="D2" s="3">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="E2" s="3">
         <v>4.0</v>
+      </c>
+      <c r="G2" s="3">
+        <v>0.286</v>
       </c>
       <c r="H2" s="3">
         <v>13.0</v>
@@ -9510,7 +9516,7 @@
         <v>3.0</v>
       </c>
       <c r="P2" s="3">
-        <v>14.0</v>
+        <v>15.0</v>
       </c>
       <c r="Q2" s="4" t="s">
         <v>408</v>
@@ -9519,7 +9525,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -9534,7 +9540,7 @@
         <v>409</v>
       </c>
       <c r="P3" s="3">
-        <v>22.0</v>
+        <v>23.0</v>
       </c>
       <c r="Q3" s="4" t="s">
         <v>410</v>
@@ -9548,10 +9554,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B4" s="3">
-        <v>11.0</v>
+        <v>12.0</v>
       </c>
       <c r="D4" s="3">
         <v>21.0</v>
@@ -9562,8 +9568,11 @@
       <c r="F4" s="3">
         <v>8.0</v>
       </c>
+      <c r="G4" s="3">
+        <v>-0.095</v>
+      </c>
       <c r="H4" s="3">
-        <v>13.0</v>
+        <v>14.0</v>
       </c>
       <c r="I4" s="3">
         <v>2.0</v>
@@ -9592,7 +9601,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -9603,6 +9612,9 @@
       <c r="D5" s="3">
         <v>4.0</v>
       </c>
+      <c r="G5" s="3">
+        <v>0.0</v>
+      </c>
       <c r="H5" s="3">
         <v>9.0</v>
       </c>
@@ -9617,7 +9629,7 @@
       </c>
       <c r="Q5" s="4"/>
       <c r="S5" s="3">
-        <v>4.0</v>
+        <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
         <v>416</v>
@@ -9625,7 +9637,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B6" s="3">
         <v>3.0</v>
@@ -9639,6 +9651,9 @@
       <c r="F6" s="3">
         <v>1.0</v>
       </c>
+      <c r="G6" s="3">
+        <v>0.2</v>
+      </c>
       <c r="H6" s="3">
         <v>12.0</v>
       </c>
@@ -9659,10 +9674,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="C7" s="3">
         <v>2.0</v>
@@ -9676,6 +9691,9 @@
       <c r="F7" s="3">
         <v>2.0</v>
       </c>
+      <c r="G7" s="3">
+        <v>-0.143</v>
+      </c>
       <c r="H7" s="3">
         <v>10.0</v>
       </c>
@@ -9695,18 +9713,18 @@
         <v>3.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="S7" s="3">
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>9.0</v>
@@ -9717,27 +9735,33 @@
       <c r="F8" s="3">
         <v>2.0</v>
       </c>
+      <c r="G8" s="3">
+        <v>-0.111</v>
+      </c>
       <c r="K8" s="5"/>
       <c r="T8" s="5"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D9" s="3">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
       <c r="E9" s="3">
         <v>2.0</v>
       </c>
+      <c r="G9" s="3">
+        <v>0.2</v>
+      </c>
       <c r="H9" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="J9" s="3">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>62</v>
+        <v>424</v>
       </c>
       <c r="M9" s="3">
         <v>1.0</v>
@@ -9747,12 +9771,12 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -9766,22 +9790,25 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="T11" s="5"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
+      </c>
+      <c r="G12" s="3">
+        <v>0.0</v>
       </c>
       <c r="T12" s="5"/>
     </row>
@@ -9793,37 +9820,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9840,7 +9867,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -9857,24 +9884,24 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" s="3">
         <v>2.0</v>
       </c>
       <c r="C19" s="3">
+        <v>7.0</v>
+      </c>
+      <c r="F19" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="G19" s="3">
         <v>6.0</v>
-      </c>
-      <c r="F19" s="3">
-        <v>2.0</v>
-      </c>
-      <c r="G19" s="3">
-        <v>5.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="21">
@@ -9884,7 +9911,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D23" s="17"/>
       <c r="E23" s="17"/>
@@ -9995,7 +10022,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -10025,7 +10052,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="L2" s="3">
         <v>2.69</v>
@@ -10054,7 +10081,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10097,7 +10124,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -10115,7 +10142,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10128,7 +10155,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10136,7 +10163,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10166,7 +10193,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="L5" s="3">
         <v>2.63</v>
@@ -10178,7 +10205,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="R5" s="3">
         <v>1.71</v>
@@ -10187,7 +10214,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -10195,7 +10222,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10216,7 +10243,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="L6" s="3">
         <v>2.65</v>
@@ -10228,7 +10255,7 @@
         <v>20.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="R6" s="3">
         <v>1.0</v>
@@ -10237,7 +10264,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10245,7 +10272,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D7" s="3">
         <v>14.0</v>
@@ -10270,7 +10297,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10300,7 +10327,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -10312,7 +10339,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -10321,7 +10348,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="U8" s="3">
         <v>1.83</v>
@@ -10329,7 +10356,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10341,7 +10368,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -10351,7 +10378,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10369,7 +10396,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -10394,37 +10421,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G16" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H16" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I16" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10441,7 +10468,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10458,7 +10485,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10475,7 +10502,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10497,7 +10524,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10633,7 +10660,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10657,7 +10684,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10669,7 +10696,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10678,7 +10705,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10686,7 +10713,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10704,7 +10731,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10717,7 +10744,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10725,7 +10752,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10752,7 +10779,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10764,7 +10791,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10773,7 +10800,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10781,7 +10808,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10793,7 +10820,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10802,7 +10829,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10811,7 +10838,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10819,7 +10846,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10843,7 +10870,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10855,7 +10882,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10864,7 +10891,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10872,7 +10899,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10899,7 +10926,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10911,7 +10938,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>15.0</v>
@@ -10936,7 +10963,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10945,7 +10972,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10963,7 +10990,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10976,7 +11003,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10984,7 +11011,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10998,7 +11025,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -11013,7 +11040,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -11022,13 +11049,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -11043,7 +11070,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -11059,10 +11086,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -11125,7 +11152,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11173,7 +11200,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11220,7 +11247,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11267,7 +11294,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11314,7 +11341,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11358,7 +11385,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11378,37 +11405,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11425,7 +11452,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11442,7 +11469,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11459,7 +11486,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11493,7 +11520,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11629,7 +11656,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11653,7 +11680,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -11665,7 +11692,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="R2" s="3">
         <v>1.46</v>
@@ -11682,7 +11709,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11712,7 +11739,7 @@
         <v>7.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L3" s="3">
         <v>1.62</v>
@@ -11724,7 +11751,7 @@
         <v>6.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="R3" s="3">
         <v>1.17</v>
@@ -11733,7 +11760,7 @@
         <v>11.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="U3" s="3">
         <v>2.36</v>
@@ -11741,7 +11768,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11768,7 +11795,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="L4" s="3">
         <v>2.0</v>
@@ -11781,7 +11808,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -11789,7 +11816,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11819,7 +11846,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="L5" s="3">
         <v>2.86</v>
@@ -11831,7 +11858,7 @@
         <v>32.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="R5" s="3">
         <v>1.59</v>
@@ -11840,7 +11867,7 @@
         <v>23.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="U5" s="3">
         <v>2.43</v>
@@ -11848,7 +11875,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11869,7 +11896,7 @@
         <v>15.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="L6" s="3">
         <v>2.33</v>
@@ -11881,7 +11908,7 @@
         <v>19.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="R6" s="3">
         <v>1.79</v>
@@ -11890,7 +11917,7 @@
         <v>17.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="U6" s="3">
         <v>2.47</v>
@@ -11898,7 +11925,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -11929,7 +11956,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -11937,7 +11964,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -11961,7 +11988,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="L8" s="3">
         <v>2.76</v>
@@ -11973,7 +12000,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -11982,7 +12009,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3">
         <v>1.0</v>
@@ -12011,7 +12038,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -12025,7 +12052,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12034,7 +12061,7 @@
         <v>2.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="U11" s="3">
         <v>2.0</v>
@@ -12042,7 +12069,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12054,7 +12081,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12068,37 +12095,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12115,7 +12142,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12132,7 +12159,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12149,7 +12176,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12183,7 +12210,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12319,7 +12346,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12343,7 +12370,7 @@
         <v>26.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R2" s="3">
         <v>1.73</v>
@@ -12352,7 +12379,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12360,7 +12387,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12384,7 +12411,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -12396,7 +12423,7 @@
         <v>19.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="R3" s="3">
         <v>1.59</v>
@@ -12405,7 +12432,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="U3" s="3">
         <v>2.8</v>
@@ -12413,7 +12440,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12440,7 +12467,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -12452,7 +12479,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12461,7 +12488,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12469,7 +12496,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12499,7 +12526,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="L5" s="3">
         <v>2.1</v>
@@ -12511,7 +12538,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
       <c r="R5" s="3">
         <v>1.7</v>
@@ -12520,7 +12547,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="U5" s="3">
         <v>2.75</v>
@@ -12528,7 +12555,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12540,7 +12567,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="L6" s="3">
         <v>2.67</v>
@@ -12550,7 +12577,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12571,7 +12598,7 @@
         <v>4.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="L7" s="3">
         <v>0.0</v>
@@ -12586,7 +12613,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12595,7 +12622,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12617,7 +12644,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12640,13 +12667,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12655,7 +12682,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12664,7 +12691,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12685,7 +12712,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12706,7 +12733,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -12724,7 +12751,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12739,7 +12766,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12751,7 +12778,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12787,37 +12814,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12834,7 +12861,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12845,7 +12872,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12862,7 +12889,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22">
@@ -12872,7 +12899,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -13008,7 +13035,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -13020,7 +13047,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
       <c r="L2" s="3">
         <v>1.36</v>
@@ -13030,7 +13057,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="R2" s="3">
         <v>1.38</v>
@@ -13039,7 +13066,7 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="U2" s="3">
         <v>2.17</v>
@@ -13047,7 +13074,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13067,7 +13094,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13091,7 +13118,7 @@
         <v>6.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>456</v>
+        <v>464</v>
       </c>
       <c r="L4" s="3">
         <v>3.12</v>
@@ -13100,7 +13127,7 @@
         <v>18.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>458</v>
+        <v>465</v>
       </c>
       <c r="R4" s="3">
         <v>1.39</v>
@@ -13109,7 +13136,7 @@
         <v>10.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>459</v>
+        <v>466</v>
       </c>
       <c r="U4" s="3">
         <v>2.4</v>
@@ -13117,7 +13144,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13147,7 +13174,7 @@
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>461</v>
+        <v>467</v>
       </c>
       <c r="L5" s="3">
         <v>2.17</v>
@@ -13159,7 +13186,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>462</v>
+        <v>468</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -13168,7 +13195,7 @@
         <v>7.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>463</v>
+        <v>469</v>
       </c>
       <c r="U5" s="3">
         <v>2.57</v>
@@ -13176,7 +13203,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13203,7 +13230,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="L6" s="3">
         <v>2.18</v>
@@ -13215,7 +13242,7 @@
         <v>22.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -13224,7 +13251,7 @@
         <v>10.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="U6" s="3">
         <v>2.4</v>
@@ -13232,7 +13259,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13254,7 +13281,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13262,7 +13289,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13286,7 +13313,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="L8" s="3">
         <v>2.31</v>
@@ -13295,7 +13322,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13303,7 +13330,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D9" s="3">
         <v>18.0</v>
@@ -13332,7 +13359,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13355,7 +13382,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13363,7 +13390,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13375,7 +13402,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L11" s="3">
         <v>2.4</v>
@@ -13387,7 +13414,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13405,7 +13432,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13417,7 +13444,7 @@
         <v>5.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -13426,7 +13453,7 @@
         <v>4.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -13466,37 +13493,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H17" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I17" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13513,7 +13540,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13530,7 +13557,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13544,7 +13571,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13575,7 +13602,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13711,7 +13738,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3">
         <v>3.0</v>
@@ -13739,7 +13766,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13754,7 +13781,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13766,7 +13793,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13775,7 +13802,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13799,7 +13826,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13812,7 +13839,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13820,7 +13847,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13847,7 +13874,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>69</v>
+        <v>49</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13859,7 +13886,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>70</v>
+        <v>53</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13868,7 +13895,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13895,7 +13922,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>76</v>
+        <v>60</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -13907,7 +13934,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -13916,7 +13943,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>80</v>
+        <v>67</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -13924,7 +13951,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -13948,7 +13975,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -13960,7 +13987,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -13969,7 +13996,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -13977,7 +14004,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -13995,7 +14022,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -14007,7 +14034,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -14016,7 +14043,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14024,7 +14051,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -14038,7 +14065,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14047,7 +14074,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14059,7 +14086,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>100</v>
+        <v>91</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14068,7 +14095,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14076,7 +14103,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14085,7 +14112,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14097,7 +14124,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14118,7 +14145,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14134,10 +14161,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
@@ -14200,7 +14227,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14242,7 +14269,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14289,7 +14316,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14336,7 +14363,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14380,7 +14407,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14418,7 +14445,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>144</v>
+        <v>125</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14441,37 +14468,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14488,7 +14515,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14505,7 +14532,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14522,7 +14549,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -14532,7 +14559,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14668,7 +14695,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14695,7 +14722,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14707,7 +14734,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14716,7 +14743,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>25</v>
+        <v>41</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14724,7 +14751,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14751,7 +14778,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>28</v>
+        <v>48</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14766,7 +14793,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14775,7 +14802,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14796,7 +14823,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14808,7 +14835,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14817,7 +14844,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14825,7 +14852,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14835,7 +14862,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14848,7 +14875,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14875,7 +14902,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14887,7 +14914,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14896,7 +14923,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -14904,7 +14931,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -14931,7 +14958,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>56</v>
+        <v>85</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -14943,7 +14970,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>58</v>
+        <v>87</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -14952,7 +14979,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -14960,7 +14987,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>13.0</v>
@@ -14988,7 +15015,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -14997,7 +15024,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -15009,7 +15036,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -15018,7 +15045,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15027,7 +15054,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15035,7 +15062,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15050,7 +15077,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15059,7 +15086,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15068,7 +15095,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15089,7 +15116,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15102,7 +15129,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15110,7 +15137,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15125,7 +15152,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15134,7 +15161,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15143,7 +15170,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15151,7 +15178,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15163,7 +15190,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15181,7 +15208,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15199,7 +15226,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15215,10 +15242,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
@@ -15277,7 +15304,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15324,7 +15351,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15365,7 +15392,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15412,7 +15439,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15453,7 +15480,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15500,7 +15527,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15520,37 +15547,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15567,7 +15594,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15584,7 +15611,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15601,7 +15628,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15623,7 +15650,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15759,7 +15786,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15790,7 +15817,7 @@
         <v>14.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="R2" s="3">
         <v>1.57</v>
@@ -15799,7 +15826,7 @@
         <v>9.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="U2" s="3">
         <v>2.56</v>
@@ -15807,7 +15834,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15837,7 +15864,7 @@
         <v>9.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="L3" s="3">
         <v>2.1</v>
@@ -15856,7 +15883,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B4" s="18">
         <v>9.0</v>
@@ -15882,7 +15909,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="22" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="L4" s="21">
         <v>2.63</v>
@@ -15896,7 +15923,7 @@
         <v>3.0</v>
       </c>
       <c r="Q4" s="23" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="R4" s="21">
         <v>1.0</v>
@@ -15905,7 +15932,7 @@
         <v>3.0</v>
       </c>
       <c r="T4" s="23" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
       <c r="U4" s="21">
         <v>2.33</v>
@@ -15924,7 +15951,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -15951,7 +15978,7 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="L5" s="3">
         <v>2.38</v>
@@ -15963,7 +15990,7 @@
         <v>20.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -15972,7 +15999,7 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>163</v>
+        <v>180</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -15980,7 +16007,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -15999,7 +16026,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16017,7 +16044,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>164</v>
+        <v>183</v>
       </c>
       <c r="L7" s="3">
         <v>2.38</v>
@@ -16029,7 +16056,7 @@
         <v>16.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>165</v>
+        <v>185</v>
       </c>
       <c r="R7" s="3">
         <v>1.69</v>
@@ -16038,7 +16065,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>22.0</v>
@@ -16067,7 +16094,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16082,7 +16109,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>166</v>
+        <v>190</v>
       </c>
       <c r="L9" s="3">
         <v>2.36</v>
@@ -16094,7 +16121,7 @@
         <v>24.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>167</v>
+        <v>192</v>
       </c>
       <c r="R9" s="3">
         <v>2.04</v>
@@ -16103,7 +16130,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16111,7 +16138,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16123,7 +16150,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>168</v>
+        <v>195</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -16135,7 +16162,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16153,7 +16180,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16162,7 +16189,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16177,7 +16204,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16193,10 +16220,10 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
@@ -16252,7 +16279,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>169</v>
+        <v>203</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16299,7 +16326,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>170</v>
+        <v>207</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -16343,7 +16370,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16390,7 +16417,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>172</v>
+        <v>215</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16437,7 +16464,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>173</v>
+        <v>220</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16484,7 +16511,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>176</v>
+        <v>224</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16507,37 +16534,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H23" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K23" s="16"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16554,7 +16581,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16571,7 +16598,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16588,7 +16615,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16613,7 +16640,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16749,7 +16776,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16773,7 +16800,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>174</v>
+        <v>155</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -16785,7 +16812,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>175</v>
+        <v>157</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -16794,7 +16821,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>177</v>
+        <v>159</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -16802,7 +16829,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16813,7 +16840,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16840,7 +16867,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>178</v>
+        <v>161</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -16852,7 +16879,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>179</v>
+        <v>162</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -16861,7 +16888,7 @@
         <v>7.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="U4" s="3">
         <v>2.29</v>
@@ -16869,7 +16896,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16881,7 +16908,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16890,7 +16917,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
       <c r="R5" s="3">
         <v>1.45</v>
@@ -16899,7 +16926,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -16907,7 +16934,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16937,7 +16964,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>182</v>
+        <v>166</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -16952,7 +16979,7 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="R6" s="3">
         <v>0.5</v>
@@ -16961,7 +16988,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -16969,7 +16996,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -16987,7 +17014,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>184</v>
+        <v>170</v>
       </c>
       <c r="L7" s="3">
         <v>2.36</v>
@@ -16999,7 +17026,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>185</v>
+        <v>171</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -17007,7 +17034,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17028,7 +17055,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>186</v>
+        <v>173</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -17040,7 +17067,7 @@
         <v>9.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R8" s="3">
         <v>1.11</v>
@@ -17049,7 +17076,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="U8" s="3">
         <v>2.0</v>
@@ -17057,7 +17084,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C9" s="3">
         <v>1.0</v>
@@ -17082,7 +17109,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17091,7 +17118,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17103,7 +17130,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="L10" s="3">
         <v>1.75</v>
@@ -17115,7 +17142,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17124,7 +17151,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17145,7 +17172,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17157,7 +17184,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17166,7 +17193,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17187,7 +17214,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="L12" s="3">
         <v>2.25</v>
@@ -17199,7 +17226,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="R12" s="3">
         <v>0.75</v>
@@ -17208,7 +17235,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17216,7 +17243,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17231,7 +17258,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17243,14 +17270,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17259,7 +17286,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17275,10 +17302,10 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
@@ -17334,7 +17361,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17381,7 +17408,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>194</v>
+        <v>206</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17425,7 +17452,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17472,7 +17499,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>196</v>
+        <v>213</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17519,7 +17546,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>197</v>
+        <v>217</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17566,7 +17593,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>198</v>
+        <v>223</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17589,37 +17616,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I25" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17636,7 +17663,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17653,7 +17680,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17670,7 +17697,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17686,7 +17713,7 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17822,7 +17849,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17846,7 +17873,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>199</v>
+        <v>172</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17858,7 +17885,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>200</v>
+        <v>176</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17867,7 +17894,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>201</v>
+        <v>179</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17875,7 +17902,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17896,7 +17923,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -17906,7 +17933,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>204</v>
+        <v>182</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -17914,7 +17941,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -17941,7 +17968,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>207</v>
+        <v>186</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -17950,7 +17977,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>209</v>
+        <v>187</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -17959,7 +17986,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>210</v>
+        <v>188</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -17967,7 +17994,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -17991,7 +18018,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>213</v>
+        <v>189</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -18015,7 +18042,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -18033,7 +18060,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>216</v>
+        <v>194</v>
       </c>
       <c r="L6" s="3">
         <v>1.429</v>
@@ -18054,7 +18081,7 @@
         <v>3.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>219</v>
+        <v>196</v>
       </c>
       <c r="U6" s="3">
         <v>1.333</v>
@@ -18062,7 +18089,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18078,7 +18105,7 @@
         <v>13.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>220</v>
+        <v>198</v>
       </c>
       <c r="R7" s="3">
         <v>1.615</v>
@@ -18087,7 +18114,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>222</v>
+        <v>199</v>
       </c>
       <c r="U7" s="3">
         <v>2.75</v>
@@ -18095,7 +18122,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -18114,7 +18141,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18126,7 +18153,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>226</v>
+        <v>200</v>
       </c>
       <c r="L9" s="3">
         <v>1.833</v>
@@ -18136,7 +18163,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18167,7 +18194,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18183,10 +18210,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -18242,7 +18269,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>232</v>
+        <v>216</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18286,7 +18313,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18328,7 +18355,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18369,7 +18396,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18404,7 +18431,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18451,7 +18478,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18471,37 +18498,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18530,7 +18557,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18559,12 +18586,12 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -18574,7 +18601,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18710,7 +18737,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18752,7 +18779,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18761,7 +18788,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18769,7 +18796,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18808,7 +18835,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18825,7 +18852,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18859,7 +18886,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18871,7 +18898,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -18883,7 +18910,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R5" s="3">
         <v>1.176</v>
@@ -18892,7 +18919,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="U5" s="3">
         <v>1.667</v>
@@ -18900,7 +18927,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -18924,7 +18951,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="L6" s="3">
         <v>3.375</v>
@@ -18936,7 +18963,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="R6" s="3">
         <v>1.667</v>
@@ -18945,7 +18972,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -18953,7 +18980,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -18971,7 +18998,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="L7" s="3">
         <v>2.5</v>
@@ -18983,7 +19010,7 @@
         <v>8.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -18992,7 +19019,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -19000,7 +19027,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -19016,7 +19043,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -19036,7 +19063,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -19060,7 +19087,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -19073,7 +19100,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>203</v>
+        <v>181</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19081,7 +19108,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19099,7 +19126,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -19108,7 +19135,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>40</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19117,7 +19144,7 @@
         <v>2.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -19126,7 +19153,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19141,7 +19168,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19153,7 +19180,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19169,10 +19196,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -19225,7 +19252,7 @@
         <v>19.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="M16" s="3">
         <v>1.053</v>
@@ -19272,7 +19299,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="M17" s="3">
         <v>1.4</v>
@@ -19313,7 +19340,7 @@
         <v>4.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="M18" s="3">
         <v>1.75</v>
@@ -19360,7 +19387,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M19" s="3">
         <v>1.818</v>
@@ -19459,38 +19486,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19517,7 +19544,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19547,7 +19574,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19576,7 +19603,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
     </row>
     <row r="29">
@@ -19586,7 +19613,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19722,7 +19749,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19761,7 +19788,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>53</v>
+        <v>80</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19817,7 +19844,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19870,7 +19897,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -19921,7 +19948,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -19929,7 +19956,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -19959,7 +19986,7 @@
         <v>7.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="L6" s="3">
         <v>2.43</v>
@@ -19977,7 +20004,7 @@
         <v>13.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="R6" s="3">
         <v>1.69</v>
@@ -19986,7 +20013,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -19994,7 +20021,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -20019,7 +20046,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -20027,7 +20054,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D8" s="3">
         <v>16.0</v>
@@ -20051,7 +20078,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="L8" s="3">
         <v>2.44</v>
@@ -20069,7 +20096,7 @@
         <v>3.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="R8" s="3">
         <v>2.33</v>
@@ -20078,7 +20105,7 @@
         <v>3.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="U8" s="3">
         <v>1.0</v>
@@ -20086,7 +20113,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20113,7 +20140,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L9" s="3">
         <v>2.18</v>
@@ -20126,7 +20153,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="U9" s="3">
         <v>2.0</v>
@@ -20151,7 +20178,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20167,10 +20194,10 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
@@ -20276,7 +20303,7 @@
         <v>9.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="M17" s="3">
         <v>2.33</v>
@@ -20461,7 +20488,7 @@
         <v>9.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="M21" s="3">
         <v>1.67</v>
@@ -20484,37 +20511,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="H24" s="14" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="I24" s="15" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20531,7 +20558,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20548,7 +20575,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20565,7 +20592,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20599,7 +20626,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -20,7 +20,7 @@
     <sheet state="hidden" name="Cornerstone 923" sheetId="15" r:id="rId19"/>
     <sheet state="hidden" name="Heritage 923" sheetId="16" r:id="rId20"/>
     <sheet state="visible" name="Copy - do not fill" sheetId="17" r:id="rId21"/>
-    <sheet state="visible" name="Cornerstone 930" sheetId="18" r:id="rId22"/>
+    <sheet state="hidden" name="Cornerstone 930" sheetId="18" r:id="rId22"/>
     <sheet state="hidden" name="SMCS 924" sheetId="19" r:id="rId23"/>
     <sheet state="hidden" name="Whitefield 925" sheetId="20" r:id="rId24"/>
     <sheet state="hidden" name="Eagle Heights - 922" sheetId="21" r:id="rId25"/>
@@ -97,46 +97,91 @@
     <t>FB receive rating (grade divided by attempts)</t>
   </si>
   <si>
+    <t>Shiloh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
     <t>Cora</t>
   </si>
   <si>
-    <t>Shiloh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
+    <t xml:space="preserve">Nataly </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - </t>
+  </si>
+  <si>
+    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
   </si>
   <si>
     <t>Anna</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
+    <t xml:space="preserve">3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Agnes</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">Nataly </t>
+    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t>Nataly</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
   </si>
   <si>
     <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>Agnes</t>
+    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Bridget</t>
+  </si>
+  <si>
+    <t>Addy</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - </t>
@@ -145,43 +190,70 @@
     <t>Annabelle</t>
   </si>
   <si>
+    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>Kinley</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
+    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - </t>
+    <t xml:space="preserve">3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
+    <t>Gaby</t>
+  </si>
+  <si>
+    <t>Audri</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t>Bridget</t>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
@@ -190,64 +262,79 @@
     <t xml:space="preserve">2 - 1 - </t>
   </si>
   <si>
-    <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - </t>
+    <t>3 - 0 - 1</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
   </si>
   <si>
+    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - </t>
   </si>
   <si>
-    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
     <t>Corena</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t>Gaby</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>1 - 1 - 1 - 0 - 0</t>
+  </si>
+  <si>
+    <t>Tea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Addy</t>
+    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 3 - </t>
   </si>
   <si>
+    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+  </si>
+  <si>
     <t>Elena</t>
   </si>
   <si>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
     <t>Rotation (follow setter starting position)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
   </si>
   <si>
     <t>Kill Efficiency</t>
@@ -256,13 +343,19 @@
     <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
   </si>
   <si>
-    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
   </si>
   <si>
     <t>Block (partial touch)</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
+    <t xml:space="preserve">3 - 0 - </t>
   </si>
   <si>
     <t>Serve Receive Attempts</t>
@@ -271,118 +364,82 @@
     <t>Serve Receive Grade (0-3)</t>
   </si>
   <si>
+    <t>Emma</t>
+  </si>
+  <si>
     <t>Serve Receive Avg Score</t>
   </si>
   <si>
     <t>Serve Aces</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
     <t>Serve Errors</t>
   </si>
   <si>
     <t>Points Scored in Rotation</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
     <t>Points Scored Against Rotation</t>
   </si>
   <si>
+    <t>Piper</t>
+  </si>
+  <si>
     <t>Rotation Net Score (+ or -)</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>Kinley</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
   </si>
   <si>
-    <t>Audri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - </t>
+    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
   </si>
   <si>
-    <t>3 - 0 - 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
     <t>Team</t>
   </si>
   <si>
-    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
     <t>Total Aces (us)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t>Service error (us)</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
-  </si>
-  <si>
     <t>Ace % (us)</t>
   </si>
   <si>
-    <t>Tea</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
+    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
     <t>Service Error % (us)</t>
@@ -391,108 +448,51 @@
     <t>Aces (them)</t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t>Service Errors (them)</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
+    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
     <t>Ace % (them)</t>
   </si>
   <si>
-    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t>Service Error % (Them)</t>
   </si>
   <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t>Set 1</t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
     <t>Set 2</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
     <t>Set 3</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
-  </si>
-  <si>
     <t>Set 4</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 2 - </t>
-  </si>
-  <si>
     <t>Set 5</t>
   </si>
   <si>
     <t>Total</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - </t>
-  </si>
-  <si>
-    <t>Emma</t>
-  </si>
-  <si>
     <t>Team Kill Efficiency (all games)</t>
   </si>
   <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>Team Passer Rating (all games)</t>
   </si>
   <si>
@@ -511,36 +511,36 @@
     <t xml:space="preserve">3 - 2 - 1 - 2 - 5 - 0 - 5 - 1 - 5 - 5 - 1 - 5 - 3 - 0 - 5 - 1 - 1 - 5 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 1 - 1 - 3 - 1 - 2 - 0 - 2 - 2 - 2 - 3 - 1 - 2 - 2 - 1 - 3 - 2 - 2 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 5 - 2 - 2 - 1 - 3 - 3 - 0 - 5 - 3 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 3 - 1 - 1 - 1 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 2 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 1 - 1 - 1 - 1 - 2 - 1 - 2 - 2 - 3 - 1 - 2 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
   </si>
   <si>
@@ -550,12 +550,12 @@
     <t xml:space="preserve">0 - 0 - 3 - 2 - 3 - 2 - 5 - 2 - 5 - 0 - 3 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 3 - 1 - 0 - 1 - 3 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - </t>
   </si>
   <si>
@@ -577,12 +577,12 @@
     <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
   </si>
   <si>
@@ -592,72 +592,72 @@
     <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t>2- 1- 0- 3- 1</t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>0- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t>2- 2- 3- 3- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
+  </si>
+  <si>
+    <t>2- 3- 2- 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+    <t>3- 2- 3- 5- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
-  </si>
-  <si>
-    <t>2- 1- 0- 3- 1</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2- 3- 2- 3</t>
-  </si>
-  <si>
-    <t>0- 0</t>
-  </si>
-  <si>
-    <t>2- 2- 3- 3- 2</t>
-  </si>
-  <si>
-    <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
-  </si>
-  <si>
-    <t>2- 3- 2- 2</t>
-  </si>
-  <si>
-    <t>3- 2- 3- 5- 3</t>
-  </si>
-  <si>
     <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
@@ -673,15 +673,63 @@
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
+    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
+  </si>
+  <si>
+    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 3- 2- </t>
+  </si>
+  <si>
+    <t>2- 1- 2- 0- 0</t>
+  </si>
+  <si>
+    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
+  </si>
+  <si>
+    <t>3- 1- 2- 1</t>
+  </si>
+  <si>
     <t>1- 3- 0- 3- 1</t>
   </si>
   <si>
+    <t>3- 1- 5- 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
   </si>
   <si>
+    <t>3- 0</t>
+  </si>
+  <si>
+    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0- 2- 3- </t>
+  </si>
+  <si>
+    <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
+  </si>
+  <si>
+    <t>2- 2- 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- </t>
+  </si>
+  <si>
+    <t>1- 3- 0- 1- 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">2- 1- 1- </t>
   </si>
   <si>
+    <t>1- 2- 0- 0- 1- 0</t>
+  </si>
+  <si>
+    <t>2- 3- 1- 2</t>
+  </si>
+  <si>
     <t>1- 0- 3- 2- 0- 1- 1</t>
   </si>
   <si>
@@ -691,54 +739,6 @@
     <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
-    <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- 3- 2- </t>
-  </si>
-  <si>
-    <t>2- 1- 2- 0- 0</t>
-  </si>
-  <si>
-    <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
-  </si>
-  <si>
-    <t>3- 1- 2- 1</t>
-  </si>
-  <si>
-    <t>3- 1- 5- 2</t>
-  </si>
-  <si>
-    <t>3- 0</t>
-  </si>
-  <si>
-    <t>0- 2- 1- 1- 1- 0- 1- 1- 2- 0- 0- 1- 2- 2- 2- 1- 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0- 2- 3- </t>
-  </si>
-  <si>
-    <t>3- 2- 3- 5- 5- 3- 0- 3- 3</t>
-  </si>
-  <si>
-    <t>2- 2- 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3- </t>
-  </si>
-  <si>
-    <t>1- 3- 0- 1- 0</t>
-  </si>
-  <si>
-    <t>1- 2- 0- 0- 1- 0</t>
-  </si>
-  <si>
-    <t>2- 3- 1- 2</t>
-  </si>
-  <si>
     <t>5- 3- 0- 0</t>
   </si>
   <si>
@@ -949,24 +949,30 @@
     <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 1- 1 - 0 - 2 - 3 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
   </si>
   <si>
@@ -976,9 +982,6 @@
     <t xml:space="preserve">2- 2- 2- 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 0- 2 - 5 - 3 - 3 - 1 - 5 - 3 - 5 - 3 - 5 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
@@ -988,33 +991,48 @@
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 0 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 3 - 3 - 1 - 0 - 3 - 0 - 5 - 2 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 0 - 2 - 2 - 1 - 1 - 2 - 3 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 1 - 3 - 2 - 2 - 2 - 2 - 2 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 2 - 2 - 3 - 2 - 3 - 3 - 3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2- 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - 2 - 0 - 1 - 3 - 2 - 1 - 3 - 3 - 5 - 3 - 5 - 3 - 5 - 5 - 3 - 3 - 5 - 5 - 5 - 5 - 3 - 5 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1036,27 +1054,12 @@
     <t xml:space="preserve">1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 5 - 3 - 5 - 3 - 0 - 3 - 3 - 3 - 3 - 0 - 5 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 0 - 2 - 1 - 2 - 2 - 2 - 3 - 3 - 3 - 0 - 3 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 0 - 2 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 3 - 3 - 0 - 3 - 5 - 3 - 3 - 0 - </t>
   </si>
   <si>
@@ -1066,9 +1069,6 @@
     <t xml:space="preserve">3 - 3 - 1 - 3 - 3 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1- 1 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 5 - 0 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
@@ -1153,67 +1153,67 @@
     <t xml:space="preserve">3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 3 - 2 - 0 - 1 - 3 - 3 - 3 - 3 - 2 - 3 - 3 - 2 - 2 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 0 - 2 - 3 - 1 - 1 - 3 - 2 - 2 - 1 - 3 - 2 - 1 - 0 - 0 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
+  </si>
+  <si>
     <t>119 attack attempts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
@@ -1555,6 +1555,7 @@
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
@@ -1579,7 +1580,6 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="9" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
@@ -1988,7 +1988,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -2012,7 +2012,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2024,7 +2024,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2060,7 +2060,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2072,7 +2072,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2081,7 +2081,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2099,7 +2099,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>87</v>
+        <v>53</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2114,7 +2114,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2135,7 +2135,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2144,7 +2144,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2153,7 +2153,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>97</v>
+        <v>71</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2177,7 +2177,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>101</v>
+        <v>73</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2186,7 +2186,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>104</v>
+        <v>76</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2195,7 +2195,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2207,7 +2207,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>106</v>
+        <v>81</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2219,7 +2219,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>107</v>
+        <v>85</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2228,7 +2228,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2241,7 +2241,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2268,7 +2268,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>123</v>
+        <v>94</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2283,7 +2283,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2292,7 +2292,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B10" s="3">
         <v>5.0</v>
@@ -2319,7 +2319,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>131</v>
+        <v>103</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2328,7 +2328,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2337,7 +2337,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2358,7 +2358,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2376,7 +2376,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2415,40 +2415,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2488,37 +2488,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2547,7 +2547,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2573,7 +2573,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2602,7 +2602,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2631,12 +2631,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2644,10 +2644,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.33</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.12</v>
       </c>
       <c r="F31" s="3">
@@ -2656,10 +2656,10 @@
       <c r="G31" s="3">
         <v>17.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.18</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.19</v>
       </c>
     </row>
@@ -2668,7 +2668,7 @@
         <v>153</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
     </row>
     <row r="34">
@@ -2777,7 +2777,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2819,7 +2819,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2827,7 +2827,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -2863,7 +2863,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2903,7 +2903,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2911,7 +2911,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2959,7 +2959,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2967,7 +2967,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -3023,7 +3023,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
         <v>8.0</v>
@@ -3044,7 +3044,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3068,7 +3068,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3121,7 +3121,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3133,7 +3133,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3146,7 +3146,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3155,7 +3155,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3180,7 +3180,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3196,36 +3196,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3495,37 +3495,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3556,7 +3556,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3573,17 +3573,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3591,10 +3591,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.14</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.18</v>
       </c>
       <c r="F31" s="3">
@@ -3603,16 +3603,16 @@
       <c r="G31" s="3">
         <v>14.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.25</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.18</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -3719,7 +3719,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
         <v>17.0</v>
@@ -3764,7 +3764,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3814,7 +3814,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3831,7 +3831,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3890,7 +3890,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3946,7 +3946,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3969,7 +3969,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3977,7 +3977,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -4010,7 +4010,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4019,7 +4019,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4027,7 +4027,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -4057,7 +4057,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4085,7 +4085,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4093,7 +4093,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4108,7 +4108,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4118,7 +4118,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4136,7 +4136,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4145,7 +4145,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4175,7 +4175,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4193,7 +4193,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4205,7 +4205,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4238,7 +4238,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4250,7 +4250,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4269,7 +4269,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4285,36 +4285,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4394,7 +4394,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4438,7 +4438,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4482,7 +4482,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -4529,7 +4529,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>318</v>
+        <v>308</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4596,37 +4596,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K25" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4660,7 +4660,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4677,17 +4677,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4695,10 +4695,10 @@
       <c r="C32" s="3">
         <v>12.0</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.23</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.16</v>
       </c>
       <c r="F32" s="3">
@@ -4707,16 +4707,16 @@
       <c r="G32" s="3">
         <v>9.0</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.27</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.12</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
@@ -4823,7 +4823,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -4851,7 +4851,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4868,7 +4868,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4895,7 +4895,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4907,7 +4907,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4916,7 +4916,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4951,7 +4951,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4963,7 +4963,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4972,7 +4972,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4980,7 +4980,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5007,7 +5007,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5019,7 +5019,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5028,7 +5028,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5036,7 +5036,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="H6" s="3">
         <v>13.0</v>
@@ -5069,7 +5069,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5084,7 +5084,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5093,7 +5093,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5117,7 +5117,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5129,7 +5129,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5137,7 +5137,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5165,7 +5165,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5192,7 +5192,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5217,7 +5217,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5233,36 +5233,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5295,7 +5295,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>334</v>
+        <v>324</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5342,7 +5342,7 @@
         <v>10.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>335</v>
+        <v>325</v>
       </c>
       <c r="M17" s="3">
         <v>1.0</v>
@@ -5389,7 +5389,7 @@
         <v>5.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>338</v>
+        <v>326</v>
       </c>
       <c r="M18" s="3">
         <v>1.0</v>
@@ -5433,7 +5433,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>339</v>
+        <v>327</v>
       </c>
       <c r="M19" s="3">
         <v>1.0</v>
@@ -5477,7 +5477,7 @@
         <v>5.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>340</v>
+        <v>328</v>
       </c>
       <c r="M20" s="3">
         <v>1.2</v>
@@ -5521,7 +5521,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>344</v>
+        <v>329</v>
       </c>
       <c r="M21" s="3">
         <v>0.8</v>
@@ -5544,37 +5544,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5603,7 +5603,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5620,7 +5620,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5637,7 +5637,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5654,12 +5654,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5667,34 +5667,34 @@
       <c r="C31" s="3">
         <v>15.0</v>
       </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
       <c r="F31" s="3">
         <v>13.0</v>
       </c>
       <c r="G31" s="3">
         <v>17.0</v>
       </c>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="32">
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.28</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.16</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.19</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.25</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5828,7 +5828,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="L2" s="3">
         <v>2.17</v>
@@ -5840,7 +5840,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="R2" s="3">
         <v>1.92</v>
@@ -5849,7 +5849,7 @@
         <v>10.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -5857,7 +5857,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5887,7 +5887,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="L3" s="3">
         <v>3.42</v>
@@ -5899,7 +5899,7 @@
         <v>14.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="R3" s="3">
         <v>1.64</v>
@@ -5908,7 +5908,7 @@
         <v>21.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="U3" s="3">
         <v>2.49</v>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5946,7 +5946,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="L4" s="3">
         <v>2.07</v>
@@ -5961,7 +5961,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -5970,7 +5970,7 @@
         <v>8.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="U4" s="3">
         <v>2.13</v>
@@ -5978,7 +5978,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -6001,7 +6001,7 @@
         <v>2.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="U5" s="3">
         <v>1.0</v>
@@ -6009,7 +6009,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6031,7 +6031,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6048,7 +6048,7 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B7" s="19">
         <v>4.0</v>
@@ -6068,7 +6068,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="22" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="L7" s="21">
         <v>2.94</v>
@@ -6082,7 +6082,7 @@
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="R7" s="21">
         <v>1.93</v>
@@ -6091,7 +6091,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6110,7 +6110,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B8" s="3">
         <v>4.0</v>
@@ -6125,7 +6125,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="L8" s="3">
         <v>2.5</v>
@@ -6134,7 +6134,7 @@
         <v>14.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="R8" s="3">
         <v>1.64</v>
@@ -6143,7 +6143,7 @@
         <v>9.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="U8" s="3">
         <v>2.67</v>
@@ -6151,7 +6151,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3">
         <v>28.0</v>
@@ -6177,7 +6177,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6225,7 +6225,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6253,7 +6253,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6269,36 +6269,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6589,37 +6589,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6636,7 +6636,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6653,7 +6653,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6670,7 +6670,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6687,7 +6687,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6704,7 +6704,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6712,10 +6712,10 @@
       <c r="C31" s="3">
         <v>14.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.17</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.13</v>
       </c>
       <c r="F31" s="3">
@@ -6724,16 +6724,16 @@
       <c r="G31" s="3">
         <v>15.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.17</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6840,7 +6840,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6871,7 +6871,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6930,7 +6930,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -6968,7 +6968,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -7021,7 +7021,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7075,7 +7075,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7083,7 +7083,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7105,7 +7105,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7166,7 +7166,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7216,7 +7216,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D10" s="3">
         <v>14.0</v>
@@ -7243,7 +7243,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7276,7 +7276,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7291,7 +7291,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7311,7 +7311,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7327,36 +7327,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7527,7 +7527,7 @@
         <v>19.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="M19" s="3">
         <v>1.68</v>
@@ -7574,7 +7574,7 @@
         <v>4.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="M20" s="3">
         <v>1.75</v>
@@ -7618,7 +7618,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7641,37 +7641,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7688,7 +7688,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7705,7 +7705,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7722,7 +7722,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7739,12 +7739,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7752,10 +7752,10 @@
       <c r="C31" s="3">
         <v>13.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.2</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.15</v>
       </c>
       <c r="F31" s="3">
@@ -7764,16 +7764,16 @@
       <c r="G31" s="3">
         <v>13.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.1</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -7782,7 +7782,7 @@
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
     </row>
   </sheetData>
@@ -7883,7 +7883,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7910,7 +7910,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7928,7 +7928,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7937,7 +7937,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7958,7 +7958,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7971,7 +7971,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -7998,7 +7998,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8010,7 +8010,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8019,7 +8019,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8027,7 +8027,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8048,7 +8048,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8060,7 +8060,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8069,7 +8069,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8077,7 +8077,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8100,7 +8100,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8108,7 +8108,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -8120,7 +8120,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8129,7 +8129,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8138,7 +8138,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8146,7 +8146,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8167,7 +8167,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8179,7 +8179,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8203,7 +8203,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8216,7 +8216,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8224,7 +8224,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -8253,7 +8253,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8268,7 +8268,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8277,7 +8277,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8301,7 +8301,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8331,37 +8331,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K16" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8378,7 +8378,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8395,7 +8395,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8412,7 +8412,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8429,7 +8429,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8446,7 +8446,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8454,10 +8454,10 @@
       <c r="C23" s="3">
         <v>21.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.3</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.24</v>
       </c>
       <c r="F23" s="3">
@@ -8466,16 +8466,16 @@
       <c r="G23" s="3">
         <v>22.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.32</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <v>0.22</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -8582,7 +8582,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8635,7 +8635,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -8668,7 +8668,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8676,7 +8676,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8715,7 +8715,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8732,7 +8732,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D5" s="3">
         <v>10.0</v>
@@ -8752,7 +8752,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8792,7 +8792,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8800,7 +8800,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8848,7 +8848,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8856,7 +8856,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8877,7 +8877,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8897,14 +8897,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8921,7 +8921,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8933,7 +8933,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8948,37 +8948,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K16" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -8995,7 +8995,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9012,7 +9012,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9029,17 +9029,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9047,10 +9047,10 @@
       <c r="C23" s="3">
         <v>8.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.35</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.12</v>
       </c>
       <c r="F23" s="3">
@@ -9059,16 +9059,16 @@
       <c r="G23" s="3">
         <v>13.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.18</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -9230,7 +9230,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9246,36 +9246,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9321,71 +9321,71 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="D31" s="16"/>
-      <c r="E31" s="16"/>
-      <c r="H31" s="16"/>
-      <c r="I31" s="16"/>
+        <v>151</v>
+      </c>
+      <c r="D31" s="17"/>
+      <c r="E31" s="17"/>
+      <c r="H31" s="17"/>
+      <c r="I31" s="17"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -9486,7 +9486,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -9531,7 +9531,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -9569,7 +9569,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3">
         <v>12.0</v>
@@ -9625,7 +9625,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -9667,7 +9667,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B6" s="3">
         <v>3.0</v>
@@ -9707,7 +9707,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -9766,7 +9766,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>9.0</v>
@@ -9785,7 +9785,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D9" s="3">
         <v>10.0</v>
@@ -9816,7 +9816,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -9824,7 +9824,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -9838,13 +9838,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -9853,7 +9853,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -9874,37 +9874,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K16" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -9921,7 +9921,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -9938,7 +9938,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B19" s="3">
         <v>2.0</v>
@@ -9955,17 +9955,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>10.0</v>
@@ -9973,22 +9973,28 @@
       <c r="C23" s="3">
         <v>14.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.15</v>
       </c>
-      <c r="E23" s="16"/>
+      <c r="E23" s="17">
+        <v>0.22</v>
+      </c>
       <c r="F23" s="3">
         <v>12.0</v>
       </c>
       <c r="G23" s="3">
         <v>16.0</v>
       </c>
-      <c r="H23" s="16"/>
-      <c r="I23" s="16"/>
+      <c r="H23" s="17">
+        <v>0.16</v>
+      </c>
+      <c r="I23" s="17">
+        <v>0.22</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10092,7 +10098,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -10151,7 +10157,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -10194,7 +10200,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -10212,7 +10218,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -10225,7 +10231,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -10233,7 +10239,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -10292,7 +10298,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -10334,7 +10340,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10342,7 +10348,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D7" s="3">
         <v>14.0</v>
@@ -10367,7 +10373,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -10426,7 +10432,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -10448,7 +10454,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -10491,37 +10497,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G16" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I16" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K16" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B16" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C16" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D16" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E16" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H16" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="16"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -10538,7 +10544,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -10555,7 +10561,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -10572,7 +10578,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -10589,12 +10595,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -10602,10 +10608,10 @@
       <c r="C23" s="3">
         <v>9.0</v>
       </c>
-      <c r="D23" s="16">
+      <c r="D23" s="17">
         <v>0.27</v>
       </c>
-      <c r="E23" s="16">
+      <c r="E23" s="17">
         <v>0.11</v>
       </c>
       <c r="F23" s="3">
@@ -10614,16 +10620,16 @@
       <c r="G23" s="3">
         <v>17.0</v>
       </c>
-      <c r="H23" s="16">
+      <c r="H23" s="17">
         <v>0.26</v>
       </c>
-      <c r="I23" s="16">
+      <c r="I23" s="17">
         <v>0.2</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B25" s="2"/>
     </row>
@@ -10730,7 +10736,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10754,7 +10760,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10766,7 +10772,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10775,7 +10781,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10783,7 +10789,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10801,7 +10807,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10814,7 +10820,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10822,7 +10828,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10849,7 +10855,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10861,7 +10867,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10870,7 +10876,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10878,7 +10884,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -10890,7 +10896,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10899,7 +10905,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10908,7 +10914,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10916,7 +10922,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10952,7 +10958,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10961,7 +10967,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10969,7 +10975,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -11008,7 +11014,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>15.0</v>
@@ -11033,7 +11039,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -11042,7 +11048,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -11060,7 +11066,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -11073,7 +11079,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -11081,7 +11087,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -11095,7 +11101,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -11110,7 +11116,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -11119,13 +11125,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -11140,7 +11146,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -11156,40 +11162,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -11222,7 +11228,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -11239,7 +11245,7 @@
       <c r="Q16" s="3">
         <v>6.0</v>
       </c>
-      <c r="R16" s="17">
+      <c r="R16" s="9">
         <f>10</f>
         <v>10</v>
       </c>
@@ -11270,7 +11276,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>142</v>
+        <v>124</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -11317,7 +11323,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -11364,7 +11370,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11411,7 +11417,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11455,7 +11461,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11475,37 +11481,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11522,7 +11528,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11539,7 +11545,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11556,7 +11562,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11573,7 +11579,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11590,7 +11596,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11598,10 +11604,10 @@
       <c r="C31" s="3">
         <v>22.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.29</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.22</v>
       </c>
       <c r="F31" s="3">
@@ -11610,16 +11616,16 @@
       <c r="G31" s="3">
         <v>8.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.19</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.07</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -11726,7 +11732,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -11779,7 +11785,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -11838,7 +11844,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11886,7 +11892,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -11945,7 +11951,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -11995,7 +12001,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -12026,7 +12032,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -12034,7 +12040,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -12070,7 +12076,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -12079,7 +12085,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3">
         <v>1.0</v>
@@ -12108,7 +12114,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -12122,7 +12128,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12131,7 +12137,7 @@
         <v>2.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U11" s="3">
         <v>2.0</v>
@@ -12139,7 +12145,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12151,7 +12157,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12165,37 +12171,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K17" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12212,7 +12218,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12229,7 +12235,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12246,7 +12252,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12263,7 +12269,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12280,7 +12286,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12288,10 +12294,10 @@
       <c r="C24" s="3">
         <v>14.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>0.16</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.15</v>
       </c>
       <c r="F24" s="3">
@@ -12300,16 +12306,16 @@
       <c r="G24" s="3">
         <v>14.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.18</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -12416,7 +12422,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3">
         <v>9.0</v>
@@ -12449,7 +12455,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12457,7 +12463,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12510,7 +12516,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12549,7 +12555,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12558,7 +12564,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12566,7 +12572,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12625,7 +12631,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12647,7 +12653,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12683,7 +12689,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12692,7 +12698,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12714,7 +12720,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12737,13 +12743,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12752,7 +12758,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -12761,7 +12767,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12782,7 +12788,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12803,7 +12809,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -12821,7 +12827,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -12836,7 +12842,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -12848,7 +12854,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -12884,37 +12890,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K17" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -12931,7 +12937,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -12942,7 +12948,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -12959,17 +12965,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -12977,10 +12983,10 @@
       <c r="C24" s="3">
         <v>5.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>0.12</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.12</v>
       </c>
       <c r="F24" s="3">
@@ -12989,16 +12995,16 @@
       <c r="G24" s="3">
         <v>8.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.26</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>0.11</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13105,7 +13111,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -13144,7 +13150,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13164,7 +13170,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13214,7 +13220,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13273,7 +13279,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13329,7 +13335,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13351,7 +13357,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13359,7 +13365,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13392,7 +13398,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13400,7 +13406,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D9" s="3">
         <v>18.0</v>
@@ -13429,7 +13435,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13452,7 +13458,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13460,7 +13466,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13484,7 +13490,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13502,7 +13508,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13563,37 +13569,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F17" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G17" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H17" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I17" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K17" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B17" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C17" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E17" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G17" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H17" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K17" s="16"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13610,7 +13616,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13627,7 +13633,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13641,7 +13647,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13658,7 +13664,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13672,7 +13678,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13680,10 +13686,10 @@
       <c r="C24" s="3">
         <v>9.0</v>
       </c>
-      <c r="D24" s="16">
+      <c r="D24" s="17">
         <v>0.16</v>
       </c>
-      <c r="E24" s="16">
+      <c r="E24" s="17">
         <v>0.11</v>
       </c>
       <c r="F24" s="3">
@@ -13692,16 +13698,16 @@
       <c r="G24" s="3">
         <v>13.0</v>
       </c>
-      <c r="H24" s="16">
+      <c r="H24" s="17">
         <v>0.25</v>
       </c>
-      <c r="I24" s="16">
+      <c r="I24" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B26" s="2"/>
     </row>
@@ -13808,7 +13814,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D2" s="3">
         <v>3.0</v>
@@ -13836,7 +13842,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -13851,7 +13857,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -13863,7 +13869,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -13872,7 +13878,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -13896,7 +13902,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -13909,7 +13915,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -13917,7 +13923,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -13944,7 +13950,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -13956,7 +13962,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -13965,7 +13971,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -13992,7 +13998,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -14004,7 +14010,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -14013,7 +14019,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>45</v>
+        <v>69</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -14021,7 +14027,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -14045,7 +14051,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -14057,7 +14063,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -14066,7 +14072,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -14074,7 +14080,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -14092,7 +14098,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>55</v>
+        <v>77</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -14104,7 +14110,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -14113,7 +14119,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14121,7 +14127,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -14135,7 +14141,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14144,7 +14150,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14156,7 +14162,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14165,7 +14171,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14173,7 +14179,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14182,7 +14188,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>67</v>
+        <v>93</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14194,7 +14200,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14215,7 +14221,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14231,40 +14237,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>75</v>
+        <v>106</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14297,7 +14303,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14339,7 +14345,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14386,7 +14392,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>96</v>
+        <v>122</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14433,7 +14439,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14477,7 +14483,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>103</v>
+        <v>126</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14515,7 +14521,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14538,37 +14544,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14585,7 +14591,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14602,7 +14608,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14619,17 +14625,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14637,10 +14643,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.27</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.16</v>
       </c>
       <c r="F31" s="3">
@@ -14649,16 +14655,16 @@
       <c r="G31" s="3">
         <v>12.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.32</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
@@ -14765,7 +14771,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -14792,7 +14798,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -14804,7 +14810,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>65</v>
+        <v>42</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -14813,7 +14819,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>81</v>
+        <v>47</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -14821,7 +14827,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -14848,7 +14854,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>89</v>
+        <v>55</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -14863,7 +14869,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>92</v>
+        <v>58</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -14872,7 +14878,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14893,7 +14899,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>98</v>
+        <v>63</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -14905,7 +14911,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -14914,7 +14920,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -14922,7 +14928,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -14932,7 +14938,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -14945,7 +14951,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14972,7 +14978,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -14984,7 +14990,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>111</v>
+        <v>82</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -14993,7 +14999,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>113</v>
+        <v>84</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -15001,7 +15007,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -15028,7 +15034,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -15040,7 +15046,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>121</v>
+        <v>90</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -15049,7 +15055,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -15057,7 +15063,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>13.0</v>
@@ -15085,7 +15091,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -15094,7 +15100,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -15106,7 +15112,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -15115,7 +15121,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>129</v>
+        <v>100</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15124,7 +15130,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15132,7 +15138,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15147,7 +15153,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>134</v>
+        <v>104</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15156,7 +15162,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15165,7 +15171,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15186,7 +15192,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15199,7 +15205,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15207,7 +15213,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15222,7 +15228,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15231,7 +15237,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>141</v>
+        <v>115</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15240,7 +15246,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15248,7 +15254,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15260,7 +15266,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15278,7 +15284,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15296,7 +15302,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15312,36 +15318,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15374,7 +15380,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>146</v>
+        <v>125</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15421,7 +15427,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>148</v>
+        <v>128</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15462,7 +15468,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>149</v>
+        <v>132</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15509,7 +15515,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15550,7 +15556,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15597,7 +15603,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15617,37 +15623,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K25" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15664,7 +15670,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15681,7 +15687,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15698,7 +15704,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15715,12 +15721,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15728,10 +15734,10 @@
       <c r="C32" s="3">
         <v>8.0</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.19</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.14</v>
       </c>
       <c r="F32" s="3">
@@ -15740,16 +15746,16 @@
       <c r="G32" s="3">
         <v>13.0</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.22</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -15856,7 +15862,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -15904,7 +15910,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -15953,7 +15959,7 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B4" s="19">
         <v>9.0</v>
@@ -15993,16 +15999,16 @@
         <v>3.0</v>
       </c>
       <c r="Q4" s="23" t="s">
+        <v>159</v>
+      </c>
+      <c r="R4" s="21">
+        <v>1.0</v>
+      </c>
+      <c r="S4" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="T4" s="23" t="s">
         <v>160</v>
-      </c>
-      <c r="R4" s="21">
-        <v>1.0</v>
-      </c>
-      <c r="S4" s="18">
-        <v>3.0</v>
-      </c>
-      <c r="T4" s="23" t="s">
-        <v>163</v>
       </c>
       <c r="U4" s="21">
         <v>2.33</v>
@@ -16021,7 +16027,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -16060,7 +16066,7 @@
         <v>20.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -16069,7 +16075,7 @@
         <v>6.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -16077,7 +16083,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16096,7 +16102,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16126,7 +16132,7 @@
         <v>16.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="R7" s="3">
         <v>1.69</v>
@@ -16135,7 +16141,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>22.0</v>
@@ -16164,7 +16170,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B9" s="3">
         <v>11.0</v>
@@ -16200,7 +16206,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16208,7 +16214,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16220,7 +16226,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -16232,7 +16238,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16250,7 +16256,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16259,7 +16265,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16274,7 +16280,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16290,36 +16296,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16349,7 +16355,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16440,7 +16446,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16487,7 +16493,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16534,7 +16540,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>192</v>
+        <v>204</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16581,7 +16587,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>195</v>
+        <v>207</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16604,37 +16610,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C23" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D23" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E23" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G23" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H23" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I23" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K23" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B23" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D23" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E23" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F23" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G23" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H23" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I23" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K23" s="16"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16651,7 +16657,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16668,7 +16674,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16685,7 +16691,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16702,7 +16708,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16710,7 +16716,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16718,10 +16724,10 @@
       <c r="C30" s="3">
         <v>23.0</v>
       </c>
-      <c r="D30" s="16">
+      <c r="D30" s="17">
         <v>0.32</v>
       </c>
-      <c r="E30" s="16">
+      <c r="E30" s="17">
         <v>0.22</v>
       </c>
       <c r="F30" s="3">
@@ -16730,16 +16736,16 @@
       <c r="G30" s="3">
         <v>13.0</v>
       </c>
-      <c r="H30" s="16">
+      <c r="H30" s="17">
         <v>0.16</v>
       </c>
-      <c r="I30" s="16">
+      <c r="I30" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B32" s="2"/>
     </row>
@@ -16846,7 +16852,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -16870,7 +16876,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -16882,7 +16888,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -16891,7 +16897,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -16899,7 +16905,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -16910,7 +16916,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -16937,7 +16943,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -16949,7 +16955,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -16966,7 +16972,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -16978,7 +16984,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -16996,7 +17002,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -17004,7 +17010,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -17034,7 +17040,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -17058,7 +17064,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -17066,7 +17072,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -17104,7 +17110,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17146,7 +17152,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U8" s="3">
         <v>2.0</v>
@@ -17154,7 +17160,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="C9" s="3">
         <v>1.0</v>
@@ -17179,7 +17185,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17188,7 +17194,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17212,7 +17218,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>137</v>
+        <v>107</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17221,7 +17227,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17242,7 +17248,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17254,7 +17260,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>56</v>
+        <v>27</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17263,7 +17269,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17305,7 +17311,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17313,7 +17319,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17328,7 +17334,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17340,14 +17346,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17356,7 +17362,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17372,36 +17378,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17431,7 +17437,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17478,7 +17484,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17522,7 +17528,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17569,7 +17575,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17616,7 +17622,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17663,7 +17669,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17686,37 +17692,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D25" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E25" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F25" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G25" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H25" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I25" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K25" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B25" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C25" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D25" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E25" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F25" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I25" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K25" s="16"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17733,7 +17739,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17750,7 +17756,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -17767,7 +17773,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -17778,12 +17784,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -17791,10 +17797,10 @@
       <c r="C32" s="3">
         <v>13.0</v>
       </c>
-      <c r="D32" s="16">
+      <c r="D32" s="17">
         <v>0.21</v>
       </c>
-      <c r="E32" s="16">
+      <c r="E32" s="17">
         <v>0.18</v>
       </c>
       <c r="F32" s="3">
@@ -17803,16 +17809,16 @@
       <c r="G32" s="3">
         <v>12.0</v>
       </c>
-      <c r="H32" s="16">
+      <c r="H32" s="17">
         <v>0.31</v>
       </c>
-      <c r="I32" s="16">
+      <c r="I32" s="17">
         <v>0.13</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B34" s="2"/>
     </row>
@@ -17919,7 +17925,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -17943,7 +17949,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -17955,7 +17961,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -17964,7 +17970,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -17972,7 +17978,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -17993,7 +17999,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -18003,7 +18009,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -18011,7 +18017,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18038,7 +18044,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="L4" s="3">
         <v>2.385</v>
@@ -18047,7 +18053,7 @@
         <v>11.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="R4" s="3">
         <v>1.818</v>
@@ -18056,7 +18062,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="U4" s="3">
         <v>2.25</v>
@@ -18064,7 +18070,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="C5" s="3">
         <v>2.0</v>
@@ -18088,7 +18094,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -18112,7 +18118,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D6" s="3">
         <v>1.0</v>
@@ -18159,7 +18165,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3">
         <v>5.0</v>
@@ -18192,7 +18198,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -18211,7 +18217,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -18233,7 +18239,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -18264,7 +18270,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -18280,36 +18286,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -18339,7 +18345,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="M16" s="3">
         <v>1.6</v>
@@ -18383,7 +18389,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>214</v>
+        <v>221</v>
       </c>
       <c r="M17" s="3">
         <v>2.67</v>
@@ -18397,7 +18403,7 @@
       <c r="Q17" s="3">
         <v>7.0</v>
       </c>
-      <c r="R17" s="17">
+      <c r="R17" s="9">
         <f>10</f>
         <v>10</v>
       </c>
@@ -18425,7 +18431,7 @@
         <v>3.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -18466,7 +18472,7 @@
         <v>7.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="M19" s="3">
         <v>1.14</v>
@@ -18501,7 +18507,7 @@
         <v>3.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="M20" s="3">
         <v>1.33</v>
@@ -18548,7 +18554,7 @@
         <v>5.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="M21" s="3">
         <v>1.6</v>
@@ -18568,37 +18574,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>3.0</v>
@@ -18627,7 +18633,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -18635,10 +18641,10 @@
       <c r="C26" s="3">
         <v>5.0</v>
       </c>
-      <c r="D26" s="16">
+      <c r="D26" s="17">
         <v>0.16</v>
       </c>
-      <c r="E26" s="16">
+      <c r="E26" s="17">
         <v>0.2</v>
       </c>
       <c r="F26" s="3">
@@ -18656,22 +18662,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -18682,7 +18688,7 @@
       <c r="D31" s="24">
         <v>0.14286</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.14286</v>
       </c>
       <c r="F31" s="3">
@@ -18691,16 +18697,16 @@
       <c r="G31" s="3">
         <v>9.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.1212</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.2727</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2">
         <v>0.2</v>
@@ -18807,7 +18813,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B2" s="3">
         <v>8.0</v>
@@ -18837,7 +18843,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="L2" s="3">
         <v>2.364</v>
@@ -18849,7 +18855,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="R2" s="3">
         <v>1.333</v>
@@ -18858,7 +18864,7 @@
         <v>3.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="U2" s="3">
         <v>2.667</v>
@@ -18866,7 +18872,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -18890,7 +18896,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="L3" s="3">
         <v>2.5</v>
@@ -18905,7 +18911,7 @@
         <v>21.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="R3" s="3">
         <v>1.571</v>
@@ -18914,7 +18920,7 @@
         <v>4.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="U3" s="3">
         <v>1.75</v>
@@ -18922,7 +18928,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>88</v>
+        <v>59</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -18946,7 +18952,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="L4" s="3">
         <v>2.75</v>
@@ -18956,7 +18962,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -18968,7 +18974,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -18980,7 +18986,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="R5" s="3">
         <v>1.176</v>
@@ -18989,7 +18995,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="U5" s="3">
         <v>1.667</v>
@@ -18997,7 +19003,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="D6" s="3">
         <v>12.0</v>
@@ -19021,7 +19027,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="L6" s="3">
         <v>3.375</v>
@@ -19033,7 +19039,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="R6" s="3">
         <v>1.667</v>
@@ -19042,7 +19048,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -19050,7 +19056,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -19068,7 +19074,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="L7" s="3">
         <v>2.5</v>
@@ -19080,7 +19086,7 @@
         <v>8.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -19089,7 +19095,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -19097,7 +19103,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>5.0</v>
@@ -19113,7 +19119,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -19133,7 +19139,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -19170,7 +19176,7 @@
         <v>2.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -19178,7 +19184,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>66</v>
+        <v>49</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -19205,7 +19211,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -19223,7 +19229,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>138</v>
+        <v>110</v>
       </c>
       <c r="P13" s="3">
         <v>1.0</v>
@@ -19238,7 +19244,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -19250,7 +19256,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -19266,36 +19272,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -19556,38 +19562,38 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>1.0</v>
@@ -19595,7 +19601,7 @@
       <c r="D25" s="24">
         <v>0.0769</v>
       </c>
-      <c r="E25" s="16">
+      <c r="E25" s="17">
         <v>0.0</v>
       </c>
       <c r="F25" s="3">
@@ -19604,17 +19610,17 @@
       <c r="G25" s="3">
         <v>3.0</v>
       </c>
-      <c r="H25" s="16">
+      <c r="H25" s="17">
         <v>0.2</v>
       </c>
-      <c r="I25" s="16">
+      <c r="I25" s="17">
         <v>0.12</v>
       </c>
       <c r="L25" s="3"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -19644,7 +19650,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -19655,7 +19661,7 @@
       <c r="D27" s="24">
         <v>0.125</v>
       </c>
-      <c r="E27" s="16">
+      <c r="E27" s="17">
         <v>0.25</v>
       </c>
       <c r="F27" s="3">
@@ -19664,26 +19670,26 @@
       <c r="G27" s="3">
         <v>2.0</v>
       </c>
-      <c r="H27" s="16">
+      <c r="H27" s="17">
         <v>0.24</v>
       </c>
-      <c r="I27" s="16">
+      <c r="I27" s="17">
         <v>0.08</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>6.0</v>
@@ -19691,10 +19697,10 @@
       <c r="C31" s="3">
         <v>9.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.15</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.22</v>
       </c>
       <c r="F31" s="3">
@@ -19703,16 +19709,16 @@
       <c r="G31" s="3">
         <v>10.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.18</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.14</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2">
         <v>-0.152</v>
@@ -19819,7 +19825,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -19858,7 +19864,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="B3" s="3">
         <v>6.0</v>
@@ -19914,7 +19920,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -19967,7 +19973,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B5" s="3">
         <v>5.0</v>
@@ -20018,7 +20024,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="U5" s="3">
         <v>3.0</v>
@@ -20026,7 +20032,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -20083,7 +20089,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -20091,7 +20097,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>60</v>
+        <v>83</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -20116,7 +20122,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="U7" s="3">
         <v>2.0</v>
@@ -20124,7 +20130,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="D8" s="3">
         <v>16.0</v>
@@ -20183,7 +20189,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -20248,7 +20254,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>69</v>
+        <v>98</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -20264,36 +20270,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>72</v>
+        <v>101</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>78</v>
+        <v>109</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>79</v>
+        <v>111</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>112</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>83</v>
+        <v>113</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>85</v>
+        <v>116</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -20581,37 +20587,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B24" s="9" t="s">
-        <v>110</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="D24" s="10" t="s">
-        <v>114</v>
-      </c>
-      <c r="E24" s="10" t="s">
-        <v>117</v>
-      </c>
-      <c r="F24" s="11" t="s">
-        <v>118</v>
-      </c>
-      <c r="G24" s="12" t="s">
-        <v>120</v>
-      </c>
-      <c r="H24" s="13" t="s">
-        <v>122</v>
-      </c>
-      <c r="I24" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="K24" s="15"/>
+        <v>129</v>
+      </c>
+      <c r="B24" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="C24" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="E24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="F24" s="12" t="s">
+        <v>137</v>
+      </c>
+      <c r="G24" s="13" t="s">
+        <v>139</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="I24" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="K24" s="16"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="B25" s="3">
         <v>6.0</v>
@@ -20628,7 +20634,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>127</v>
+        <v>147</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -20645,7 +20651,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -20662,7 +20668,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B28" s="3">
         <v>2.0</v>
@@ -20679,7 +20685,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>135</v>
+        <v>150</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -20696,7 +20702,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>136</v>
+        <v>151</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -20704,10 +20710,10 @@
       <c r="C31" s="3">
         <v>19.0</v>
       </c>
-      <c r="D31" s="16">
+      <c r="D31" s="17">
         <v>0.19</v>
       </c>
-      <c r="E31" s="16">
+      <c r="E31" s="17">
         <v>0.19</v>
       </c>
       <c r="F31" s="3">
@@ -20716,16 +20722,16 @@
       <c r="G31" s="3">
         <v>23.0</v>
       </c>
-      <c r="H31" s="16">
+      <c r="H31" s="17">
         <v>0.16</v>
       </c>
-      <c r="I31" s="16">
+      <c r="I31" s="17">
         <v>0.2</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="B33" s="2"/>
     </row>

--- a/source/varsity_stat_workbook.xlsx
+++ b/source/varsity_stat_workbook.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1812" uniqueCount="477">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1819" uniqueCount="478">
   <si>
     <t>Player</t>
   </si>
@@ -101,402 +101,402 @@
     <t>Cora</t>
   </si>
   <si>
+    <t xml:space="preserve">0 - </t>
+  </si>
+  <si>
+    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+  </si>
+  <si>
     <t>Shiloh</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - </t>
+    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+  </si>
+  <si>
+    <t>Addy</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t>Kinley</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t>Annabelle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t>Audri</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 1 - 3 - 5 - 3 - 5 - 3 - 2 - 5 - 3 - 0 - 5 - 0 - 1 - 1 - 5 - 5 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
-    <t>0 - 1 - 2 - 1 - 0 - 1 - 0</t>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t>3 - 3 - 5 - 1 - 3 - 0</t>
+  </si>
+  <si>
+    <t>Anna</t>
+  </si>
+  <si>
+    <t>3 - 0 - 1</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 2 - 1 - 2 - 3 - 2 - 2 - 2 - 2 - 1 - 2 - 2 - 3 - 2 -3 - 2 - 2 - 2 - </t>
   </si>
   <si>
+    <t>Agnes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t>1 - 1 - 1 - 0 - 0</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 3 - </t>
+  </si>
+  <si>
+    <t>Corena</t>
+  </si>
+  <si>
+    <t>Gaby</t>
+  </si>
+  <si>
     <t xml:space="preserve">Nataly </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 5 - 5 - 5 - 1 - 3 - 5 - 0 - 3 - 5 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 3 - 0 - 5 - 3 - 1 - 1 - 5 - 5 - 3 - 5 -3 - 3 - 3 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t>2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 0 - 1 - 2 -</t>
+    <t>Nataly</t>
+  </si>
+  <si>
+    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 3 - </t>
   </si>
   <si>
-    <t>Agnes</t>
-  </si>
-  <si>
-    <t>Addy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 5 - 5 - 3 - 5 - 3 - 3 - 5 - 5 - 3 - 3 - </t>
+    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
+  </si>
+  <si>
+    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 3 - 5 - 3 - 0 - 5 - 0 - 0 - 3 - 3 - 0 - 0 - </t>
   </si>
   <si>
-    <t>Kinley</t>
+    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
+  </si>
+  <si>
+    <t>Tea</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - 0 - 1 - 0 - 2 - 1 - 0 - 2 - 1 - 0 - 0 - 3 - 0 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - </t>
   </si>
   <si>
+    <t>Elena</t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 5 - 2 - 3 - 3 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t>Anna</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 2 - 1 - 1 - 2 - 0 - 2 - </t>
+    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t>Emma</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 0 - </t>
   </si>
   <si>
-    <t>Audri</t>
+    <t>Piper</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 2 - </t>
   </si>
   <si>
-    <t>3 - 3 - 5 - 1 - 3 - 0</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 3 - 2 - 3 - </t>
   </si>
   <si>
-    <t>3 - 0 - 1</t>
+    <t>Rotation (follow setter starting position)</t>
   </si>
   <si>
     <t>Bridget</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 1 - 5 - 3 - 5 - 3 - </t>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t>Kill Efficiency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
   </si>
   <si>
     <t>5 - 5 - 3 - 3 - 1 - 2 - 2 - 5 - 3 - 0 - 0 - 1 - 3 - 3 - 3 - 5 - 0</t>
   </si>
   <si>
-    <t>1 - 1 - 1 - 0 - 0</t>
-  </si>
-  <si>
-    <t>Corena</t>
-  </si>
-  <si>
-    <t>Annabelle</t>
-  </si>
-  <si>
-    <t>3 - 0 - 5 - 0 - 5 - 5 - 2 - 1 - 3 - 0</t>
-  </si>
-  <si>
-    <t>1 - 1 - 0 - 2 - 2 - 1 - 0 - 2 - 2 - 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 2 - 2 - 5 - 3 - 3 - 0 - 1 - 3 - 3 - 0 - </t>
+    <t xml:space="preserve">3 - </t>
+  </si>
+  <si>
+    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 0 - 0 - 2 - 1 - 1 - 1 - 3 - 1 -0 - </t>
   </si>
   <si>
-    <t>1 - 3 - 1 - 1 - 3 - 0 - 1 - 1 - 2 - 2 - 3 - 2 - 1 - 3 - 3 - 1 - 1</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 2 - </t>
   </si>
   <si>
-    <t>Elena</t>
-  </si>
-  <si>
-    <t>Emma</t>
+    <t>Block (partial touch)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t>Serve Receive Attempts</t>
+  </si>
+  <si>
+    <t>Serve Receive Grade (0-3)</t>
+  </si>
+  <si>
+    <t>Serve Receive Avg Score</t>
+  </si>
+  <si>
+    <t>Serve Aces</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 5 - 5 - 5 - 3 - 5 - 2 - 5 -0 - 5 - 3 - 3 - 5 - 0 - 0 - 0 - </t>
   </si>
   <si>
-    <t>Piper</t>
-  </si>
-  <si>
-    <t>Rotation (follow setter starting position)</t>
+    <t>Serve Errors</t>
+  </si>
+  <si>
+    <t>Points Scored in Rotation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - </t>
+  </si>
+  <si>
+    <t>Points Scored Against Rotation</t>
+  </si>
+  <si>
+    <t>Rotation Net Score (+ or -)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 0 - 0 - 5 - 0 -0 - </t>
-  </si>
-  <si>
-    <t>Kill Efficiency</t>
+    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 0 - 2 - 3 - 0 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 1 - 3 - 3 - 3 - 1 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - </t>
+  </si>
+  <si>
+    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t>Unforced Error (hit into the net, out of bounds, errant pass/set</t>
-  </si>
-  <si>
-    <t>Nataly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - </t>
-  </si>
-  <si>
-    <t>Block (partial touch)</t>
-  </si>
-  <si>
-    <t>Serve Receive Attempts</t>
-  </si>
-  <si>
-    <t>3 - 5 - 5 - 1 - 5 - 2 - 2 -</t>
-  </si>
-  <si>
-    <t>Serve Receive Grade (0-3)</t>
-  </si>
-  <si>
-    <t>Serve Receive Avg Score</t>
+    <t>Team</t>
+  </si>
+  <si>
+    <t>Total Aces (us)</t>
+  </si>
+  <si>
+    <t>Service error (us)</t>
   </si>
   <si>
     <t xml:space="preserve">2 - 3 - </t>
   </si>
   <si>
-    <t>Serve Aces</t>
-  </si>
-  <si>
-    <t>Gaby</t>
-  </si>
-  <si>
-    <t>Serve Errors</t>
-  </si>
-  <si>
-    <t>Points Scored in Rotation</t>
-  </si>
-  <si>
-    <t>Points Scored Against Rotation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - </t>
-  </si>
-  <si>
-    <t>Rotation Net Score (+ or -)</t>
+    <t>Ace % (us)</t>
+  </si>
+  <si>
+    <t>Service Error % (us)</t>
+  </si>
+  <si>
+    <t>Aces (them)</t>
   </si>
   <si>
     <t xml:space="preserve">3 - 3 - 3 - 5 - 3 - 5 - 5 - 3 - 5 - 3 - 3 - 2 - 3 - 5 - 3 - 0 - 1 - </t>
   </si>
   <si>
+    <t>Service Errors (them)</t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 0 - 0 - 2 - </t>
   </si>
   <si>
+    <t>Ace % (them)</t>
+  </si>
+  <si>
+    <t>Service Error % (Them)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 5 - 0 - 3 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t>Team</t>
+    <t>Set 1</t>
   </si>
   <si>
     <t xml:space="preserve">0 - 3 - 3 - 2 - 0 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 5 - 3 -2- 1 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Total Aces (us)</t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 1 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t>Service error (us)</t>
-  </si>
-  <si>
-    <t>Ace % (us)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 3 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t>Service Error % (us)</t>
+    <t>Set 2</t>
+  </si>
+  <si>
+    <t>Set 3</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 3 - 0 - 2 - 1 - 1 - 0 - </t>
   </si>
   <si>
-    <t>Aces (them)</t>
+    <t>Set 4</t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 1 - 1 - 0 - 1 - 0 - 0 - 0 - 3 - 0 - 1 - 1 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
-    <t>Service Errors (them)</t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 2 - 3 - 3 - 3 - 5 - 5 - 1 - 5 - 1 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t>Ace % (them)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 1 - </t>
+    <t>Set 5</t>
+  </si>
+  <si>
+    <t>Total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 5 - 2 - 1 - 5 - 1 - 1 - 2 - </t>
   </si>
   <si>
-    <t>Service Error % (Them)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 3 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 0 - </t>
+    <t>Team Passer Rating (all games)</t>
+  </si>
+  <si>
+    <t>Team Kill Efficiency (all games)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
-    <t>Set 1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 3 - 1 - 0 - 1 - 1 - 3 - 0 - 3 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 1 - 0 - 3 - 3 - 3 - 3 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - </t>
+    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 0 - 1 - </t>
   </si>
   <si>
-    <t>Set 3</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 3 - </t>
   </si>
   <si>
-    <t>Set 4</t>
-  </si>
-  <si>
-    <t>1 - 0 - 5 - 2 - 1 - 2 - 5 - 3 - 2 - 5 - 0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Set 5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 1 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t>Tea</t>
-  </si>
-  <si>
-    <t>Total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 5 - 1 - 0 - 5 - 0 - 3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 3 - 3 - 1 - 3 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t>Team Passer Rating (all games)</t>
-  </si>
-  <si>
-    <t>Team Kill Efficiency (all games)</t>
+    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 2 - 0 - 2 - 2 - 1 - 0 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 3 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 3 - 3 - 3 - 3 - 1 - 3 - </t>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">0 - 2 - 3 - 2 - 0 - 0 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 1 - 2 - 1 - 3 - 2 - 1 - 2 - 3 - 1 - 1 - 0 - 1 - </t>
+    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 0 - 2 - 2 - 2 - 0 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 2 - 3 - 0 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 1 - 3 - 0 - 3 - 1 - </t>
+    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">1 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 3 - 1 - 2 - 0 - 1 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - </t>
+    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 0 - 3 - 3 - 1 - 0 - 0 - 0 - 3 -1 - 1 - 0 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 0 - 0 - 3 - 2 - 0 - 0 -2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 1 - 2 - 3 - 2 - 3 - 1 - 1 - 2 - 1 - 0 - 1 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 2 - 3 - 1 - 0- 1 - 1 - 3 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 0 - 2 - 3 - 0 - 0 - 0 - 2 - 0 - 1 - 1 - 2 -3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 2 - 0 - 3 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 1 - 1 - 0 - 0 - 2 - 2 - 0 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 5 - 3 - 3 - 1 - 5 - 2 - 5 - 2 - 3 - 3 - 5 - 1 - 1 - 2 - 3 - 5 - 5 - 2 - 0 - 1 - 3 - 1 - 1 - 5 - 5 - 3 - 1 - 5 - 5 - 3 - 1 - </t>
   </si>
   <si>
@@ -527,6 +527,39 @@
     <t xml:space="preserve">3 - 3 - 3 - 2 - 2 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 3 - 2 - 3 - 2 - 5 - 2 - 5 - 0 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 3 - 1 - 0 - 1 - 3 - 2 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 5 - 5 - 2 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 3 - 3 - 2 - 0 - 1 - 0 - 2 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 3 - 2 - 1 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 3 - 2 - 2 - 5 - 3 - 0 - 5 - 2 - 1 - 3 - 3 - 3 - 1 - 0 - 1 - </t>
   </si>
   <si>
@@ -536,25 +569,67 @@
     <t xml:space="preserve">3 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 3 - 2 - 3 - 2 - 5 - 2 - 5 - 0 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 5 - 5 - 5 - 5 - 0 - 1 - 3 - 3 - 3 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 3 - 1 - 0 - 1 - 3 - 2 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 2 - 1 - 3 - 0 - 2 - 2 - 1 - 2 - 3 - 1 - </t>
   </si>
   <si>
     <t xml:space="preserve">3 - 2 - 3 - 2 - 2 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 5 - 5 - 5 - 2 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 3 - 3 - 2 - 0 - 1 - 0 - 2 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 3 - 2 - 1 - 2 - 3 - </t>
+    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
   </si>
   <si>
     <t>3- 2- 3- 2- 3- 1- 5- 5- 2- 3- 2- 2- 1- 5- 1</t>
@@ -566,153 +641,78 @@
     <t>2- 2- 3- 3- 2- 3- 2- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 3 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 5 - 0 - </t>
-  </si>
-  <si>
     <t>0- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 3 - 3 - 0 - 3 - 5 - 2 - 5 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>2- 2- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - </t>
-  </si>
-  <si>
     <t>1- 3- 2- 5- 5- 5- 1- 1- 3- 3- 2- 0- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 1 - 5 - 0 - 3 - 3 - 3 - 3 - 5 - 0 - </t>
-  </si>
-  <si>
     <t>3- 1- 1- 3- 2- 1- 2- 2- 2- 1- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - </t>
-  </si>
-  <si>
     <t>2- 3- 2- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 2 - 5 - 5 - 3 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
     <t>3- 2- 3- 5- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 3 - 0 - 0 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - </t>
-  </si>
-  <si>
     <t>1- 2- 2- 3- 1- 1- 0</t>
   </si>
   <si>
     <t>1- 3- 0</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - 2 - 0 - </t>
-  </si>
-  <si>
     <t>3-0-2-3-3-0-3-1-0-2-3-0-1</t>
   </si>
   <si>
     <t>3- 3- 3- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
     <t>2- 0- 3- 2- 1- 3</t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 2 - 1 - 0 - 3 - 3 - 2 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 0 - 5 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 0 - 0 - 2 - 2 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 1 - 1 - 0 - 1 - 1 - 0 - 1 - 2 - 1 - 1 - 2 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 1 - 0 - 2 - 1 -2 - 0 - 1 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 2 - 1 - 0 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 1 - 3 - 2 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t>1- 3- 0- 3- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 1 - 2 - 1 - 1 - 3 - 3 - 0 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 3- 3- 2- 3- 3- </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 3 - 3 - 2 - 2 - 0 - 0 - 2 - 2 - 0 - 0 - 2 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 1 - 2 - 2 - 0 - 2 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - 2 - 0 - 3 - </t>
+    <t xml:space="preserve">2- 1- 1- </t>
+  </si>
+  <si>
+    <t>1- 0- 3- 2- 0- 1- 1</t>
+  </si>
+  <si>
+    <t>0- 1- 3</t>
+  </si>
+  <si>
+    <t>2- 1- 2- 1- 2</t>
   </si>
   <si>
     <t>5- 2- 2- 3- 1- 3- 1- 5- 0- 2- 2</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 0 - 1 - 0 - 0 - 1 - 0 - 3 - </t>
-  </si>
-  <si>
     <t>0- 2- 1- 1- 3- 1- 2- 2- 0</t>
   </si>
   <si>
     <t xml:space="preserve">3- 3- 2- </t>
   </si>
   <si>
-    <t xml:space="preserve">2- 1- 1- </t>
-  </si>
-  <si>
     <t>2- 1- 2- 0- 0</t>
   </si>
   <si>
     <t>1- 1- 1- 3- 0- 2- 3- 1- 3- 1- 2- 0- 1- 2- 2- 1- 0- 3- 1- 2- 3</t>
   </si>
   <si>
-    <t>1- 0- 3- 2- 0- 1- 1</t>
-  </si>
-  <si>
     <t>3- 1- 2- 1</t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 3 - 2 - 0 - 2 - 3 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t>0- 1- 3</t>
-  </si>
-  <si>
     <t>3- 1- 5- 2</t>
   </si>
   <si>
-    <t>2- 1- 2- 1- 2</t>
-  </si>
-  <si>
     <t>3- 0</t>
   </si>
   <si>
@@ -893,15 +893,15 @@
     <t xml:space="preserve">1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 0 - 0 - 1 - 0 - 1 - 2 - 2 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 3 - 5 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 2 - 1 - 1 - 1 - 3 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 1 - 5 - 3 - 5 - 1 - 5 - 5 - 3 - 3 - 3 - 0 - 3 - </t>
   </si>
   <si>
@@ -929,15 +929,42 @@
     <t>5 - 2 - 3 - 0 -</t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1- 0 - 3 - 1 - 1 - 1 - 0 - 1 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 5- 0 - 3 - 3 - 3 - 3 - 3 - 2 - 5 - 5 - 0 - 3 - 5 - 1 - 3 - </t>
   </si>
   <si>
@@ -947,9 +974,6 @@
     <t xml:space="preserve">3- 3 - 2 - 2 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 3 - 5 - 3 - 3 - 5 - 5 -0 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5- 5- 2- 5- 5- 5- 3- 5- 5- 3- 3- 3 - 3 - 5 - 3 - 0 - 0 - 5 - 1 - </t>
   </si>
   <si>
@@ -968,9 +992,6 @@
     <t xml:space="preserve">2- 3 - 2 - 3 - 2 - 2 - 2 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 2 - 5 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 5- 0 - 5 - 0 - 3 - 0 - 3 - 3 - 0 - 5 - 2 - 2 - </t>
   </si>
   <si>
@@ -980,36 +1001,15 @@
     <t xml:space="preserve">0- 5 - 0 - 1 - 3 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3- 5- 1- 3 - 5 - 0 - 5 - 5 - 0 - 3 - 5 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 1 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 1 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 1 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2- 0- 1 - 1 - 3 - 3 - 1 - 3 - 1 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 0 - 0 - 3 - 1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">1- 1 - 3 - 1 - 1 - 1 - 1 - 0 - 1 - </t>
   </si>
   <si>
@@ -1076,15 +1076,27 @@
     <t xml:space="preserve">1 - 2 - 1 - 3 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 2 - 0 - 1 - 1 - 2 - 1 - 1 - 2 - 3 - 0 - 2 - 2 - 1 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">0 - 2 - 2 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 1 - 1 - 1 - 3 - 2 - 2 - 3 - 1 - 2 - 2 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">0 - 2 - 3 - 5 - 1 - 2 - 1 - 3 - 3 - 0 - 3 - 3 - 2 - 5 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1094,9 +1106,6 @@
     <t xml:space="preserve">3 - 3 - 3 - 2 - 1 - 3 - 3 - 1 - 3 - 2 - 2 - 3 - 2 - 2 - 2 - 2 - 3 - 3 - 2 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 1 - 3 - 3 - 1 - 3 - 2 - 3 - 3 - 0 - 2 - 1 - 2 - 2 - 1 - 1 - 0 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 3 - 5 - 3 - </t>
   </si>
   <si>
@@ -1106,9 +1115,6 @@
     <t xml:space="preserve">3 - 3 - 2 - 1 - 2 - </t>
   </si>
   <si>
-    <t xml:space="preserve">2 - 1 - 1 - 2 - 2 - 2 - 2 - 3 - 2 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 2 - 3 - 1 - 2 - 5 - 3 - 3 - 2 - 2 - 5 - 2 - </t>
   </si>
   <si>
@@ -1118,12 +1124,6 @@
     <t xml:space="preserve">2 - 3 - 3 - 2 - 3 - 2 - 2 - 2 - 3 - 1 - 1 - 1 - 3 - </t>
   </si>
   <si>
-    <t xml:space="preserve">3 - 1 - 3 - 3 - 2 - 3 - 3 - 1 - 1 - 0 - 3 - 0 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 0 - 2 - 3 - 3 - 1 - 0 - 2 - 3 - 0 - 3 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">3 - 0 - 1 - 5 - 0 - 0 - 5 - 3 - 3 - 5 - 3 - 3 - 1 - 0 - 5 - 0 - </t>
   </si>
   <si>
@@ -1160,66 +1160,66 @@
     <t xml:space="preserve">2 - 3 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 1 - 1 - 1 - 1 - 2 - 1 - 1 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
+  </si>
+  <si>
     <t>119 attack attempts</t>
   </si>
   <si>
-    <t xml:space="preserve">5 - 3 - 5 - 2 - 5 - 0 - 0 - 5 - 3 - 2 - 3 - 3 - 3 - 0 - 5 - 5 - 3 - 5 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 3 - 0 - 1 - 0 - 0 - 0 - 2 - 0 - 3 - 2 - 0 - 3 - 3 - 3 - 1 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 5 - 3 - 2 - 0 - 3 - 5 - 5 - 2 - 3 - 3 - 3 - 1 - 3 - 5 - 2 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 2 - 2 - 2 - 2 - 1 - 3 - 1 - 2 - 1 - 3 - 2 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 1 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 5 - 0 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 0 - 2 - 0 - 1 - 0 - 2 - 3 - 2 - 3 - 2 - 3 - 3 - 1 - 0 - 0 - 0 - 0 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 2 - 5 - 3 - 3 - 2 - 3 - 2 - 5 - 2 - 0 - 5 - 0 - 5 - 0 - 3 - 5 - 1 - 0 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 3 - 5 - 0 - 2 - 3 - 5 - 0 - 5 - 5 - 3 - 5 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 5 - 5 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 0 - 0 - 2 - 3 - 0 - 1 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">5 - 5 - 3 - 5 - 5 - 5 - 2 - 5 - 5 - 5 - 1 - 3 - 3 - 3 - 3 - </t>
   </si>
   <si>
@@ -1256,6 +1256,9 @@
     <t xml:space="preserve">0 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 1 - 1 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">5 - 0 - 5 - 2 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 1 - 2 - </t>
   </si>
   <si>
@@ -1286,48 +1289,90 @@
     <t xml:space="preserve">1 - 2 - 2 - 1 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 3 - 2 - 0 - 5 - 3 - 1 - 3 - 3 - 5 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 0 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 2 - 0 - 2 - 0 - 1 - 1 - 0 - 0 - 1 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 1 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 5 - 3- 5 - 3 - 0 - 2 - 0- 3 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 3 - 3 - 5 - 0 - 3 - 1 - 5 - 0 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">2 - 1 - 3 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 0 - 5 - 1 - 3 - 5 - 5 - 3 - 2 - 3 - 3 - 3 - 1 - 5 - 1 - 5 - 0 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 - 1 - 3 - 2 - 3 - 3 - 2 - 1 - 2 - 2 - 1 - 0 - 1 - 2 - 3 - 0 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">0 - 0 - 0 - </t>
   </si>
   <si>
-    <t xml:space="preserve">1 - 5 - 5 - 1 - 0 - 1 - 3 - 5 - 5 - 1 - 2 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 0 - 2 - 1 - 2 - 3 - 2 - 3 - 1 - 3 - 2 - 2 - 0 - 2 - 0 - 1 - 1 - 0 - 0 - 1 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 1 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 5 - 3- 5 - 3 - 0 - 2 - 0- 3 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 0 - 5 - 1 - 3 - 5 - 5 - 3 - 2 - 3 - 3 - 3 - 1 - 5 - 1 - 5 - 0 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 1 - 3 - 2 - 3 - 3 - 2 - 1 - 2 - 2 - 1 - 0 - 1 - 2 - 3 - 0 - 2 - </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 - 3 - 2 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">2 - 5 - 2 - 1 - 2 - 1 - 5 - 3 - 2 - 1 - 2 - 3 - 1 - 5 - 2 - 3 - 3 - 3 - 5 - 2 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 2 - 2 - 1 - 0 - 0 - 0 - 0 - 2 - 1 - 0 - 3 - 0 - 2 - 1 - 2 - 1 - 0 - 2 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 5 - 3 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 2 - 0 - 3 - 2 - 3 - 5 - 1 - 2 - 3 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 2 - 2 - 3 - 0 - 2 - 2 - 0 - 2 - 2 - 2 - 1 - 2 - 3 - 3 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 2 - 1 - 2 - 2 - 2 - 0 - 1 - 2 - 1 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 2 - 3 - 3 - 2 - 3 - 1 - 3 - 2 - 3 - 2 - 2 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 - 3 - 3 - 1 - 2 - 3 - 2 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 2 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 1 - 5 - 1 - 5 - 5 - 0 - 5 - 0 - 5 - 0 - 3 - </t>
   </si>
   <si>
+    <t xml:space="preserve">3 - 2 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - 0 - 2 - 1 - 2 - </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 - 3 - 2 - 3 - 2 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 3 - 3 - 2 - 2 - 3 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">1 - 0 - 0 - 2 - 0 - </t>
   </si>
   <si>
@@ -1337,52 +1382,10 @@
     <t xml:space="preserve">5 - 2 - 0 - 3 - 0 - </t>
   </si>
   <si>
+    <t xml:space="preserve">5 - 5 - 3 - 0 - 0 - 5 - 5 - 1 - 3 - 5 - 3 - 2 - 3 - 0 - 2 - 5 - 0 - </t>
+  </si>
+  <si>
     <t xml:space="preserve">3 - 5 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 0 - 3 - 3 - 2 - 5 - 5 - 1 - 3 - 3 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 - 2 - 3 - 0 - 1 - 1 - 0 - 0 - 1 - 2 - 3 - 1 - 2 - 0 - 2 - 2 - 1 - 1 - 3 - 3 - 1 - 1 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 2 - 3 - 3 - 3 - 2 - 3 - 3 - 3 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 5 - 0 - 0 - 3 - 1 - 0 - 0 - 0 - 2 - 0 - 0 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">0 - 1 - 0 - 2 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 2 - 1 - 3 - 2 - 3 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 0 - 3 - 2 - 5 - 0 - 0 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 3 - 3 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 5 - 3 - 3 - 3 - 3 - 3 - 2 - 2 - 5 - 2 - 0 - 3 - 2 - 3 - 5 - 1 - 2 - 3 - 5 - 3 - 3 - 3 - 3 - 3 - 3 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 2 - 2 - 3 - 0 - 2 - 2 - 0 - 2 - 2 - 2 - 1 - 2 - 3 - 3 - 0 - 1 - 3 - 1 - 0 - 1 - 3 - 1 - 2 - 1 - 2 - 2 - 2 - 0 - 1 - 2 - 1 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 3 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 2 - 3 - 3 - 2 - 3 - 1 - 3 - 2 - 3 - 2 - 2 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 - 3 - 3 - 1 - 2 - 3 - 2 - 2 - 3 - 2 - 2 - 3 - 2 - 3 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 2 - 3 - 0 - 3 - 2 - 2 - 2 - 3 - 2 - 3 - 2 - 1 - 0 - 1 - 0 - 2 - 1 - 2 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">3 - 3 - 2 - 3 - 2 - 3 - 3 - 3 - 3 - 1 - 0 - 3 - 3 - 3 - 2 - 2 - 3 - </t>
-  </si>
-  <si>
-    <t xml:space="preserve">5 - 5 - 3 - 0 - 0 - 5 - 5 - 1 - 3 - 5 - 3 - 2 - 3 - 0 - 2 - 5 - 0 - </t>
   </si>
   <si>
     <t xml:space="preserve">5 - 1 - 3 - 1 - 2 - </t>
@@ -1582,10 +1585,10 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -2017,7 +2020,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L2" s="3">
         <v>0.0</v>
@@ -2029,7 +2032,7 @@
         <v>7.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="R2" s="3">
         <v>0.71</v>
@@ -2038,7 +2041,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -2065,7 +2068,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="L3" s="3">
         <v>3.89</v>
@@ -2077,7 +2080,7 @@
         <v>11.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="R3" s="3">
         <v>1.67</v>
@@ -2086,7 +2089,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D4" s="3">
         <v>1.0</v>
@@ -2104,7 +2107,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="L4" s="3">
         <v>3.67</v>
@@ -2119,7 +2122,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D5" s="3">
         <v>1.0</v>
@@ -2140,7 +2143,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="L5" s="3">
         <v>3.2</v>
@@ -2149,7 +2152,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="R5" s="3">
         <v>1.3</v>
@@ -2158,7 +2161,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -2182,7 +2185,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="L6" s="3">
         <v>2.5</v>
@@ -2191,7 +2194,7 @@
         <v>3.0</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="R6" s="3">
         <v>1.33</v>
@@ -2200,7 +2203,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C7" s="3">
         <v>5.0</v>
@@ -2212,7 +2215,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="L7" s="3">
         <v>3.29</v>
@@ -2224,7 +2227,7 @@
         <v>5.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="R7" s="3">
         <v>0.6</v>
@@ -2233,7 +2236,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C8" s="3">
         <v>3.0</v>
@@ -2246,7 +2249,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -2273,7 +2276,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L9" s="3">
         <v>2.4</v>
@@ -2288,7 +2291,7 @@
         <v>10.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="R9" s="3">
         <v>1.4</v>
@@ -2324,7 +2327,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="L10" s="3">
         <v>2.5</v>
@@ -2333,7 +2336,7 @@
         <v>17.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="R10" s="3">
         <v>1.59</v>
@@ -2342,7 +2345,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3">
         <v>4.0</v>
@@ -2363,7 +2366,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3">
         <v>3.0</v>
@@ -2381,7 +2384,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D13" s="3">
         <v>3.0</v>
@@ -2402,7 +2405,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>1</v>
@@ -2420,40 +2423,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -2493,37 +2496,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -2552,7 +2555,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>9.0</v>
@@ -2578,7 +2581,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -2607,7 +2610,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -2636,12 +2639,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>25.0</v>
@@ -2670,10 +2673,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
     </row>
     <row r="34">
@@ -2782,7 +2785,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B2" s="3">
         <v>7.0</v>
@@ -2824,7 +2827,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -2868,7 +2871,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -2908,7 +2911,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -2916,7 +2919,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C5" s="3">
         <v>1.0</v>
@@ -2964,7 +2967,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="U5" s="3">
         <v>2.0</v>
@@ -2972,7 +2975,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>8.0</v>
@@ -3049,7 +3052,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="L7" s="3">
         <v>1.0</v>
@@ -3064,7 +3067,7 @@
         <v>2.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="R7" s="3">
         <v>0.5</v>
@@ -3073,7 +3076,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -3126,7 +3129,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -3138,7 +3141,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L9" s="3">
         <v>2.5</v>
@@ -3151,7 +3154,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3">
         <v>2.0</v>
@@ -3160,7 +3163,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -3185,7 +3188,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -3201,36 +3204,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -3477,7 +3480,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="M21" s="3">
         <v>0.9</v>
@@ -3500,37 +3503,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C25" s="3">
         <v>1.0</v>
@@ -3544,7 +3547,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>2.0</v>
@@ -3561,7 +3564,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -3578,17 +3581,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>7.0</v>
@@ -3617,12 +3620,12 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="19">
+      <c r="A34" s="18">
         <v>0.378</v>
       </c>
     </row>
@@ -3748,7 +3751,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="L2" s="3">
         <v>2.33</v>
@@ -3760,7 +3763,7 @@
         <v>8.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -3769,7 +3772,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -3777,7 +3780,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>5.0</v>
@@ -3819,7 +3822,7 @@
         <v>3.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="R3" s="3">
         <v>2.67</v>
@@ -3836,7 +3839,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -3895,7 +3898,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -3951,7 +3954,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -3974,7 +3977,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -3982,7 +3985,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D7" s="3">
         <v>4.0</v>
@@ -4015,7 +4018,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" s="3">
         <v>0.0</v>
@@ -4024,7 +4027,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -4045,7 +4048,7 @@
         <v>7.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="R8" s="3">
         <v>2.29</v>
@@ -4054,7 +4057,7 @@
         <v>4.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="U8" s="3">
         <v>2.25</v>
@@ -4062,7 +4065,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -4080,7 +4083,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="L9" s="3">
         <v>3.33</v>
@@ -4090,7 +4093,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -4098,7 +4101,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -4113,7 +4116,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -4123,7 +4126,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -4141,7 +4144,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -4150,7 +4153,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -4171,7 +4174,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>311</v>
+        <v>301</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -4180,7 +4183,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -4198,7 +4201,7 @@
         <v>1.0</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L13" s="3">
         <v>0.0</v>
@@ -4210,7 +4213,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D14" s="3">
         <v>2.0</v>
@@ -4231,7 +4234,7 @@
         <v>1.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -4243,7 +4246,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
@@ -4255,7 +4258,7 @@
         <v>1.0</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L15" s="3">
         <v>0.0</v>
@@ -4265,7 +4268,7 @@
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>317</v>
+        <v>303</v>
       </c>
       <c r="R15" s="3">
         <v>0.333</v>
@@ -4274,7 +4277,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -4290,36 +4293,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -4352,7 +4355,7 @@
         <v>6.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>319</v>
+        <v>304</v>
       </c>
       <c r="M17" s="3">
         <v>1.17</v>
@@ -4399,7 +4402,7 @@
         <v>6.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>320</v>
+        <v>305</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -4443,7 +4446,7 @@
         <v>6.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>321</v>
+        <v>306</v>
       </c>
       <c r="M19" s="3">
         <v>0.667</v>
@@ -4487,7 +4490,7 @@
         <v>6.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>322</v>
+        <v>307</v>
       </c>
       <c r="M20" s="3">
         <v>1.67</v>
@@ -4534,7 +4537,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>324</v>
+        <v>308</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -4578,7 +4581,7 @@
         <v>7.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="M22" s="3">
         <v>2.29</v>
@@ -4601,37 +4604,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3">
         <v>3.0</v>
@@ -4648,7 +4651,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B27" s="3">
         <v>10.0</v>
@@ -4665,7 +4668,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -4682,17 +4685,17 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B32" s="3">
         <v>17.0</v>
@@ -4721,14 +4724,14 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2">
         <v>0.185</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="18"/>
+      <c r="A35" s="19"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -4856,7 +4859,7 @@
         <v>9.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="R2" s="3">
         <v>1.0</v>
@@ -4873,7 +4876,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -4900,7 +4903,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="L3" s="3">
         <v>2.94</v>
@@ -4912,7 +4915,7 @@
         <v>7.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="R3" s="3">
         <v>1.57</v>
@@ -4921,7 +4924,7 @@
         <v>9.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="U3" s="3">
         <v>2.56</v>
@@ -4929,7 +4932,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -4956,7 +4959,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="L4" s="3">
         <v>3.47</v>
@@ -4968,7 +4971,7 @@
         <v>7.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="R4" s="3">
         <v>1.14</v>
@@ -4977,7 +4980,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="U4" s="3">
         <v>2.0</v>
@@ -4985,7 +4988,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3">
         <v>4.0</v>
@@ -5012,7 +5015,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="L5" s="3">
         <v>3.0</v>
@@ -5024,7 +5027,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="R5" s="3">
         <v>1.15</v>
@@ -5033,7 +5036,7 @@
         <v>8.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="U5" s="3">
         <v>2.13</v>
@@ -5053,7 +5056,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="L6" s="3">
         <v>2.31</v>
@@ -5065,7 +5068,7 @@
         <v>5.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="R6" s="3">
         <v>0.8</v>
@@ -5074,7 +5077,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B7" s="3">
         <v>1.0</v>
@@ -5089,7 +5092,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="L7" s="3">
         <v>1.8</v>
@@ -5098,7 +5101,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C8" s="3">
         <v>1.0</v>
@@ -5122,7 +5125,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L8" s="3">
         <v>3.08</v>
@@ -5134,7 +5137,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="U8" s="3">
         <v>1.5</v>
@@ -5142,7 +5145,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3">
         <v>8.0</v>
@@ -5170,7 +5173,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -5197,7 +5200,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -5222,7 +5225,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -5238,36 +5241,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -5300,7 +5303,7 @@
         <v>9.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="M16" s="3">
         <v>1.67</v>
@@ -5549,37 +5552,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="7"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>10.0</v>
@@ -5608,7 +5611,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>7.0</v>
@@ -5625,7 +5628,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>5.0</v>
@@ -5642,7 +5645,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -5659,12 +5662,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>26.0</v>
@@ -5699,12 +5702,12 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="19">
+      <c r="A34" s="18">
         <v>0.045</v>
       </c>
     </row>
@@ -5806,7 +5809,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -5862,7 +5865,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>13.0</v>
@@ -5921,7 +5924,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -5983,7 +5986,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B5" s="3">
         <v>1.0</v>
@@ -6014,7 +6017,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C6" s="3">
         <v>1.0</v>
@@ -6036,7 +6039,7 @@
         <v>1.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="R6" s="3">
         <v>2.0</v>
@@ -6053,9 +6056,9 @@
     </row>
     <row r="7">
       <c r="A7" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="B7" s="19">
+        <v>77</v>
+      </c>
+      <c r="B7" s="18">
         <v>4.0</v>
       </c>
       <c r="C7" s="20"/>
@@ -6063,10 +6066,10 @@
       <c r="E7" s="20"/>
       <c r="F7" s="20"/>
       <c r="G7" s="20"/>
-      <c r="H7" s="19">
+      <c r="H7" s="18">
         <v>18.0</v>
       </c>
-      <c r="I7" s="19">
+      <c r="I7" s="18">
         <v>2.0</v>
       </c>
       <c r="J7" s="21">
@@ -6078,12 +6081,12 @@
       <c r="L7" s="21">
         <v>2.94</v>
       </c>
-      <c r="M7" s="19">
+      <c r="M7" s="18">
         <v>2.0</v>
       </c>
       <c r="N7" s="20"/>
       <c r="O7" s="20"/>
-      <c r="P7" s="19">
+      <c r="P7" s="18">
         <v>14.0</v>
       </c>
       <c r="Q7" s="22" t="s">
@@ -6096,7 +6099,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="21" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="U7" s="21">
         <v>2.5</v>
@@ -6182,7 +6185,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B10" s="3">
         <v>6.0</v>
@@ -6230,7 +6233,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3">
         <v>2.0</v>
@@ -6258,7 +6261,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -6274,36 +6277,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -6336,7 +6339,7 @@
         <v>6.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -6383,7 +6386,7 @@
         <v>14.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="M17" s="3">
         <v>1.79</v>
@@ -6430,7 +6433,7 @@
         <v>17.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="M18" s="3">
         <v>1.71</v>
@@ -6477,7 +6480,7 @@
         <v>13.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="M19" s="3">
         <v>2.08</v>
@@ -6524,7 +6527,7 @@
         <v>14.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>361</v>
+        <v>351</v>
       </c>
       <c r="M20" s="3">
         <v>2.0</v>
@@ -6571,7 +6574,7 @@
         <v>15.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>362</v>
+        <v>352</v>
       </c>
       <c r="M21" s="3">
         <v>1.53</v>
@@ -6594,37 +6597,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>2.0</v>
@@ -6641,7 +6644,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -6658,7 +6661,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>6.0</v>
@@ -6675,7 +6678,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -6692,7 +6695,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3">
         <v>2.0</v>
@@ -6709,7 +6712,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>19.0</v>
@@ -6738,7 +6741,7 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
@@ -6845,7 +6848,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B2" s="3">
         <v>4.0</v>
@@ -6863,7 +6866,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="L2" s="3">
         <v>1.53</v>
@@ -6876,7 +6879,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -6906,7 +6909,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="L3" s="3">
         <v>2.47</v>
@@ -6918,7 +6921,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="R3" s="3">
         <v>2.32</v>
@@ -6927,7 +6930,7 @@
         <v>23.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="U3" s="3">
         <v>2.48</v>
@@ -6947,7 +6950,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="L4" s="3">
         <v>4.2</v>
@@ -6956,7 +6959,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="R4" s="3">
         <v>2.24</v>
@@ -6965,7 +6968,7 @@
         <v>5.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="U4" s="3">
         <v>2.2</v>
@@ -6973,7 +6976,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3">
         <v>14.0</v>
@@ -6997,7 +7000,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="L5" s="3">
         <v>2.75</v>
@@ -7009,7 +7012,7 @@
         <v>16.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="R5" s="3">
         <v>1.75</v>
@@ -7018,7 +7021,7 @@
         <v>13.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="U5" s="3">
         <v>2.15</v>
@@ -7026,7 +7029,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>6.0</v>
@@ -7080,7 +7083,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -7088,7 +7091,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3">
         <v>9.0</v>
@@ -7110,7 +7113,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -7127,7 +7130,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B8" s="3">
         <v>9.0</v>
@@ -7171,7 +7174,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B9" s="3">
         <v>4.0</v>
@@ -7248,7 +7251,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D11" s="3">
         <v>5.0</v>
@@ -7281,7 +7284,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -7296,7 +7299,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C13" s="3">
         <v>1.0</v>
@@ -7305,7 +7308,7 @@
         <v>2.0</v>
       </c>
       <c r="T13" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U13" s="3">
         <v>1.5</v>
@@ -7316,7 +7319,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -7332,36 +7335,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -7623,7 +7626,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M21" s="3">
         <v>1.25</v>
@@ -7646,37 +7649,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>4.0</v>
@@ -7693,7 +7696,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>4.0</v>
@@ -7710,7 +7713,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -7727,7 +7730,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -7744,12 +7747,12 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>17.0</v>
@@ -7778,16 +7781,16 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="19">
+      <c r="A34" s="18">
         <v>0.076</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>376</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>
@@ -7888,7 +7891,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -7915,7 +7918,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="L2" s="3">
         <v>3.11</v>
@@ -7933,7 +7936,7 @@
         <v>20.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="R2" s="3">
         <v>1.6</v>
@@ -7942,7 +7945,7 @@
     </row>
     <row r="3" ht="16.5" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C3" s="3">
         <v>1.0</v>
@@ -7963,7 +7966,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="L3" s="3">
         <v>0.75</v>
@@ -7976,7 +7979,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -8003,7 +8006,7 @@
         <v>2.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L4" s="3">
         <v>3.05</v>
@@ -8015,7 +8018,7 @@
         <v>17.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="R4" s="3">
         <v>1.59</v>
@@ -8024,7 +8027,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="U4" s="3">
         <v>2.17</v>
@@ -8032,7 +8035,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B5" s="3">
         <v>2.0</v>
@@ -8053,7 +8056,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="L5" s="3">
         <v>2.6</v>
@@ -8065,7 +8068,7 @@
         <v>5.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="R5" s="3">
         <v>1.6</v>
@@ -8074,7 +8077,7 @@
         <v>3.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="U5" s="3">
         <v>2.33</v>
@@ -8082,7 +8085,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B6" s="3">
         <v>2.0</v>
@@ -8105,7 +8108,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U6" s="3">
         <v>1.0</v>
@@ -8125,7 +8128,7 @@
         <v>1.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="L7" s="3">
         <v>2.25</v>
@@ -8134,7 +8137,7 @@
         <v>20.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="R7" s="3">
         <v>1.15</v>
@@ -8143,7 +8146,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -8151,7 +8154,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -8172,7 +8175,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="L8" s="3">
         <v>2.8</v>
@@ -8184,7 +8187,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B9" s="3">
         <v>3.0</v>
@@ -8208,7 +8211,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="L9" s="3">
         <v>3.42</v>
@@ -8221,7 +8224,7 @@
         <v>4.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="U9" s="3">
         <v>1.5</v>
@@ -8258,7 +8261,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8273,7 +8276,7 @@
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -8282,7 +8285,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B12" s="3">
         <v>2.0</v>
@@ -8306,7 +8309,7 @@
         <v>4.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="L12" s="3">
         <v>1.67</v>
@@ -8318,7 +8321,7 @@
         <v>7.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="R12" s="3">
         <v>0.86</v>
@@ -8336,37 +8339,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3">
         <v>9.0</v>
@@ -8383,7 +8386,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -8400,7 +8403,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -8417,7 +8420,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3">
         <v>9.0</v>
@@ -8434,7 +8437,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -8451,7 +8454,7 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3">
         <v>26.0</v>
@@ -8480,12 +8483,12 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <v>0.167</v>
       </c>
     </row>
@@ -8587,7 +8590,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>3.0</v>
@@ -8673,7 +8676,7 @@
         <v>2.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="U3" s="3">
         <v>2.5</v>
@@ -8681,7 +8684,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B4" s="3">
         <v>5.0</v>
@@ -8720,7 +8723,7 @@
         <v>2.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="R4" s="3">
         <v>1.5</v>
@@ -8757,7 +8760,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -8797,7 +8800,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -8805,7 +8808,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -8853,7 +8856,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -8861,7 +8864,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H8" s="3">
         <v>11.0</v>
@@ -8882,7 +8885,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3">
         <v>4.0</v>
@@ -8902,14 +8905,14 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="K10" s="4"/>
       <c r="P10" s="3">
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="R10" s="3">
         <v>2.5</v>
@@ -8926,7 +8929,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -8938,7 +8941,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -8953,37 +8956,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3">
         <v>11.0</v>
@@ -9000,7 +9003,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3">
         <v>9.0</v>
@@ -9017,7 +9020,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -9034,17 +9037,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3">
         <v>23.0</v>
@@ -9073,12 +9076,12 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <v>0.289</v>
       </c>
     </row>
@@ -9235,7 +9238,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -9251,36 +9254,36 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6"/>
       <c r="J15" s="7"/>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -9326,62 +9329,62 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D31" s="16"/>
       <c r="E31" s="16"/>
@@ -9390,12 +9393,12 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
+      <c r="A34" s="19"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9496,34 +9499,74 @@
       <c r="K2" s="4"/>
       <c r="M2" s="4"/>
       <c r="P2" s="3">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>392</v>
+        <v>407</v>
       </c>
       <c r="T2" s="4"/>
     </row>
     <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.0</v>
+      </c>
       <c r="K3" s="4"/>
       <c r="Q3" s="4"/>
       <c r="T3" s="4"/>
     </row>
     <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>55</v>
+      </c>
       <c r="K4" s="4"/>
       <c r="Q4" s="4"/>
-      <c r="T4" s="4"/>
+      <c r="S4" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="T4" s="4" t="s">
+        <v>185</v>
+      </c>
     </row>
     <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>65</v>
+      </c>
       <c r="K5" s="4"/>
-      <c r="Q5" s="4"/>
+      <c r="P5" s="3">
+        <v>1.0</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>82</v>
+      </c>
       <c r="T5" s="4"/>
     </row>
     <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="D6" s="3">
+        <v>2.0</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1.0</v>
+      </c>
       <c r="K6" s="4"/>
       <c r="Q6" s="4"/>
       <c r="T6" s="4"/>
     </row>
     <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1.0</v>
+      </c>
       <c r="K7" s="4"/>
       <c r="T7" s="5"/>
     </row>
@@ -9555,65 +9598,65 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F15" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G15" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I15" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K15" s="15"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F16" s="3">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D22" s="16"/>
       <c r="E22" s="16"/>
@@ -9622,12 +9665,12 @@
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B24" s="2"/>
     </row>
     <row r="25">
-      <c r="A25" s="18"/>
+      <c r="A25" s="19"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -9723,7 +9766,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B2" s="3">
         <v>5.0</v>
@@ -9747,7 +9790,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L2" s="3">
         <v>2.77</v>
@@ -9759,7 +9802,7 @@
         <v>15.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="R2" s="3">
         <v>1.8</v>
@@ -9780,7 +9823,7 @@
         <v>1.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L3" s="3">
         <v>1.67</v>
@@ -9789,7 +9832,7 @@
         <v>23.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="R3" s="3">
         <v>1.52</v>
@@ -9798,7 +9841,7 @@
         <v>6.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="U3" s="3">
         <v>2.33</v>
@@ -9806,7 +9849,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B4" s="3">
         <v>12.0</v>
@@ -9833,7 +9876,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L4" s="3">
         <v>2.64</v>
@@ -9845,7 +9888,7 @@
         <v>13.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="R4" s="3">
         <v>1.54</v>
@@ -9854,7 +9897,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="U4" s="3">
         <v>2.66</v>
@@ -9862,7 +9905,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -9883,7 +9926,7 @@
         <v>3.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="L5" s="3">
         <v>1.56</v>
@@ -9896,7 +9939,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="U5" s="3">
         <v>1.8</v>
@@ -9904,7 +9947,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B6" s="3">
         <v>3.0</v>
@@ -9931,7 +9974,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L6" s="3">
         <v>2.75</v>
@@ -9944,7 +9987,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>10.0</v>
@@ -9974,7 +10017,7 @@
         <v>4.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
       <c r="L7" s="3">
         <v>2.0</v>
@@ -9995,7 +10038,7 @@
         <v>4.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
       <c r="U7" s="3">
         <v>2.25</v>
@@ -10022,7 +10065,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D9" s="3">
         <v>10.0</v>
@@ -10040,7 +10083,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>420</v>
+        <v>431</v>
       </c>
       <c r="L9" s="3">
         <v>0.0</v>
@@ -10053,7 +10096,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10061,7 +10104,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10075,13 +10118,13 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="P11" s="3">
         <v>2.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="R11" s="3">
         <v>0.5</v>
@@ -10090,7 +10133,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D12" s="3">
         <v>1.0</v>
@@ -10111,37 +10154,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3">
         <v>3.0</v>
@@ -10158,7 +10201,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -10175,7 +10218,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3">
         <v>2.0</v>
@@ -10192,17 +10235,17 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3">
         <v>10.0</v>
@@ -10231,12 +10274,12 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <v>0.042</v>
       </c>
     </row>
@@ -10335,7 +10378,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>2.0</v>
@@ -10359,7 +10402,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="L2" s="3">
         <v>2.78</v>
@@ -10371,7 +10414,7 @@
         <v>19.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="R2" s="3">
         <v>2.0</v>
@@ -10380,7 +10423,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
       <c r="U2" s="3">
         <v>2.29</v>
@@ -10388,7 +10431,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>28</v>
+        <v>53</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -10406,7 +10449,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="L3" s="3">
         <v>2.92</v>
@@ -10419,7 +10462,7 @@
         <v>3.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>32</v>
+        <v>57</v>
       </c>
       <c r="U3" s="3">
         <v>2.67</v>
@@ -10427,7 +10470,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -10454,7 +10497,7 @@
         <v>5.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="L4" s="3">
         <v>2.25</v>
@@ -10466,7 +10509,7 @@
         <v>19.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>38</v>
+        <v>66</v>
       </c>
       <c r="R4" s="3">
         <v>1.37</v>
@@ -10475,7 +10518,7 @@
         <v>4.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>39</v>
+        <v>68</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -10495,7 +10538,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>43</v>
+        <v>72</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -10504,7 +10547,7 @@
         <v>13.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="R5" s="3">
         <v>1.77</v>
@@ -10513,7 +10556,7 @@
         <v>5.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>47</v>
+        <v>75</v>
       </c>
       <c r="U5" s="3">
         <v>2.6</v>
@@ -10521,7 +10564,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="D6" s="3">
         <v>5.0</v>
@@ -10545,7 +10588,7 @@
         <v>3.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="L6" s="3">
         <v>2.59</v>
@@ -10557,7 +10600,7 @@
         <v>11.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>58</v>
+        <v>84</v>
       </c>
       <c r="R6" s="3">
         <v>1.09</v>
@@ -10566,7 +10609,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -10574,7 +10617,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="C7" s="3">
         <v>1.0</v>
@@ -10601,7 +10644,7 @@
         <v>5.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>63</v>
+        <v>92</v>
       </c>
       <c r="L7" s="3">
         <v>2.67</v>
@@ -10638,7 +10681,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="R8" s="3">
         <v>2.0</v>
@@ -10647,7 +10690,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -10665,7 +10708,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>70</v>
+        <v>104</v>
       </c>
       <c r="L9" s="3">
         <v>1.4</v>
@@ -10678,7 +10721,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -10686,7 +10729,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -10700,7 +10743,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -10715,7 +10758,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="R11" s="3">
         <v>1.0</v>
@@ -10724,13 +10767,13 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="P12" s="3">
         <v>1.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R12" s="3">
         <v>0.0</v>
@@ -10745,7 +10788,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -10761,40 +10804,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -10827,7 +10870,7 @@
         <v>5.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>113</v>
+        <v>138</v>
       </c>
       <c r="M16" s="3">
         <v>1.2</v>
@@ -10875,7 +10918,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -10922,7 +10965,7 @@
         <v>8.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -10969,7 +11012,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="M19" s="3">
         <v>1.36</v>
@@ -11016,7 +11059,7 @@
         <v>9.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="M20" s="3">
         <v>1.89</v>
@@ -11060,7 +11103,7 @@
         <v>14.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="M21" s="3">
         <v>1.14</v>
@@ -11080,37 +11123,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>9.0</v>
@@ -11127,7 +11170,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>10.0</v>
@@ -11144,7 +11187,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>4.0</v>
@@ -11161,7 +11204,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3">
         <v>5.0</v>
@@ -11178,7 +11221,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -11195,7 +11238,7 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>29.0</v>
@@ -11224,12 +11267,12 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2"/>
     </row>
     <row r="34">
-      <c r="A34" s="18">
+      <c r="A34" s="19">
         <v>0.186</v>
       </c>
     </row>
@@ -11331,7 +11374,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -11361,7 +11404,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="L2" s="3">
         <v>2.69</v>
@@ -11373,7 +11416,7 @@
         <v>22.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="R2" s="3">
         <v>1.45</v>
@@ -11382,7 +11425,7 @@
         <v>4.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -11390,7 +11433,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B3" s="3">
         <v>2.0</v>
@@ -11414,7 +11457,7 @@
         <v>3.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -11433,7 +11476,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -11451,7 +11494,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -11464,7 +11507,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -11472,7 +11515,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>6.0</v>
@@ -11502,7 +11545,7 @@
         <v>2.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L5" s="3">
         <v>2.63</v>
@@ -11514,7 +11557,7 @@
         <v>17.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="R5" s="3">
         <v>1.71</v>
@@ -11523,7 +11566,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
       <c r="U5" s="3">
         <v>2.5</v>
@@ -11552,7 +11595,7 @@
         <v>4.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="L6" s="3">
         <v>2.65</v>
@@ -11564,7 +11607,7 @@
         <v>20.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>429</v>
+        <v>437</v>
       </c>
       <c r="R6" s="3">
         <v>1.0</v>
@@ -11573,7 +11616,7 @@
         <v>1.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="U6" s="3">
         <v>2.0</v>
@@ -11606,7 +11649,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B8" s="3">
         <v>12.0</v>
@@ -11636,7 +11679,7 @@
         <v>3.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="L8" s="3">
         <v>2.75</v>
@@ -11648,7 +11691,7 @@
         <v>5.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>431</v>
+        <v>446</v>
       </c>
       <c r="R8" s="3">
         <v>0.6</v>
@@ -11657,7 +11700,7 @@
         <v>6.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>432</v>
+        <v>447</v>
       </c>
       <c r="U8" s="3">
         <v>1.83</v>
@@ -11665,7 +11708,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="H9" s="3">
         <v>5.0</v>
@@ -11677,7 +11720,7 @@
         <v>2.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>433</v>
+        <v>448</v>
       </c>
       <c r="L9" s="3">
         <v>2.0</v>
@@ -11687,7 +11730,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="C10" s="3">
         <v>1.0</v>
@@ -11705,7 +11748,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>434</v>
+        <v>450</v>
       </c>
       <c r="L10" s="3">
         <v>3.67</v>
@@ -11730,37 +11773,37 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G16" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I16" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K16" s="15"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B17" s="3">
         <v>8.0</v>
@@ -11777,7 +11820,7 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B18" s="3">
         <v>4.0</v>
@@ -11794,7 +11837,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3">
         <v>6.0</v>
@@ -11811,7 +11854,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B20" s="3">
         <v>4.0</v>
@@ -11828,12 +11871,12 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B23" s="3">
         <v>22.0</v>
@@ -11862,12 +11905,12 @@
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B25" s="2"/>
     </row>
     <row r="26">
-      <c r="A26" s="19">
+      <c r="A26" s="18">
         <v>0.123</v>
       </c>
     </row>
@@ -11993,7 +12036,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="L2" s="3">
         <v>2.58</v>
@@ -12005,7 +12048,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="R2" s="3">
         <v>1.46</v>
@@ -12014,7 +12057,7 @@
         <v>12.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="U2" s="3">
         <v>2.58</v>
@@ -12022,7 +12065,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>11.0</v>
@@ -12052,7 +12095,7 @@
         <v>7.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
       <c r="L3" s="3">
         <v>1.62</v>
@@ -12064,7 +12107,7 @@
         <v>6.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>439</v>
+        <v>433</v>
       </c>
       <c r="R3" s="3">
         <v>1.17</v>
@@ -12073,7 +12116,7 @@
         <v>11.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>440</v>
+        <v>434</v>
       </c>
       <c r="U3" s="3">
         <v>2.36</v>
@@ -12081,7 +12124,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3">
         <v>6.0</v>
@@ -12108,7 +12151,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="L4" s="3">
         <v>2.0</v>
@@ -12121,7 +12164,7 @@
         <v>6.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -12129,7 +12172,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12159,7 +12202,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="L5" s="3">
         <v>2.86</v>
@@ -12171,7 +12214,7 @@
         <v>32.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="R5" s="3">
         <v>1.59</v>
@@ -12180,7 +12223,7 @@
         <v>23.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="U5" s="3">
         <v>2.43</v>
@@ -12188,7 +12231,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B6" s="3">
         <v>10.0</v>
@@ -12209,7 +12252,7 @@
         <v>15.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="L6" s="3">
         <v>2.33</v>
@@ -12221,7 +12264,7 @@
         <v>19.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="R6" s="3">
         <v>1.79</v>
@@ -12230,7 +12273,7 @@
         <v>17.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="U6" s="3">
         <v>2.47</v>
@@ -12238,7 +12281,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -12269,7 +12312,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U7" s="3">
         <v>1.0</v>
@@ -12277,7 +12320,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>3.0</v>
@@ -12313,7 +12356,7 @@
         <v>2.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="R8" s="3">
         <v>1.0</v>
@@ -12351,7 +12394,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -12365,7 +12408,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -12374,7 +12417,7 @@
         <v>2.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="U11" s="3">
         <v>2.0</v>
@@ -12382,7 +12425,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -12394,7 +12437,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -12408,37 +12451,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3">
         <v>6.0</v>
@@ -12455,7 +12498,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B19" s="3">
         <v>3.0</v>
@@ -12472,7 +12515,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B20" s="3">
         <v>3.0</v>
@@ -12489,7 +12532,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>2.0</v>
@@ -12506,7 +12549,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B22" s="3">
         <v>1.0</v>
@@ -12523,7 +12566,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3">
         <v>15.0</v>
@@ -12552,12 +12595,12 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="19">
+      <c r="A27" s="18">
         <v>0.202</v>
       </c>
     </row>
@@ -12671,7 +12714,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L2" s="3">
         <v>2.4</v>
@@ -12683,7 +12726,7 @@
         <v>26.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="R2" s="3">
         <v>1.73</v>
@@ -12692,7 +12735,7 @@
         <v>2.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="U2" s="3">
         <v>2.0</v>
@@ -12700,7 +12743,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B3" s="3">
         <v>10.0</v>
@@ -12724,7 +12767,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="L3" s="3">
         <v>2.82</v>
@@ -12736,7 +12779,7 @@
         <v>19.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="R3" s="3">
         <v>1.59</v>
@@ -12745,7 +12788,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="U3" s="3">
         <v>2.8</v>
@@ -12753,7 +12796,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3">
         <v>4.0</v>
@@ -12780,7 +12823,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -12792,7 +12835,7 @@
         <v>1.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="R4" s="3">
         <v>2.0</v>
@@ -12801,7 +12844,7 @@
         <v>1.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U4" s="3">
         <v>1.0</v>
@@ -12809,7 +12852,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -12839,7 +12882,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L5" s="3">
         <v>2.1</v>
@@ -12851,7 +12894,7 @@
         <v>10.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="R5" s="3">
         <v>1.7</v>
@@ -12860,7 +12903,7 @@
         <v>4.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="U5" s="3">
         <v>2.75</v>
@@ -12868,7 +12911,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H6" s="3">
         <v>6.0</v>
@@ -12880,7 +12923,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="L6" s="3">
         <v>2.67</v>
@@ -12890,7 +12933,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -12911,7 +12954,7 @@
         <v>4.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="L7" s="3">
         <v>0.0</v>
@@ -12926,7 +12969,7 @@
         <v>1.0</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="R7" s="3">
         <v>3.0</v>
@@ -12935,7 +12978,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D8" s="3">
         <v>2.0</v>
@@ -12957,7 +13000,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D9" s="3">
         <v>5.0</v>
@@ -12980,13 +13023,13 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L10" s="3">
         <v>3.0</v>
@@ -12995,7 +13038,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="R10" s="3">
         <v>2.0</v>
@@ -13004,7 +13047,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B11" s="3">
         <v>2.0</v>
@@ -13025,7 +13068,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -13064,7 +13107,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B14" s="3">
         <v>1.0</v>
@@ -13079,7 +13122,7 @@
         <v>2.0</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="L14" s="3">
         <v>2.5</v>
@@ -13091,7 +13134,7 @@
         <v>1.0</v>
       </c>
       <c r="T14" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U14" s="3">
         <v>1.0</v>
@@ -13127,37 +13170,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3">
         <v>2.0</v>
@@ -13174,7 +13217,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B19" s="3">
         <v>1.0</v>
@@ -13185,7 +13228,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13202,17 +13245,17 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3">
         <v>5.0</v>
@@ -13241,12 +13284,12 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="19">
+      <c r="A27" s="18">
         <v>-0.014</v>
       </c>
     </row>
@@ -13360,7 +13403,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L2" s="3">
         <v>1.36</v>
@@ -13370,7 +13413,7 @@
         <v>24.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="R2" s="3">
         <v>1.38</v>
@@ -13379,7 +13422,7 @@
         <v>6.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="U2" s="3">
         <v>2.17</v>
@@ -13387,7 +13430,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D3" s="3">
         <v>1.0</v>
@@ -13407,7 +13450,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3">
         <v>8.0</v>
@@ -13431,7 +13474,7 @@
         <v>6.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="L4" s="3">
         <v>3.12</v>
@@ -13440,7 +13483,7 @@
         <v>18.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="R4" s="3">
         <v>1.39</v>
@@ -13449,7 +13492,7 @@
         <v>10.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="U4" s="3">
         <v>2.4</v>
@@ -13457,7 +13500,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>10.0</v>
@@ -13487,7 +13530,7 @@
         <v>5.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="L5" s="3">
         <v>2.17</v>
@@ -13499,7 +13542,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="R5" s="3">
         <v>1.27</v>
@@ -13508,7 +13551,7 @@
         <v>7.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="U5" s="3">
         <v>2.57</v>
@@ -13516,7 +13559,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>5.0</v>
@@ -13543,7 +13586,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="L6" s="3">
         <v>2.18</v>
@@ -13555,7 +13598,7 @@
         <v>22.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="R6" s="3">
         <v>1.59</v>
@@ -13564,7 +13607,7 @@
         <v>10.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="U6" s="3">
         <v>2.4</v>
@@ -13572,7 +13615,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" s="3">
         <v>6.0</v>
@@ -13594,7 +13637,7 @@
         <v>1.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -13602,7 +13645,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -13626,7 +13669,7 @@
         <v>4.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="L8" s="3">
         <v>2.31</v>
@@ -13635,7 +13678,7 @@
         <v>1.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U8" s="3">
         <v>3.0</v>
@@ -13672,7 +13715,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B10" s="3">
         <v>1.0</v>
@@ -13695,7 +13738,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U10" s="3">
         <v>3.0</v>
@@ -13703,7 +13746,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="H11" s="3">
         <v>10.0</v>
@@ -13715,7 +13758,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="L11" s="3">
         <v>2.4</v>
@@ -13727,7 +13770,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B12" s="3">
         <v>4.0</v>
@@ -13745,7 +13788,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -13757,7 +13800,7 @@
         <v>5.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -13766,7 +13809,7 @@
         <v>4.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -13806,37 +13849,37 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G17" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I17" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K17" s="15"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B18" s="3">
         <v>5.0</v>
@@ -13853,7 +13896,7 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B19" s="3">
         <v>5.0</v>
@@ -13870,7 +13913,7 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B20" s="3">
         <v>2.0</v>
@@ -13884,7 +13927,7 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B21" s="3">
         <v>1.0</v>
@@ -13901,7 +13944,7 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C22" s="3">
         <v>1.0</v>
@@ -13915,7 +13958,7 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B24" s="3">
         <v>13.0</v>
@@ -13944,12 +13987,12 @@
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B26" s="2"/>
     </row>
     <row r="27">
-      <c r="A27" s="19">
+      <c r="A27" s="18">
         <v>0.07</v>
       </c>
     </row>
@@ -14094,7 +14137,7 @@
         <v>4.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="L3" s="3">
         <v>2.0</v>
@@ -14106,7 +14149,7 @@
         <v>22.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>69</v>
+        <v>101</v>
       </c>
       <c r="R3" s="3">
         <v>1.36</v>
@@ -14115,7 +14158,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B4" s="3">
         <v>3.0</v>
@@ -14139,7 +14182,7 @@
         <v>3.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>76</v>
+        <v>103</v>
       </c>
       <c r="L4" s="3">
         <v>3.29</v>
@@ -14152,7 +14195,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>79</v>
+        <v>108</v>
       </c>
       <c r="U4" s="3">
         <v>2.5</v>
@@ -14160,7 +14203,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B5" s="3">
         <v>3.0</v>
@@ -14187,7 +14230,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="L5" s="3">
         <v>3.06</v>
@@ -14199,7 +14242,7 @@
         <v>4.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>88</v>
+        <v>114</v>
       </c>
       <c r="R5" s="3">
         <v>1.0</v>
@@ -14208,7 +14251,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -14235,7 +14278,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="L6" s="3">
         <v>1.86</v>
@@ -14247,7 +14290,7 @@
         <v>7.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>91</v>
+        <v>120</v>
       </c>
       <c r="R6" s="3">
         <v>1.71</v>
@@ -14256,7 +14299,7 @@
         <v>5.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>94</v>
+        <v>121</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -14264,7 +14307,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B7" s="3">
         <v>2.0</v>
@@ -14288,7 +14331,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="L7" s="3">
         <v>1.13</v>
@@ -14300,7 +14343,7 @@
         <v>17.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>102</v>
+        <v>126</v>
       </c>
       <c r="R7" s="3">
         <v>1.0</v>
@@ -14309,7 +14352,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>104</v>
+        <v>127</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -14317,7 +14360,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="B8" s="3">
         <v>2.0</v>
@@ -14335,7 +14378,7 @@
         <v>2.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -14347,7 +14390,7 @@
         <v>8.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="R8" s="3">
         <v>1.5</v>
@@ -14356,7 +14399,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>111</v>
+        <v>134</v>
       </c>
       <c r="U8" s="3">
         <v>2.5</v>
@@ -14364,7 +14407,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C9" s="3">
         <v>2.0</v>
@@ -14378,7 +14421,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="H10" s="3">
         <v>1.0</v>
@@ -14387,7 +14430,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L10" s="3">
         <v>0.0</v>
@@ -14399,7 +14442,7 @@
         <v>3.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="R10" s="3">
         <v>0.67</v>
@@ -14408,7 +14451,7 @@
         <v>1.0</v>
       </c>
       <c r="T10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="U10" s="3">
         <v>0.0</v>
@@ -14416,7 +14459,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H11" s="3">
         <v>2.0</v>
@@ -14425,7 +14468,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="L11" s="3">
         <v>4.0</v>
@@ -14437,7 +14480,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -14458,7 +14501,7 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="2" t="s">
@@ -14474,40 +14517,40 @@
         <v>5</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H15" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I15" s="6" t="s">
         <v>13</v>
       </c>
       <c r="J15" s="7" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="K15" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L15" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P15" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R15" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S15" s="8"/>
       <c r="T15" s="6"/>
@@ -14540,7 +14583,7 @@
         <v>16.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M16" s="3">
         <v>1.44</v>
@@ -14582,7 +14625,7 @@
         <v>7.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="M17" s="3">
         <v>1.14</v>
@@ -14629,7 +14672,7 @@
         <v>10.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="M18" s="3">
         <v>1.3</v>
@@ -14676,7 +14719,7 @@
         <v>4.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="M19" s="3">
         <v>1.25</v>
@@ -14720,7 +14763,7 @@
         <v>10.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -14758,7 +14801,7 @@
         <v>13.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="M21" s="3">
         <v>1.15</v>
@@ -14781,37 +14824,37 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E24" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F24" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15"/>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>5.0</v>
@@ -14828,7 +14871,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -14845,7 +14888,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3">
         <v>2.0</v>
@@ -14862,17 +14905,17 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B31" s="3">
         <v>15.0</v>
@@ -14901,14 +14944,14 @@
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B33" s="2">
         <v>0.057</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="18"/>
+      <c r="A34" s="19"/>
     </row>
   </sheetData>
   <printOptions gridLines="1" horizontalCentered="1"/>
@@ -15008,7 +15051,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>10.0</v>
@@ -15035,7 +15078,7 @@
         <v>1.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>92</v>
+        <v>28</v>
       </c>
       <c r="L2" s="3">
         <v>2.6</v>
@@ -15047,7 +15090,7 @@
         <v>16.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>95</v>
+        <v>30</v>
       </c>
       <c r="R2" s="3">
         <v>1.56</v>
@@ -15056,7 +15099,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>98</v>
+        <v>32</v>
       </c>
       <c r="U2" s="3">
         <v>2.86</v>
@@ -15064,7 +15107,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>1.0</v>
@@ -15091,7 +15134,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>105</v>
+        <v>36</v>
       </c>
       <c r="L3" s="3">
         <v>2.77</v>
@@ -15106,7 +15149,7 @@
         <v>5.0</v>
       </c>
       <c r="Q3" s="4" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="R3" s="3">
         <v>1.0</v>
@@ -15136,7 +15179,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>112</v>
+        <v>45</v>
       </c>
       <c r="L4" s="3">
         <v>0.0</v>
@@ -15148,7 +15191,7 @@
         <v>25.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>115</v>
+        <v>47</v>
       </c>
       <c r="R4" s="3">
         <v>1.52</v>
@@ -15157,7 +15200,7 @@
         <v>2.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="U4" s="3">
         <v>3.0</v>
@@ -15165,7 +15208,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="B5" s="3"/>
       <c r="H5" s="3">
@@ -15175,7 +15218,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L5" s="3">
         <v>0.0</v>
@@ -15188,7 +15231,7 @@
     </row>
     <row r="6" ht="15.0" customHeight="1">
       <c r="A6" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B6" s="3">
         <v>4.0</v>
@@ -15215,7 +15258,7 @@
         <v>2.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>122</v>
+        <v>59</v>
       </c>
       <c r="L6" s="3">
         <v>2.36</v>
@@ -15227,7 +15270,7 @@
         <v>6.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="R6" s="3">
         <v>1.17</v>
@@ -15236,7 +15279,7 @@
         <v>6.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>125</v>
+        <v>61</v>
       </c>
       <c r="U6" s="3">
         <v>1.5</v>
@@ -15244,7 +15287,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B7" s="3">
         <v>7.0</v>
@@ -15271,7 +15314,7 @@
         <v>2.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>128</v>
+        <v>69</v>
       </c>
       <c r="L7" s="3">
         <v>2.7</v>
@@ -15283,7 +15326,7 @@
         <v>9.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="R7" s="3">
         <v>1.44</v>
@@ -15292,7 +15335,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="U7" s="3">
         <v>3.0</v>
@@ -15328,7 +15371,7 @@
         <v>1.0</v>
       </c>
       <c r="Q8" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="3">
         <v>0.0</v>
@@ -15337,7 +15380,7 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B9" s="3">
         <v>1.0</v>
@@ -15349,7 +15392,7 @@
         <v>1.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>133</v>
+        <v>78</v>
       </c>
       <c r="L9" s="3">
         <v>2.6</v>
@@ -15358,7 +15401,7 @@
         <v>8.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>137</v>
+        <v>80</v>
       </c>
       <c r="R9" s="3">
         <v>1.5</v>
@@ -15367,7 +15410,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -15375,7 +15418,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="D10" s="3">
         <v>1.0</v>
@@ -15390,7 +15433,7 @@
         <v>1.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>140</v>
+        <v>87</v>
       </c>
       <c r="L10" s="3">
         <v>1.67</v>
@@ -15399,7 +15442,7 @@
         <v>1.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R10" s="3">
         <v>0.0</v>
@@ -15408,7 +15451,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B11" s="3">
         <v>1.0</v>
@@ -15429,7 +15472,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="L11" s="3">
         <v>1.5</v>
@@ -15442,7 +15485,7 @@
         <v>1.0</v>
       </c>
       <c r="T11" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U11" s="3">
         <v>3.0</v>
@@ -15450,7 +15493,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="B12" s="3">
         <v>1.0</v>
@@ -15465,7 +15508,7 @@
         <v>2.0</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="L12" s="3">
         <v>3.0</v>
@@ -15474,7 +15517,7 @@
         <v>4.0</v>
       </c>
       <c r="Q12" s="3" t="s">
-        <v>145</v>
+        <v>100</v>
       </c>
       <c r="R12" s="3">
         <v>1.0</v>
@@ -15483,7 +15526,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="U12" s="3">
         <v>1.0</v>
@@ -15491,7 +15534,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="B13" s="3">
         <v>1.0</v>
@@ -15503,7 +15546,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -15521,7 +15564,7 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D15" s="3">
         <v>2.0</v>
@@ -15539,7 +15582,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -15555,36 +15598,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -15617,7 +15660,7 @@
         <v>17.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="M17" s="3">
         <v>1.71</v>
@@ -15664,7 +15707,7 @@
         <v>18.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>148</v>
+        <v>130</v>
       </c>
       <c r="M18" s="3">
         <v>1.44</v>
@@ -15705,7 +15748,7 @@
         <v>9.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="M19" s="3">
         <v>1.44</v>
@@ -15752,7 +15795,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="M20" s="3">
         <v>0.875</v>
@@ -15793,7 +15836,7 @@
         <v>10.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="M21" s="3">
         <v>1.5</v>
@@ -15840,7 +15883,7 @@
         <v>11.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="M22" s="3">
         <v>0.909</v>
@@ -15860,37 +15903,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3">
         <v>6.0</v>
@@ -15907,7 +15950,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B27" s="3">
         <v>1.0</v>
@@ -15924,7 +15967,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3">
         <v>3.0</v>
@@ -15941,7 +15984,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B29" s="3">
         <v>1.0</v>
@@ -15958,12 +16001,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B32" s="3">
         <v>11.0</v>
@@ -15992,12 +16035,12 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2"/>
     </row>
     <row r="35">
-      <c r="A35" s="19">
+      <c r="A35" s="18">
         <v>-0.05</v>
       </c>
     </row>
@@ -16099,7 +16142,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>15.0</v>
@@ -16147,7 +16190,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B3" s="3">
         <v>3.0</v>
@@ -16196,15 +16239,15 @@
     </row>
     <row r="4">
       <c r="A4" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="B4" s="19">
+        <v>55</v>
+      </c>
+      <c r="B4" s="18">
         <v>9.0</v>
       </c>
-      <c r="C4" s="19">
+      <c r="C4" s="18">
         <v>16.0</v>
       </c>
-      <c r="D4" s="19">
+      <c r="D4" s="18">
         <v>2.0</v>
       </c>
       <c r="E4" s="20"/>
@@ -16212,13 +16255,13 @@
       <c r="G4" s="21">
         <v>0.0</v>
       </c>
-      <c r="H4" s="19">
+      <c r="H4" s="18">
         <v>19.0</v>
       </c>
-      <c r="I4" s="19">
+      <c r="I4" s="18">
         <v>7.0</v>
       </c>
-      <c r="J4" s="19">
+      <c r="J4" s="18">
         <v>3.0</v>
       </c>
       <c r="K4" s="22" t="s">
@@ -16227,12 +16270,12 @@
       <c r="L4" s="21">
         <v>2.63</v>
       </c>
-      <c r="M4" s="19">
+      <c r="M4" s="18">
         <v>5.0</v>
       </c>
       <c r="N4" s="20"/>
       <c r="O4" s="20"/>
-      <c r="P4" s="18">
+      <c r="P4" s="19">
         <v>3.0</v>
       </c>
       <c r="Q4" s="23" t="s">
@@ -16241,7 +16284,7 @@
       <c r="R4" s="21">
         <v>1.0</v>
       </c>
-      <c r="S4" s="18">
+      <c r="S4" s="19">
         <v>3.0</v>
       </c>
       <c r="T4" s="23" t="s">
@@ -16264,7 +16307,7 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B5" s="3">
         <v>9.0</v>
@@ -16320,7 +16363,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -16339,7 +16382,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B7" s="3">
         <v>4.0</v>
@@ -16357,7 +16400,7 @@
         <v>3.0</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="L7" s="3">
         <v>2.38</v>
@@ -16369,7 +16412,7 @@
         <v>16.0</v>
       </c>
       <c r="Q7" s="4" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="R7" s="3">
         <v>1.69</v>
@@ -16422,7 +16465,7 @@
         <v>3.0</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
       <c r="L9" s="3">
         <v>2.36</v>
@@ -16434,7 +16477,7 @@
         <v>24.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
       <c r="R9" s="3">
         <v>2.04</v>
@@ -16443,7 +16486,7 @@
         <v>1.0</v>
       </c>
       <c r="T9" s="4" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="U9" s="3">
         <v>3.0</v>
@@ -16451,7 +16494,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -16463,7 +16506,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="L10" s="3">
         <v>2.0</v>
@@ -16475,7 +16518,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D11" s="3">
         <v>1.0</v>
@@ -16493,7 +16536,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -16502,7 +16545,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C12" s="3">
         <v>1.0</v>
@@ -16517,7 +16560,7 @@
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="2" t="s">
@@ -16533,36 +16576,36 @@
         <v>5</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H14" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I14" s="6"/>
       <c r="J14" s="7"/>
       <c r="K14" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L14" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P14" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R14" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S14" s="8"/>
       <c r="T14" s="6"/>
@@ -16592,7 +16635,7 @@
         <v>8.0</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>197</v>
+        <v>169</v>
       </c>
       <c r="M15" s="3">
         <v>2.63</v>
@@ -16639,7 +16682,7 @@
         <v>10.0</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="M16" s="3">
         <v>1.5</v>
@@ -16683,7 +16726,7 @@
         <v>23.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="M17" s="3">
         <v>1.57</v>
@@ -16730,7 +16773,7 @@
         <v>12.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="M18" s="3">
         <v>1.33</v>
@@ -16777,7 +16820,7 @@
         <v>12.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="M19" s="3">
         <v>2.17</v>
@@ -16824,7 +16867,7 @@
         <v>8.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>206</v>
+        <v>174</v>
       </c>
       <c r="M20" s="3">
         <v>2.25</v>
@@ -16847,37 +16890,37 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E23" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F23" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G23" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I23" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K23" s="15"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B24" s="3">
         <v>4.0</v>
@@ -16894,7 +16937,7 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3">
         <v>7.0</v>
@@ -16911,7 +16954,7 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -16928,7 +16971,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B27" s="3">
         <v>8.0</v>
@@ -16945,7 +16988,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3">
         <v>6.0</v>
@@ -16953,7 +16996,7 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B30" s="3">
         <v>33.0</v>
@@ -16982,12 +17025,12 @@
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B32" s="2"/>
     </row>
     <row r="33">
-      <c r="A33" s="19">
+      <c r="A33" s="18">
         <v>0.179</v>
       </c>
     </row>
@@ -17089,7 +17132,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="D2" s="3">
         <v>7.0</v>
@@ -17113,7 +17156,7 @@
         <v>2.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="L2" s="3">
         <v>2.31</v>
@@ -17125,7 +17168,7 @@
         <v>21.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="R2" s="3">
         <v>1.62</v>
@@ -17134,7 +17177,7 @@
         <v>7.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="U2" s="3">
         <v>2.57</v>
@@ -17142,7 +17185,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K3" s="4"/>
       <c r="M3" s="3">
@@ -17153,7 +17196,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B4" s="3">
         <v>10.0</v>
@@ -17180,7 +17223,7 @@
         <v>1.0</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="L4" s="3">
         <v>3.0</v>
@@ -17192,7 +17235,7 @@
         <v>15.0</v>
       </c>
       <c r="Q4" s="4" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="R4" s="3">
         <v>1.87</v>
@@ -17201,7 +17244,7 @@
         <v>7.0</v>
       </c>
       <c r="T4" s="4" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="U4" s="3">
         <v>2.29</v>
@@ -17221,7 +17264,7 @@
         <v>1.0</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="L5" s="3">
         <v>1.5</v>
@@ -17230,7 +17273,7 @@
         <v>11.0</v>
       </c>
       <c r="Q5" s="4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="R5" s="3">
         <v>1.45</v>
@@ -17239,7 +17282,7 @@
         <v>1.0</v>
       </c>
       <c r="T5" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="U5" s="3">
         <v>1.5</v>
@@ -17247,7 +17290,7 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="B6" s="3">
         <v>1.0</v>
@@ -17277,7 +17320,7 @@
         <v>1.0</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L6" s="3">
         <v>2.91</v>
@@ -17292,7 +17335,7 @@
         <v>2.0</v>
       </c>
       <c r="Q6" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="R6" s="3">
         <v>0.5</v>
@@ -17301,7 +17344,7 @@
         <v>2.0</v>
       </c>
       <c r="T6" s="4" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="U6" s="3">
         <v>3.0</v>
@@ -17309,7 +17352,7 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B7" s="3">
         <v>3.0</v>
@@ -17339,7 +17382,7 @@
         <v>2.0</v>
       </c>
       <c r="T7" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="U7" s="3">
         <v>1.5</v>
@@ -17347,7 +17390,7 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="B8" s="3">
         <v>1.0</v>
@@ -17368,7 +17411,7 @@
         <v>1.0</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="L8" s="3">
         <v>2.25</v>
@@ -17380,7 +17423,7 @@
         <v>9.0</v>
       </c>
       <c r="Q8" s="4" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="R8" s="3">
         <v>1.11</v>
@@ -17389,7 +17432,7 @@
         <v>2.0</v>
       </c>
       <c r="T8" s="4" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="U8" s="3">
         <v>2.0</v>
@@ -17422,7 +17465,7 @@
         <v>1.0</v>
       </c>
       <c r="Q9" s="4" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="R9" s="3">
         <v>1.0</v>
@@ -17431,7 +17474,7 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="H10" s="3">
         <v>4.0</v>
@@ -17443,7 +17486,7 @@
         <v>2.0</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="L10" s="3">
         <v>1.75</v>
@@ -17455,7 +17498,7 @@
         <v>2.0</v>
       </c>
       <c r="Q10" s="4" t="s">
-        <v>142</v>
+        <v>95</v>
       </c>
       <c r="R10" s="3">
         <v>1.5</v>
@@ -17464,7 +17507,7 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" s="3">
         <v>4.0</v>
@@ -17485,7 +17528,7 @@
         <v>1.0</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L11" s="3">
         <v>0.0</v>
@@ -17497,7 +17540,7 @@
         <v>1.0</v>
       </c>
       <c r="Q11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R11" s="3">
         <v>0.0</v>
@@ -17506,7 +17549,7 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D12" s="3">
         <v>2.0</v>
@@ -17527,7 +17570,7 @@
         <v>1.0</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="L12" s="3">
         <v>2.25</v>
@@ -17539,7 +17582,7 @@
         <v>8.0</v>
       </c>
       <c r="Q12" s="4" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="R12" s="3">
         <v>0.75</v>
@@ -17548,7 +17591,7 @@
         <v>1.0</v>
       </c>
       <c r="T12" s="4" t="s">
-        <v>66</v>
+        <v>99</v>
       </c>
       <c r="U12" s="3">
         <v>2.0</v>
@@ -17556,7 +17599,7 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>62</v>
+        <v>71</v>
       </c>
       <c r="D13" s="3">
         <v>1.0</v>
@@ -17571,7 +17614,7 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>64</v>
+        <v>73</v>
       </c>
       <c r="D14" s="3">
         <v>1.0</v>
@@ -17583,14 +17626,14 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="D15" s="3"/>
       <c r="P15" s="3">
         <v>3.0</v>
       </c>
       <c r="Q15" s="3" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="R15" s="3">
         <v>1.0</v>
@@ -17599,7 +17642,7 @@
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
-        <v>65</v>
+        <v>76</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="2" t="s">
@@ -17615,36 +17658,36 @@
         <v>5</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="H16" s="6" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="I16" s="6"/>
       <c r="J16" s="7"/>
       <c r="K16" s="7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="L16" s="6" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="P16" s="6" t="s">
-        <v>83</v>
+        <v>94</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="R16" s="8" t="s">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="S16" s="8"/>
       <c r="T16" s="6"/>
@@ -17674,7 +17717,7 @@
         <v>13.0</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="M17" s="3">
         <v>1.46</v>
@@ -17721,7 +17764,7 @@
         <v>16.0</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="M18" s="3">
         <v>1.63</v>
@@ -17765,7 +17808,7 @@
         <v>11.0</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="M19" s="3">
         <v>1.45</v>
@@ -17812,7 +17855,7 @@
         <v>11.0</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>212</v>
+        <v>196</v>
       </c>
       <c r="M20" s="3">
         <v>1.0</v>
@@ -17859,7 +17902,7 @@
         <v>8.0</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="M21" s="3">
         <v>0.63</v>
@@ -17906,7 +17949,7 @@
         <v>9.0</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>222</v>
+        <v>198</v>
       </c>
       <c r="M22" s="3">
         <v>2.0</v>
@@ -17929,37 +17972,37 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="s">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>93</v>
+        <v>106</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>97</v>
+        <v>109</v>
       </c>
       <c r="E25" s="10" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="F25" s="11" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="K25" s="15"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3">
         <v>8.0</v>
@@ -17976,7 +18019,7 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="B27" s="3">
         <v>3.0</v>
@@ -17993,7 +18036,7 @@
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B28" s="3">
         <v>4.0</v>
@@ -18010,7 +18053,7 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C29" s="3">
         <v>2.0</v>
@@ -18021,12 +18064,12 @@
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B32" s="3">
         <v>15.0</v>
@@ -18055,12 +18098,12 @@
     </row>
     <row r="34">
       <c r="A34" s="6" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="B34" s="2"/>
     </row>
     <row r="35">
-      <c r="A35" s="19">
+      <c r="A35" s="18">
         <v>0.186</v>
       </c>
     </row>
@@ -18162,7 +18205,7 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B2" s="3">
         <v>6.0</v>
@@ -18186,7 +18229,7 @@
         <v>3.0</v>
       </c>
       <c r="K2" s="4" t="s">
-        <v>174</v>
+        <v>199</v>
       </c>
       <c r="L2" s="3">
         <v>2.667</v>
@@ -18198,7 +18241,7 @@
         <v>5.0</v>
       </c>
       <c r="Q2" s="4" t="s">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="R2" s="3">
         <v>1.4</v>
@@ -18207,7 +18250,7 @@
         <v>8.0</v>
       </c>
       <c r="T2" s="4" t="s">
-        <v>176</v>
+        <v>201</v>
       </c>
       <c r="U2" s="3">
         <v>2.5</v>
@@ -18215,7 +18258,7 @@
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="B3" s="3">
         <v>4.0</v>
@@ -18236,7 +18279,7 @@
         <v>2.0</v>
       </c>
       <c r="K3" s="4" t="s">
-        <v>179</v>
+        <v>202</v>
       </c>
       <c r="L3" s="3">
         <v>0.0</v>
@@ -18246,7 +18289,7 @@
         <v>5.0</v>
       </c>
       <c r="T3" s="4" t="s">
-        <v>181</v>
+        <v>203</v>
       </c>
       <c r="U3" s="3">
         <v>2.4</v>
@@ -18254,7 +18297,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>126</v>
+        <v>65</v>
       </c>
       <c r="B4" s